--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>29238</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.97599995136261</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.97200000286102</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>11741</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.9559999704361</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -62917,7 +62917,7 @@
         <v>11741</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.95000004768372</v>
+        <v>1.9559999704361</v>
       </c>
       <c r="D2720" t="n">
         <v>1.92999994754791</v>
@@ -62929,6 +62929,29 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>11941</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.93599998950958</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.9559999704361</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>11945</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.94200003147125</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.95799994468689</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>18633</v>
+        <v>26041</v>
       </c>
       <c r="C2715" t="n">
-        <v>1.92999994754791</v>
+        <v>1.92599999904633</v>
       </c>
       <c r="D2715" t="n">
-        <v>1.89400005340576</v>
+        <v>1.90199995040894</v>
       </c>
       <c r="E2715" t="n">
+        <v>1.92599999904633</v>
+      </c>
+      <c r="F2715" t="n">
         <v>1.9099999666214</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>1.91999995708466</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>40592</v>
+        <v>18633</v>
       </c>
       <c r="C2716" t="n">
-        <v>1.94799995422363</v>
+        <v>1.92999994754791</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.91199994087219</v>
+        <v>1.89400005340576</v>
       </c>
       <c r="E2716" t="n">
-        <v>1.91199994087219</v>
+        <v>1.9099999666214</v>
       </c>
       <c r="F2716" t="n">
-        <v>1.94200003147125</v>
+        <v>1.91999995708466</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>57967</v>
+        <v>40592</v>
       </c>
       <c r="C2717" t="n">
-        <v>1.95000004768372</v>
+        <v>1.94799995422363</v>
       </c>
       <c r="D2717" t="n">
-        <v>1.91999995708466</v>
+        <v>1.91199994087219</v>
       </c>
       <c r="E2717" t="n">
-        <v>1.95000004768372</v>
+        <v>1.91199994087219</v>
       </c>
       <c r="F2717" t="n">
-        <v>1.95000004768372</v>
+        <v>1.94200003147125</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>101428</v>
+        <v>57967</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.97000002861023</v>
+        <v>1.95000004768372</v>
       </c>
       <c r="D2718" t="n">
-        <v>1.92599999904633</v>
+        <v>1.91999995708466</v>
       </c>
       <c r="E2718" t="n">
         <v>1.95000004768372</v>
       </c>
       <c r="F2718" t="n">
-        <v>1.97000002861023</v>
+        <v>1.95000004768372</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>29238</v>
+        <v>101428</v>
       </c>
       <c r="C2719" t="n">
-        <v>1.97599995136261</v>
+        <v>1.97000002861023</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.92999994754791</v>
+        <v>1.92599999904633</v>
       </c>
       <c r="E2719" t="n">
-        <v>1.97200000286102</v>
+        <v>1.95000004768372</v>
       </c>
       <c r="F2719" t="n">
-        <v>1.96000003814697</v>
+        <v>1.97000002861023</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>11741</v>
+        <v>29238</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.9559999704361</v>
+        <v>1.97599995136261</v>
       </c>
       <c r="D2720" t="n">
         <v>1.92999994754791</v>
       </c>
       <c r="E2720" t="n">
-        <v>1.92999994754791</v>
+        <v>1.97200000286102</v>
       </c>
       <c r="F2720" t="n">
-        <v>1.9559999704361</v>
+        <v>1.96000003814697</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>11941</v>
+        <v>11741</v>
       </c>
       <c r="C2721" t="n">
-        <v>1.96000003814697</v>
+        <v>1.9559999704361</v>
       </c>
       <c r="D2721" t="n">
-        <v>1.93599998950958</v>
+        <v>1.92999994754791</v>
       </c>
       <c r="E2721" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="F2721" t="n">
         <v>1.9559999704361</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>1.96000003814697</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>11945</v>
+        <v>11941</v>
       </c>
       <c r="C2722" t="n">
         <v>1.96000003814697</v>
       </c>
       <c r="D2722" t="n">
-        <v>1.94200003147125</v>
+        <v>1.93599998950958</v>
       </c>
       <c r="E2722" t="n">
+        <v>1.9559999704361</v>
+      </c>
+      <c r="F2722" t="n">
         <v>1.96000003814697</v>
       </c>
-      <c r="F2722" t="n">
-        <v>1.95799994468689</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>50176</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.94799995422363</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.89400005340576</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.87800002098083</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.88199996948242</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>10444</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.87999999523163</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.9099999666214</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.90400004386902</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>56514</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.90799999237061</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.8639999628067</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.90799999237061</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.90799999237061</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.87399995326996</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>88480</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.8860000371933</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.84800004959106</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.85000002384186</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.85000002384186</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>40242</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.84800004959106</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>26290</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.86199998855591</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.87199997901917</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.485062271356583</v>
+        <v>0.485062211751938</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.488176047801971</v>
+        <v>0.488176077604294</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.48160246014595</v>
+        <v>0.481602489948273</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.689499974250793</v>
       </c>
       <c r="G5" t="n">
-        <v>0.477104723453522</v>
+        <v>0.477104753255844</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.479872584342957</v>
+        <v>0.479872554540634</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483678311109543</v>
+        <v>0.48367828130722</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G11" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G13" t="n">
-        <v>0.466379404067993</v>
+        <v>0.466379463672638</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G15" t="n">
-        <v>0.460151761770248</v>
+        <v>0.460151791572571</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G16" t="n">
-        <v>0.464303523302078</v>
+        <v>0.464303582906723</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G18" t="n">
-        <v>0.477450788021088</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G19" t="n">
-        <v>0.480910509824753</v>
+        <v>0.480910539627075</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G20" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G22" t="n">
-        <v>0.471915006637573</v>
+        <v>0.471915066242218</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G24" t="n">
-        <v>0.453232169151306</v>
+        <v>0.453232198953629</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G27" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620715618134</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G28" t="n">
-        <v>0.422786056995392</v>
+        <v>0.422786027193069</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.619499981403351</v>
       </c>
       <c r="G29" t="n">
-        <v>0.428667724132538</v>
+        <v>0.428667664527893</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G32" t="n">
-        <v>0.438009202480316</v>
+        <v>0.438009172677994</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G33" t="n">
-        <v>0.433165401220322</v>
+        <v>0.433165431022644</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G35" t="n">
-        <v>0.435933262109756</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G37" t="n">
-        <v>0.437317192554474</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.435933262109756</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G40" t="n">
-        <v>0.433857351541519</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G41" t="n">
-        <v>0.432127445936203</v>
+        <v>0.432127505540848</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.623499989509583</v>
       </c>
       <c r="G42" t="n">
-        <v>0.431435525417328</v>
+        <v>0.43143555521965</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G44" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620715618134</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G45" t="n">
-        <v>0.440084964036942</v>
+        <v>0.440084993839264</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>0.438701122999191</v>
+        <v>0.438701093196869</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.621500015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>0.430051624774933</v>
+        <v>0.43005159497261</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G50" t="n">
-        <v>0.433857351541519</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>0.441468954086304</v>
+        <v>0.441468924283981</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G52" t="n">
-        <v>0.438701122999191</v>
+        <v>0.438701093196869</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G53" t="n">
-        <v>0.439739018678665</v>
+        <v>0.439738988876343</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>0.636500000953674</v>
       </c>
       <c r="G54" t="n">
-        <v>0.440430968999863</v>
+        <v>0.440431028604507</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G55" t="n">
-        <v>0.437317192554474</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G58" t="n">
-        <v>0.43351137638092</v>
+        <v>0.433511435985565</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G59" t="n">
-        <v>0.439739018678665</v>
+        <v>0.439738988876343</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G60" t="n">
-        <v>0.439739018678665</v>
+        <v>0.439738988876343</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G61" t="n">
-        <v>0.434549391269684</v>
+        <v>0.434549361467361</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.435933262109756</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>0.434549391269684</v>
+        <v>0.434549361467361</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.629499971866608</v>
       </c>
       <c r="G64" t="n">
-        <v>0.435587286949158</v>
+        <v>0.43558731675148</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G65" t="n">
-        <v>0.431781530380249</v>
+        <v>0.431781560182571</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G66" t="n">
-        <v>0.432127445936203</v>
+        <v>0.432127505540848</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>0.617500007152557</v>
       </c>
       <c r="G67" t="n">
-        <v>0.42728379368782</v>
+        <v>0.427283823490143</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G68" t="n">
-        <v>0.422786056995392</v>
+        <v>0.422786027193069</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.615499973297119</v>
       </c>
       <c r="G71" t="n">
-        <v>0.425899863243103</v>
+        <v>0.425899893045425</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G72" t="n">
-        <v>0.433857351541519</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.629499971866608</v>
       </c>
       <c r="G74" t="n">
-        <v>0.435587286949158</v>
+        <v>0.43558731675148</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>0.435933262109756</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G77" t="n">
-        <v>0.49336576461792</v>
+        <v>0.493365705013275</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G78" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G80" t="n">
-        <v>0.479872584342957</v>
+        <v>0.479872554540634</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>0.483678311109543</v>
+        <v>0.48367828130722</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>0.683499991893768</v>
       </c>
       <c r="G83" t="n">
-        <v>0.472952961921692</v>
+        <v>0.472952991724014</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G84" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G85" t="n">
-        <v>0.453924179077148</v>
+        <v>0.453924238681793</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.648500025272369</v>
       </c>
       <c r="G87" t="n">
-        <v>0.448734492063522</v>
+        <v>0.4487344622612</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>0.450464338064194</v>
+        <v>0.450464397668839</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G89" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620715618134</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>0.637000024318695</v>
       </c>
       <c r="G90" t="n">
-        <v>0.440776944160461</v>
+        <v>0.440776973962784</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G91" t="n">
-        <v>0.438701122999191</v>
+        <v>0.438701093196869</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>0.435933262109756</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G93" t="n">
-        <v>0.442852824926376</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.656499981880188</v>
       </c>
       <c r="G95" t="n">
-        <v>0.454270154237747</v>
+        <v>0.454270124435425</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G97" t="n">
-        <v>0.442852824926376</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G98" t="n">
-        <v>0.442852824926376</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G100" t="n">
-        <v>0.440084964036942</v>
+        <v>0.440084993839264</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.6875</v>
       </c>
       <c r="G104" t="n">
-        <v>0.475720822811127</v>
+        <v>0.475720852613449</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G106" t="n">
-        <v>0.473990917205811</v>
+        <v>0.473990887403488</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G107" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.698499977588654</v>
       </c>
       <c r="G109" t="n">
-        <v>0.483332276344299</v>
+        <v>0.483332306146622</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G110" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G111" t="n">
-        <v>0.477450788021088</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G113" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.674499988555908</v>
       </c>
       <c r="G114" t="n">
-        <v>0.46672534942627</v>
+        <v>0.466725409030914</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G116" t="n">
-        <v>0.442852824926376</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G117" t="n">
-        <v>0.449080437421799</v>
+        <v>0.449080467224121</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G118" t="n">
-        <v>0.437317192554474</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G119" t="n">
-        <v>0.447004616260529</v>
+        <v>0.447004586458206</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G120" t="n">
-        <v>0.442852824926376</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G121" t="n">
-        <v>0.453924179077148</v>
+        <v>0.453924238681793</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G122" t="n">
-        <v>0.44596666097641</v>
+        <v>0.445966601371765</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G126" t="n">
-        <v>0.436625212430954</v>
+        <v>0.436625242233276</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G127" t="n">
-        <v>0.442852824926376</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>0.441468954086304</v>
+        <v>0.441468924283981</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G129" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G131" t="n">
-        <v>0.453924179077148</v>
+        <v>0.453924238681793</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G132" t="n">
-        <v>0.438701122999191</v>
+        <v>0.438701093196869</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G133" t="n">
-        <v>0.442852824926376</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G135" t="n">
-        <v>0.450464338064194</v>
+        <v>0.450464397668839</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>0.675499975681305</v>
       </c>
       <c r="G136" t="n">
-        <v>0.467417359352112</v>
+        <v>0.467417329549789</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G137" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G138" t="n">
-        <v>0.473990917205811</v>
+        <v>0.473990887403488</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>0.476758778095245</v>
+        <v>0.476758748292923</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G141" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>0.476758778095245</v>
+        <v>0.476758748292923</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G144" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>0.66949999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>0.463265627622604</v>
+        <v>0.463265597820282</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.477450788021088</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G149" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G150" t="n">
-        <v>0.466033428907394</v>
+        <v>0.466033399105072</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G151" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>0.656499981880188</v>
       </c>
       <c r="G153" t="n">
-        <v>0.454270154237747</v>
+        <v>0.454270124435425</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G154" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G157" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>0.466033428907394</v>
+        <v>0.466033399105072</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G163" t="n">
-        <v>0.459459781646729</v>
+        <v>0.459459811449051</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G164" t="n">
-        <v>0.460151761770248</v>
+        <v>0.460151791572571</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G165" t="n">
-        <v>0.469839215278625</v>
+        <v>0.469839185476303</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G166" t="n">
-        <v>0.469147205352783</v>
+        <v>0.469147145748138</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G167" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>0.473298966884613</v>
+        <v>0.473298996686935</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G169" t="n">
-        <v>0.473298966884613</v>
+        <v>0.473298996686935</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G170" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G171" t="n">
-        <v>0.469147205352783</v>
+        <v>0.469147145748138</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>0.679499983787537</v>
       </c>
       <c r="G172" t="n">
-        <v>0.470185160636902</v>
+        <v>0.470185130834579</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G173" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G177" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>0.658500015735626</v>
       </c>
       <c r="G179" t="n">
-        <v>0.45565402507782</v>
+        <v>0.455653995275497</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G181" t="n">
-        <v>0.459459781646729</v>
+        <v>0.459459811449051</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G184" t="n">
-        <v>0.447004616260529</v>
+        <v>0.447004586458206</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.655499994754791</v>
       </c>
       <c r="G187" t="n">
-        <v>0.45357820391655</v>
+        <v>0.453578174114227</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>0.457383930683136</v>
+        <v>0.457383990287781</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G189" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.686500012874603</v>
       </c>
       <c r="G192" t="n">
-        <v>0.475028902292252</v>
+        <v>0.475028812885284</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>0.672500014305115</v>
       </c>
       <c r="G194" t="n">
-        <v>0.465341448783875</v>
+        <v>0.465341418981552</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G195" t="n">
-        <v>0.467763304710388</v>
+        <v>0.467763274908066</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G196" t="n">
-        <v>0.470531165599823</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G197" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>0.6875</v>
       </c>
       <c r="G200" t="n">
-        <v>0.475720822811127</v>
+        <v>0.475720852613449</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G203" t="n">
-        <v>0.498555392026901</v>
+        <v>0.498555421829224</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>0.489214032888412</v>
+        <v>0.489214062690735</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G205" t="n">
-        <v>0.493019729852676</v>
+        <v>0.493019759654999</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>0.50305312871933</v>
+        <v>0.503053188323975</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G211" t="n">
-        <v>0.51689225435257</v>
+        <v>0.516892313957214</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G214" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>0.50997269153595</v>
+        <v>0.509972751140594</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>0.497863441705704</v>
+        <v>0.497863501310349</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G218" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G219" t="n">
-        <v>0.497863441705704</v>
+        <v>0.497863501310349</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G221" t="n">
-        <v>0.49544158577919</v>
+        <v>0.495441615581512</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G222" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G223" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G224" t="n">
-        <v>0.498209446668625</v>
+        <v>0.498209476470947</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G226" t="n">
-        <v>0.49544158577919</v>
+        <v>0.495441615581512</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G227" t="n">
-        <v>0.494057714939117</v>
+        <v>0.494057685136795</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G230" t="n">
-        <v>0.485754251480103</v>
+        <v>0.48575422167778</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G231" t="n">
-        <v>0.493019729852676</v>
+        <v>0.493019759654999</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G232" t="n">
-        <v>0.497863441705704</v>
+        <v>0.497863501310349</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G233" t="n">
-        <v>0.498209446668625</v>
+        <v>0.498209476470947</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.706499993801117</v>
       </c>
       <c r="G234" t="n">
-        <v>0.488867998123169</v>
+        <v>0.488868027925491</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G236" t="n">
-        <v>0.4926737844944</v>
+        <v>0.492673754692078</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G237" t="n">
-        <v>0.4926737844944</v>
+        <v>0.492673754692078</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G238" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G242" t="n">
-        <v>0.503745138645172</v>
+        <v>0.503745079040527</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.731500029563904</v>
       </c>
       <c r="G243" t="n">
-        <v>0.506166934967041</v>
+        <v>0.506166994571686</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G247" t="n">
-        <v>0.51689225435257</v>
+        <v>0.516892313957214</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G250" t="n">
-        <v>0.521736025810242</v>
+        <v>0.521735966205597</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G257" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352005958557</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>0.539380848407745</v>
+        <v>0.53938090801239</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G260" t="n">
-        <v>0.534883260726929</v>
+        <v>0.534883201122284</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.786499977111816</v>
       </c>
       <c r="G261" t="n">
-        <v>0.544224560260773</v>
+        <v>0.544224619865417</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G263" t="n">
-        <v>0.531423509120941</v>
+        <v>0.531423389911652</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G265" t="n">
-        <v>0.533499300479889</v>
+        <v>0.533499360084534</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G266" t="n">
-        <v>0.535575151443481</v>
+        <v>0.535575211048126</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>0.77649998664856</v>
       </c>
       <c r="G267" t="n">
-        <v>0.537305057048798</v>
+        <v>0.537305116653442</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G274" t="n">
-        <v>0.542494773864746</v>
+        <v>0.542494714260101</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>0.539380848407745</v>
+        <v>0.53938090801239</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G277" t="n">
-        <v>0.538689017295837</v>
+        <v>0.538688957691193</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G279" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352005958557</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G288" t="n">
-        <v>0.535575151443481</v>
+        <v>0.535575211048126</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G295" t="n">
-        <v>0.51412445306778</v>
+        <v>0.514124393463135</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G298" t="n">
-        <v>0.515508413314819</v>
+        <v>0.515508353710175</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G299" t="n">
-        <v>0.524503827095032</v>
+        <v>0.524503886699677</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>0.515508413314819</v>
+        <v>0.515508353710175</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G303" t="n">
-        <v>0.509280800819397</v>
+        <v>0.509280741214752</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G304" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>0.738499999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>0.511010706424713</v>
+        <v>0.511010646820068</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>0.50305312871933</v>
+        <v>0.503053188323975</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>0.732500016689301</v>
       </c>
       <c r="G309" t="n">
-        <v>0.506858944892883</v>
+        <v>0.506858885288239</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G312" t="n">
-        <v>0.505474925041199</v>
+        <v>0.505475044250488</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G316" t="n">
-        <v>0.50582093000412</v>
+        <v>0.505820989608765</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>0.731500029563904</v>
       </c>
       <c r="G317" t="n">
-        <v>0.506166934967041</v>
+        <v>0.506166994571686</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G318" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896959781647</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G328" t="n">
-        <v>0.50582093000412</v>
+        <v>0.505820989608765</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G329" t="n">
-        <v>0.505474925041199</v>
+        <v>0.505475044250488</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G331" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896959781647</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>0.728500008583069</v>
       </c>
       <c r="G332" t="n">
-        <v>0.504091143608093</v>
+        <v>0.504091084003448</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G333" t="n">
-        <v>0.498555392026901</v>
+        <v>0.498555421829224</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.726499974727631</v>
       </c>
       <c r="G336" t="n">
-        <v>0.502707123756409</v>
+        <v>0.502707183361053</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G337" t="n">
-        <v>0.50582093000412</v>
+        <v>0.505820989608765</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>0.731500029563904</v>
       </c>
       <c r="G339" t="n">
-        <v>0.506166934967041</v>
+        <v>0.506166994571686</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G340" t="n">
-        <v>0.509280800819397</v>
+        <v>0.509280741214752</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G341" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.731500029563904</v>
       </c>
       <c r="G342" t="n">
-        <v>0.506166934967041</v>
+        <v>0.506166994571686</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G344" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896959781647</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G345" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896959781647</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G348" t="n">
-        <v>0.523119926452637</v>
+        <v>0.523119866847992</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>0.762499988079071</v>
       </c>
       <c r="G350" t="n">
-        <v>0.527617633342743</v>
+        <v>0.527617573738098</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>0.742500007152557</v>
       </c>
       <c r="G358" t="n">
-        <v>0.513778448104858</v>
+        <v>0.513778507709503</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G360" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352005958557</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>0.532807290554047</v>
+        <v>0.532807350158691</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G366" t="n">
-        <v>0.533499300479889</v>
+        <v>0.533499360084534</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>0.809499979019165</v>
       </c>
       <c r="G369" t="n">
-        <v>0.560139656066895</v>
+        <v>0.56013959646225</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G370" t="n">
-        <v>0.568097233772278</v>
+        <v>0.568097174167633</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>0.82150000333786</v>
       </c>
       <c r="G371" t="n">
-        <v>0.568443119525909</v>
+        <v>0.568443179130554</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G373" t="n">
-        <v>0.56740528345108</v>
+        <v>0.567405164241791</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G377" t="n">
-        <v>0.590239822864532</v>
+        <v>0.590239763259888</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G378" t="n">
-        <v>0.606846749782562</v>
+        <v>0.606846809387207</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>0.920499980449677</v>
       </c>
       <c r="G379" t="n">
-        <v>0.636946856975555</v>
+        <v>0.6369469165802</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G380" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G382" t="n">
-        <v>0.640060782432556</v>
+        <v>0.640060722827911</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G384" t="n">
-        <v>0.646980285644531</v>
+        <v>0.646980345249176</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G389" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G391" t="n">
-        <v>0.646980285644531</v>
+        <v>0.646980345249176</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G392" t="n">
-        <v>0.638676822185516</v>
+        <v>0.638676881790161</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G394" t="n">
-        <v>0.635563015937805</v>
+        <v>0.63556307554245</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G395" t="n">
-        <v>0.638676822185516</v>
+        <v>0.638676881790161</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G398" t="n">
-        <v>0.640060782432556</v>
+        <v>0.640060722827911</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G401" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G405" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G408" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G413" t="n">
-        <v>0.617918074131012</v>
+        <v>0.617918133735657</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G414" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G415" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G419" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G424" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>0.887499988079071</v>
       </c>
       <c r="G429" t="n">
-        <v>0.614112377166748</v>
+        <v>0.614112317562103</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G431" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G432" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G433" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G435" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>0.887499988079071</v>
       </c>
       <c r="G438" t="n">
-        <v>0.614112377166748</v>
+        <v>0.614112317562103</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G442" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>0.916499972343445</v>
       </c>
       <c r="G445" t="n">
-        <v>0.63417911529541</v>
+        <v>0.634179055690765</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G447" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>0.92849999666214</v>
       </c>
       <c r="G451" t="n">
-        <v>0.642482578754425</v>
+        <v>0.64248263835907</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>0.934499979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>0.64663428068161</v>
+        <v>0.646634340286255</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G454" t="n">
-        <v>0.655283868312836</v>
+        <v>0.655283808708191</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G455" t="n">
-        <v>0.693341374397278</v>
+        <v>0.693341493606567</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G456" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G460" t="n">
-        <v>0.708564579486847</v>
+        <v>0.708564519882202</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G461" t="n">
-        <v>0.715484142303467</v>
+        <v>0.715484082698822</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>0.996500015258789</v>
       </c>
       <c r="G466" t="n">
-        <v>0.689535677433014</v>
+        <v>0.689535737037659</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G469" t="n">
-        <v>0.694725394248962</v>
+        <v>0.694725334644318</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G470" t="n">
-        <v>0.693341374397278</v>
+        <v>0.693341493606567</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.00899994373322</v>
       </c>
       <c r="G475" t="n">
-        <v>0.698185086250305</v>
+        <v>0.69818514585495</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>0.970499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>0.671544790267944</v>
+        <v>0.671544849872589</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G481" t="n">
-        <v>0.652169942855835</v>
+        <v>0.65217000246048</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>0.935500025749207</v>
       </c>
       <c r="G482" t="n">
-        <v>0.647326350212097</v>
+        <v>0.647326290607452</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G483" t="n">
-        <v>0.644212424755096</v>
+        <v>0.644212484359741</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>0.92849999666214</v>
       </c>
       <c r="G484" t="n">
-        <v>0.642482578754425</v>
+        <v>0.64248263835907</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G485" t="n">
-        <v>0.655283868312836</v>
+        <v>0.655283808708191</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G486" t="n">
-        <v>0.655283868312836</v>
+        <v>0.655283808708191</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>0.966499984264374</v>
       </c>
       <c r="G488" t="n">
-        <v>0.66877692937851</v>
+        <v>0.668776988983154</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G489" t="n">
-        <v>0.67050689458847</v>
+        <v>0.670506834983826</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G490" t="n">
-        <v>0.666355073451996</v>
+        <v>0.666355133056641</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>0.961000025272369</v>
       </c>
       <c r="G491" t="n">
-        <v>0.664971232414246</v>
+        <v>0.66497129201889</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>0.669122934341431</v>
+        <v>0.669122993946075</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G493" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>0.990499973297119</v>
       </c>
       <c r="G499" t="n">
-        <v>0.685383975505829</v>
+        <v>0.685383915901184</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>0.995500028133392</v>
       </c>
       <c r="G502" t="n">
-        <v>0.688843786716461</v>
+        <v>0.688843846321106</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G503" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G504" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>0.999499976634979</v>
       </c>
       <c r="G505" t="n">
-        <v>0.691611588001251</v>
+        <v>0.691611528396606</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G507" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G508" t="n">
-        <v>0.674658596515656</v>
+        <v>0.674658715724945</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>0.940500020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>0.650786161422729</v>
+        <v>0.650786101818085</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G511" t="n">
-        <v>0.656667709350586</v>
+        <v>0.656667768955231</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G517" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G518" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G523" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G527" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G532" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G534" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G535" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G537" t="n">
-        <v>0.673966646194458</v>
+        <v>0.673966705799103</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G538" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G546" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>0.672582805156708</v>
+        <v>0.672582745552063</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G552" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G553" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G561" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G562" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G563" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G565" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G566" t="n">
-        <v>0.672582805156708</v>
+        <v>0.672582745552063</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G567" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G569" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G571" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G575" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G576" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G577" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G578" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G579" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G580" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G581" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G582" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G583" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G584" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G586" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G587" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G589" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G590" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G591" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G592" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G593" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G595" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G598" t="n">
-        <v>0.682270109653473</v>
+        <v>0.682270169258118</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G599" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G600" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G602" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G603" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G604" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G605" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G606" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G607" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G608" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G609" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G610" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G611" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G613" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G617" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G621" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G622" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G624" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G625" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G628" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G630" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G634" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G635" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G638" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G644" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G645" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G646" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G647" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G648" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G649" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G650" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G651" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G652" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G653" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G654" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G655" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G656" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G658" t="n">
-        <v>0.669814944267273</v>
+        <v>0.669814884662628</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G660" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G661" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G662" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G663" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G664" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G665" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G670" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G672" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G673" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G675" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G678" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G681" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G687" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G691" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G692" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G698" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G699" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G700" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G703" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G707" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G708" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G713" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G716" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G717" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G720" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G722" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G728" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G730" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G734" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G735" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G736" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G738" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G740" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G742" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G743" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G747" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G748" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G750" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G754" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G755" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G756" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G757" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G760" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G764" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G765" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G767" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G768" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G769" t="n">
-        <v>0.672582805156708</v>
+        <v>0.672582745552063</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G777" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G778" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G782" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G783" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G785" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G786" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G790" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G792" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G794" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G795" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G800" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G803" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G806" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G808" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G809" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G810" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G812" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G813" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G815" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G816" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G818" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G819" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G821" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G822" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G823" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G825" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G826" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G827" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G828" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G829" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G832" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G835" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G836" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G837" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G838" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G839" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G840" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G841" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G842" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G843" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G844" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G845" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G846" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G847" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G849" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G850" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G852" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G853" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G854" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G855" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G856" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G860" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G862" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G864" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G865" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G869" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G872" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G873" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G875" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G888" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G894" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G895" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G897" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G898" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G900" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G901" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G902" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G903" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G909" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G910" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G911" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G912" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G914" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G915" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G916" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G921" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G922" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G954" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G955" t="n">
-        <v>0.682270109653473</v>
+        <v>0.682270169258118</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G956" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G957" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G958" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G959" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G960" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G961" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G964" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G965" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G967" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G969" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G970" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G971" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G976" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G977" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G979" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G983" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G988" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G989" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G990" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G993" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G996" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G998" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.575708746910095</v>
+        <v>0.575708627700806</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.631065368652344</v>
+        <v>0.631065309047699</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.618610024452209</v>
+        <v>0.618610084056854</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.595083594322205</v>
+        <v>0.59508353471756</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.60615485906601</v>
+        <v>0.606154799461365</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.58539605140686</v>
+        <v>0.585396111011505</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.577092528343201</v>
+        <v>0.57709264755249</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.58401221036911</v>
+        <v>0.584012150764465</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.60200309753418</v>
+        <v>0.602003037929535</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.60200309753418</v>
+        <v>0.602003037929535</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.588163912296295</v>
+        <v>0.58816397190094</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.60753870010376</v>
+        <v>0.607538759708405</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.613074362277985</v>
+        <v>0.613074421882629</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.631065368652344</v>
+        <v>0.631065309047699</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.631065368652344</v>
+        <v>0.631065309047699</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.631065368652344</v>
+        <v>0.631065309047699</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.649056136608124</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.682270109653473</v>
+        <v>0.682270169258118</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.689189791679382</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.736934840679169</v>
+        <v>0.736934900283813</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.736934840679169</v>
+        <v>0.736934900283813</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.719635844230652</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.788831651210785</v>
+        <v>0.78883159160614</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.788831651210785</v>
+        <v>0.78883159160614</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.768072903156281</v>
+        <v>0.768072843551636</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>1.125</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.778452277183533</v>
+        <v>0.778452336788177</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.785371899604797</v>
+        <v>0.785371840000153</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.806130468845367</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.788831651210785</v>
+        <v>0.78883159160614</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.788831651210785</v>
+        <v>0.78883159160614</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.806130468845367</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.806130468845367</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.806130468845367</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.837268650531769</v>
+        <v>0.837268710136414</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.826889336109161</v>
+        <v>0.826889276504517</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.826889336109161</v>
+        <v>0.826889276504517</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.837268650531769</v>
+        <v>0.837268710136414</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.847647964954376</v>
+        <v>0.847648024559021</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.854567587375641</v>
+        <v>0.854567646980286</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.833808898925781</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.833808898925781</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.837268650531769</v>
+        <v>0.837268710136414</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.833808898925781</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.837268650531769</v>
+        <v>0.837268710136414</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.920303523540497</v>
+        <v>0.920303583145142</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.906464338302612</v>
+        <v>0.906464397907257</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.927223145961761</v>
+        <v>0.927223265171051</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.941062331199646</v>
+        <v>0.941062271595001</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.947981834411621</v>
+        <v>0.947981774806976</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602639198303</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602639198303</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.947981834411621</v>
+        <v>0.947981774806976</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.972200393676758</v>
+        <v>0.972200334072113</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.965280890464783</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.965280890464783</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.965280890464783</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.96874064207077</v>
+        <v>0.968740582466125</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.99641889333725</v>
+        <v>0.996418952941895</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.999878644943237</v>
+        <v>0.999878704547882</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.999878644943237</v>
+        <v>0.999878704547882</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.00333857536316</v>
+        <v>1.00333845615387</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.99641889333725</v>
+        <v>0.996418952941895</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.986039459705353</v>
+        <v>0.986039519309998</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.986039459705353</v>
+        <v>0.986039519309998</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.961821019649506</v>
+        <v>0.96182107925415</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.961821019649506</v>
+        <v>0.96182107925415</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.920303523540497</v>
+        <v>0.920303583145142</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.920303523540497</v>
+        <v>0.920303583145142</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602639198303</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.927223145961761</v>
+        <v>0.927223265171051</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.965280890464783</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.96874064207077</v>
+        <v>0.968740582466125</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.965280890464783</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.989499390125275</v>
+        <v>0.989499151706696</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.989499390125275</v>
+        <v>0.989499151706696</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.00333857536316</v>
+        <v>1.00333845615387</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.03101682662964</v>
+        <v>1.03101670742035</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.09675288200378</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.11751139163971</v>
+        <v>1.117511510849</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.10367226600647</v>
+        <v>1.10367238521576</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.09675288200378</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.09329283237457</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.09329283237457</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.07599401473999</v>
+        <v>1.07599413394928</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.09329283237457</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.05523526668549</v>
+        <v>1.0552351474762</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.07599401473999</v>
+        <v>1.07599413394928</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.07599401473999</v>
+        <v>1.07599413394928</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.06907451152802</v>
+        <v>1.06907439231873</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.11751139163971</v>
+        <v>1.117511510849</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.20054638385773</v>
+        <v>1.20054650306702</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.13481056690216</v>
+        <v>1.13481032848358</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.07599401473999</v>
+        <v>1.07599413394928</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.09675288200378</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.1867071390152</v>
+        <v>1.18670725822449</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.20054638385773</v>
+        <v>1.20054650306702</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.2282247543335</v>
+        <v>1.22822463512421</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.26282274723053</v>
+        <v>1.26282250881195</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.25244307518005</v>
+        <v>1.25244319438934</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.22130501270294</v>
+        <v>1.22130513191223</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.2282247543335</v>
+        <v>1.22822463512421</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.2282247543335</v>
+        <v>1.22822463512421</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.22476482391357</v>
+        <v>1.22476494312286</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.19016718864441</v>
+        <v>1.19016706943512</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.00590598583221</v>
+        <v>1.00590586662292</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.0266889333725</v>
+        <v>1.02668905258179</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.00174915790558</v>
+        <v>1.00174927711487</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.0266889333725</v>
+        <v>1.02668905258179</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.00174915790558</v>
+        <v>1.00174927711487</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.12644827365875</v>
+        <v>1.12644839286804</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.13891816139221</v>
+        <v>1.13891804218292</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.13891816139221</v>
+        <v>1.13891804218292</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.0433155298233</v>
+        <v>1.04331564903259</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.05162882804871</v>
+        <v>1.05162870883942</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.05162882804871</v>
+        <v>1.05162870883942</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.05162882804871</v>
+        <v>1.05162870883942</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.00590598583221</v>
+        <v>1.00590586662292</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.13891816139221</v>
+        <v>1.13891804218292</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.13891816139221</v>
+        <v>1.13891804218292</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.23452067375183</v>
+        <v>1.23452079296112</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.23867750167847</v>
+        <v>1.23867738246918</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>1.5</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.24699068069458</v>
+        <v>1.24699079990387</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.2636171579361</v>
+        <v>1.26361727714539</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.2719304561615</v>
+        <v>1.27193033695221</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.31349682807922</v>
+        <v>1.31349694728851</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.31349682807922</v>
+        <v>1.31349694728851</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.30102705955505</v>
+        <v>1.30102694034576</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.30102705955505</v>
+        <v>1.30102694034576</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.30518352985382</v>
+        <v>1.30518364906311</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.2636171579361</v>
+        <v>1.26361727714539</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.25114738941193</v>
+        <v>1.25114727020264</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1818" t="n">
-        <v>1.23452067375183</v>
+        <v>1.23452079296112</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1822" t="n">
-        <v>1.19711124897003</v>
+        <v>1.19711112976074</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1845" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1851" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.20209896564484</v>
+        <v>1.20209908485413</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.18547248840332</v>
+        <v>1.18547236919403</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1862" t="n">
-        <v>1.20617949962616</v>
+        <v>1.20617938041687</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.20617949962616</v>
+        <v>1.20617938041687</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.20617949962616</v>
+        <v>1.20617938041687</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.20617949962616</v>
+        <v>1.20617938041687</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.19064927101135</v>
+        <v>1.19064915180206</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.18029582500458</v>
+        <v>1.18029570579529</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.19064927101135</v>
+        <v>1.19064915180206</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.22343516349792</v>
+        <v>1.22343528270721</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.22343516349792</v>
+        <v>1.22343528270721</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.23723995685577</v>
+        <v>1.23723983764648</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.26312339305878</v>
+        <v>1.26312351226807</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2014" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G2032" t="n">
-        <v>1.2907327413559</v>
+        <v>1.29073286056519</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G2039" t="n">
-        <v>1.33904898166656</v>
+        <v>1.33904910087585</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2043" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2047" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2051" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G2053" t="n">
-        <v>1.31661641597748</v>
+        <v>1.31661653518677</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.28728151321411</v>
+        <v>1.2872816324234</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G2068" t="n">
-        <v>1.29590952396393</v>
+        <v>1.29590940475464</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G2069" t="n">
-        <v>1.2907327413559</v>
+        <v>1.29073286056519</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.3856395483017</v>
+        <v>1.38563966751099</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.40289533138275</v>
+        <v>1.40289545059204</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.40634644031525</v>
+        <v>1.40634655952454</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.40979766845703</v>
+        <v>1.40979778766632</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.40807199478149</v>
+        <v>1.40807211399078</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.39254188537598</v>
+        <v>1.39254176616669</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.3821884393692</v>
+        <v>1.38218855857849</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G2095" t="n">
-        <v>1.36493265628815</v>
+        <v>1.36493253707886</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.37873721122742</v>
+        <v>1.37873733043671</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>1.85599994659424</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>43652</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.87800002098083</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.85800004005432</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.85599994659424</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.85599994659424</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.48506224155426</v>
+        <v>0.485062211751938</v>
       </c>
       <c r="H2" t="n">
         <v>191859</v>
@@ -456,7 +456,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.488176047801971</v>
+        <v>0.488176077604294</v>
       </c>
       <c r="H3" t="n">
         <v>84538</v>
@@ -485,7 +485,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.48160246014595</v>
+        <v>0.481602489948273</v>
       </c>
       <c r="H4" t="n">
         <v>28934</v>
@@ -514,7 +514,7 @@
         <v>0.689499974250793</v>
       </c>
       <c r="G5" t="n">
-        <v>0.477104723453522</v>
+        <v>0.477104753255844</v>
       </c>
       <c r="H5" t="n">
         <v>118824</v>
@@ -543,7 +543,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G6" t="n">
-        <v>0.478142648935318</v>
+        <v>0.47814267873764</v>
       </c>
       <c r="H6" t="n">
         <v>49636</v>
@@ -572,7 +572,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.478142648935318</v>
+        <v>0.47814267873764</v>
       </c>
       <c r="H7" t="n">
         <v>41531</v>
@@ -601,7 +601,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.479872524738312</v>
+        <v>0.479872554540634</v>
       </c>
       <c r="H8" t="n">
         <v>46220</v>
@@ -630,7 +630,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483678311109543</v>
+        <v>0.48367828130722</v>
       </c>
       <c r="H9" t="n">
         <v>53793</v>
@@ -688,7 +688,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G11" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H11" t="n">
         <v>328341</v>
@@ -746,7 +746,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G13" t="n">
-        <v>0.466379404067993</v>
+        <v>0.466379463672638</v>
       </c>
       <c r="H13" t="n">
         <v>70046</v>
@@ -775,7 +775,7 @@
         <v>0.647499978542328</v>
       </c>
       <c r="G14" t="n">
-        <v>0.448042541742325</v>
+        <v>0.448042511940002</v>
       </c>
       <c r="H14" t="n">
         <v>185010</v>
@@ -833,7 +833,7 @@
         <v>0.671000003814697</v>
       </c>
       <c r="G16" t="n">
-        <v>0.464303553104401</v>
+        <v>0.464303582906723</v>
       </c>
       <c r="H16" t="n">
         <v>84029</v>
@@ -891,7 +891,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G18" t="n">
-        <v>0.477450728416443</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H18" t="n">
         <v>119370</v>
@@ -920,7 +920,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G19" t="n">
-        <v>0.480910509824753</v>
+        <v>0.480910539627075</v>
       </c>
       <c r="H19" t="n">
         <v>50528</v>
@@ -949,7 +949,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G20" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H20" t="n">
         <v>46550</v>
@@ -1036,7 +1036,7 @@
         <v>0.66049998998642</v>
       </c>
       <c r="G23" t="n">
-        <v>0.457037955522537</v>
+        <v>0.457037925720215</v>
       </c>
       <c r="H23" t="n">
         <v>70489</v>
@@ -1065,7 +1065,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G24" t="n">
-        <v>0.453232169151306</v>
+        <v>0.453232198953629</v>
       </c>
       <c r="H24" t="n">
         <v>58754</v>
@@ -1094,7 +1094,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G25" t="n">
-        <v>0.455308079719543</v>
+        <v>0.455308049917221</v>
       </c>
       <c r="H25" t="n">
         <v>168696</v>
@@ -1123,7 +1123,7 @@
         <v>0.658999979496002</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456000030040741</v>
+        <v>0.456000000238419</v>
       </c>
       <c r="H26" t="n">
         <v>91179</v>
@@ -1152,7 +1152,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G27" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620715618134</v>
       </c>
       <c r="H27" t="n">
         <v>128286</v>
@@ -1181,7 +1181,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G28" t="n">
-        <v>0.422786056995392</v>
+        <v>0.422786027193069</v>
       </c>
       <c r="H28" t="n">
         <v>174406</v>
@@ -1210,7 +1210,7 @@
         <v>0.619499981403351</v>
       </c>
       <c r="G29" t="n">
-        <v>0.428667724132538</v>
+        <v>0.428667664527893</v>
       </c>
       <c r="H29" t="n">
         <v>258654</v>
@@ -1268,7 +1268,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>0.425553917884827</v>
+        <v>0.425553888082504</v>
       </c>
       <c r="H31" t="n">
         <v>128707</v>
@@ -1326,7 +1326,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G33" t="n">
-        <v>0.433165460824966</v>
+        <v>0.433165431022644</v>
       </c>
       <c r="H33" t="n">
         <v>214463</v>
@@ -1413,7 +1413,7 @@
         <v>0.625</v>
       </c>
       <c r="G36" t="n">
-        <v>0.432473480701447</v>
+        <v>0.432473450899124</v>
       </c>
       <c r="H36" t="n">
         <v>45866</v>
@@ -1442,7 +1442,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G37" t="n">
-        <v>0.437317192554474</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H37" t="n">
         <v>59186</v>
@@ -1500,7 +1500,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>0.429013669490814</v>
+        <v>0.429013699293137</v>
       </c>
       <c r="H39" t="n">
         <v>68431</v>
@@ -1529,7 +1529,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G40" t="n">
-        <v>0.433857351541519</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H40" t="n">
         <v>83632</v>
@@ -1558,7 +1558,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G41" t="n">
-        <v>0.432127475738525</v>
+        <v>0.432127505540848</v>
       </c>
       <c r="H41" t="n">
         <v>54191</v>
@@ -1616,7 +1616,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G43" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H43" t="n">
         <v>51995</v>
@@ -1645,7 +1645,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G44" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620715618134</v>
       </c>
       <c r="H44" t="n">
         <v>148615</v>
@@ -1732,7 +1732,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G47" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H47" t="n">
         <v>26658</v>
@@ -1761,7 +1761,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G48" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H48" t="n">
         <v>122811</v>
@@ -1790,7 +1790,7 @@
         <v>0.621500015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>0.430051624774933</v>
+        <v>0.43005159497261</v>
       </c>
       <c r="H49" t="n">
         <v>65600</v>
@@ -1819,7 +1819,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G50" t="n">
-        <v>0.433857351541519</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H50" t="n">
         <v>138176</v>
@@ -1848,7 +1848,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>0.441468954086304</v>
+        <v>0.441468924283981</v>
       </c>
       <c r="H51" t="n">
         <v>265251</v>
@@ -1906,7 +1906,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G53" t="n">
-        <v>0.439739048480988</v>
+        <v>0.439738988876343</v>
       </c>
       <c r="H53" t="n">
         <v>22435</v>
@@ -1935,7 +1935,7 @@
         <v>0.636500000953674</v>
       </c>
       <c r="G54" t="n">
-        <v>0.440430998802185</v>
+        <v>0.440431028604507</v>
       </c>
       <c r="H54" t="n">
         <v>86858</v>
@@ -1964,7 +1964,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G55" t="n">
-        <v>0.437317192554474</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H55" t="n">
         <v>76343</v>
@@ -1993,7 +1993,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>0.439393013715744</v>
+        <v>0.439393043518066</v>
       </c>
       <c r="H56" t="n">
         <v>61433</v>
@@ -2051,7 +2051,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G58" t="n">
-        <v>0.433511406183243</v>
+        <v>0.433511435985565</v>
       </c>
       <c r="H58" t="n">
         <v>68965</v>
@@ -2080,7 +2080,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G59" t="n">
-        <v>0.439739048480988</v>
+        <v>0.439738988876343</v>
       </c>
       <c r="H59" t="n">
         <v>123639</v>
@@ -2109,7 +2109,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G60" t="n">
-        <v>0.439739048480988</v>
+        <v>0.439738988876343</v>
       </c>
       <c r="H60" t="n">
         <v>91266</v>
@@ -2254,7 +2254,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G65" t="n">
-        <v>0.431781530380249</v>
+        <v>0.431781560182571</v>
       </c>
       <c r="H65" t="n">
         <v>57188</v>
@@ -2283,7 +2283,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G66" t="n">
-        <v>0.432127475738525</v>
+        <v>0.432127505540848</v>
       </c>
       <c r="H66" t="n">
         <v>90493</v>
@@ -2312,7 +2312,7 @@
         <v>0.617500007152557</v>
       </c>
       <c r="G67" t="n">
-        <v>0.427283763885498</v>
+        <v>0.427283823490143</v>
       </c>
       <c r="H67" t="n">
         <v>56153</v>
@@ -2341,7 +2341,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G68" t="n">
-        <v>0.422786056995392</v>
+        <v>0.422786027193069</v>
       </c>
       <c r="H68" t="n">
         <v>79242</v>
@@ -2370,7 +2370,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>0.429013669490814</v>
+        <v>0.429013699293137</v>
       </c>
       <c r="H69" t="n">
         <v>66538</v>
@@ -2399,7 +2399,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>0.425553917884827</v>
+        <v>0.425553888082504</v>
       </c>
       <c r="H70" t="n">
         <v>76151</v>
@@ -2457,7 +2457,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G72" t="n">
-        <v>0.433857351541519</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H72" t="n">
         <v>69507</v>
@@ -2486,7 +2486,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G73" t="n">
-        <v>0.430397599935532</v>
+        <v>0.430397570133209</v>
       </c>
       <c r="H73" t="n">
         <v>77451</v>
@@ -2573,7 +2573,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G76" t="n">
-        <v>0.456692010164261</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H76" t="n">
         <v>204695</v>
@@ -2602,7 +2602,7 @@
         <v>0.712999999523163</v>
       </c>
       <c r="G77" t="n">
-        <v>0.49336576461792</v>
+        <v>0.493365705013275</v>
       </c>
       <c r="H77" t="n">
         <v>309777</v>
@@ -2631,7 +2631,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G78" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H78" t="n">
         <v>132097</v>
@@ -2660,7 +2660,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G79" t="n">
-        <v>0.48229444026947</v>
+        <v>0.482294470071793</v>
       </c>
       <c r="H79" t="n">
         <v>117083</v>
@@ -2689,7 +2689,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G80" t="n">
-        <v>0.479872524738312</v>
+        <v>0.479872554540634</v>
       </c>
       <c r="H80" t="n">
         <v>22198</v>
@@ -2718,7 +2718,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>0.483678311109543</v>
+        <v>0.48367828130722</v>
       </c>
       <c r="H81" t="n">
         <v>129245</v>
@@ -2776,7 +2776,7 @@
         <v>0.683499991893768</v>
       </c>
       <c r="G83" t="n">
-        <v>0.472952961921692</v>
+        <v>0.472952991724014</v>
       </c>
       <c r="H83" t="n">
         <v>57129</v>
@@ -2805,7 +2805,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G84" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H84" t="n">
         <v>97915</v>
@@ -2834,7 +2834,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G85" t="n">
-        <v>0.453924179077148</v>
+        <v>0.453924238681793</v>
       </c>
       <c r="H85" t="n">
         <v>69792</v>
@@ -2892,7 +2892,7 @@
         <v>0.648500025272369</v>
       </c>
       <c r="G87" t="n">
-        <v>0.448734492063522</v>
+        <v>0.4487344622612</v>
       </c>
       <c r="H87" t="n">
         <v>20302</v>
@@ -2921,7 +2921,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G88" t="n">
-        <v>0.450464367866516</v>
+        <v>0.450464397668839</v>
       </c>
       <c r="H88" t="n">
         <v>17790</v>
@@ -2950,7 +2950,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G89" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620715618134</v>
       </c>
       <c r="H89" t="n">
         <v>81033</v>
@@ -3095,7 +3095,7 @@
         <v>0.640999972820282</v>
       </c>
       <c r="G94" t="n">
-        <v>0.443544745445251</v>
+        <v>0.443544775247574</v>
       </c>
       <c r="H94" t="n">
         <v>54113</v>
@@ -3153,7 +3153,7 @@
         <v>0.647499978542328</v>
       </c>
       <c r="G96" t="n">
-        <v>0.448042541742325</v>
+        <v>0.448042511940002</v>
       </c>
       <c r="H96" t="n">
         <v>27367</v>
@@ -3240,7 +3240,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>0.439393013715744</v>
+        <v>0.439393043518066</v>
       </c>
       <c r="H99" t="n">
         <v>79566</v>
@@ -3298,7 +3298,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>0.443890750408173</v>
+        <v>0.443890780210495</v>
       </c>
       <c r="H101" t="n">
         <v>21942</v>
@@ -3385,7 +3385,7 @@
         <v>0.6875</v>
       </c>
       <c r="G104" t="n">
-        <v>0.475720822811127</v>
+        <v>0.475720852613449</v>
       </c>
       <c r="H104" t="n">
         <v>124171</v>
@@ -3414,7 +3414,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>0.478142648935318</v>
+        <v>0.47814267873764</v>
       </c>
       <c r="H105" t="n">
         <v>164848</v>
@@ -3443,7 +3443,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G106" t="n">
-        <v>0.473990917205811</v>
+        <v>0.473990887403488</v>
       </c>
       <c r="H106" t="n">
         <v>8390</v>
@@ -3472,7 +3472,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G107" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H107" t="n">
         <v>51910</v>
@@ -3530,7 +3530,7 @@
         <v>0.698499977588654</v>
       </c>
       <c r="G109" t="n">
-        <v>0.483332276344299</v>
+        <v>0.483332306146622</v>
       </c>
       <c r="H109" t="n">
         <v>100009</v>
@@ -3559,7 +3559,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G110" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H110" t="n">
         <v>62146</v>
@@ -3588,7 +3588,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G111" t="n">
-        <v>0.477450728416443</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H111" t="n">
         <v>81596</v>
@@ -3646,7 +3646,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G113" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H113" t="n">
         <v>77229</v>
@@ -3675,7 +3675,7 @@
         <v>0.674499988555908</v>
       </c>
       <c r="G114" t="n">
-        <v>0.46672534942627</v>
+        <v>0.466725409030914</v>
       </c>
       <c r="H114" t="n">
         <v>30620</v>
@@ -3704,7 +3704,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>0.443890750408173</v>
+        <v>0.443890780210495</v>
       </c>
       <c r="H115" t="n">
         <v>154035</v>
@@ -3762,7 +3762,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G117" t="n">
-        <v>0.449080437421799</v>
+        <v>0.449080467224121</v>
       </c>
       <c r="H117" t="n">
         <v>50524</v>
@@ -3791,7 +3791,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G118" t="n">
-        <v>0.437317192554474</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H118" t="n">
         <v>37197</v>
@@ -3878,7 +3878,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G121" t="n">
-        <v>0.453924179077148</v>
+        <v>0.453924238681793</v>
       </c>
       <c r="H121" t="n">
         <v>57381</v>
@@ -3907,7 +3907,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G122" t="n">
-        <v>0.445966631174088</v>
+        <v>0.445966601371765</v>
       </c>
       <c r="H122" t="n">
         <v>33393</v>
@@ -3965,7 +3965,7 @@
         <v>0.604499995708466</v>
       </c>
       <c r="G124" t="n">
-        <v>0.418288379907608</v>
+        <v>0.418288350105286</v>
       </c>
       <c r="H124" t="n">
         <v>486768</v>
@@ -3994,7 +3994,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G125" t="n">
-        <v>0.419326275587082</v>
+        <v>0.419326305389404</v>
       </c>
       <c r="H125" t="n">
         <v>164285</v>
@@ -4023,7 +4023,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G126" t="n">
-        <v>0.436625182628632</v>
+        <v>0.436625242233276</v>
       </c>
       <c r="H126" t="n">
         <v>99483</v>
@@ -4081,7 +4081,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>0.441468954086304</v>
+        <v>0.441468924283981</v>
       </c>
       <c r="H128" t="n">
         <v>49996</v>
@@ -4110,7 +4110,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G129" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H129" t="n">
         <v>182844</v>
@@ -4139,7 +4139,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>0.455308079719543</v>
+        <v>0.455308049917221</v>
       </c>
       <c r="H130" t="n">
         <v>41364</v>
@@ -4168,7 +4168,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G131" t="n">
-        <v>0.453924179077148</v>
+        <v>0.453924238681793</v>
       </c>
       <c r="H131" t="n">
         <v>46996</v>
@@ -4284,7 +4284,7 @@
         <v>0.651000022888184</v>
       </c>
       <c r="G135" t="n">
-        <v>0.450464367866516</v>
+        <v>0.450464397668839</v>
       </c>
       <c r="H135" t="n">
         <v>39341</v>
@@ -4313,7 +4313,7 @@
         <v>0.675499975681305</v>
       </c>
       <c r="G136" t="n">
-        <v>0.467417359352112</v>
+        <v>0.467417329549789</v>
       </c>
       <c r="H136" t="n">
         <v>182312</v>
@@ -4342,7 +4342,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G137" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H137" t="n">
         <v>44437</v>
@@ -4371,7 +4371,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G138" t="n">
-        <v>0.473990917205811</v>
+        <v>0.473990887403488</v>
       </c>
       <c r="H138" t="n">
         <v>15038</v>
@@ -4400,7 +4400,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>0.476758778095245</v>
+        <v>0.476758748292923</v>
       </c>
       <c r="H139" t="n">
         <v>24754</v>
@@ -4458,7 +4458,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G141" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H141" t="n">
         <v>80976</v>
@@ -4487,7 +4487,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G142" t="n">
-        <v>0.478142648935318</v>
+        <v>0.47814267873764</v>
       </c>
       <c r="H142" t="n">
         <v>36816</v>
@@ -4516,7 +4516,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>0.476758778095245</v>
+        <v>0.476758748292923</v>
       </c>
       <c r="H143" t="n">
         <v>31703</v>
@@ -4545,7 +4545,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G144" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H144" t="n">
         <v>51317</v>
@@ -4603,7 +4603,7 @@
         <v>0.66949999332428</v>
       </c>
       <c r="G146" t="n">
-        <v>0.46326556801796</v>
+        <v>0.463265597820282</v>
       </c>
       <c r="H146" t="n">
         <v>17700</v>
@@ -4661,7 +4661,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.477450728416443</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H148" t="n">
         <v>324437</v>
@@ -4690,7 +4690,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G149" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H149" t="n">
         <v>70330</v>
@@ -4719,7 +4719,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G150" t="n">
-        <v>0.466033428907394</v>
+        <v>0.466033399105072</v>
       </c>
       <c r="H150" t="n">
         <v>34614</v>
@@ -4748,7 +4748,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G151" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H151" t="n">
         <v>33263</v>
@@ -4777,7 +4777,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G152" t="n">
-        <v>0.456692010164261</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H152" t="n">
         <v>55357</v>
@@ -4835,7 +4835,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G154" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H154" t="n">
         <v>28966</v>
@@ -4893,7 +4893,7 @@
         <v>0.664499998092651</v>
       </c>
       <c r="G156" t="n">
-        <v>0.459805816411972</v>
+        <v>0.45980578660965</v>
       </c>
       <c r="H156" t="n">
         <v>20377</v>
@@ -4922,7 +4922,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G157" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H157" t="n">
         <v>185257</v>
@@ -4951,7 +4951,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>0.466033428907394</v>
+        <v>0.466033399105072</v>
       </c>
       <c r="H158" t="n">
         <v>5763</v>
@@ -4980,7 +4980,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G159" t="n">
-        <v>0.460497707128525</v>
+        <v>0.460497736930847</v>
       </c>
       <c r="H159" t="n">
         <v>12129</v>
@@ -5009,7 +5009,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G160" t="n">
-        <v>0.456692010164261</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H160" t="n">
         <v>36233</v>
@@ -5154,7 +5154,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G165" t="n">
-        <v>0.469839215278625</v>
+        <v>0.469839185476303</v>
       </c>
       <c r="H165" t="n">
         <v>29550</v>
@@ -5183,7 +5183,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G166" t="n">
-        <v>0.469147205352783</v>
+        <v>0.469147145748138</v>
       </c>
       <c r="H166" t="n">
         <v>9905</v>
@@ -5212,7 +5212,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G167" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H167" t="n">
         <v>30130</v>
@@ -5241,7 +5241,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>0.473298966884613</v>
+        <v>0.473298996686935</v>
       </c>
       <c r="H168" t="n">
         <v>14300</v>
@@ -5270,7 +5270,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G169" t="n">
-        <v>0.473298966884613</v>
+        <v>0.473298996686935</v>
       </c>
       <c r="H169" t="n">
         <v>1644</v>
@@ -5299,7 +5299,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G170" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H170" t="n">
         <v>58222</v>
@@ -5328,7 +5328,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G171" t="n">
-        <v>0.469147205352783</v>
+        <v>0.469147145748138</v>
       </c>
       <c r="H171" t="n">
         <v>30801</v>
@@ -5357,7 +5357,7 @@
         <v>0.679499983787537</v>
       </c>
       <c r="G172" t="n">
-        <v>0.470185101032257</v>
+        <v>0.470185130834579</v>
       </c>
       <c r="H172" t="n">
         <v>20045</v>
@@ -5386,7 +5386,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G173" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H173" t="n">
         <v>25441</v>
@@ -5415,7 +5415,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G174" t="n">
-        <v>0.460497707128525</v>
+        <v>0.460497736930847</v>
       </c>
       <c r="H174" t="n">
         <v>28021</v>
@@ -5473,7 +5473,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G176" t="n">
-        <v>0.460497707128525</v>
+        <v>0.460497736930847</v>
       </c>
       <c r="H176" t="n">
         <v>54782</v>
@@ -5502,7 +5502,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G177" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H177" t="n">
         <v>71591</v>
@@ -5531,7 +5531,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G178" t="n">
-        <v>0.456692010164261</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H178" t="n">
         <v>143013</v>
@@ -5560,7 +5560,7 @@
         <v>0.658500015735626</v>
       </c>
       <c r="G179" t="n">
-        <v>0.455654054880142</v>
+        <v>0.455653995275497</v>
       </c>
       <c r="H179" t="n">
         <v>20378</v>
@@ -5647,7 +5647,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G182" t="n">
-        <v>0.456692010164261</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H182" t="n">
         <v>58262</v>
@@ -5821,7 +5821,7 @@
         <v>0.66100001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>0.457383960485458</v>
+        <v>0.457383990287781</v>
       </c>
       <c r="H188" t="n">
         <v>37935</v>
@@ -5850,7 +5850,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G189" t="n">
-        <v>0.461535692214966</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H189" t="n">
         <v>176240</v>
@@ -5879,7 +5879,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G190" t="n">
-        <v>0.464995503425598</v>
+        <v>0.464995473623276</v>
       </c>
       <c r="H190" t="n">
         <v>160048</v>
@@ -5937,7 +5937,7 @@
         <v>0.686500012874603</v>
       </c>
       <c r="G192" t="n">
-        <v>0.475028842687607</v>
+        <v>0.475028812885284</v>
       </c>
       <c r="H192" t="n">
         <v>129442</v>
@@ -5995,7 +5995,7 @@
         <v>0.672500014305115</v>
       </c>
       <c r="G194" t="n">
-        <v>0.465341448783875</v>
+        <v>0.465341418981552</v>
       </c>
       <c r="H194" t="n">
         <v>23902</v>
@@ -6024,7 +6024,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G195" t="n">
-        <v>0.467763304710388</v>
+        <v>0.467763274908066</v>
       </c>
       <c r="H195" t="n">
         <v>18570</v>
@@ -6053,7 +6053,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G196" t="n">
-        <v>0.470531105995178</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H196" t="n">
         <v>98271</v>
@@ -6082,7 +6082,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G197" t="n">
-        <v>0.463611572980881</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H197" t="n">
         <v>99568</v>
@@ -6169,7 +6169,7 @@
         <v>0.6875</v>
       </c>
       <c r="G200" t="n">
-        <v>0.475720822811127</v>
+        <v>0.475720852613449</v>
       </c>
       <c r="H200" t="n">
         <v>120951</v>
@@ -6198,7 +6198,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G201" t="n">
-        <v>0.48229444026947</v>
+        <v>0.482294470071793</v>
       </c>
       <c r="H201" t="n">
         <v>209149</v>
@@ -6256,7 +6256,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G203" t="n">
-        <v>0.498555451631546</v>
+        <v>0.498555421829224</v>
       </c>
       <c r="H203" t="n">
         <v>121289</v>
@@ -6285,7 +6285,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>0.489214032888412</v>
+        <v>0.489214062690735</v>
       </c>
       <c r="H204" t="n">
         <v>146400</v>
@@ -6314,7 +6314,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G205" t="n">
-        <v>0.493019729852676</v>
+        <v>0.493019759654999</v>
       </c>
       <c r="H205" t="n">
         <v>36091</v>
@@ -6343,7 +6343,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>0.50305312871933</v>
+        <v>0.503053188323975</v>
       </c>
       <c r="H206" t="n">
         <v>66811</v>
@@ -6430,7 +6430,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H209" t="n">
         <v>531491</v>
@@ -6488,7 +6488,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G211" t="n">
-        <v>0.51689225435257</v>
+        <v>0.516892313957214</v>
       </c>
       <c r="H211" t="n">
         <v>202768</v>
@@ -6604,7 +6604,7 @@
         <v>0.736999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>0.50997269153595</v>
+        <v>0.509972751140594</v>
       </c>
       <c r="H215" t="n">
         <v>24480</v>
@@ -6691,7 +6691,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G218" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H218" t="n">
         <v>56648</v>
@@ -6778,7 +6778,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G221" t="n">
-        <v>0.495441645383835</v>
+        <v>0.495441615581512</v>
       </c>
       <c r="H221" t="n">
         <v>150686</v>
@@ -6807,7 +6807,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G222" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H222" t="n">
         <v>140896</v>
@@ -6836,7 +6836,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G223" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H223" t="n">
         <v>73200</v>
@@ -6865,7 +6865,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G224" t="n">
-        <v>0.49820950627327</v>
+        <v>0.498209476470947</v>
       </c>
       <c r="H224" t="n">
         <v>27258</v>
@@ -6894,7 +6894,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H225" t="n">
         <v>52932</v>
@@ -6923,7 +6923,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G226" t="n">
-        <v>0.495441645383835</v>
+        <v>0.495441615581512</v>
       </c>
       <c r="H226" t="n">
         <v>79074</v>
@@ -6952,7 +6952,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G227" t="n">
-        <v>0.494057714939117</v>
+        <v>0.494057685136795</v>
       </c>
       <c r="H227" t="n">
         <v>51852</v>
@@ -7039,7 +7039,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G230" t="n">
-        <v>0.485754191875458</v>
+        <v>0.48575422167778</v>
       </c>
       <c r="H230" t="n">
         <v>149866</v>
@@ -7068,7 +7068,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G231" t="n">
-        <v>0.493019729852676</v>
+        <v>0.493019759654999</v>
       </c>
       <c r="H231" t="n">
         <v>140299</v>
@@ -7126,7 +7126,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G233" t="n">
-        <v>0.49820950627327</v>
+        <v>0.498209476470947</v>
       </c>
       <c r="H233" t="n">
         <v>26904</v>
@@ -7155,7 +7155,7 @@
         <v>0.706499993801117</v>
       </c>
       <c r="G234" t="n">
-        <v>0.488867998123169</v>
+        <v>0.488868027925491</v>
       </c>
       <c r="H234" t="n">
         <v>54717</v>
@@ -7213,7 +7213,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G236" t="n">
-        <v>0.4926737844944</v>
+        <v>0.492673754692078</v>
       </c>
       <c r="H236" t="n">
         <v>271535</v>
@@ -7242,7 +7242,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G237" t="n">
-        <v>0.4926737844944</v>
+        <v>0.492673754692078</v>
       </c>
       <c r="H237" t="n">
         <v>16612</v>
@@ -7271,7 +7271,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G238" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H238" t="n">
         <v>43905</v>
@@ -7387,7 +7387,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G242" t="n">
-        <v>0.503745138645172</v>
+        <v>0.503745079040527</v>
       </c>
       <c r="H242" t="n">
         <v>81153</v>
@@ -7445,7 +7445,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G244" t="n">
-        <v>0.513432502746582</v>
+        <v>0.513432443141937</v>
       </c>
       <c r="H244" t="n">
         <v>119688</v>
@@ -7503,7 +7503,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G246" t="n">
-        <v>0.513432502746582</v>
+        <v>0.513432443141937</v>
       </c>
       <c r="H246" t="n">
         <v>60167</v>
@@ -7532,7 +7532,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G247" t="n">
-        <v>0.51689225435257</v>
+        <v>0.516892313957214</v>
       </c>
       <c r="H247" t="n">
         <v>57020</v>
@@ -7619,7 +7619,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G250" t="n">
-        <v>0.521736025810242</v>
+        <v>0.521735966205597</v>
       </c>
       <c r="H250" t="n">
         <v>387529</v>
@@ -7735,7 +7735,7 @@
         <v>0.752499997615814</v>
       </c>
       <c r="G254" t="n">
-        <v>0.520698130130768</v>
+        <v>0.520698070526123</v>
       </c>
       <c r="H254" t="n">
         <v>83322</v>
@@ -7764,7 +7764,7 @@
         <v>0.75</v>
       </c>
       <c r="G255" t="n">
-        <v>0.518968164920807</v>
+        <v>0.518968224525452</v>
       </c>
       <c r="H255" t="n">
         <v>190032</v>
@@ -7793,7 +7793,7 @@
         <v>0.750999987125397</v>
       </c>
       <c r="G256" t="n">
-        <v>0.51966005563736</v>
+        <v>0.519660115242004</v>
       </c>
       <c r="H256" t="n">
         <v>37472</v>
@@ -7822,7 +7822,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G257" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352005958557</v>
       </c>
       <c r="H257" t="n">
         <v>97060</v>
@@ -7996,7 +7996,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G263" t="n">
-        <v>0.531423449516296</v>
+        <v>0.531423389911652</v>
       </c>
       <c r="H263" t="n">
         <v>280499</v>
@@ -8054,7 +8054,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G265" t="n">
-        <v>0.533499240875244</v>
+        <v>0.533499360084534</v>
       </c>
       <c r="H265" t="n">
         <v>57142</v>
@@ -8083,7 +8083,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G266" t="n">
-        <v>0.535575151443481</v>
+        <v>0.535575211048126</v>
       </c>
       <c r="H266" t="n">
         <v>145736</v>
@@ -8112,7 +8112,7 @@
         <v>0.77649998664856</v>
       </c>
       <c r="G267" t="n">
-        <v>0.537305057048798</v>
+        <v>0.537305116653442</v>
       </c>
       <c r="H267" t="n">
         <v>188591</v>
@@ -8141,7 +8141,7 @@
         <v>0.780499994754791</v>
       </c>
       <c r="G268" t="n">
-        <v>0.540072917938232</v>
+        <v>0.540072858333588</v>
       </c>
       <c r="H268" t="n">
         <v>230939</v>
@@ -8170,7 +8170,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G269" t="n">
-        <v>0.539726912975311</v>
+        <v>0.539726853370667</v>
       </c>
       <c r="H269" t="n">
         <v>88289</v>
@@ -8315,7 +8315,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G274" t="n">
-        <v>0.542494773864746</v>
+        <v>0.542494714260101</v>
       </c>
       <c r="H274" t="n">
         <v>94788</v>
@@ -8402,7 +8402,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G277" t="n">
-        <v>0.538689017295837</v>
+        <v>0.538688957691193</v>
       </c>
       <c r="H277" t="n">
         <v>76279</v>
@@ -8431,7 +8431,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H278" t="n">
         <v>193866</v>
@@ -8460,7 +8460,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G279" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352005958557</v>
       </c>
       <c r="H279" t="n">
         <v>87634</v>
@@ -8518,7 +8518,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G281" t="n">
-        <v>0.526925623416901</v>
+        <v>0.526925683021545</v>
       </c>
       <c r="H281" t="n">
         <v>46227</v>
@@ -8576,7 +8576,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G283" t="n">
-        <v>0.527271628379822</v>
+        <v>0.527271687984467</v>
       </c>
       <c r="H283" t="n">
         <v>131626</v>
@@ -8634,7 +8634,7 @@
         <v>0.752499997615814</v>
       </c>
       <c r="G285" t="n">
-        <v>0.520698130130768</v>
+        <v>0.520698070526123</v>
       </c>
       <c r="H285" t="n">
         <v>82797</v>
@@ -8721,7 +8721,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G288" t="n">
-        <v>0.535575151443481</v>
+        <v>0.535575211048126</v>
       </c>
       <c r="H288" t="n">
         <v>191680</v>
@@ -8895,7 +8895,7 @@
         <v>0.741500020027161</v>
       </c>
       <c r="G294" t="n">
-        <v>0.513086557388306</v>
+        <v>0.513086497783661</v>
       </c>
       <c r="H294" t="n">
         <v>194132</v>
@@ -8924,7 +8924,7 @@
         <v>0.742999970912933</v>
       </c>
       <c r="G295" t="n">
-        <v>0.51412445306778</v>
+        <v>0.514124393463135</v>
       </c>
       <c r="H295" t="n">
         <v>184553</v>
@@ -9011,7 +9011,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G298" t="n">
-        <v>0.515508413314819</v>
+        <v>0.515508353710175</v>
       </c>
       <c r="H298" t="n">
         <v>476154</v>
@@ -9040,7 +9040,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G299" t="n">
-        <v>0.524503827095032</v>
+        <v>0.524503886699677</v>
       </c>
       <c r="H299" t="n">
         <v>291053</v>
@@ -9069,7 +9069,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H300" t="n">
         <v>148794</v>
@@ -9127,7 +9127,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>0.515508413314819</v>
+        <v>0.515508353710175</v>
       </c>
       <c r="H302" t="n">
         <v>169321</v>
@@ -9156,7 +9156,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G303" t="n">
-        <v>0.509280800819397</v>
+        <v>0.509280741214752</v>
       </c>
       <c r="H303" t="n">
         <v>281858</v>
@@ -9243,7 +9243,7 @@
         <v>0.738499999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>0.511010706424713</v>
+        <v>0.511010646820068</v>
       </c>
       <c r="H306" t="n">
         <v>46683</v>
@@ -9301,7 +9301,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>0.50305312871933</v>
+        <v>0.503053188323975</v>
       </c>
       <c r="H308" t="n">
         <v>393889</v>
@@ -9330,7 +9330,7 @@
         <v>0.732500016689301</v>
       </c>
       <c r="G309" t="n">
-        <v>0.506858944892883</v>
+        <v>0.506858885288239</v>
       </c>
       <c r="H309" t="n">
         <v>354387</v>
@@ -9417,7 +9417,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G312" t="n">
-        <v>0.505474984645844</v>
+        <v>0.505475044250488</v>
       </c>
       <c r="H312" t="n">
         <v>231484</v>
@@ -9591,7 +9591,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G318" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896959781647</v>
       </c>
       <c r="H318" t="n">
         <v>156057</v>
@@ -9620,7 +9620,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G319" t="n">
-        <v>0.513432502746582</v>
+        <v>0.513432443141937</v>
       </c>
       <c r="H319" t="n">
         <v>220996</v>
@@ -9910,7 +9910,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G329" t="n">
-        <v>0.505474984645844</v>
+        <v>0.505475044250488</v>
       </c>
       <c r="H329" t="n">
         <v>80896</v>
@@ -9968,7 +9968,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G331" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896959781647</v>
       </c>
       <c r="H331" t="n">
         <v>177163</v>
@@ -9997,7 +9997,7 @@
         <v>0.728500008583069</v>
       </c>
       <c r="G332" t="n">
-        <v>0.504091143608093</v>
+        <v>0.504091084003448</v>
       </c>
       <c r="H332" t="n">
         <v>61694</v>
@@ -10026,7 +10026,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G333" t="n">
-        <v>0.498555451631546</v>
+        <v>0.498555421829224</v>
       </c>
       <c r="H333" t="n">
         <v>457777</v>
@@ -10113,7 +10113,7 @@
         <v>0.726499974727631</v>
       </c>
       <c r="G336" t="n">
-        <v>0.502707123756409</v>
+        <v>0.502707183361053</v>
       </c>
       <c r="H336" t="n">
         <v>229492</v>
@@ -10229,7 +10229,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G340" t="n">
-        <v>0.509280800819397</v>
+        <v>0.509280741214752</v>
       </c>
       <c r="H340" t="n">
         <v>26445</v>
@@ -10345,7 +10345,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G344" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896959781647</v>
       </c>
       <c r="H344" t="n">
         <v>119791</v>
@@ -10374,7 +10374,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G345" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896959781647</v>
       </c>
       <c r="H345" t="n">
         <v>167117</v>
@@ -10461,7 +10461,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G348" t="n">
-        <v>0.523119926452637</v>
+        <v>0.523119866847992</v>
       </c>
       <c r="H348" t="n">
         <v>810246</v>
@@ -10490,7 +10490,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H349" t="n">
         <v>179526</v>
@@ -10519,7 +10519,7 @@
         <v>0.762499988079071</v>
       </c>
       <c r="G350" t="n">
-        <v>0.527617633342743</v>
+        <v>0.527617573738098</v>
       </c>
       <c r="H350" t="n">
         <v>372168</v>
@@ -10751,7 +10751,7 @@
         <v>0.742500007152557</v>
       </c>
       <c r="G358" t="n">
-        <v>0.513778448104858</v>
+        <v>0.513778507709503</v>
       </c>
       <c r="H358" t="n">
         <v>125302</v>
@@ -10780,7 +10780,7 @@
         <v>0.75</v>
       </c>
       <c r="G359" t="n">
-        <v>0.518968164920807</v>
+        <v>0.518968224525452</v>
       </c>
       <c r="H359" t="n">
         <v>262928</v>
@@ -10809,7 +10809,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G360" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352005958557</v>
       </c>
       <c r="H360" t="n">
         <v>471079</v>
@@ -10838,7 +10838,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H361" t="n">
         <v>250363</v>
@@ -10867,7 +10867,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G362" t="n">
-        <v>0.526579678058624</v>
+        <v>0.526579737663269</v>
       </c>
       <c r="H362" t="n">
         <v>397546</v>
@@ -10896,7 +10896,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>0.526925623416901</v>
+        <v>0.526925683021545</v>
       </c>
       <c r="H363" t="n">
         <v>157123</v>
@@ -10954,7 +10954,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>0.532807290554047</v>
+        <v>0.532807350158691</v>
       </c>
       <c r="H365" t="n">
         <v>384026</v>
@@ -10983,7 +10983,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G366" t="n">
-        <v>0.533499240875244</v>
+        <v>0.533499360084534</v>
       </c>
       <c r="H366" t="n">
         <v>218685</v>
@@ -11128,7 +11128,7 @@
         <v>0.82150000333786</v>
       </c>
       <c r="G371" t="n">
-        <v>0.568443119525909</v>
+        <v>0.568443179130554</v>
       </c>
       <c r="H371" t="n">
         <v>388142</v>
@@ -11186,7 +11186,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G373" t="n">
-        <v>0.567405223846436</v>
+        <v>0.567405164241791</v>
       </c>
       <c r="H373" t="n">
         <v>193166</v>
@@ -11302,7 +11302,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G377" t="n">
-        <v>0.590239822864532</v>
+        <v>0.590239763259888</v>
       </c>
       <c r="H377" t="n">
         <v>1194426</v>
@@ -11331,7 +11331,7 @@
         <v>0.876999974250793</v>
       </c>
       <c r="G378" t="n">
-        <v>0.606846749782562</v>
+        <v>0.606846809387207</v>
       </c>
       <c r="H378" t="n">
         <v>1707069</v>
@@ -11389,7 +11389,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G380" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H380" t="n">
         <v>867530</v>
@@ -11505,7 +11505,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G384" t="n">
-        <v>0.646980285644531</v>
+        <v>0.646980345249176</v>
       </c>
       <c r="H384" t="n">
         <v>344710</v>
@@ -11534,7 +11534,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G385" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H385" t="n">
         <v>451253</v>
@@ -11563,7 +11563,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G386" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H386" t="n">
         <v>410438</v>
@@ -11621,7 +11621,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G388" t="n">
-        <v>0.634525120258331</v>
+        <v>0.634525060653687</v>
       </c>
       <c r="H388" t="n">
         <v>135604</v>
@@ -11650,7 +11650,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G389" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H389" t="n">
         <v>169577</v>
@@ -11708,7 +11708,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G391" t="n">
-        <v>0.646980285644531</v>
+        <v>0.646980345249176</v>
       </c>
       <c r="H391" t="n">
         <v>101808</v>
@@ -11737,7 +11737,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G392" t="n">
-        <v>0.638676822185516</v>
+        <v>0.638676881790161</v>
       </c>
       <c r="H392" t="n">
         <v>245408</v>
@@ -11795,7 +11795,7 @@
         <v>0.918500006198883</v>
       </c>
       <c r="G394" t="n">
-        <v>0.635563015937805</v>
+        <v>0.63556307554245</v>
       </c>
       <c r="H394" t="n">
         <v>186650</v>
@@ -11824,7 +11824,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G395" t="n">
-        <v>0.638676822185516</v>
+        <v>0.638676881790161</v>
       </c>
       <c r="H395" t="n">
         <v>155679</v>
@@ -11969,7 +11969,7 @@
         <v>0.921000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>0.637292981147766</v>
+        <v>0.637292921543121</v>
       </c>
       <c r="H400" t="n">
         <v>173975</v>
@@ -11998,7 +11998,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G401" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H401" t="n">
         <v>322849</v>
@@ -12114,7 +12114,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G405" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H405" t="n">
         <v>290812</v>
@@ -12143,7 +12143,7 @@
         <v>0.890999972820282</v>
       </c>
       <c r="G406" t="n">
-        <v>0.616534113883972</v>
+        <v>0.616534173488617</v>
       </c>
       <c r="H406" t="n">
         <v>246358</v>
@@ -12201,7 +12201,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G408" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H408" t="n">
         <v>80988</v>
@@ -12317,7 +12317,7 @@
         <v>0.887000024318695</v>
       </c>
       <c r="G412" t="n">
-        <v>0.613766312599182</v>
+        <v>0.613766372203827</v>
       </c>
       <c r="H412" t="n">
         <v>304473</v>
@@ -12375,7 +12375,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G414" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H414" t="n">
         <v>199929</v>
@@ -12404,7 +12404,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G415" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H415" t="n">
         <v>41393</v>
@@ -12433,7 +12433,7 @@
         <v>0.890500009059906</v>
       </c>
       <c r="G416" t="n">
-        <v>0.616188168525696</v>
+        <v>0.616188228130341</v>
       </c>
       <c r="H416" t="n">
         <v>43288</v>
@@ -12491,7 +12491,7 @@
         <v>0.886500000953674</v>
       </c>
       <c r="G418" t="n">
-        <v>0.613420307636261</v>
+        <v>0.613420367240906</v>
       </c>
       <c r="H418" t="n">
         <v>36859</v>
@@ -12520,7 +12520,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G419" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H419" t="n">
         <v>99917</v>
@@ -12549,7 +12549,7 @@
         <v>0.886500000953674</v>
       </c>
       <c r="G420" t="n">
-        <v>0.613420307636261</v>
+        <v>0.613420367240906</v>
       </c>
       <c r="H420" t="n">
         <v>57848</v>
@@ -12578,7 +12578,7 @@
         <v>0.886500000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>0.613420307636261</v>
+        <v>0.613420367240906</v>
       </c>
       <c r="H421" t="n">
         <v>56552</v>
@@ -12607,7 +12607,7 @@
         <v>0.886500000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>0.613420307636261</v>
+        <v>0.613420367240906</v>
       </c>
       <c r="H422" t="n">
         <v>100028</v>
@@ -12665,7 +12665,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G424" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H424" t="n">
         <v>51445</v>
@@ -12694,7 +12694,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H425" t="n">
         <v>113618</v>
@@ -12723,7 +12723,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H426" t="n">
         <v>30382</v>
@@ -12810,7 +12810,7 @@
         <v>0.887499988079071</v>
       </c>
       <c r="G429" t="n">
-        <v>0.614112377166748</v>
+        <v>0.614112317562103</v>
       </c>
       <c r="H429" t="n">
         <v>21849</v>
@@ -12839,7 +12839,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G430" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H430" t="n">
         <v>257986</v>
@@ -12868,7 +12868,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G431" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H431" t="n">
         <v>101366</v>
@@ -12897,7 +12897,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G432" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H432" t="n">
         <v>78599</v>
@@ -12926,7 +12926,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G433" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H433" t="n">
         <v>94241</v>
@@ -12955,7 +12955,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H434" t="n">
         <v>63978</v>
@@ -12984,7 +12984,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G435" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H435" t="n">
         <v>112829</v>
@@ -13013,7 +13013,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H436" t="n">
         <v>192904</v>
@@ -13042,7 +13042,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H437" t="n">
         <v>185924</v>
@@ -13071,7 +13071,7 @@
         <v>0.887499988079071</v>
       </c>
       <c r="G438" t="n">
-        <v>0.614112377166748</v>
+        <v>0.614112317562103</v>
       </c>
       <c r="H438" t="n">
         <v>179485</v>
@@ -13158,7 +13158,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>0.621377885341644</v>
+        <v>0.621377944946289</v>
       </c>
       <c r="H441" t="n">
         <v>218077</v>
@@ -13187,7 +13187,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G442" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H442" t="n">
         <v>301435</v>
@@ -13274,7 +13274,7 @@
         <v>0.916499972343445</v>
       </c>
       <c r="G445" t="n">
-        <v>0.634179174900055</v>
+        <v>0.634179055690765</v>
       </c>
       <c r="H445" t="n">
         <v>191783</v>
@@ -13332,7 +13332,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G447" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H447" t="n">
         <v>197331</v>
@@ -13390,7 +13390,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G449" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H449" t="n">
         <v>259567</v>
@@ -13448,7 +13448,7 @@
         <v>0.92849999666214</v>
       </c>
       <c r="G451" t="n">
-        <v>0.642482578754425</v>
+        <v>0.64248263835907</v>
       </c>
       <c r="H451" t="n">
         <v>119045</v>
@@ -13506,7 +13506,7 @@
         <v>0.934499979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>0.64663428068161</v>
+        <v>0.646634340286255</v>
       </c>
       <c r="H453" t="n">
         <v>146365</v>
@@ -13564,7 +13564,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G455" t="n">
-        <v>0.693341434001923</v>
+        <v>0.693341493606567</v>
       </c>
       <c r="H455" t="n">
         <v>3011766</v>
@@ -13593,7 +13593,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G456" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H456" t="n">
         <v>867305</v>
@@ -13622,7 +13622,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H457" t="n">
         <v>684112</v>
@@ -13709,7 +13709,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G460" t="n">
-        <v>0.708564579486847</v>
+        <v>0.708564519882202</v>
       </c>
       <c r="H460" t="n">
         <v>939858</v>
@@ -13825,7 +13825,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G464" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H464" t="n">
         <v>148439</v>
@@ -13912,7 +13912,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G467" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H467" t="n">
         <v>470474</v>
@@ -13970,7 +13970,7 @@
         <v>1.00399994850159</v>
       </c>
       <c r="G469" t="n">
-        <v>0.694725394248962</v>
+        <v>0.694725334644318</v>
       </c>
       <c r="H469" t="n">
         <v>146373</v>
@@ -13999,7 +13999,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G470" t="n">
-        <v>0.693341434001923</v>
+        <v>0.693341493606567</v>
       </c>
       <c r="H470" t="n">
         <v>106142</v>
@@ -14028,7 +14028,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>0.696109294891357</v>
+        <v>0.696109354496002</v>
       </c>
       <c r="H471" t="n">
         <v>102166</v>
@@ -14057,7 +14057,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G472" t="n">
-        <v>0.696109294891357</v>
+        <v>0.696109354496002</v>
       </c>
       <c r="H472" t="n">
         <v>233549</v>
@@ -14173,7 +14173,7 @@
         <v>0.970499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>0.6715447306633</v>
+        <v>0.671544849872589</v>
       </c>
       <c r="H476" t="n">
         <v>1137121</v>
@@ -14231,7 +14231,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H478" t="n">
         <v>300513</v>
@@ -14318,7 +14318,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G481" t="n">
-        <v>0.652169942855835</v>
+        <v>0.65217000246048</v>
       </c>
       <c r="H481" t="n">
         <v>621225</v>
@@ -14347,7 +14347,7 @@
         <v>0.935500025749207</v>
       </c>
       <c r="G482" t="n">
-        <v>0.647326350212097</v>
+        <v>0.647326290607452</v>
       </c>
       <c r="H482" t="n">
         <v>210242</v>
@@ -14405,7 +14405,7 @@
         <v>0.92849999666214</v>
       </c>
       <c r="G484" t="n">
-        <v>0.642482578754425</v>
+        <v>0.64248263835907</v>
       </c>
       <c r="H484" t="n">
         <v>191469</v>
@@ -14521,7 +14521,7 @@
         <v>0.966499984264374</v>
       </c>
       <c r="G488" t="n">
-        <v>0.66877692937851</v>
+        <v>0.668776988983154</v>
       </c>
       <c r="H488" t="n">
         <v>98374</v>
@@ -14550,7 +14550,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G489" t="n">
-        <v>0.67050689458847</v>
+        <v>0.670506834983826</v>
       </c>
       <c r="H489" t="n">
         <v>212997</v>
@@ -14579,7 +14579,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G490" t="n">
-        <v>0.666355073451996</v>
+        <v>0.666355133056641</v>
       </c>
       <c r="H490" t="n">
         <v>229851</v>
@@ -14608,7 +14608,7 @@
         <v>0.961000025272369</v>
       </c>
       <c r="G491" t="n">
-        <v>0.664971232414246</v>
+        <v>0.66497129201889</v>
       </c>
       <c r="H491" t="n">
         <v>248336</v>
@@ -14637,7 +14637,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>0.669122934341431</v>
+        <v>0.669122993946075</v>
       </c>
       <c r="H492" t="n">
         <v>72723</v>
@@ -14666,7 +14666,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G493" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H493" t="n">
         <v>99793</v>
@@ -14724,7 +14724,7 @@
         <v>0.971000015735626</v>
       </c>
       <c r="G495" t="n">
-        <v>0.671890735626221</v>
+        <v>0.671890795230865</v>
       </c>
       <c r="H495" t="n">
         <v>211644</v>
@@ -14840,7 +14840,7 @@
         <v>0.990499973297119</v>
       </c>
       <c r="G499" t="n">
-        <v>0.685383975505829</v>
+        <v>0.685383915901184</v>
       </c>
       <c r="H499" t="n">
         <v>219371</v>
@@ -14869,7 +14869,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G500" t="n">
-        <v>0.696109294891357</v>
+        <v>0.696109354496002</v>
       </c>
       <c r="H500" t="n">
         <v>290076</v>
@@ -14927,7 +14927,7 @@
         <v>0.995500028133392</v>
       </c>
       <c r="G502" t="n">
-        <v>0.688843786716461</v>
+        <v>0.688843846321106</v>
       </c>
       <c r="H502" t="n">
         <v>178398</v>
@@ -14956,7 +14956,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G503" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H503" t="n">
         <v>189129</v>
@@ -14985,7 +14985,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G504" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H504" t="n">
         <v>94375</v>
@@ -15014,7 +15014,7 @@
         <v>0.999499976634979</v>
       </c>
       <c r="G505" t="n">
-        <v>0.691611588001251</v>
+        <v>0.691611528396606</v>
       </c>
       <c r="H505" t="n">
         <v>151127</v>
@@ -15043,7 +15043,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H506" t="n">
         <v>140023</v>
@@ -15072,7 +15072,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G507" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H507" t="n">
         <v>93279</v>
@@ -15101,7 +15101,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G508" t="n">
-        <v>0.674658596515656</v>
+        <v>0.674658715724945</v>
       </c>
       <c r="H508" t="n">
         <v>240363</v>
@@ -15130,7 +15130,7 @@
         <v>0.940500020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>0.650786161422729</v>
+        <v>0.650786101818085</v>
       </c>
       <c r="H509" t="n">
         <v>972119</v>
@@ -15159,7 +15159,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H510" t="n">
         <v>173133</v>
@@ -15188,7 +15188,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G511" t="n">
-        <v>0.656667709350586</v>
+        <v>0.656667768955231</v>
       </c>
       <c r="H511" t="n">
         <v>126002</v>
@@ -15217,7 +15217,7 @@
         <v>0.959500014781952</v>
       </c>
       <c r="G512" t="n">
-        <v>0.663933336734772</v>
+        <v>0.663933277130127</v>
       </c>
       <c r="H512" t="n">
         <v>60967</v>
@@ -15362,7 +15362,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G517" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H517" t="n">
         <v>257171</v>
@@ -15391,7 +15391,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G518" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H518" t="n">
         <v>325321</v>
@@ -15536,7 +15536,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G523" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H523" t="n">
         <v>144135</v>
@@ -15594,7 +15594,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H525" t="n">
         <v>271747</v>
@@ -15652,7 +15652,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G527" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H527" t="n">
         <v>364335</v>
@@ -15681,7 +15681,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G528" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H528" t="n">
         <v>178501</v>
@@ -15710,7 +15710,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H529" t="n">
         <v>250609</v>
@@ -15797,7 +15797,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G532" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H532" t="n">
         <v>107041</v>
@@ -15826,7 +15826,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G533" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H533" t="n">
         <v>70016</v>
@@ -15855,7 +15855,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G534" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H534" t="n">
         <v>103090</v>
@@ -15884,7 +15884,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G535" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H535" t="n">
         <v>255484</v>
@@ -15942,7 +15942,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G537" t="n">
-        <v>0.673966646194458</v>
+        <v>0.673966705799103</v>
       </c>
       <c r="H537" t="n">
         <v>636928</v>
@@ -15971,7 +15971,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G538" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H538" t="n">
         <v>233300</v>
@@ -16000,7 +16000,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G539" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H539" t="n">
         <v>285889</v>
@@ -16116,7 +16116,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G543" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H543" t="n">
         <v>181643</v>
@@ -16145,7 +16145,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H544" t="n">
         <v>451706</v>
@@ -16203,7 +16203,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G546" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H546" t="n">
         <v>63666</v>
@@ -16261,7 +16261,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H548" t="n">
         <v>167644</v>
@@ -16406,7 +16406,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G553" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H553" t="n">
         <v>70654</v>
@@ -16435,7 +16435,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G554" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H554" t="n">
         <v>444239</v>
@@ -16464,7 +16464,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G555" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H555" t="n">
         <v>657891</v>
@@ -16551,7 +16551,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G558" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H558" t="n">
         <v>236616</v>
@@ -16580,7 +16580,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G559" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H559" t="n">
         <v>149177</v>
@@ -16638,7 +16638,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G561" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H561" t="n">
         <v>246628</v>
@@ -16696,7 +16696,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G563" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H563" t="n">
         <v>63387</v>
@@ -16870,7 +16870,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G569" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H569" t="n">
         <v>210457</v>
@@ -16899,7 +16899,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H570" t="n">
         <v>38212</v>
@@ -16928,7 +16928,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G571" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H571" t="n">
         <v>36832</v>
@@ -16957,7 +16957,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G572" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H572" t="n">
         <v>227865</v>
@@ -16986,7 +16986,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H573" t="n">
         <v>153618</v>
@@ -17015,7 +17015,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H574" t="n">
         <v>121341</v>
@@ -17044,7 +17044,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G575" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H575" t="n">
         <v>149054</v>
@@ -17073,7 +17073,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G576" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H576" t="n">
         <v>91964</v>
@@ -17102,7 +17102,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G577" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H577" t="n">
         <v>59474</v>
@@ -17131,7 +17131,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G578" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H578" t="n">
         <v>195846</v>
@@ -17189,7 +17189,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G580" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H580" t="n">
         <v>47052</v>
@@ -17276,7 +17276,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G583" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H583" t="n">
         <v>28035</v>
@@ -17305,7 +17305,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G584" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H584" t="n">
         <v>69874</v>
@@ -17334,7 +17334,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G585" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H585" t="n">
         <v>65412</v>
@@ -17363,7 +17363,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G586" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H586" t="n">
         <v>71072</v>
@@ -17392,7 +17392,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G587" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H587" t="n">
         <v>102968</v>
@@ -17508,7 +17508,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G591" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H591" t="n">
         <v>138385</v>
@@ -17537,7 +17537,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G592" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H592" t="n">
         <v>29068</v>
@@ -17566,7 +17566,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G593" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H593" t="n">
         <v>6330</v>
@@ -17595,7 +17595,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G594" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H594" t="n">
         <v>13853</v>
@@ -17624,7 +17624,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G595" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H595" t="n">
         <v>71366</v>
@@ -17798,7 +17798,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G601" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H601" t="n">
         <v>173212</v>
@@ -17827,7 +17827,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G602" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H602" t="n">
         <v>254564</v>
@@ -17914,7 +17914,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G605" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H605" t="n">
         <v>317195</v>
@@ -17943,7 +17943,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G606" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H606" t="n">
         <v>246778</v>
@@ -18001,7 +18001,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G608" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H608" t="n">
         <v>267381</v>
@@ -18059,7 +18059,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G610" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H610" t="n">
         <v>63700</v>
@@ -18088,7 +18088,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G611" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H611" t="n">
         <v>60260</v>
@@ -18117,7 +18117,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H612" t="n">
         <v>182363</v>
@@ -18146,7 +18146,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G613" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H613" t="n">
         <v>294664</v>
@@ -18262,7 +18262,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G617" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H617" t="n">
         <v>118710</v>
@@ -18291,7 +18291,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H618" t="n">
         <v>504140</v>
@@ -18320,7 +18320,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H619" t="n">
         <v>135616</v>
@@ -18639,7 +18639,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G630" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H630" t="n">
         <v>140311</v>
@@ -18668,7 +18668,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G631" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H631" t="n">
         <v>93832</v>
@@ -18784,7 +18784,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G635" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H635" t="n">
         <v>55341</v>
@@ -18871,7 +18871,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G638" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H638" t="n">
         <v>64520</v>
@@ -18958,7 +18958,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G641" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H641" t="n">
         <v>101434</v>
@@ -19045,7 +19045,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G644" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H644" t="n">
         <v>147968</v>
@@ -19074,7 +19074,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G645" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H645" t="n">
         <v>256363</v>
@@ -19103,7 +19103,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G646" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H646" t="n">
         <v>28006</v>
@@ -19132,7 +19132,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G647" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H647" t="n">
         <v>49621</v>
@@ -19161,7 +19161,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G648" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H648" t="n">
         <v>40470</v>
@@ -19190,7 +19190,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G649" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H649" t="n">
         <v>42833</v>
@@ -19248,7 +19248,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G651" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H651" t="n">
         <v>142778</v>
@@ -19277,7 +19277,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G652" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H652" t="n">
         <v>90336</v>
@@ -19306,7 +19306,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G653" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H653" t="n">
         <v>46227</v>
@@ -19335,7 +19335,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G654" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H654" t="n">
         <v>52109</v>
@@ -19364,7 +19364,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G655" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H655" t="n">
         <v>62277</v>
@@ -19509,7 +19509,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G660" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H660" t="n">
         <v>301287</v>
@@ -19538,7 +19538,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G661" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H661" t="n">
         <v>119386</v>
@@ -19567,7 +19567,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G662" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H662" t="n">
         <v>138753</v>
@@ -19596,7 +19596,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G663" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H663" t="n">
         <v>140254</v>
@@ -19625,7 +19625,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G664" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H664" t="n">
         <v>4092</v>
@@ -19654,7 +19654,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G665" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H665" t="n">
         <v>69274</v>
@@ -19683,7 +19683,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G666" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H666" t="n">
         <v>93861</v>
@@ -19712,7 +19712,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H667" t="n">
         <v>167650</v>
@@ -19799,7 +19799,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G670" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H670" t="n">
         <v>163980</v>
@@ -19857,7 +19857,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G672" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H672" t="n">
         <v>96842</v>
@@ -19886,7 +19886,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G673" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H673" t="n">
         <v>167043</v>
@@ -19915,7 +19915,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H674" t="n">
         <v>22563</v>
@@ -19944,7 +19944,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G675" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H675" t="n">
         <v>52830</v>
@@ -19973,7 +19973,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H676" t="n">
         <v>76484</v>
@@ -20002,7 +20002,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H677" t="n">
         <v>30551</v>
@@ -20031,7 +20031,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G678" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H678" t="n">
         <v>99343</v>
@@ -20060,7 +20060,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G679" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H679" t="n">
         <v>99007</v>
@@ -20118,7 +20118,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G681" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H681" t="n">
         <v>57141</v>
@@ -20205,7 +20205,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H684" t="n">
         <v>67179</v>
@@ -20234,7 +20234,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G685" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H685" t="n">
         <v>172394</v>
@@ -20437,7 +20437,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G692" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H692" t="n">
         <v>112543</v>
@@ -20466,7 +20466,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G693" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H693" t="n">
         <v>51317</v>
@@ -20495,7 +20495,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H694" t="n">
         <v>13680</v>
@@ -20524,7 +20524,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G695" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H695" t="n">
         <v>25114</v>
@@ -20553,7 +20553,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G696" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H696" t="n">
         <v>82434</v>
@@ -20611,7 +20611,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G698" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H698" t="n">
         <v>67665</v>
@@ -20640,7 +20640,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G699" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H699" t="n">
         <v>129526</v>
@@ -20669,7 +20669,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G700" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H700" t="n">
         <v>8812</v>
@@ -20756,7 +20756,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G703" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H703" t="n">
         <v>121260</v>
@@ -20843,7 +20843,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H706" t="n">
         <v>24697</v>
@@ -20872,7 +20872,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G707" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H707" t="n">
         <v>82347</v>
@@ -20930,7 +20930,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G709" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H709" t="n">
         <v>101043</v>
@@ -21017,7 +21017,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H712" t="n">
         <v>83637</v>
@@ -21046,7 +21046,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G713" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H713" t="n">
         <v>61904</v>
@@ -21133,7 +21133,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G716" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H716" t="n">
         <v>131470</v>
@@ -21162,7 +21162,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G717" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H717" t="n">
         <v>89967</v>
@@ -21191,7 +21191,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>0.621377885341644</v>
+        <v>0.621377944946289</v>
       </c>
       <c r="H718" t="n">
         <v>90743</v>
@@ -21249,7 +21249,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G720" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H720" t="n">
         <v>49505</v>
@@ -21278,7 +21278,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H721" t="n">
         <v>468123</v>
@@ -21307,7 +21307,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G722" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H722" t="n">
         <v>239951</v>
@@ -21336,7 +21336,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H723" t="n">
         <v>182993</v>
@@ -21365,7 +21365,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H724" t="n">
         <v>222642</v>
@@ -21452,7 +21452,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H727" t="n">
         <v>57669</v>
@@ -21481,7 +21481,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G728" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H728" t="n">
         <v>78523</v>
@@ -21510,7 +21510,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H729" t="n">
         <v>248654</v>
@@ -21626,7 +21626,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G733" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H733" t="n">
         <v>63953</v>
@@ -21771,7 +21771,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G738" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H738" t="n">
         <v>135534</v>
@@ -21829,7 +21829,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G740" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H740" t="n">
         <v>48907</v>
@@ -21887,7 +21887,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G742" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H742" t="n">
         <v>82682</v>
@@ -22032,7 +22032,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G747" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663242340088</v>
       </c>
       <c r="H747" t="n">
         <v>246168</v>
@@ -22177,7 +22177,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H752" t="n">
         <v>388590</v>
@@ -22235,7 +22235,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G754" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H754" t="n">
         <v>247058</v>
@@ -22264,7 +22264,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G755" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H755" t="n">
         <v>31595</v>
@@ -22322,7 +22322,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G757" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H757" t="n">
         <v>161007</v>
@@ -22351,7 +22351,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G758" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H758" t="n">
         <v>103377</v>
@@ -22380,7 +22380,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G759" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H759" t="n">
         <v>92669</v>
@@ -22409,7 +22409,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G760" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H760" t="n">
         <v>174775</v>
@@ -22467,7 +22467,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G762" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H762" t="n">
         <v>213022</v>
@@ -22496,7 +22496,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G763" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H763" t="n">
         <v>39624</v>
@@ -22525,7 +22525,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G764" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H764" t="n">
         <v>146710</v>
@@ -22554,7 +22554,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G765" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H765" t="n">
         <v>103087</v>
@@ -22583,7 +22583,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G766" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H766" t="n">
         <v>109701</v>
@@ -22612,7 +22612,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G767" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H767" t="n">
         <v>116328</v>
@@ -22641,7 +22641,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G768" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H768" t="n">
         <v>9686</v>
@@ -22844,7 +22844,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H775" t="n">
         <v>359900</v>
@@ -22873,7 +22873,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H776" t="n">
         <v>210137</v>
@@ -22902,7 +22902,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G777" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H777" t="n">
         <v>174998</v>
@@ -22931,7 +22931,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G778" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H778" t="n">
         <v>275985</v>
@@ -22989,7 +22989,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H780" t="n">
         <v>526304</v>
@@ -23018,7 +23018,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G781" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H781" t="n">
         <v>178402</v>
@@ -23047,7 +23047,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G782" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H782" t="n">
         <v>290447</v>
@@ -23076,7 +23076,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G783" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H783" t="n">
         <v>79965</v>
@@ -23105,7 +23105,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H784" t="n">
         <v>376786</v>
@@ -23134,7 +23134,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G785" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H785" t="n">
         <v>180557</v>
@@ -23163,7 +23163,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G786" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H786" t="n">
         <v>117707</v>
@@ -23250,7 +23250,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G789" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H789" t="n">
         <v>229318</v>
@@ -23279,7 +23279,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G790" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H790" t="n">
         <v>290276</v>
@@ -23308,7 +23308,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G791" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H791" t="n">
         <v>146801</v>
@@ -23337,7 +23337,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G792" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H792" t="n">
         <v>619773</v>
@@ -23395,7 +23395,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G794" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H794" t="n">
         <v>353515</v>
@@ -23424,7 +23424,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G795" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H795" t="n">
         <v>349231</v>
@@ -23482,7 +23482,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H797" t="n">
         <v>3149209</v>
@@ -23511,7 +23511,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G798" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H798" t="n">
         <v>2153597</v>
@@ -23569,7 +23569,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G800" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H800" t="n">
         <v>325657</v>
@@ -23656,7 +23656,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G803" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H803" t="n">
         <v>211249</v>
@@ -23743,7 +23743,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G806" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H806" t="n">
         <v>320023</v>
@@ -23801,7 +23801,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G808" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H808" t="n">
         <v>226093</v>
@@ -23830,7 +23830,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G809" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H809" t="n">
         <v>208609</v>
@@ -23859,7 +23859,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G810" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H810" t="n">
         <v>525234</v>
@@ -23917,7 +23917,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G812" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H812" t="n">
         <v>436802</v>
@@ -23946,7 +23946,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G813" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H813" t="n">
         <v>175222</v>
@@ -24004,7 +24004,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G815" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H815" t="n">
         <v>305887</v>
@@ -24033,7 +24033,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G816" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H816" t="n">
         <v>673843</v>
@@ -24062,7 +24062,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G817" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H817" t="n">
         <v>80902</v>
@@ -24091,7 +24091,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G818" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H818" t="n">
         <v>277155</v>
@@ -24120,7 +24120,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G819" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H819" t="n">
         <v>100932</v>
@@ -24149,7 +24149,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H820" t="n">
         <v>65351</v>
@@ -24178,7 +24178,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G821" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H821" t="n">
         <v>470108</v>
@@ -24207,7 +24207,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G822" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H822" t="n">
         <v>219572</v>
@@ -24236,7 +24236,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G823" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H823" t="n">
         <v>104698</v>
@@ -24265,7 +24265,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H824" t="n">
         <v>77471</v>
@@ -24294,7 +24294,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G825" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H825" t="n">
         <v>85392</v>
@@ -24323,7 +24323,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G826" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H826" t="n">
         <v>122721</v>
@@ -24352,7 +24352,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G827" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H827" t="n">
         <v>136318</v>
@@ -24381,7 +24381,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G828" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H828" t="n">
         <v>190889</v>
@@ -24410,7 +24410,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G829" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H829" t="n">
         <v>193723</v>
@@ -24497,7 +24497,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G832" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H832" t="n">
         <v>266065</v>
@@ -24555,7 +24555,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G834" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H834" t="n">
         <v>204614</v>
@@ -24584,7 +24584,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G835" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H835" t="n">
         <v>61953</v>
@@ -24613,7 +24613,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G836" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H836" t="n">
         <v>385944</v>
@@ -24642,7 +24642,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G837" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H837" t="n">
         <v>311717</v>
@@ -24671,7 +24671,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G838" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H838" t="n">
         <v>229066</v>
@@ -24700,7 +24700,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G839" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H839" t="n">
         <v>261587</v>
@@ -24729,7 +24729,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G840" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H840" t="n">
         <v>86068</v>
@@ -24758,7 +24758,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G841" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H841" t="n">
         <v>153205</v>
@@ -24787,7 +24787,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G842" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H842" t="n">
         <v>105509</v>
@@ -24816,7 +24816,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G843" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H843" t="n">
         <v>123649</v>
@@ -24845,7 +24845,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G844" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H844" t="n">
         <v>80388</v>
@@ -24874,7 +24874,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G845" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H845" t="n">
         <v>128303</v>
@@ -24903,7 +24903,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G846" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H846" t="n">
         <v>52402</v>
@@ -24932,7 +24932,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G847" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H847" t="n">
         <v>61956</v>
@@ -24961,7 +24961,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H848" t="n">
         <v>73636</v>
@@ -24990,7 +24990,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G849" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H849" t="n">
         <v>197550</v>
@@ -25019,7 +25019,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G850" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H850" t="n">
         <v>114935</v>
@@ -25077,7 +25077,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G852" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H852" t="n">
         <v>244060</v>
@@ -25106,7 +25106,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G853" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H853" t="n">
         <v>275627</v>
@@ -25135,7 +25135,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G854" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H854" t="n">
         <v>124964</v>
@@ -25164,7 +25164,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G855" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H855" t="n">
         <v>372391</v>
@@ -25193,7 +25193,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G856" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H856" t="n">
         <v>90403</v>
@@ -25309,7 +25309,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G860" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H860" t="n">
         <v>409423</v>
@@ -25367,7 +25367,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G862" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H862" t="n">
         <v>54163</v>
@@ -25425,7 +25425,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G864" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H864" t="n">
         <v>126310</v>
@@ -25454,7 +25454,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G865" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H865" t="n">
         <v>29199</v>
@@ -25570,7 +25570,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G869" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H869" t="n">
         <v>107676</v>
@@ -25657,7 +25657,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G872" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H872" t="n">
         <v>105169</v>
@@ -25686,7 +25686,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G873" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H873" t="n">
         <v>78637</v>
@@ -25715,7 +25715,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H874" t="n">
         <v>84308</v>
@@ -25744,7 +25744,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G875" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H875" t="n">
         <v>90938</v>
@@ -25773,7 +25773,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G876" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H876" t="n">
         <v>81601</v>
@@ -25802,7 +25802,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G877" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H877" t="n">
         <v>104497</v>
@@ -26005,7 +26005,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H884" t="n">
         <v>474251</v>
@@ -26063,7 +26063,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G886" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H886" t="n">
         <v>216811</v>
@@ -26121,7 +26121,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G888" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H888" t="n">
         <v>173883</v>
@@ -26150,7 +26150,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G889" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H889" t="n">
         <v>132291</v>
@@ -26179,7 +26179,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G890" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H890" t="n">
         <v>159006</v>
@@ -26295,7 +26295,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G894" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H894" t="n">
         <v>140826</v>
@@ -26324,7 +26324,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G895" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H895" t="n">
         <v>151252</v>
@@ -26382,7 +26382,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G897" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H897" t="n">
         <v>217289</v>
@@ -26411,7 +26411,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G898" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H898" t="n">
         <v>72882</v>
@@ -26469,7 +26469,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G900" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H900" t="n">
         <v>60612</v>
@@ -26498,7 +26498,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G901" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H901" t="n">
         <v>25048</v>
@@ -26527,7 +26527,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G902" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H902" t="n">
         <v>101811</v>
@@ -26556,7 +26556,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G903" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H903" t="n">
         <v>167282</v>
@@ -26643,7 +26643,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H906" t="n">
         <v>107319</v>
@@ -26672,7 +26672,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H907" t="n">
         <v>347972</v>
@@ -26701,7 +26701,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H908" t="n">
         <v>40674</v>
@@ -26730,7 +26730,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G909" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H909" t="n">
         <v>92055</v>
@@ -26759,7 +26759,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G910" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H910" t="n">
         <v>65644</v>
@@ -26788,7 +26788,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G911" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H911" t="n">
         <v>55541</v>
@@ -26817,7 +26817,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G912" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H912" t="n">
         <v>191208</v>
@@ -26875,7 +26875,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G914" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H914" t="n">
         <v>53182</v>
@@ -26904,7 +26904,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G915" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H915" t="n">
         <v>37385</v>
@@ -26933,7 +26933,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G916" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H916" t="n">
         <v>86268</v>
@@ -27078,7 +27078,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G921" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H921" t="n">
         <v>21650</v>
@@ -27107,7 +27107,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G922" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H922" t="n">
         <v>14376</v>
@@ -27136,7 +27136,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G923" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H923" t="n">
         <v>55248</v>
@@ -27223,7 +27223,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G926" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H926" t="n">
         <v>632493</v>
@@ -27803,7 +27803,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G946" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H946" t="n">
         <v>87148</v>
@@ -27861,7 +27861,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G948" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H948" t="n">
         <v>63867</v>
@@ -27890,7 +27890,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G949" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H949" t="n">
         <v>41116</v>
@@ -27977,7 +27977,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G952" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H952" t="n">
         <v>133528</v>
@@ -28006,7 +28006,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G953" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H953" t="n">
         <v>44179</v>
@@ -28035,7 +28035,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G954" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H954" t="n">
         <v>94934</v>
@@ -28093,7 +28093,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G956" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H956" t="n">
         <v>140861</v>
@@ -28122,7 +28122,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G957" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H957" t="n">
         <v>80784</v>
@@ -28151,7 +28151,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G958" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H958" t="n">
         <v>91567</v>
@@ -28180,7 +28180,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G959" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H959" t="n">
         <v>94807</v>
@@ -28209,7 +28209,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G960" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H960" t="n">
         <v>66194</v>
@@ -28238,7 +28238,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G961" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H961" t="n">
         <v>37841</v>
@@ -28296,7 +28296,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G963" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H963" t="n">
         <v>49902</v>
@@ -28325,7 +28325,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G964" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H964" t="n">
         <v>59488</v>
@@ -28354,7 +28354,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G965" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H965" t="n">
         <v>29568</v>
@@ -28412,7 +28412,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G967" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H967" t="n">
         <v>37985</v>
@@ -28441,7 +28441,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G968" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H968" t="n">
         <v>98290</v>
@@ -28470,7 +28470,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G969" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H969" t="n">
         <v>40709</v>
@@ -28499,7 +28499,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G970" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H970" t="n">
         <v>21334</v>
@@ -28528,7 +28528,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G971" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H971" t="n">
         <v>37262</v>
@@ -28586,7 +28586,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G973" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H973" t="n">
         <v>105764</v>
@@ -28673,7 +28673,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G976" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H976" t="n">
         <v>123267</v>
@@ -28702,7 +28702,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G977" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H977" t="n">
         <v>78477</v>
@@ -28760,7 +28760,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G979" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H979" t="n">
         <v>61186</v>
@@ -28876,7 +28876,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G983" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H983" t="n">
         <v>217834</v>
@@ -28905,7 +28905,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H984" t="n">
         <v>62066</v>
@@ -28934,7 +28934,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H985" t="n">
         <v>78120</v>
@@ -28963,7 +28963,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G986" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H986" t="n">
         <v>66452</v>
@@ -28992,7 +28992,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G987" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H987" t="n">
         <v>95757</v>
@@ -29021,7 +29021,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G988" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H988" t="n">
         <v>102998</v>
@@ -29050,7 +29050,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G989" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H989" t="n">
         <v>75430</v>
@@ -29079,7 +29079,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G990" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H990" t="n">
         <v>26658</v>
@@ -29108,7 +29108,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G991" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H991" t="n">
         <v>7575</v>
@@ -29137,7 +29137,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G992" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H992" t="n">
         <v>96747</v>
@@ -29166,7 +29166,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G993" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H993" t="n">
         <v>191111</v>
@@ -29195,7 +29195,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H994" t="n">
         <v>78705</v>
@@ -29224,7 +29224,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H995" t="n">
         <v>105388</v>
@@ -29253,7 +29253,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G996" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H996" t="n">
         <v>130509</v>
@@ -29282,7 +29282,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H997" t="n">
         <v>110766</v>
@@ -29311,7 +29311,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G998" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H998" t="n">
         <v>114518</v>
@@ -29456,7 +29456,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1003" t="n">
         <v>235612</v>
@@ -29485,7 +29485,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1004" t="n">
         <v>192053</v>
@@ -29514,7 +29514,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1005" t="n">
         <v>342278</v>
@@ -29543,7 +29543,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1006" t="n">
         <v>322567</v>
@@ -29630,7 +29630,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1009" t="n">
         <v>174124</v>
@@ -29659,7 +29659,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1010" t="n">
         <v>113260</v>
@@ -29688,7 +29688,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1011" t="n">
         <v>387485</v>
@@ -29717,7 +29717,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1012" t="n">
         <v>249244</v>
@@ -29746,7 +29746,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1013" t="n">
         <v>286241</v>
@@ -29775,7 +29775,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1014" t="n">
         <v>318580</v>
@@ -29804,7 +29804,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1015" t="n">
         <v>60551</v>
@@ -29833,7 +29833,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1016" t="n">
         <v>46451</v>
@@ -29862,7 +29862,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1017" t="n">
         <v>15354</v>
@@ -29891,7 +29891,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1018" t="n">
         <v>35801</v>
@@ -29920,7 +29920,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1019" t="n">
         <v>38573</v>
@@ -29949,7 +29949,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1020" t="n">
         <v>109677</v>
@@ -29978,7 +29978,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1021" t="n">
         <v>156016</v>
@@ -30007,7 +30007,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1022" t="n">
         <v>226546</v>
@@ -30036,7 +30036,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1023" t="n">
         <v>25132</v>
@@ -30065,7 +30065,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1024" t="n">
         <v>200686</v>
@@ -30152,7 +30152,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H1027" t="n">
         <v>347568</v>
@@ -30181,7 +30181,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1028" t="n">
         <v>164587</v>
@@ -30210,7 +30210,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1029" t="n">
         <v>145814</v>
@@ -30297,7 +30297,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H1032" t="n">
         <v>156870</v>
@@ -30645,7 +30645,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1044" t="n">
         <v>234674</v>
@@ -30674,7 +30674,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1045" t="n">
         <v>171115</v>
@@ -30703,7 +30703,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1046" t="n">
         <v>76577</v>
@@ -30761,7 +30761,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1048" t="n">
         <v>1713322</v>
@@ -30819,7 +30819,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799210965633392</v>
       </c>
       <c r="H1050" t="n">
         <v>1197758</v>
@@ -30848,7 +30848,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1051" t="n">
         <v>273699</v>
@@ -30906,7 +30906,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1053" t="n">
         <v>823602</v>
@@ -30993,7 +30993,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1056" t="n">
         <v>602371</v>
@@ -31080,7 +31080,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1059" t="n">
         <v>163770</v>
@@ -31196,7 +31196,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.668431043624878</v>
+        <v>0.668430984020233</v>
       </c>
       <c r="H1063" t="n">
         <v>775877</v>
@@ -31254,7 +31254,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H1065" t="n">
         <v>357849</v>
@@ -31283,7 +31283,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.57570868730545</v>
+        <v>0.575708627700806</v>
       </c>
       <c r="H1066" t="n">
         <v>506587</v>
@@ -31370,7 +31370,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1069" t="n">
         <v>131300</v>
@@ -31428,7 +31428,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1071" t="n">
         <v>34398</v>
@@ -31573,7 +31573,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1076" t="n">
         <v>34801</v>
@@ -31602,7 +31602,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.631065368652344</v>
+        <v>0.631065309047699</v>
       </c>
       <c r="H1077" t="n">
         <v>56265</v>
@@ -31747,7 +31747,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1082" t="n">
         <v>86399</v>
@@ -31776,7 +31776,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1083" t="n">
         <v>131641</v>
@@ -31805,7 +31805,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1084" t="n">
         <v>166709</v>
@@ -31834,7 +31834,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H1085" t="n">
         <v>23669</v>
@@ -31921,7 +31921,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1088" t="n">
         <v>69667</v>
@@ -31950,7 +31950,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1089" t="n">
         <v>108498</v>
@@ -32008,7 +32008,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1091" t="n">
         <v>32955</v>
@@ -32037,7 +32037,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.618610024452209</v>
+        <v>0.618610084056854</v>
       </c>
       <c r="H1092" t="n">
         <v>82022</v>
@@ -32095,7 +32095,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1094" t="n">
         <v>39008</v>
@@ -32124,7 +32124,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1095" t="n">
         <v>172934</v>
@@ -32153,7 +32153,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1096" t="n">
         <v>78354</v>
@@ -32182,7 +32182,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1097" t="n">
         <v>284734</v>
@@ -32211,7 +32211,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.615842163562775</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1098" t="n">
         <v>28827</v>
@@ -32240,7 +32240,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H1099" t="n">
         <v>28036</v>
@@ -32269,7 +32269,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H1100" t="n">
         <v>37867</v>
@@ -32298,7 +32298,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.615842163562775</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1101" t="n">
         <v>10506</v>
@@ -32327,7 +32327,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1102" t="n">
         <v>14360</v>
@@ -32356,7 +32356,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.595083594322205</v>
+        <v>0.59508353471756</v>
       </c>
       <c r="H1103" t="n">
         <v>27031</v>
@@ -32385,7 +32385,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1104" t="n">
         <v>17833</v>
@@ -32414,7 +32414,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1105" t="n">
         <v>58667</v>
@@ -32443,7 +32443,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.615842163562775</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1106" t="n">
         <v>72994</v>
@@ -32530,7 +32530,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1109" t="n">
         <v>143966</v>
@@ -32559,7 +32559,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1110" t="n">
         <v>74390</v>
@@ -32588,7 +32588,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1111" t="n">
         <v>75700</v>
@@ -32617,7 +32617,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.59231573343277</v>
+        <v>0.592315673828125</v>
       </c>
       <c r="H1112" t="n">
         <v>326668</v>
@@ -32675,7 +32675,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.577092587947845</v>
+        <v>0.57709264755249</v>
       </c>
       <c r="H1114" t="n">
         <v>63168</v>
@@ -32704,7 +32704,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.58401221036911</v>
+        <v>0.584012150764465</v>
       </c>
       <c r="H1115" t="n">
         <v>77035</v>
@@ -32733,7 +32733,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.59231573343277</v>
+        <v>0.592315673828125</v>
       </c>
       <c r="H1116" t="n">
         <v>61326</v>
@@ -32849,7 +32849,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.60200309753418</v>
+        <v>0.602003037929535</v>
       </c>
       <c r="H1120" t="n">
         <v>76838</v>
@@ -32878,7 +32878,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.60200309753418</v>
+        <v>0.602003037929535</v>
       </c>
       <c r="H1121" t="n">
         <v>115137</v>
@@ -32936,7 +32936,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.588163912296295</v>
+        <v>0.58816397190094</v>
       </c>
       <c r="H1123" t="n">
         <v>186789</v>
@@ -32994,7 +32994,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.613074362277985</v>
+        <v>0.613074421882629</v>
       </c>
       <c r="H1125" t="n">
         <v>101717</v>
@@ -33023,7 +33023,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.611690521240234</v>
+        <v>0.61169046163559</v>
       </c>
       <c r="H1126" t="n">
         <v>122265</v>
@@ -33168,7 +33168,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1131" t="n">
         <v>143550</v>
@@ -33255,7 +33255,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1134" t="n">
         <v>95950</v>
@@ -33342,7 +33342,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1137" t="n">
         <v>73997</v>
@@ -33458,7 +33458,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.631065368652344</v>
+        <v>0.631065309047699</v>
       </c>
       <c r="H1141" t="n">
         <v>51457</v>
@@ -33487,7 +33487,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1142" t="n">
         <v>15327</v>
@@ -33632,7 +33632,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1147" t="n">
         <v>34283</v>
@@ -33777,7 +33777,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1152" t="n">
         <v>107933</v>
@@ -33835,7 +33835,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1154" t="n">
         <v>25608</v>
@@ -33864,7 +33864,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.661511421203613</v>
+        <v>0.661511361598969</v>
       </c>
       <c r="H1155" t="n">
         <v>53197</v>
@@ -33922,7 +33922,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1157" t="n">
         <v>79152</v>
@@ -33951,7 +33951,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H1158" t="n">
         <v>35471</v>
@@ -33980,7 +33980,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H1159" t="n">
         <v>5309</v>
@@ -34038,7 +34038,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1161" t="n">
         <v>26496</v>
@@ -34096,7 +34096,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H1163" t="n">
         <v>69255</v>
@@ -34125,7 +34125,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H1164" t="n">
         <v>26925</v>
@@ -34154,7 +34154,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1165" t="n">
         <v>71238</v>
@@ -34270,7 +34270,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1169" t="n">
         <v>11833</v>
@@ -34299,7 +34299,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H1170" t="n">
         <v>13657</v>
@@ -34328,7 +34328,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H1171" t="n">
         <v>8054</v>
@@ -34386,7 +34386,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1173" t="n">
         <v>3808</v>
@@ -34618,7 +34618,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H1181" t="n">
         <v>3104</v>
@@ -34647,7 +34647,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1182" t="n">
         <v>33962</v>
@@ -34734,7 +34734,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1185" t="n">
         <v>47037</v>
@@ -34763,7 +34763,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.631065368652344</v>
+        <v>0.631065309047699</v>
       </c>
       <c r="H1186" t="n">
         <v>20018</v>
@@ -34850,7 +34850,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1189" t="n">
         <v>120000</v>
@@ -34879,7 +34879,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1190" t="n">
         <v>19673</v>
@@ -35053,7 +35053,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1196" t="n">
         <v>159851</v>
@@ -35140,7 +35140,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.631065368652344</v>
+        <v>0.631065309047699</v>
       </c>
       <c r="H1199" t="n">
         <v>9681</v>
@@ -35169,7 +35169,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1200" t="n">
         <v>72568</v>
@@ -35256,7 +35256,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H1203" t="n">
         <v>43390</v>
@@ -35285,7 +35285,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1204" t="n">
         <v>113573</v>
@@ -35314,7 +35314,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.640752732753754</v>
+        <v>0.640752673149109</v>
       </c>
       <c r="H1205" t="n">
         <v>34960</v>
@@ -35459,7 +35459,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1210" t="n">
         <v>19679</v>
@@ -35488,7 +35488,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H1211" t="n">
         <v>14578</v>
@@ -35633,7 +35633,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1216" t="n">
         <v>19052</v>
@@ -35662,7 +35662,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1217" t="n">
         <v>115503</v>
@@ -35691,7 +35691,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1218" t="n">
         <v>160496</v>
@@ -35720,7 +35720,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H1219" t="n">
         <v>211755</v>
@@ -35749,7 +35749,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.629681348800659</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1220" t="n">
         <v>58098</v>
@@ -35778,7 +35778,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.633833169937134</v>
+        <v>0.633833110332489</v>
       </c>
       <c r="H1221" t="n">
         <v>28000</v>
@@ -35981,7 +35981,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H1228" t="n">
         <v>23100</v>
@@ -36010,7 +36010,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.625529646873474</v>
+        <v>0.625529587268829</v>
       </c>
       <c r="H1229" t="n">
         <v>41212</v>
@@ -36068,7 +36068,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1231" t="n">
         <v>14537</v>
@@ -36300,7 +36300,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.636601030826569</v>
+        <v>0.636600971221924</v>
       </c>
       <c r="H1239" t="n">
         <v>43202</v>
@@ -36387,7 +36387,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1242" t="n">
         <v>155539</v>
@@ -36416,7 +36416,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.660127460956573</v>
+        <v>0.660127520561218</v>
       </c>
       <c r="H1243" t="n">
         <v>12321</v>
@@ -36474,7 +36474,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1245" t="n">
         <v>74860</v>
@@ -36561,7 +36561,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H1248" t="n">
         <v>207160</v>
@@ -36648,7 +36648,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H1251" t="n">
         <v>36590</v>
@@ -36677,7 +36677,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1252" t="n">
         <v>75238</v>
@@ -36735,7 +36735,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1254" t="n">
         <v>248043</v>
@@ -36764,7 +36764,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.687805891036987</v>
+        <v>0.687805771827698</v>
       </c>
       <c r="H1255" t="n">
         <v>73905</v>
@@ -36793,7 +36793,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H1256" t="n">
         <v>27967</v>
@@ -36851,7 +36851,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H1258" t="n">
         <v>93042</v>
@@ -36880,7 +36880,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1259" t="n">
         <v>104468</v>
@@ -36909,7 +36909,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1260" t="n">
         <v>95974</v>
@@ -36938,7 +36938,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1261" t="n">
         <v>40481</v>
@@ -37054,7 +37054,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1265" t="n">
         <v>177918</v>
@@ -37083,7 +37083,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.689189732074738</v>
+        <v>0.689189672470093</v>
       </c>
       <c r="H1266" t="n">
         <v>60348</v>
@@ -37112,7 +37112,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H1267" t="n">
         <v>336052</v>
@@ -37141,7 +37141,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.70233690738678</v>
+        <v>0.702336966991425</v>
       </c>
       <c r="H1268" t="n">
         <v>44400</v>
@@ -37228,7 +37228,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1271" t="n">
         <v>213141</v>
@@ -37257,7 +37257,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.7092564702034</v>
+        <v>0.709256529808044</v>
       </c>
       <c r="H1272" t="n">
         <v>667086</v>
@@ -37286,7 +37286,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.716176092624664</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1273" t="n">
         <v>175476</v>
@@ -37373,7 +37373,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1276" t="n">
         <v>52660</v>
@@ -37489,7 +37489,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.736934840679169</v>
+        <v>0.736934900283813</v>
       </c>
       <c r="H1280" t="n">
         <v>62148</v>
@@ -37518,7 +37518,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1281" t="n">
         <v>28087</v>
@@ -37547,7 +37547,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1282" t="n">
         <v>43403</v>
@@ -37576,7 +37576,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1283" t="n">
         <v>36252</v>
@@ -37605,7 +37605,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.736934840679169</v>
+        <v>0.736934900283813</v>
       </c>
       <c r="H1284" t="n">
         <v>76794</v>
@@ -37634,7 +37634,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1285" t="n">
         <v>129493</v>
@@ -37692,7 +37692,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1287" t="n">
         <v>170197</v>
@@ -37721,7 +37721,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1288" t="n">
         <v>84581</v>
@@ -37750,7 +37750,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1289" t="n">
         <v>98666</v>
@@ -37837,7 +37837,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1292" t="n">
         <v>224416</v>
@@ -37866,7 +37866,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1293" t="n">
         <v>140397</v>
@@ -37895,7 +37895,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1294" t="n">
         <v>63340</v>
@@ -37924,7 +37924,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1295" t="n">
         <v>133140</v>
@@ -37953,7 +37953,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1296" t="n">
         <v>219334</v>
@@ -38011,7 +38011,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1298" t="n">
         <v>269434</v>
@@ -38040,7 +38040,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1299" t="n">
         <v>347129</v>
@@ -38069,7 +38069,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1300" t="n">
         <v>100350</v>
@@ -38185,7 +38185,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.78883171081543</v>
+        <v>0.78883159160614</v>
       </c>
       <c r="H1304" t="n">
         <v>2016020</v>
@@ -38214,7 +38214,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.78883171081543</v>
+        <v>0.78883159160614</v>
       </c>
       <c r="H1305" t="n">
         <v>622316</v>
@@ -38243,7 +38243,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.774992406368256</v>
+        <v>0.7749924659729</v>
       </c>
       <c r="H1306" t="n">
         <v>168242</v>
@@ -38533,7 +38533,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1316" t="n">
         <v>137499</v>
@@ -38649,7 +38649,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1320" t="n">
         <v>44291</v>
@@ -38678,7 +38678,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1321" t="n">
         <v>113521</v>
@@ -38707,7 +38707,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1322" t="n">
         <v>79157</v>
@@ -38765,7 +38765,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733474910259247</v>
       </c>
       <c r="H1324" t="n">
         <v>88274</v>
@@ -38881,7 +38881,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1328" t="n">
         <v>51128</v>
@@ -38910,7 +38910,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1329" t="n">
         <v>70641</v>
@@ -38968,7 +38968,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1331" t="n">
         <v>97824</v>
@@ -39026,7 +39026,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1333" t="n">
         <v>66358</v>
@@ -39055,7 +39055,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773966312408</v>
       </c>
       <c r="H1334" t="n">
         <v>300870</v>
@@ -39084,7 +39084,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1335" t="n">
         <v>106831</v>
@@ -39113,7 +39113,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1336" t="n">
         <v>533202</v>
@@ -39142,7 +39142,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1337" t="n">
         <v>116215</v>
@@ -39229,7 +39229,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.768072903156281</v>
+        <v>0.768072843551636</v>
       </c>
       <c r="H1340" t="n">
         <v>97960</v>
@@ -39287,7 +39287,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.754233658313751</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1342" t="n">
         <v>231631</v>
@@ -39374,7 +39374,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1345" t="n">
         <v>537402</v>
@@ -39403,7 +39403,7 @@
         <v>1.125</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.778452277183533</v>
+        <v>0.778452336788177</v>
       </c>
       <c r="H1346" t="n">
         <v>130572</v>
@@ -39432,7 +39432,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.774992406368256</v>
+        <v>0.7749924659729</v>
       </c>
       <c r="H1347" t="n">
         <v>50868</v>
@@ -39461,7 +39461,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.774992406368256</v>
+        <v>0.7749924659729</v>
       </c>
       <c r="H1348" t="n">
         <v>140318</v>
@@ -39490,7 +39490,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1349" t="n">
         <v>202221</v>
@@ -39519,7 +39519,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1350" t="n">
         <v>305250</v>
@@ -39548,7 +39548,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1351" t="n">
         <v>45974</v>
@@ -39577,7 +39577,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1352" t="n">
         <v>26682</v>
@@ -39664,7 +39664,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1355" t="n">
         <v>288218</v>
@@ -39751,7 +39751,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1358" t="n">
         <v>83258</v>
@@ -39809,7 +39809,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.806130468845367</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1360" t="n">
         <v>83021</v>
@@ -39867,7 +39867,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1362" t="n">
         <v>313246</v>
@@ -39983,7 +39983,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1366" t="n">
         <v>281388</v>
@@ -40041,7 +40041,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799210965633392</v>
       </c>
       <c r="H1368" t="n">
         <v>80674</v>
@@ -40070,7 +40070,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799210965633392</v>
       </c>
       <c r="H1369" t="n">
         <v>90790</v>
@@ -40099,7 +40099,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799210965633392</v>
       </c>
       <c r="H1370" t="n">
         <v>56184</v>
@@ -40157,7 +40157,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.78883171081543</v>
+        <v>0.78883159160614</v>
       </c>
       <c r="H1372" t="n">
         <v>81114</v>
@@ -40186,7 +40186,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.78883171081543</v>
+        <v>0.78883159160614</v>
       </c>
       <c r="H1373" t="n">
         <v>168113</v>
@@ -40244,7 +40244,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1375" t="n">
         <v>86876</v>
@@ -40273,7 +40273,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1376" t="n">
         <v>14034</v>
@@ -40302,7 +40302,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1377" t="n">
         <v>27809</v>
@@ -40360,7 +40360,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1379" t="n">
         <v>147569</v>
@@ -40389,7 +40389,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1380" t="n">
         <v>84546</v>
@@ -40418,7 +40418,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.802670836448669</v>
+        <v>0.802670776844025</v>
       </c>
       <c r="H1381" t="n">
         <v>180521</v>
@@ -40476,7 +40476,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799210965633392</v>
       </c>
       <c r="H1383" t="n">
         <v>162202</v>
@@ -40505,7 +40505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1384" t="n">
         <v>90158</v>
@@ -40592,7 +40592,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1387" t="n">
         <v>156054</v>
@@ -40621,7 +40621,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1388" t="n">
         <v>49722</v>
@@ -40650,7 +40650,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1389" t="n">
         <v>189258</v>
@@ -40679,7 +40679,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.806130468845367</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1390" t="n">
         <v>192841</v>
@@ -40708,7 +40708,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.802670836448669</v>
+        <v>0.802670776844025</v>
       </c>
       <c r="H1391" t="n">
         <v>60030</v>
@@ -40737,7 +40737,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.802670836448669</v>
+        <v>0.802670776844025</v>
       </c>
       <c r="H1392" t="n">
         <v>73274</v>
@@ -40766,7 +40766,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1393" t="n">
         <v>200154</v>
@@ -40795,7 +40795,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.802670836448669</v>
+        <v>0.802670776844025</v>
       </c>
       <c r="H1394" t="n">
         <v>43075</v>
@@ -40824,7 +40824,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.802670836448669</v>
+        <v>0.802670776844025</v>
       </c>
       <c r="H1395" t="n">
         <v>109252</v>
@@ -40853,7 +40853,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.802670836448669</v>
+        <v>0.802670776844025</v>
       </c>
       <c r="H1396" t="n">
         <v>75731</v>
@@ -40882,7 +40882,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799210965633392</v>
       </c>
       <c r="H1397" t="n">
         <v>17197</v>
@@ -40940,7 +40940,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.806130468845367</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1399" t="n">
         <v>470494</v>
@@ -40998,7 +40998,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.806130468845367</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1401" t="n">
         <v>120762</v>
@@ -41172,7 +41172,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.802670836448669</v>
+        <v>0.802670776844025</v>
       </c>
       <c r="H1407" t="n">
         <v>200876</v>
@@ -41201,7 +41201,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.802670836448669</v>
+        <v>0.802670776844025</v>
       </c>
       <c r="H1408" t="n">
         <v>422416</v>
@@ -41346,7 +41346,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1413" t="n">
         <v>583052</v>
@@ -41375,7 +41375,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1414" t="n">
         <v>94810</v>
@@ -41404,7 +41404,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1415" t="n">
         <v>926778</v>
@@ -41433,7 +41433,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1416" t="n">
         <v>335083</v>
@@ -41491,7 +41491,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1418" t="n">
         <v>281905</v>
@@ -41520,7 +41520,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1419" t="n">
         <v>190170</v>
@@ -41549,7 +41549,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1420" t="n">
         <v>114650</v>
@@ -41578,7 +41578,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1421" t="n">
         <v>66926</v>
@@ -41607,7 +41607,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1422" t="n">
         <v>148582</v>
@@ -41636,7 +41636,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1423" t="n">
         <v>274643</v>
@@ -41665,7 +41665,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1424" t="n">
         <v>138269</v>
@@ -41694,7 +41694,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1425" t="n">
         <v>60081</v>
@@ -41723,7 +41723,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1426" t="n">
         <v>92896</v>
@@ -41752,7 +41752,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1427" t="n">
         <v>69676</v>
@@ -41781,7 +41781,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1428" t="n">
         <v>27419</v>
@@ -41810,7 +41810,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1429" t="n">
         <v>16294</v>
@@ -41839,7 +41839,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.826889395713806</v>
+        <v>0.826889276504517</v>
       </c>
       <c r="H1430" t="n">
         <v>34025</v>
@@ -41868,7 +41868,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.826889395713806</v>
+        <v>0.826889276504517</v>
       </c>
       <c r="H1431" t="n">
         <v>4343</v>
@@ -42216,7 +42216,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.847647905349731</v>
+        <v>0.847648024559021</v>
       </c>
       <c r="H1443" t="n">
         <v>259888</v>
@@ -42245,7 +42245,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.854567527770996</v>
+        <v>0.854567646980286</v>
       </c>
       <c r="H1444" t="n">
         <v>272372</v>
@@ -42274,7 +42274,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.851107835769653</v>
+        <v>0.851107776165009</v>
       </c>
       <c r="H1445" t="n">
         <v>242876</v>
@@ -42448,7 +42448,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.833808839321136</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1451" t="n">
         <v>28378</v>
@@ -42477,7 +42477,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.833808839321136</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1452" t="n">
         <v>824448</v>
@@ -42535,7 +42535,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.833808839321136</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1454" t="n">
         <v>320343</v>
@@ -42593,7 +42593,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.858027338981628</v>
+        <v>0.858027398586273</v>
       </c>
       <c r="H1456" t="n">
         <v>272511</v>
@@ -42622,7 +42622,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.878786027431488</v>
+        <v>0.878786087036133</v>
       </c>
       <c r="H1457" t="n">
         <v>357522</v>
@@ -42709,7 +42709,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.903004586696625</v>
+        <v>0.90300464630127</v>
       </c>
       <c r="H1460" t="n">
         <v>479584</v>
@@ -42796,7 +42796,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.906464338302612</v>
+        <v>0.906464397907257</v>
       </c>
       <c r="H1463" t="n">
         <v>657445</v>
@@ -42854,7 +42854,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.927223145961761</v>
+        <v>0.927223265171051</v>
       </c>
       <c r="H1465" t="n">
         <v>86673</v>
@@ -42970,7 +42970,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.941062211990356</v>
+        <v>0.941062271595001</v>
       </c>
       <c r="H1469" t="n">
         <v>129426</v>
@@ -43057,7 +43057,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.947981834411621</v>
+        <v>0.947981774806976</v>
       </c>
       <c r="H1472" t="n">
         <v>69196</v>
@@ -43115,7 +43115,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602639198303</v>
       </c>
       <c r="H1474" t="n">
         <v>142236</v>
@@ -43144,7 +43144,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602639198303</v>
       </c>
       <c r="H1475" t="n">
         <v>50984</v>
@@ -43202,7 +43202,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.947981834411621</v>
+        <v>0.947981774806976</v>
       </c>
       <c r="H1477" t="n">
         <v>106073</v>
@@ -43231,7 +43231,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.972200274467468</v>
+        <v>0.972200334072113</v>
       </c>
       <c r="H1478" t="n">
         <v>702015</v>
@@ -43260,7 +43260,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.965280771255493</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1479" t="n">
         <v>279723</v>
@@ -43289,7 +43289,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.965280771255493</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1480" t="n">
         <v>122253</v>
@@ -43318,7 +43318,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.965280771255493</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1481" t="n">
         <v>54841</v>
@@ -43376,7 +43376,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.96874064207077</v>
+        <v>0.968740582466125</v>
       </c>
       <c r="H1483" t="n">
         <v>274130</v>
@@ -43405,7 +43405,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.996419012546539</v>
+        <v>0.996418952941895</v>
       </c>
       <c r="H1484" t="n">
         <v>249252</v>
@@ -43463,7 +43463,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.999878644943237</v>
+        <v>0.999878704547882</v>
       </c>
       <c r="H1486" t="n">
         <v>120478</v>
@@ -43492,7 +43492,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.999878644943237</v>
+        <v>0.999878704547882</v>
       </c>
       <c r="H1487" t="n">
         <v>171820</v>
@@ -43579,7 +43579,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.00333857536316</v>
+        <v>1.00333845615387</v>
       </c>
       <c r="H1490" t="n">
         <v>98471</v>
@@ -43608,7 +43608,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.996419012546539</v>
+        <v>0.996418952941895</v>
       </c>
       <c r="H1491" t="n">
         <v>62978</v>
@@ -43666,7 +43666,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.986039459705353</v>
+        <v>0.986039519309998</v>
       </c>
       <c r="H1493" t="n">
         <v>139022</v>
@@ -43695,7 +43695,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.986039459705353</v>
+        <v>0.986039519309998</v>
       </c>
       <c r="H1494" t="n">
         <v>79009</v>
@@ -43724,7 +43724,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.961821019649506</v>
+        <v>0.96182107925415</v>
       </c>
       <c r="H1495" t="n">
         <v>274571</v>
@@ -43753,7 +43753,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.961821019649506</v>
+        <v>0.96182107925415</v>
       </c>
       <c r="H1496" t="n">
         <v>319492</v>
@@ -43927,7 +43927,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602639198303</v>
       </c>
       <c r="H1502" t="n">
         <v>755734</v>
@@ -43956,7 +43956,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.927223145961761</v>
+        <v>0.927223265171051</v>
       </c>
       <c r="H1503" t="n">
         <v>329891</v>
@@ -44043,7 +44043,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.965280771255493</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1506" t="n">
         <v>99940</v>
@@ -44072,7 +44072,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.96874064207077</v>
+        <v>0.968740582466125</v>
       </c>
       <c r="H1507" t="n">
         <v>253006</v>
@@ -44101,7 +44101,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.965280771255493</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1508" t="n">
         <v>176991</v>
@@ -44130,7 +44130,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.989499390125275</v>
+        <v>0.989499151706696</v>
       </c>
       <c r="H1509" t="n">
         <v>407671</v>
@@ -44217,7 +44217,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1512" t="n">
         <v>458228</v>
@@ -44246,7 +44246,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1513" t="n">
         <v>220523</v>
@@ -44275,7 +44275,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1514" t="n">
         <v>249496</v>
@@ -44304,7 +44304,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.989499390125275</v>
+        <v>0.989499151706696</v>
       </c>
       <c r="H1515" t="n">
         <v>224195</v>
@@ -44333,7 +44333,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1516" t="n">
         <v>437735</v>
@@ -44362,7 +44362,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.00333857536316</v>
+        <v>1.00333845615387</v>
       </c>
       <c r="H1517" t="n">
         <v>139959</v>
@@ -44507,7 +44507,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1522" t="n">
         <v>189922</v>
@@ -44536,7 +44536,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1523" t="n">
         <v>391063</v>
@@ -44565,7 +44565,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1524" t="n">
         <v>793175</v>
@@ -44594,7 +44594,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.03101682662964</v>
+        <v>1.03101670742035</v>
       </c>
       <c r="H1525" t="n">
         <v>218492</v>
@@ -44652,7 +44652,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1527" t="n">
         <v>782238</v>
@@ -44681,7 +44681,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.09675288200378</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1528" t="n">
         <v>621472</v>
@@ -44710,7 +44710,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.11751139163971</v>
+        <v>1.117511510849</v>
       </c>
       <c r="H1529" t="n">
         <v>421145</v>
@@ -44768,7 +44768,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.10021245479584</v>
+        <v>1.10021257400513</v>
       </c>
       <c r="H1531" t="n">
         <v>480528</v>
@@ -44797,7 +44797,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.09675288200378</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1532" t="n">
         <v>258600</v>
@@ -44826,7 +44826,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.08983325958252</v>
+        <v>1.08983314037323</v>
       </c>
       <c r="H1533" t="n">
         <v>163796</v>
@@ -44855,7 +44855,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.10021245479584</v>
+        <v>1.10021257400513</v>
       </c>
       <c r="H1534" t="n">
         <v>140725</v>
@@ -44884,7 +44884,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.09329295158386</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1535" t="n">
         <v>168043</v>
@@ -44913,7 +44913,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.08983325958252</v>
+        <v>1.08983314037323</v>
       </c>
       <c r="H1536" t="n">
         <v>438076</v>
@@ -44971,7 +44971,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.09329295158386</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1538" t="n">
         <v>370435</v>
@@ -45000,7 +45000,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.07599401473999</v>
+        <v>1.07599413394928</v>
       </c>
       <c r="H1539" t="n">
         <v>191861</v>
@@ -45029,7 +45029,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.09329295158386</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1540" t="n">
         <v>210213</v>
@@ -45087,7 +45087,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.04139626026154</v>
+        <v>1.04139614105225</v>
       </c>
       <c r="H1542" t="n">
         <v>266855</v>
@@ -45116,7 +45116,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.04139626026154</v>
+        <v>1.04139614105225</v>
       </c>
       <c r="H1543" t="n">
         <v>262904</v>
@@ -45174,7 +45174,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.06215476989746</v>
+        <v>1.06215488910675</v>
       </c>
       <c r="H1545" t="n">
         <v>133753</v>
@@ -45203,7 +45203,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.05523526668549</v>
+        <v>1.0552351474762</v>
       </c>
       <c r="H1546" t="n">
         <v>96630</v>
@@ -45232,7 +45232,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.07599401473999</v>
+        <v>1.07599413394928</v>
       </c>
       <c r="H1547" t="n">
         <v>82571</v>
@@ -45261,7 +45261,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.07945382595062</v>
+        <v>1.07945370674133</v>
       </c>
       <c r="H1548" t="n">
         <v>63798</v>
@@ -45290,7 +45290,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.07599401473999</v>
+        <v>1.07599413394928</v>
       </c>
       <c r="H1549" t="n">
         <v>67697</v>
@@ -45319,7 +45319,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.06215476989746</v>
+        <v>1.06215488910675</v>
       </c>
       <c r="H1550" t="n">
         <v>112492</v>
@@ -45348,7 +45348,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1551" t="n">
         <v>94039</v>
@@ -45406,7 +45406,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1553" t="n">
         <v>102708</v>
@@ -45493,7 +45493,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.07945382595062</v>
+        <v>1.07945370674133</v>
       </c>
       <c r="H1556" t="n">
         <v>187242</v>
@@ -45609,7 +45609,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.11751139163971</v>
+        <v>1.117511510849</v>
       </c>
       <c r="H1560" t="n">
         <v>2403157</v>
@@ -45667,7 +45667,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1562" t="n">
         <v>1416932</v>
@@ -45725,7 +45725,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1564" t="n">
         <v>988135</v>
@@ -45812,7 +45812,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1567" t="n">
         <v>415789</v>
@@ -45841,7 +45841,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.20054638385773</v>
+        <v>1.20054650306702</v>
       </c>
       <c r="H1568" t="n">
         <v>951811</v>
@@ -45870,7 +45870,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1569" t="n">
         <v>510397</v>
@@ -45899,7 +45899,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.13481044769287</v>
+        <v>1.13481032848358</v>
       </c>
       <c r="H1570" t="n">
         <v>651398</v>
@@ -45928,7 +45928,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1571" t="n">
         <v>1174698</v>
@@ -45957,7 +45957,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.04139626026154</v>
+        <v>1.04139614105225</v>
       </c>
       <c r="H1572" t="n">
         <v>825976</v>
@@ -45986,7 +45986,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.07599401473999</v>
+        <v>1.07599413394928</v>
       </c>
       <c r="H1573" t="n">
         <v>637653</v>
@@ -46102,7 +46102,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.10021245479584</v>
+        <v>1.10021257400513</v>
       </c>
       <c r="H1577" t="n">
         <v>491084</v>
@@ -46131,7 +46131,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.09675288200378</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1578" t="n">
         <v>231555</v>
@@ -46189,7 +46189,7 @@
         <v>1.625</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.12443113327026</v>
+        <v>1.12443101406097</v>
       </c>
       <c r="H1580" t="n">
         <v>317784</v>
@@ -46305,7 +46305,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1584" t="n">
         <v>312880</v>
@@ -46363,7 +46363,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.20054638385773</v>
+        <v>1.20054650306702</v>
       </c>
       <c r="H1586" t="n">
         <v>279699</v>
@@ -46392,7 +46392,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.2282247543335</v>
+        <v>1.22822463512421</v>
       </c>
       <c r="H1587" t="n">
         <v>812992</v>
@@ -46421,7 +46421,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.23168432712555</v>
+        <v>1.23168444633484</v>
       </c>
       <c r="H1588" t="n">
         <v>827658</v>
@@ -46450,7 +46450,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.26282262802124</v>
+        <v>1.26282250881195</v>
       </c>
       <c r="H1589" t="n">
         <v>1153238</v>
@@ -46653,7 +46653,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.2282247543335</v>
+        <v>1.22822463512421</v>
       </c>
       <c r="H1596" t="n">
         <v>405009</v>
@@ -46711,7 +46711,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.2282247543335</v>
+        <v>1.22822463512421</v>
       </c>
       <c r="H1598" t="n">
         <v>636289</v>
@@ -46740,7 +46740,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.22476482391357</v>
+        <v>1.22476494312286</v>
       </c>
       <c r="H1599" t="n">
         <v>500917</v>
@@ -46769,7 +46769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1600" t="n">
         <v>1485021</v>
@@ -46798,7 +46798,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.19016718864441</v>
+        <v>1.19016706943512</v>
       </c>
       <c r="H1601" t="n">
         <v>890205</v>
@@ -46856,7 +46856,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1603" t="n">
         <v>2203239</v>
@@ -46885,7 +46885,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1604" t="n">
         <v>2339616</v>
@@ -47001,7 +47001,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1608" t="n">
         <v>1010695</v>
@@ -47030,7 +47030,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1609" t="n">
         <v>1151534</v>
@@ -47088,7 +47088,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1611" t="n">
         <v>880818</v>
@@ -47233,7 +47233,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.00590598583221</v>
+        <v>1.00590586662292</v>
       </c>
       <c r="H1616" t="n">
         <v>1083652</v>
@@ -47262,7 +47262,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.0266889333725</v>
+        <v>1.02668905258179</v>
       </c>
       <c r="H1617" t="n">
         <v>302941</v>
@@ -47320,7 +47320,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1619" t="n">
         <v>190754</v>
@@ -47958,7 +47958,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1641" t="n">
         <v>160578</v>
@@ -48016,7 +48016,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1643" t="n">
         <v>164472</v>
@@ -48103,7 +48103,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1646" t="n">
         <v>87524</v>
@@ -48132,7 +48132,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1647" t="n">
         <v>65315</v>
@@ -48161,7 +48161,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.00174915790558</v>
+        <v>1.00174927711487</v>
       </c>
       <c r="H1648" t="n">
         <v>200636</v>
@@ -48277,7 +48277,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.01837563514709</v>
+        <v>1.01837575435638</v>
       </c>
       <c r="H1652" t="n">
         <v>59507</v>
@@ -48451,7 +48451,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.0266889333725</v>
+        <v>1.02668905258179</v>
       </c>
       <c r="H1658" t="n">
         <v>131925</v>
@@ -48654,7 +48654,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.00174915790558</v>
+        <v>1.00174927711487</v>
       </c>
       <c r="H1665" t="n">
         <v>15682</v>
@@ -48915,7 +48915,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.12644827365875</v>
+        <v>1.12644839286804</v>
       </c>
       <c r="H1674" t="n">
         <v>329517</v>
@@ -48944,7 +48944,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.13891816139221</v>
+        <v>1.13891804218292</v>
       </c>
       <c r="H1675" t="n">
         <v>180973</v>
@@ -48973,7 +48973,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.13891816139221</v>
+        <v>1.13891804218292</v>
       </c>
       <c r="H1676" t="n">
         <v>42686</v>
@@ -49060,7 +49060,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1679" t="n">
         <v>710005</v>
@@ -49089,7 +49089,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1680" t="n">
         <v>110800</v>
@@ -49118,7 +49118,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1681" t="n">
         <v>61636</v>
@@ -49176,7 +49176,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1683" t="n">
         <v>109056</v>
@@ -49205,7 +49205,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1684" t="n">
         <v>77385</v>
@@ -49234,7 +49234,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1685" t="n">
         <v>69462</v>
@@ -49263,7 +49263,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1686" t="n">
         <v>115592</v>
@@ -49292,7 +49292,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1687" t="n">
         <v>170265</v>
@@ -49582,7 +49582,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.0433155298233</v>
+        <v>1.04331564903259</v>
       </c>
       <c r="H1697" t="n">
         <v>116135</v>
@@ -49669,7 +49669,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.05162882804871</v>
+        <v>1.05162870883942</v>
       </c>
       <c r="H1700" t="n">
         <v>107236</v>
@@ -50017,7 +50017,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.05162882804871</v>
+        <v>1.05162870883942</v>
       </c>
       <c r="H1712" t="n">
         <v>160506</v>
@@ -50133,7 +50133,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.05162882804871</v>
+        <v>1.05162870883942</v>
       </c>
       <c r="H1716" t="n">
         <v>45929</v>
@@ -50162,7 +50162,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.00590598583221</v>
+        <v>1.00590586662292</v>
       </c>
       <c r="H1717" t="n">
         <v>88192</v>
@@ -50684,7 +50684,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.13891816139221</v>
+        <v>1.13891804218292</v>
       </c>
       <c r="H1735" t="n">
         <v>411500</v>
@@ -50713,7 +50713,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1736" t="n">
         <v>124290</v>
@@ -50742,7 +50742,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.13891816139221</v>
+        <v>1.13891804218292</v>
       </c>
       <c r="H1737" t="n">
         <v>156994</v>
@@ -50829,7 +50829,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1740" t="n">
         <v>144391</v>
@@ -51032,7 +51032,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1747" t="n">
         <v>176848</v>
@@ -51061,7 +51061,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1748" t="n">
         <v>347152</v>
@@ -51090,7 +51090,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1749" t="n">
         <v>169055</v>
@@ -51119,7 +51119,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1750" t="n">
         <v>375754</v>
@@ -51235,7 +51235,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1754" t="n">
         <v>132380</v>
@@ -51264,7 +51264,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1755" t="n">
         <v>72551</v>
@@ -51293,7 +51293,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1756" t="n">
         <v>358383</v>
@@ -51380,7 +51380,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1759" t="n">
         <v>122591</v>
@@ -51438,7 +51438,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1761" t="n">
         <v>75841</v>
@@ -51496,7 +51496,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1763" t="n">
         <v>173734</v>
@@ -51612,7 +51612,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1767" t="n">
         <v>3264</v>
@@ -51641,7 +51641,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1768" t="n">
         <v>10397</v>
@@ -51670,7 +51670,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1769" t="n">
         <v>56112</v>
@@ -51699,7 +51699,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1770" t="n">
         <v>109220</v>
@@ -51757,7 +51757,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1772" t="n">
         <v>87953</v>
@@ -51786,7 +51786,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1773" t="n">
         <v>65824</v>
@@ -51844,7 +51844,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1775" t="n">
         <v>50064</v>
@@ -51873,7 +51873,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1776" t="n">
         <v>221706</v>
@@ -52047,7 +52047,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1782" t="n">
         <v>77581</v>
@@ -52163,7 +52163,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1786" t="n">
         <v>323070</v>
@@ -52192,7 +52192,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1787" t="n">
         <v>134209</v>
@@ -52308,7 +52308,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.20126760005951</v>
+        <v>1.2012677192688</v>
       </c>
       <c r="H1791" t="n">
         <v>252309</v>
@@ -52366,7 +52366,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.23452067375183</v>
+        <v>1.23452079296112</v>
       </c>
       <c r="H1793" t="n">
         <v>551408</v>
@@ -52395,7 +52395,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.23867750167847</v>
+        <v>1.23867738246918</v>
       </c>
       <c r="H1794" t="n">
         <v>153832</v>
@@ -52453,7 +52453,7 @@
         <v>1.5</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.24699068069458</v>
+        <v>1.24699079990387</v>
       </c>
       <c r="H1796" t="n">
         <v>298792</v>
@@ -52511,7 +52511,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.2636171579361</v>
+        <v>1.26361727714539</v>
       </c>
       <c r="H1798" t="n">
         <v>366320</v>
@@ -52540,7 +52540,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.2719304561615</v>
+        <v>1.27193033695221</v>
       </c>
       <c r="H1799" t="n">
         <v>282328</v>
@@ -52627,7 +52627,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.31349682807922</v>
+        <v>1.31349694728851</v>
       </c>
       <c r="H1802" t="n">
         <v>618746</v>
@@ -52685,7 +52685,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.31349682807922</v>
+        <v>1.31349694728851</v>
       </c>
       <c r="H1804" t="n">
         <v>247156</v>
@@ -52743,7 +52743,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.30102705955505</v>
+        <v>1.30102694034576</v>
       </c>
       <c r="H1806" t="n">
         <v>313388</v>
@@ -52772,7 +52772,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.30102705955505</v>
+        <v>1.30102694034576</v>
       </c>
       <c r="H1807" t="n">
         <v>383037</v>
@@ -52859,7 +52859,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.30518352985382</v>
+        <v>1.30518364906311</v>
       </c>
       <c r="H1810" t="n">
         <v>175006</v>
@@ -52946,7 +52946,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.2636171579361</v>
+        <v>1.26361727714539</v>
       </c>
       <c r="H1813" t="n">
         <v>380172</v>
@@ -53033,7 +53033,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.25114738941193</v>
+        <v>1.25114727020264</v>
       </c>
       <c r="H1816" t="n">
         <v>685944</v>
@@ -53091,7 +53091,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1818" t="n">
-        <v>1.23452067375183</v>
+        <v>1.23452079296112</v>
       </c>
       <c r="H1818" t="n">
         <v>151967</v>
@@ -53207,7 +53207,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1822" t="n">
-        <v>1.19711124897003</v>
+        <v>1.19711112976074</v>
       </c>
       <c r="H1822" t="n">
         <v>74260</v>
@@ -53236,7 +53236,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1823" t="n">
         <v>99923</v>
@@ -53265,7 +53265,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1824" t="n">
         <v>159581</v>
@@ -53294,7 +53294,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.16801464557648</v>
+        <v>1.16801452636719</v>
       </c>
       <c r="H1825" t="n">
         <v>115291</v>
@@ -53352,7 +53352,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1827" t="n">
         <v>228903</v>
@@ -53468,7 +53468,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1831" t="n">
         <v>66408</v>
@@ -53497,7 +53497,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1832" t="n">
         <v>211202</v>
@@ -53526,7 +53526,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1833" t="n">
         <v>164273</v>
@@ -53555,7 +53555,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.1763277053833</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1834" t="n">
         <v>54075</v>
@@ -53584,7 +53584,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1835" t="n">
         <v>193872</v>
@@ -53613,7 +53613,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1836" t="n">
         <v>91206</v>
@@ -53642,7 +53642,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.13060474395752</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1837" t="n">
         <v>78241</v>
@@ -53758,7 +53758,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1841" t="n">
         <v>67536</v>
@@ -53787,7 +53787,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.15970122814178</v>
+        <v>1.15970134735107</v>
       </c>
       <c r="H1842" t="n">
         <v>65862</v>
@@ -53816,7 +53816,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1843" t="n">
         <v>82942</v>
@@ -53874,7 +53874,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1845" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1845" t="n">
         <v>10311</v>
@@ -53903,7 +53903,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.16385805606842</v>
+        <v>1.16385793685913</v>
       </c>
       <c r="H1846" t="n">
         <v>37842</v>
@@ -53932,7 +53932,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1847" t="n">
         <v>41416</v>
@@ -53990,7 +53990,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1849" t="n">
         <v>99465</v>
@@ -54019,7 +54019,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1850" t="n">
         <v>34436</v>
@@ -54048,7 +54048,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1851" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1851" t="n">
         <v>21830</v>
@@ -54077,7 +54077,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1852" t="n">
         <v>141398</v>
@@ -54135,7 +54135,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1854" t="n">
         <v>79997</v>
@@ -54193,7 +54193,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.18713521957397</v>
+        <v>1.18713510036469</v>
       </c>
       <c r="H1856" t="n">
         <v>84976</v>
@@ -54222,7 +54222,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.20209896564484</v>
+        <v>1.20209908485413</v>
       </c>
       <c r="H1857" t="n">
         <v>135553</v>
@@ -54309,7 +54309,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.18547248840332</v>
+        <v>1.18547236919403</v>
       </c>
       <c r="H1860" t="n">
         <v>107702</v>
@@ -54338,7 +54338,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1861" t="n">
         <v>91901</v>
@@ -54367,7 +54367,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1862" t="n">
-        <v>1.20617949962616</v>
+        <v>1.20617938041687</v>
       </c>
       <c r="H1862" t="n">
         <v>33588</v>
@@ -54628,7 +54628,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1871" t="n">
         <v>33985</v>
@@ -54715,7 +54715,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1874" t="n">
         <v>103196</v>
@@ -54744,7 +54744,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.20617949962616</v>
+        <v>1.20617938041687</v>
       </c>
       <c r="H1875" t="n">
         <v>144823</v>
@@ -54831,7 +54831,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1878" t="n">
         <v>40341</v>
@@ -54860,7 +54860,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1879" t="n">
         <v>97941</v>
@@ -55005,7 +55005,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1884" t="n">
         <v>23955</v>
@@ -55034,7 +55034,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1885" t="n">
         <v>38632</v>
@@ -55121,7 +55121,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1888" t="n">
         <v>56779</v>
@@ -55150,7 +55150,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1889" t="n">
         <v>41746</v>
@@ -55179,7 +55179,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.20617949962616</v>
+        <v>1.20617938041687</v>
       </c>
       <c r="H1890" t="n">
         <v>141477</v>
@@ -55208,7 +55208,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1891" t="n">
         <v>90261</v>
@@ -55237,7 +55237,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1892" t="n">
         <v>64215</v>
@@ -55266,7 +55266,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1893" t="n">
         <v>10161</v>
@@ -55469,7 +55469,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.20617949962616</v>
+        <v>1.20617938041687</v>
       </c>
       <c r="H1900" t="n">
         <v>84123</v>
@@ -55498,7 +55498,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1901" t="n">
         <v>56215</v>
@@ -55527,7 +55527,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.19064927101135</v>
+        <v>1.19064915180206</v>
       </c>
       <c r="H1902" t="n">
         <v>88418</v>
@@ -55556,7 +55556,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1903" t="n">
         <v>62215</v>
@@ -55614,7 +55614,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1905" t="n">
         <v>110276</v>
@@ -55643,7 +55643,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1906" t="n">
         <v>34897</v>
@@ -55788,7 +55788,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1911" t="n">
         <v>29647</v>
@@ -55817,7 +55817,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1912" t="n">
         <v>25580</v>
@@ -55875,7 +55875,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.18029582500458</v>
+        <v>1.18029570579529</v>
       </c>
       <c r="H1914" t="n">
         <v>63925</v>
@@ -55904,7 +55904,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.19064927101135</v>
+        <v>1.19064915180206</v>
       </c>
       <c r="H1915" t="n">
         <v>32722</v>
@@ -55933,7 +55933,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1916" t="n">
         <v>87092</v>
@@ -56078,7 +56078,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.22343516349792</v>
+        <v>1.22343528270721</v>
       </c>
       <c r="H1921" t="n">
         <v>41234</v>
@@ -57064,7 +57064,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.22343516349792</v>
+        <v>1.22343528270721</v>
       </c>
       <c r="H1955" t="n">
         <v>92814</v>
@@ -57296,7 +57296,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1963" t="n">
         <v>309806</v>
@@ -57383,7 +57383,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1966" t="n">
         <v>86051</v>
@@ -57441,7 +57441,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1968" t="n">
         <v>126228</v>
@@ -57470,7 +57470,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1969" t="n">
         <v>302616</v>
@@ -57499,7 +57499,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1970" t="n">
         <v>164579</v>
@@ -57528,7 +57528,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1971" t="n">
         <v>84515</v>
@@ -57557,7 +57557,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1972" t="n">
         <v>129339</v>
@@ -57615,7 +57615,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1974" t="n">
         <v>60478</v>
@@ -57644,7 +57644,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.20790505409241</v>
+        <v>1.20790493488312</v>
       </c>
       <c r="H1975" t="n">
         <v>57405</v>
@@ -57702,7 +57702,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.20963060855865</v>
+        <v>1.20963048934937</v>
       </c>
       <c r="H1977" t="n">
         <v>118187</v>
@@ -57818,7 +57818,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.23723995685577</v>
+        <v>1.23723983764648</v>
       </c>
       <c r="H1981" t="n">
         <v>146312</v>
@@ -58224,7 +58224,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.26312339305878</v>
+        <v>1.26312351226807</v>
       </c>
       <c r="H1995" t="n">
         <v>105068</v>
@@ -58369,7 +58369,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2000" t="n">
         <v>12500</v>
@@ -58775,7 +58775,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2014" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2014" t="n">
         <v>26778</v>
@@ -58862,7 +58862,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2017" t="n">
         <v>56183</v>
@@ -59297,7 +59297,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G2032" t="n">
-        <v>1.2907327413559</v>
+        <v>1.29073286056519</v>
       </c>
       <c r="H2032" t="n">
         <v>185167</v>
@@ -59500,7 +59500,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G2039" t="n">
-        <v>1.33904898166656</v>
+        <v>1.33904910087585</v>
       </c>
       <c r="H2039" t="n">
         <v>73166</v>
@@ -59558,7 +59558,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2041" t="n">
         <v>101446</v>
@@ -59616,7 +59616,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2043" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2043" t="n">
         <v>149475</v>
@@ -59732,7 +59732,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2047" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2047" t="n">
         <v>107937</v>
@@ -59819,7 +59819,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2050" t="n">
         <v>205091</v>
@@ -59848,7 +59848,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2051" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2051" t="n">
         <v>51256</v>
@@ -59877,7 +59877,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2052" t="n">
         <v>66057</v>
@@ -59906,7 +59906,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G2053" t="n">
-        <v>1.31661641597748</v>
+        <v>1.31661653518677</v>
       </c>
       <c r="H2053" t="n">
         <v>80261</v>
@@ -60109,7 +60109,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G2060" t="n">
-        <v>1.28728151321411</v>
+        <v>1.2872816324234</v>
       </c>
       <c r="H2060" t="n">
         <v>29745</v>
@@ -60341,7 +60341,7 @@
         <v>1.50199997425079</v>
       </c>
       <c r="G2068" t="n">
-        <v>1.29590952396393</v>
+        <v>1.29590940475464</v>
       </c>
       <c r="H2068" t="n">
         <v>235247</v>
@@ -60370,7 +60370,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G2069" t="n">
-        <v>1.2907327413559</v>
+        <v>1.29073286056519</v>
       </c>
       <c r="H2069" t="n">
         <v>286367</v>
@@ -60602,7 +60602,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.3856395483017</v>
+        <v>1.38563966751099</v>
       </c>
       <c r="H2077" t="n">
         <v>548812</v>
@@ -60631,7 +60631,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.40289533138275</v>
+        <v>1.40289545059204</v>
       </c>
       <c r="H2078" t="n">
         <v>275835</v>
@@ -60689,7 +60689,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.40634644031525</v>
+        <v>1.40634655952454</v>
       </c>
       <c r="H2080" t="n">
         <v>364464</v>
@@ -60776,7 +60776,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.40979766845703</v>
+        <v>1.40979778766632</v>
       </c>
       <c r="H2083" t="n">
         <v>363044</v>
@@ -60921,7 +60921,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G2088" t="n">
-        <v>1.40807199478149</v>
+        <v>1.40807211399078</v>
       </c>
       <c r="H2088" t="n">
         <v>75710</v>
@@ -60950,7 +60950,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.39254188537598</v>
+        <v>1.39254176616669</v>
       </c>
       <c r="H2089" t="n">
         <v>94709</v>
@@ -60979,7 +60979,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.3821884393692</v>
+        <v>1.38218855857849</v>
       </c>
       <c r="H2090" t="n">
         <v>128951</v>
@@ -61124,7 +61124,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G2095" t="n">
-        <v>1.36493265628815</v>
+        <v>1.36493253707886</v>
       </c>
       <c r="H2095" t="n">
         <v>223370</v>
@@ -61182,7 +61182,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.37873721122742</v>
+        <v>1.37873733043671</v>
       </c>
       <c r="H2097" t="n">
         <v>75163</v>
@@ -79980,6 +79980,35 @@
         <v>50884</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.83399999141693</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.86199998855591</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.83399999141693</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.84399998188019</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.84399998188019</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>33952</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.48506224155426</v>
+        <v>0.485062181949615</v>
       </c>
       <c r="H2" t="n">
         <v>191859</v>
@@ -543,7 +543,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G6" t="n">
-        <v>0.47814267873764</v>
+        <v>0.478142738342285</v>
       </c>
       <c r="H6" t="n">
         <v>49636</v>
@@ -572,7 +572,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.47814267873764</v>
+        <v>0.478142738342285</v>
       </c>
       <c r="H7" t="n">
         <v>41531</v>
@@ -862,7 +862,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G17" t="n">
-        <v>0.467071443796158</v>
+        <v>0.467071324586868</v>
       </c>
       <c r="H17" t="n">
         <v>129282</v>
@@ -891,7 +891,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G18" t="n">
-        <v>0.477450758218765</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H18" t="n">
         <v>119370</v>
@@ -1007,7 +1007,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G22" t="n">
-        <v>0.471915066242218</v>
+        <v>0.471915006637573</v>
       </c>
       <c r="H22" t="n">
         <v>58624</v>
@@ -1065,7 +1065,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G24" t="n">
-        <v>0.453232198953629</v>
+        <v>0.453232139348984</v>
       </c>
       <c r="H24" t="n">
         <v>58754</v>
@@ -1123,7 +1123,7 @@
         <v>0.658999979496002</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456000030040741</v>
+        <v>0.456000000238419</v>
       </c>
       <c r="H26" t="n">
         <v>91179</v>
@@ -1152,7 +1152,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G27" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620656013489</v>
       </c>
       <c r="H27" t="n">
         <v>128286</v>
@@ -1210,7 +1210,7 @@
         <v>0.619499981403351</v>
       </c>
       <c r="G29" t="n">
-        <v>0.428667694330215</v>
+        <v>0.428667664527893</v>
       </c>
       <c r="H29" t="n">
         <v>258654</v>
@@ -1239,7 +1239,7 @@
         <v>0.614499986171722</v>
       </c>
       <c r="G30" t="n">
-        <v>0.425207942724228</v>
+        <v>0.425207912921906</v>
       </c>
       <c r="H30" t="n">
         <v>100995</v>
@@ -1268,7 +1268,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>0.425553947687149</v>
+        <v>0.425553917884827</v>
       </c>
       <c r="H31" t="n">
         <v>128707</v>
@@ -1413,7 +1413,7 @@
         <v>0.625</v>
       </c>
       <c r="G36" t="n">
-        <v>0.432473450899124</v>
+        <v>0.432473480701447</v>
       </c>
       <c r="H36" t="n">
         <v>45866</v>
@@ -1442,7 +1442,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G37" t="n">
-        <v>0.437317162752151</v>
+        <v>0.437317192554474</v>
       </c>
       <c r="H37" t="n">
         <v>59186</v>
@@ -1500,7 +1500,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>0.429013669490814</v>
+        <v>0.429013699293137</v>
       </c>
       <c r="H39" t="n">
         <v>68431</v>
@@ -1558,7 +1558,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G41" t="n">
-        <v>0.432127505540848</v>
+        <v>0.432127475738525</v>
       </c>
       <c r="H41" t="n">
         <v>54191</v>
@@ -1616,7 +1616,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G43" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H43" t="n">
         <v>51995</v>
@@ -1645,7 +1645,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G44" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620656013489</v>
       </c>
       <c r="H44" t="n">
         <v>148615</v>
@@ -1732,7 +1732,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G47" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H47" t="n">
         <v>26658</v>
@@ -1761,7 +1761,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G48" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H48" t="n">
         <v>122811</v>
@@ -1790,7 +1790,7 @@
         <v>0.621500015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>0.43005159497261</v>
+        <v>0.430051654577255</v>
       </c>
       <c r="H49" t="n">
         <v>65600</v>
@@ -1935,7 +1935,7 @@
         <v>0.636500000953674</v>
       </c>
       <c r="G54" t="n">
-        <v>0.440431028604507</v>
+        <v>0.440430968999863</v>
       </c>
       <c r="H54" t="n">
         <v>86858</v>
@@ -1964,7 +1964,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G55" t="n">
-        <v>0.437317162752151</v>
+        <v>0.437317192554474</v>
       </c>
       <c r="H55" t="n">
         <v>76343</v>
@@ -1993,7 +1993,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>0.439393043518066</v>
+        <v>0.439393073320389</v>
       </c>
       <c r="H56" t="n">
         <v>61433</v>
@@ -2138,7 +2138,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G61" t="n">
-        <v>0.434549361467361</v>
+        <v>0.434549391269684</v>
       </c>
       <c r="H61" t="n">
         <v>91042</v>
@@ -2196,7 +2196,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>0.434549361467361</v>
+        <v>0.434549391269684</v>
       </c>
       <c r="H63" t="n">
         <v>33873</v>
@@ -2225,7 +2225,7 @@
         <v>0.629499971866608</v>
       </c>
       <c r="G64" t="n">
-        <v>0.435587257146835</v>
+        <v>0.43558731675148</v>
       </c>
       <c r="H64" t="n">
         <v>36109</v>
@@ -2283,7 +2283,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G66" t="n">
-        <v>0.432127505540848</v>
+        <v>0.432127475738525</v>
       </c>
       <c r="H66" t="n">
         <v>90493</v>
@@ -2370,7 +2370,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>0.429013669490814</v>
+        <v>0.429013699293137</v>
       </c>
       <c r="H69" t="n">
         <v>66538</v>
@@ -2399,7 +2399,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>0.425553947687149</v>
+        <v>0.425553917884827</v>
       </c>
       <c r="H70" t="n">
         <v>76151</v>
@@ -2428,7 +2428,7 @@
         <v>0.615499973297119</v>
       </c>
       <c r="G71" t="n">
-        <v>0.425899833440781</v>
+        <v>0.425899863243103</v>
       </c>
       <c r="H71" t="n">
         <v>41570</v>
@@ -2486,7 +2486,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G73" t="n">
-        <v>0.430397570133209</v>
+        <v>0.430397599935532</v>
       </c>
       <c r="H73" t="n">
         <v>77451</v>
@@ -2515,7 +2515,7 @@
         <v>0.629499971866608</v>
       </c>
       <c r="G74" t="n">
-        <v>0.435587257146835</v>
+        <v>0.43558731675148</v>
       </c>
       <c r="H74" t="n">
         <v>124171</v>
@@ -2747,7 +2747,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>0.479180663824081</v>
+        <v>0.479180604219437</v>
       </c>
       <c r="H82" t="n">
         <v>29041</v>
@@ -2805,7 +2805,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G84" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611572980881</v>
       </c>
       <c r="H84" t="n">
         <v>97915</v>
@@ -2863,7 +2863,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G86" t="n">
-        <v>0.446312576532364</v>
+        <v>0.446312636137009</v>
       </c>
       <c r="H86" t="n">
         <v>147100</v>
@@ -2950,7 +2950,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G89" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620656013489</v>
       </c>
       <c r="H89" t="n">
         <v>81033</v>
@@ -3066,7 +3066,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G93" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852824926376</v>
       </c>
       <c r="H93" t="n">
         <v>137577</v>
@@ -3124,7 +3124,7 @@
         <v>0.656499981880188</v>
       </c>
       <c r="G95" t="n">
-        <v>0.454270154237747</v>
+        <v>0.454270124435425</v>
       </c>
       <c r="H95" t="n">
         <v>28570</v>
@@ -3182,7 +3182,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G97" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852824926376</v>
       </c>
       <c r="H97" t="n">
         <v>41726</v>
@@ -3211,7 +3211,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G98" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852824926376</v>
       </c>
       <c r="H98" t="n">
         <v>43674</v>
@@ -3240,7 +3240,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>0.439393043518066</v>
+        <v>0.439393073320389</v>
       </c>
       <c r="H99" t="n">
         <v>79566</v>
@@ -3298,7 +3298,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>0.443890780210495</v>
+        <v>0.443890810012817</v>
       </c>
       <c r="H101" t="n">
         <v>21942</v>
@@ -3327,7 +3327,7 @@
         <v>0.649500012397766</v>
       </c>
       <c r="G102" t="n">
-        <v>0.44942644238472</v>
+        <v>0.449426412582397</v>
       </c>
       <c r="H102" t="n">
         <v>87321</v>
@@ -3414,7 +3414,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>0.47814267873764</v>
+        <v>0.478142738342285</v>
       </c>
       <c r="H105" t="n">
         <v>164848</v>
@@ -3443,7 +3443,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G106" t="n">
-        <v>0.473990947008133</v>
+        <v>0.473990887403488</v>
       </c>
       <c r="H106" t="n">
         <v>8390</v>
@@ -3501,7 +3501,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G108" t="n">
-        <v>0.479180663824081</v>
+        <v>0.479180604219437</v>
       </c>
       <c r="H108" t="n">
         <v>5363</v>
@@ -3530,7 +3530,7 @@
         <v>0.698499977588654</v>
       </c>
       <c r="G109" t="n">
-        <v>0.483332335948944</v>
+        <v>0.483332395553589</v>
       </c>
       <c r="H109" t="n">
         <v>100009</v>
@@ -3588,7 +3588,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G111" t="n">
-        <v>0.477450758218765</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H111" t="n">
         <v>81596</v>
@@ -3675,7 +3675,7 @@
         <v>0.674499988555908</v>
       </c>
       <c r="G114" t="n">
-        <v>0.466725409030914</v>
+        <v>0.46672534942627</v>
       </c>
       <c r="H114" t="n">
         <v>30620</v>
@@ -3704,7 +3704,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>0.443890780210495</v>
+        <v>0.443890810012817</v>
       </c>
       <c r="H115" t="n">
         <v>154035</v>
@@ -3733,7 +3733,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G116" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852824926376</v>
       </c>
       <c r="H116" t="n">
         <v>203916</v>
@@ -3791,7 +3791,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G118" t="n">
-        <v>0.437317162752151</v>
+        <v>0.437317192554474</v>
       </c>
       <c r="H118" t="n">
         <v>37197</v>
@@ -3849,7 +3849,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G120" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852824926376</v>
       </c>
       <c r="H120" t="n">
         <v>89237</v>
@@ -3994,7 +3994,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G125" t="n">
-        <v>0.41932624578476</v>
+        <v>0.419326275587082</v>
       </c>
       <c r="H125" t="n">
         <v>164285</v>
@@ -4023,7 +4023,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G126" t="n">
-        <v>0.436625212430954</v>
+        <v>0.436625242233276</v>
       </c>
       <c r="H126" t="n">
         <v>99483</v>
@@ -4052,7 +4052,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G127" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852824926376</v>
       </c>
       <c r="H127" t="n">
         <v>82500</v>
@@ -4226,7 +4226,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G133" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852824926376</v>
       </c>
       <c r="H133" t="n">
         <v>152250</v>
@@ -4371,7 +4371,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G138" t="n">
-        <v>0.473990947008133</v>
+        <v>0.473990887403488</v>
       </c>
       <c r="H138" t="n">
         <v>15038</v>
@@ -4487,7 +4487,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G142" t="n">
-        <v>0.47814267873764</v>
+        <v>0.478142738342285</v>
       </c>
       <c r="H142" t="n">
         <v>36816</v>
@@ -4545,7 +4545,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G144" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611572980881</v>
       </c>
       <c r="H144" t="n">
         <v>51317</v>
@@ -4574,7 +4574,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G145" t="n">
-        <v>0.467071443796158</v>
+        <v>0.467071324586868</v>
       </c>
       <c r="H145" t="n">
         <v>48503</v>
@@ -4661,7 +4661,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.477450758218765</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H148" t="n">
         <v>324437</v>
@@ -4748,7 +4748,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G151" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H151" t="n">
         <v>33263</v>
@@ -4806,7 +4806,7 @@
         <v>0.656499981880188</v>
       </c>
       <c r="G153" t="n">
-        <v>0.454270154237747</v>
+        <v>0.454270124435425</v>
       </c>
       <c r="H153" t="n">
         <v>42442</v>
@@ -4835,7 +4835,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G154" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H154" t="n">
         <v>28966</v>
@@ -4922,7 +4922,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G157" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H157" t="n">
         <v>185257</v>
@@ -5154,7 +5154,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G165" t="n">
-        <v>0.469839215278625</v>
+        <v>0.469839155673981</v>
       </c>
       <c r="H165" t="n">
         <v>29550</v>
@@ -5183,7 +5183,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G166" t="n">
-        <v>0.46914729475975</v>
+        <v>0.469147175550461</v>
       </c>
       <c r="H166" t="n">
         <v>9905</v>
@@ -5299,7 +5299,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G170" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611572980881</v>
       </c>
       <c r="H170" t="n">
         <v>58222</v>
@@ -5328,7 +5328,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G171" t="n">
-        <v>0.46914729475975</v>
+        <v>0.469147175550461</v>
       </c>
       <c r="H171" t="n">
         <v>30801</v>
@@ -5357,7 +5357,7 @@
         <v>0.679499983787537</v>
       </c>
       <c r="G172" t="n">
-        <v>0.470185190439224</v>
+        <v>0.470185160636902</v>
       </c>
       <c r="H172" t="n">
         <v>20045</v>
@@ -5386,7 +5386,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G173" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611572980881</v>
       </c>
       <c r="H173" t="n">
         <v>25441</v>
@@ -5502,7 +5502,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G177" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H177" t="n">
         <v>71591</v>
@@ -5734,7 +5734,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>0.446312576532364</v>
+        <v>0.446312636137009</v>
       </c>
       <c r="H185" t="n">
         <v>52383</v>
@@ -5763,7 +5763,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>0.446312576532364</v>
+        <v>0.446312636137009</v>
       </c>
       <c r="H186" t="n">
         <v>75110</v>
@@ -5850,7 +5850,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G189" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H189" t="n">
         <v>176240</v>
@@ -5995,7 +5995,7 @@
         <v>0.672500014305115</v>
       </c>
       <c r="G194" t="n">
-        <v>0.465341478586197</v>
+        <v>0.465341418981552</v>
       </c>
       <c r="H194" t="n">
         <v>23902</v>
@@ -6082,7 +6082,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G197" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611572980881</v>
       </c>
       <c r="H197" t="n">
         <v>99568</v>
@@ -6285,7 +6285,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>0.489213973283768</v>
+        <v>0.489214032888412</v>
       </c>
       <c r="H204" t="n">
         <v>146400</v>
@@ -6314,7 +6314,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G205" t="n">
-        <v>0.493019700050354</v>
+        <v>0.493019759654999</v>
       </c>
       <c r="H205" t="n">
         <v>36091</v>
@@ -6343,7 +6343,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>0.50305312871933</v>
+        <v>0.503053188323975</v>
       </c>
       <c r="H206" t="n">
         <v>66811</v>
@@ -6372,7 +6372,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G207" t="n">
-        <v>0.508588790893555</v>
+        <v>0.508588850498199</v>
       </c>
       <c r="H207" t="n">
         <v>181176</v>
@@ -6488,7 +6488,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G211" t="n">
-        <v>0.516892313957214</v>
+        <v>0.51689225435257</v>
       </c>
       <c r="H211" t="n">
         <v>202768</v>
@@ -6575,7 +6575,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G214" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H214" t="n">
         <v>26428</v>
@@ -6749,7 +6749,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G220" t="n">
-        <v>0.499247342348099</v>
+        <v>0.499247401952744</v>
       </c>
       <c r="H220" t="n">
         <v>33506</v>
@@ -6952,7 +6952,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G227" t="n">
-        <v>0.49405762553215</v>
+        <v>0.494057685136795</v>
       </c>
       <c r="H227" t="n">
         <v>51852</v>
@@ -6981,7 +6981,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G228" t="n">
-        <v>0.491981863975525</v>
+        <v>0.491981893777847</v>
       </c>
       <c r="H228" t="n">
         <v>257048</v>
@@ -7068,7 +7068,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G231" t="n">
-        <v>0.493019700050354</v>
+        <v>0.493019759654999</v>
       </c>
       <c r="H231" t="n">
         <v>140299</v>
@@ -7155,7 +7155,7 @@
         <v>0.706499993801117</v>
       </c>
       <c r="G234" t="n">
-        <v>0.488867968320847</v>
+        <v>0.488868027925491</v>
       </c>
       <c r="H234" t="n">
         <v>54717</v>
@@ -7184,7 +7184,7 @@
         <v>0.72350001335144</v>
       </c>
       <c r="G235" t="n">
-        <v>0.500631332397461</v>
+        <v>0.500631272792816</v>
       </c>
       <c r="H235" t="n">
         <v>46535</v>
@@ -7213,7 +7213,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G236" t="n">
-        <v>0.492673724889755</v>
+        <v>0.4926737844944</v>
       </c>
       <c r="H236" t="n">
         <v>271535</v>
@@ -7242,7 +7242,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G237" t="n">
-        <v>0.492673724889755</v>
+        <v>0.4926737844944</v>
       </c>
       <c r="H237" t="n">
         <v>16612</v>
@@ -7300,7 +7300,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G239" t="n">
-        <v>0.491981863975525</v>
+        <v>0.491981893777847</v>
       </c>
       <c r="H239" t="n">
         <v>23384</v>
@@ -7416,7 +7416,7 @@
         <v>0.731500029563904</v>
       </c>
       <c r="G243" t="n">
-        <v>0.506166994571686</v>
+        <v>0.506166934967041</v>
       </c>
       <c r="H243" t="n">
         <v>65123</v>
@@ -7532,7 +7532,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G247" t="n">
-        <v>0.516892313957214</v>
+        <v>0.51689225435257</v>
       </c>
       <c r="H247" t="n">
         <v>57020</v>
@@ -7735,7 +7735,7 @@
         <v>0.752499997615814</v>
       </c>
       <c r="G254" t="n">
-        <v>0.520698070526123</v>
+        <v>0.520698130130768</v>
       </c>
       <c r="H254" t="n">
         <v>83322</v>
@@ -7764,7 +7764,7 @@
         <v>0.75</v>
       </c>
       <c r="G255" t="n">
-        <v>0.518968164920807</v>
+        <v>0.518968224525452</v>
       </c>
       <c r="H255" t="n">
         <v>190032</v>
@@ -7822,7 +7822,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G257" t="n">
-        <v>0.520352125167847</v>
+        <v>0.520352065563202</v>
       </c>
       <c r="H257" t="n">
         <v>97060</v>
@@ -7909,7 +7909,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G260" t="n">
-        <v>0.534883201122284</v>
+        <v>0.534883141517639</v>
       </c>
       <c r="H260" t="n">
         <v>183482</v>
@@ -7967,7 +7967,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G262" t="n">
-        <v>0.543186724185944</v>
+        <v>0.543186664581299</v>
       </c>
       <c r="H262" t="n">
         <v>248719</v>
@@ -8054,7 +8054,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G265" t="n">
-        <v>0.533499300479889</v>
+        <v>0.533499360084534</v>
       </c>
       <c r="H265" t="n">
         <v>57142</v>
@@ -8141,7 +8141,7 @@
         <v>0.780499994754791</v>
       </c>
       <c r="G268" t="n">
-        <v>0.540072917938232</v>
+        <v>0.540072858333588</v>
       </c>
       <c r="H268" t="n">
         <v>230939</v>
@@ -8199,7 +8199,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G270" t="n">
-        <v>0.540418922901154</v>
+        <v>0.540418863296509</v>
       </c>
       <c r="H270" t="n">
         <v>35906</v>
@@ -8228,7 +8228,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G271" t="n">
-        <v>0.543186724185944</v>
+        <v>0.543186664581299</v>
       </c>
       <c r="H271" t="n">
         <v>288293</v>
@@ -8286,7 +8286,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G273" t="n">
-        <v>0.540418922901154</v>
+        <v>0.540418863296509</v>
       </c>
       <c r="H273" t="n">
         <v>139226</v>
@@ -8315,7 +8315,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G274" t="n">
-        <v>0.542494773864746</v>
+        <v>0.542494714260101</v>
       </c>
       <c r="H274" t="n">
         <v>94788</v>
@@ -8373,7 +8373,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G276" t="n">
-        <v>0.540418922901154</v>
+        <v>0.540418863296509</v>
       </c>
       <c r="H276" t="n">
         <v>80710</v>
@@ -8460,7 +8460,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G279" t="n">
-        <v>0.520352125167847</v>
+        <v>0.520352065563202</v>
       </c>
       <c r="H279" t="n">
         <v>87634</v>
@@ -8634,7 +8634,7 @@
         <v>0.752499997615814</v>
       </c>
       <c r="G285" t="n">
-        <v>0.520698070526123</v>
+        <v>0.520698130130768</v>
       </c>
       <c r="H285" t="n">
         <v>82797</v>
@@ -8663,7 +8663,7 @@
         <v>0.769500017166138</v>
       </c>
       <c r="G286" t="n">
-        <v>0.532461404800415</v>
+        <v>0.53246134519577</v>
       </c>
       <c r="H286" t="n">
         <v>39012</v>
@@ -8750,7 +8750,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G289" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H289" t="n">
         <v>1189431</v>
@@ -8779,7 +8779,7 @@
         <v>0.744499981403351</v>
       </c>
       <c r="G290" t="n">
-        <v>0.515162408351898</v>
+        <v>0.515162467956543</v>
       </c>
       <c r="H290" t="n">
         <v>388879</v>
@@ -8808,7 +8808,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H291" t="n">
         <v>172312</v>
@@ -8837,7 +8837,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G292" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H292" t="n">
         <v>408715</v>
@@ -8866,7 +8866,7 @@
         <v>0.740499973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>0.512394547462463</v>
+        <v>0.512394607067108</v>
       </c>
       <c r="H293" t="n">
         <v>170017</v>
@@ -8953,7 +8953,7 @@
         <v>0.740499973297119</v>
       </c>
       <c r="G296" t="n">
-        <v>0.512394547462463</v>
+        <v>0.512394607067108</v>
       </c>
       <c r="H296" t="n">
         <v>97425</v>
@@ -9040,7 +9040,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G299" t="n">
-        <v>0.524503767490387</v>
+        <v>0.524503827095032</v>
       </c>
       <c r="H299" t="n">
         <v>291053</v>
@@ -9185,7 +9185,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G304" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H304" t="n">
         <v>67866</v>
@@ -9214,7 +9214,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H305" t="n">
         <v>26613</v>
@@ -9301,7 +9301,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>0.50305312871933</v>
+        <v>0.503053188323975</v>
       </c>
       <c r="H308" t="n">
         <v>393889</v>
@@ -9330,7 +9330,7 @@
         <v>0.732500016689301</v>
       </c>
       <c r="G309" t="n">
-        <v>0.506858885288239</v>
+        <v>0.506858944892883</v>
       </c>
       <c r="H309" t="n">
         <v>354387</v>
@@ -9417,7 +9417,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G312" t="n">
-        <v>0.505474984645844</v>
+        <v>0.505475044250488</v>
       </c>
       <c r="H312" t="n">
         <v>231484</v>
@@ -9475,7 +9475,7 @@
         <v>0.737500011920929</v>
       </c>
       <c r="G314" t="n">
-        <v>0.510318696498871</v>
+        <v>0.510318756103516</v>
       </c>
       <c r="H314" t="n">
         <v>65146</v>
@@ -9504,7 +9504,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>0.506512880325317</v>
+        <v>0.506512939929962</v>
       </c>
       <c r="H315" t="n">
         <v>166630</v>
@@ -9562,7 +9562,7 @@
         <v>0.731500029563904</v>
       </c>
       <c r="G317" t="n">
-        <v>0.506166994571686</v>
+        <v>0.506166934967041</v>
       </c>
       <c r="H317" t="n">
         <v>123601</v>
@@ -9649,7 +9649,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H320" t="n">
         <v>94474</v>
@@ -9707,7 +9707,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H322" t="n">
         <v>104278</v>
@@ -9736,7 +9736,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G323" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H323" t="n">
         <v>102975</v>
@@ -9765,7 +9765,7 @@
         <v>0.737500011920929</v>
       </c>
       <c r="G324" t="n">
-        <v>0.510318696498871</v>
+        <v>0.510318756103516</v>
       </c>
       <c r="H324" t="n">
         <v>37689</v>
@@ -9794,7 +9794,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G325" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H325" t="n">
         <v>143778</v>
@@ -9823,7 +9823,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G326" t="n">
-        <v>0.508588790893555</v>
+        <v>0.508588850498199</v>
       </c>
       <c r="H326" t="n">
         <v>145557</v>
@@ -9852,7 +9852,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G327" t="n">
-        <v>0.508588790893555</v>
+        <v>0.508588850498199</v>
       </c>
       <c r="H327" t="n">
         <v>117509</v>
@@ -9910,7 +9910,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G329" t="n">
-        <v>0.505474984645844</v>
+        <v>0.505475044250488</v>
       </c>
       <c r="H329" t="n">
         <v>80896</v>
@@ -10055,7 +10055,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G334" t="n">
-        <v>0.499247342348099</v>
+        <v>0.499247401952744</v>
       </c>
       <c r="H334" t="n">
         <v>67876</v>
@@ -10084,7 +10084,7 @@
         <v>0.72350001335144</v>
       </c>
       <c r="G335" t="n">
-        <v>0.500631332397461</v>
+        <v>0.500631272792816</v>
       </c>
       <c r="H335" t="n">
         <v>111583</v>
@@ -10171,7 +10171,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H338" t="n">
         <v>513837</v>
@@ -10200,7 +10200,7 @@
         <v>0.731500029563904</v>
       </c>
       <c r="G339" t="n">
-        <v>0.506166994571686</v>
+        <v>0.506166934967041</v>
       </c>
       <c r="H339" t="n">
         <v>116264</v>
@@ -10258,7 +10258,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G341" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H341" t="n">
         <v>282369</v>
@@ -10287,7 +10287,7 @@
         <v>0.731500029563904</v>
       </c>
       <c r="G342" t="n">
-        <v>0.506166994571686</v>
+        <v>0.506166934967041</v>
       </c>
       <c r="H342" t="n">
         <v>102381</v>
@@ -10403,7 +10403,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G346" t="n">
-        <v>0.509626746177673</v>
+        <v>0.509626805782318</v>
       </c>
       <c r="H346" t="n">
         <v>103154</v>
@@ -10432,7 +10432,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G347" t="n">
-        <v>0.508588790893555</v>
+        <v>0.508588850498199</v>
       </c>
       <c r="H347" t="n">
         <v>152359</v>
@@ -10519,7 +10519,7 @@
         <v>0.762499988079071</v>
       </c>
       <c r="G350" t="n">
-        <v>0.527617692947388</v>
+        <v>0.527617633342743</v>
       </c>
       <c r="H350" t="n">
         <v>372168</v>
@@ -10577,7 +10577,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G352" t="n">
-        <v>0.512048602104187</v>
+        <v>0.512048661708832</v>
       </c>
       <c r="H352" t="n">
         <v>223896</v>
@@ -10635,7 +10635,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G354" t="n">
-        <v>0.516546308994293</v>
+        <v>0.516546249389648</v>
       </c>
       <c r="H354" t="n">
         <v>168237</v>
@@ -10664,7 +10664,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G355" t="n">
-        <v>0.509626746177673</v>
+        <v>0.509626805782318</v>
       </c>
       <c r="H355" t="n">
         <v>208331</v>
@@ -10693,7 +10693,7 @@
         <v>0.736500024795532</v>
       </c>
       <c r="G356" t="n">
-        <v>0.509626746177673</v>
+        <v>0.509626805782318</v>
       </c>
       <c r="H356" t="n">
         <v>78170</v>
@@ -10722,7 +10722,7 @@
         <v>0.743499994277954</v>
       </c>
       <c r="G357" t="n">
-        <v>0.514470398426056</v>
+        <v>0.514470338821411</v>
       </c>
       <c r="H357" t="n">
         <v>217965</v>
@@ -10780,7 +10780,7 @@
         <v>0.75</v>
       </c>
       <c r="G359" t="n">
-        <v>0.518968164920807</v>
+        <v>0.518968224525452</v>
       </c>
       <c r="H359" t="n">
         <v>262928</v>
@@ -10809,7 +10809,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G360" t="n">
-        <v>0.520352125167847</v>
+        <v>0.520352065563202</v>
       </c>
       <c r="H360" t="n">
         <v>471079</v>
@@ -10867,7 +10867,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G362" t="n">
-        <v>0.526579678058624</v>
+        <v>0.526579618453979</v>
       </c>
       <c r="H362" t="n">
         <v>397546</v>
@@ -10954,7 +10954,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>0.532807350158691</v>
+        <v>0.532807290554047</v>
       </c>
       <c r="H365" t="n">
         <v>384026</v>
@@ -10983,7 +10983,7 @@
         <v>0.771000027656555</v>
       </c>
       <c r="G366" t="n">
-        <v>0.533499300479889</v>
+        <v>0.533499360084534</v>
       </c>
       <c r="H366" t="n">
         <v>218685</v>
@@ -11012,7 +11012,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G367" t="n">
-        <v>0.553566098213196</v>
+        <v>0.553566038608551</v>
       </c>
       <c r="H367" t="n">
         <v>1324864</v>
@@ -11041,7 +11041,7 @@
         <v>0.798500001430511</v>
       </c>
       <c r="G368" t="n">
-        <v>0.552528202533722</v>
+        <v>0.552528142929077</v>
       </c>
       <c r="H368" t="n">
         <v>1262207</v>
@@ -11070,7 +11070,7 @@
         <v>0.809499979019165</v>
       </c>
       <c r="G369" t="n">
-        <v>0.56013959646225</v>
+        <v>0.560139656066895</v>
       </c>
       <c r="H369" t="n">
         <v>678004</v>
@@ -11389,7 +11389,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G380" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H380" t="n">
         <v>867530</v>
@@ -11621,7 +11621,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G388" t="n">
-        <v>0.634525060653687</v>
+        <v>0.634525120258331</v>
       </c>
       <c r="H388" t="n">
         <v>135604</v>
@@ -11650,7 +11650,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G389" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H389" t="n">
         <v>169577</v>
@@ -11737,7 +11737,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G392" t="n">
-        <v>0.638676762580872</v>
+        <v>0.638676822185516</v>
       </c>
       <c r="H392" t="n">
         <v>245408</v>
@@ -11824,7 +11824,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G395" t="n">
-        <v>0.638676762580872</v>
+        <v>0.638676822185516</v>
       </c>
       <c r="H395" t="n">
         <v>155679</v>
@@ -11940,7 +11940,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G399" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H399" t="n">
         <v>161711</v>
@@ -11969,7 +11969,7 @@
         <v>0.921000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>0.637292861938477</v>
+        <v>0.637292921543121</v>
       </c>
       <c r="H400" t="n">
         <v>173975</v>
@@ -12027,7 +12027,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G402" t="n">
-        <v>0.632449150085449</v>
+        <v>0.632449209690094</v>
       </c>
       <c r="H402" t="n">
         <v>466097</v>
@@ -12346,7 +12346,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G413" t="n">
-        <v>0.617918193340302</v>
+        <v>0.617918133735657</v>
       </c>
       <c r="H413" t="n">
         <v>39750</v>
@@ -12375,7 +12375,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G414" t="n">
-        <v>0.612036466598511</v>
+        <v>0.612036406993866</v>
       </c>
       <c r="H414" t="n">
         <v>199929</v>
@@ -12462,7 +12462,7 @@
         <v>0.892499983310699</v>
       </c>
       <c r="G417" t="n">
-        <v>0.617572128772736</v>
+        <v>0.617572069168091</v>
       </c>
       <c r="H417" t="n">
         <v>73208</v>
@@ -12723,7 +12723,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H426" t="n">
         <v>30382</v>
@@ -12752,7 +12752,7 @@
         <v>0.889500021934509</v>
       </c>
       <c r="G427" t="n">
-        <v>0.615496277809143</v>
+        <v>0.615496218204498</v>
       </c>
       <c r="H427" t="n">
         <v>51916</v>
@@ -12781,7 +12781,7 @@
         <v>0.891499996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>0.616880178451538</v>
+        <v>0.616880118846893</v>
       </c>
       <c r="H428" t="n">
         <v>79302</v>
@@ -12868,7 +12868,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G431" t="n">
-        <v>0.612036466598511</v>
+        <v>0.612036406993866</v>
       </c>
       <c r="H431" t="n">
         <v>101366</v>
@@ -12984,7 +12984,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G435" t="n">
-        <v>0.612036466598511</v>
+        <v>0.612036406993866</v>
       </c>
       <c r="H435" t="n">
         <v>112829</v>
@@ -13013,7 +13013,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H436" t="n">
         <v>192904</v>
@@ -13042,7 +13042,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H437" t="n">
         <v>185924</v>
@@ -13129,7 +13129,7 @@
         <v>0.889500021934509</v>
       </c>
       <c r="G440" t="n">
-        <v>0.615496277809143</v>
+        <v>0.615496218204498</v>
       </c>
       <c r="H440" t="n">
         <v>165779</v>
@@ -13216,7 +13216,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G443" t="n">
-        <v>0.636254906654358</v>
+        <v>0.636254966259003</v>
       </c>
       <c r="H443" t="n">
         <v>655108</v>
@@ -13245,7 +13245,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G444" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H444" t="n">
         <v>416249</v>
@@ -13332,7 +13332,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G447" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H447" t="n">
         <v>197331</v>
@@ -13361,7 +13361,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>0.636254906654358</v>
+        <v>0.636254966259003</v>
       </c>
       <c r="H448" t="n">
         <v>240947</v>
@@ -13448,7 +13448,7 @@
         <v>0.92849999666214</v>
       </c>
       <c r="G451" t="n">
-        <v>0.64248263835907</v>
+        <v>0.642482578754425</v>
       </c>
       <c r="H451" t="n">
         <v>119045</v>
@@ -13535,7 +13535,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G454" t="n">
-        <v>0.655283808708191</v>
+        <v>0.655283868312836</v>
       </c>
       <c r="H454" t="n">
         <v>300283</v>
@@ -13680,7 +13680,7 @@
         <v>1.00300002098083</v>
       </c>
       <c r="G459" t="n">
-        <v>0.694033443927765</v>
+        <v>0.69403338432312</v>
       </c>
       <c r="H459" t="n">
         <v>324236</v>
@@ -13738,7 +13738,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G461" t="n">
-        <v>0.715484201908112</v>
+        <v>0.715484142303467</v>
       </c>
       <c r="H461" t="n">
         <v>727657</v>
@@ -13767,7 +13767,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G462" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H462" t="n">
         <v>739518</v>
@@ -13796,7 +13796,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G463" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H463" t="n">
         <v>373948</v>
@@ -13883,7 +13883,7 @@
         <v>0.996500015258789</v>
       </c>
       <c r="G466" t="n">
-        <v>0.689535737037659</v>
+        <v>0.689535796642303</v>
       </c>
       <c r="H466" t="n">
         <v>381375</v>
@@ -14086,7 +14086,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G473" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H473" t="n">
         <v>79950</v>
@@ -14173,7 +14173,7 @@
         <v>0.970499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>0.671544790267944</v>
+        <v>0.671544849872589</v>
       </c>
       <c r="H476" t="n">
         <v>1137121</v>
@@ -14202,7 +14202,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G477" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H477" t="n">
         <v>169267</v>
@@ -14231,7 +14231,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H478" t="n">
         <v>300513</v>
@@ -14318,7 +14318,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G481" t="n">
-        <v>0.652169942855835</v>
+        <v>0.65217000246048</v>
       </c>
       <c r="H481" t="n">
         <v>621225</v>
@@ -14376,7 +14376,7 @@
         <v>0.930999994277954</v>
       </c>
       <c r="G483" t="n">
-        <v>0.644212484359741</v>
+        <v>0.644212543964386</v>
       </c>
       <c r="H483" t="n">
         <v>359455</v>
@@ -14405,7 +14405,7 @@
         <v>0.92849999666214</v>
       </c>
       <c r="G484" t="n">
-        <v>0.64248263835907</v>
+        <v>0.642482578754425</v>
       </c>
       <c r="H484" t="n">
         <v>191469</v>
@@ -14434,7 +14434,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G485" t="n">
-        <v>0.655283808708191</v>
+        <v>0.655283868312836</v>
       </c>
       <c r="H485" t="n">
         <v>119101</v>
@@ -14463,7 +14463,7 @@
         <v>0.947000026702881</v>
       </c>
       <c r="G486" t="n">
-        <v>0.655283808708191</v>
+        <v>0.655283868312836</v>
       </c>
       <c r="H486" t="n">
         <v>359748</v>
@@ -14579,7 +14579,7 @@
         <v>0.962999999523163</v>
       </c>
       <c r="G490" t="n">
-        <v>0.666355133056641</v>
+        <v>0.666355192661285</v>
       </c>
       <c r="H490" t="n">
         <v>229851</v>
@@ -14637,7 +14637,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>0.669122934341431</v>
+        <v>0.669122993946075</v>
       </c>
       <c r="H492" t="n">
         <v>72723</v>
@@ -14666,7 +14666,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G493" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H493" t="n">
         <v>99793</v>
@@ -14811,7 +14811,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G498" t="n">
-        <v>0.684000015258789</v>
+        <v>0.684000074863434</v>
       </c>
       <c r="H498" t="n">
         <v>105579</v>
@@ -14840,7 +14840,7 @@
         <v>0.990499973297119</v>
       </c>
       <c r="G499" t="n">
-        <v>0.685383975505829</v>
+        <v>0.685383915901184</v>
       </c>
       <c r="H499" t="n">
         <v>219371</v>
@@ -14927,7 +14927,7 @@
         <v>0.995500028133392</v>
       </c>
       <c r="G502" t="n">
-        <v>0.688843786716461</v>
+        <v>0.688843727111816</v>
       </c>
       <c r="H502" t="n">
         <v>178398</v>
@@ -15333,7 +15333,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G516" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H516" t="n">
         <v>241960</v>
@@ -15449,7 +15449,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G520" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H520" t="n">
         <v>103679</v>
@@ -15623,7 +15623,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G526" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H526" t="n">
         <v>487693</v>
@@ -15652,7 +15652,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G527" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H527" t="n">
         <v>364335</v>
@@ -15739,7 +15739,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G530" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H530" t="n">
         <v>250612</v>
@@ -15884,7 +15884,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G535" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H535" t="n">
         <v>255484</v>
@@ -16087,7 +16087,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G542" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H542" t="n">
         <v>191039</v>
@@ -16174,7 +16174,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G545" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H545" t="n">
         <v>390066</v>
@@ -16232,7 +16232,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G547" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H547" t="n">
         <v>77188</v>
@@ -16261,7 +16261,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H548" t="n">
         <v>167644</v>
@@ -16290,7 +16290,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G549" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H549" t="n">
         <v>63936</v>
@@ -16319,7 +16319,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G550" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H550" t="n">
         <v>91476</v>
@@ -16406,7 +16406,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G553" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H553" t="n">
         <v>70654</v>
@@ -16522,7 +16522,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G557" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H557" t="n">
         <v>107928</v>
@@ -16638,7 +16638,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G561" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H561" t="n">
         <v>246628</v>
@@ -16899,7 +16899,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H570" t="n">
         <v>38212</v>
@@ -16986,7 +16986,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H573" t="n">
         <v>153618</v>
@@ -17276,7 +17276,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G583" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H583" t="n">
         <v>28035</v>
@@ -17334,7 +17334,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G585" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H585" t="n">
         <v>65412</v>
@@ -17392,7 +17392,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G587" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H587" t="n">
         <v>102968</v>
@@ -17595,7 +17595,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G594" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H594" t="n">
         <v>13853</v>
@@ -17798,7 +17798,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G601" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H601" t="n">
         <v>173212</v>
@@ -17827,7 +17827,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G602" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H602" t="n">
         <v>254564</v>
@@ -17914,7 +17914,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G605" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H605" t="n">
         <v>317195</v>
@@ -18117,7 +18117,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H612" t="n">
         <v>182363</v>
@@ -18146,7 +18146,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G613" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H613" t="n">
         <v>294664</v>
@@ -18204,7 +18204,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G615" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H615" t="n">
         <v>85130</v>
@@ -18262,7 +18262,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G617" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H617" t="n">
         <v>118710</v>
@@ -18291,7 +18291,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H618" t="n">
         <v>504140</v>
@@ -18320,7 +18320,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H619" t="n">
         <v>135616</v>
@@ -18407,7 +18407,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G622" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H622" t="n">
         <v>52692</v>
@@ -18581,7 +18581,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G628" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H628" t="n">
         <v>115538</v>
@@ -18639,7 +18639,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G630" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H630" t="n">
         <v>140311</v>
@@ -18726,7 +18726,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G633" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H633" t="n">
         <v>189736</v>
@@ -18784,7 +18784,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G635" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H635" t="n">
         <v>55341</v>
@@ -18813,7 +18813,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G636" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H636" t="n">
         <v>391421</v>
@@ -18842,7 +18842,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H637" t="n">
         <v>158068</v>
@@ -18871,7 +18871,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G638" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H638" t="n">
         <v>64520</v>
@@ -18900,7 +18900,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G639" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H639" t="n">
         <v>154143</v>
@@ -18929,7 +18929,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G640" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H640" t="n">
         <v>131453</v>
@@ -19016,7 +19016,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G643" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H643" t="n">
         <v>503725</v>
@@ -19277,7 +19277,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G652" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H652" t="n">
         <v>90336</v>
@@ -19654,7 +19654,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G665" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H665" t="n">
         <v>69274</v>
@@ -19683,7 +19683,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G666" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H666" t="n">
         <v>93861</v>
@@ -19741,7 +19741,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H668" t="n">
         <v>20241</v>
@@ -19828,7 +19828,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G671" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H671" t="n">
         <v>427711</v>
@@ -20089,7 +20089,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H680" t="n">
         <v>116691</v>
@@ -20118,7 +20118,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G681" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H681" t="n">
         <v>57141</v>
@@ -20147,7 +20147,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G682" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H682" t="n">
         <v>73730</v>
@@ -20176,7 +20176,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G683" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H683" t="n">
         <v>74130</v>
@@ -20263,7 +20263,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G686" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H686" t="n">
         <v>11821</v>
@@ -20437,7 +20437,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G692" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H692" t="n">
         <v>112543</v>
@@ -20495,7 +20495,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H694" t="n">
         <v>13680</v>
@@ -20669,7 +20669,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G700" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H700" t="n">
         <v>8812</v>
@@ -20756,7 +20756,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G703" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H703" t="n">
         <v>121260</v>
@@ -20843,7 +20843,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H706" t="n">
         <v>24697</v>
@@ -20872,7 +20872,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G707" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H707" t="n">
         <v>82347</v>
@@ -20901,7 +20901,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G708" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H708" t="n">
         <v>98837</v>
@@ -21046,7 +21046,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G713" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H713" t="n">
         <v>61904</v>
@@ -21104,7 +21104,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G715" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H715" t="n">
         <v>44791</v>
@@ -21249,7 +21249,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G720" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H720" t="n">
         <v>49505</v>
@@ -21307,7 +21307,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G722" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H722" t="n">
         <v>239951</v>
@@ -21336,7 +21336,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H723" t="n">
         <v>182993</v>
@@ -21365,7 +21365,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H724" t="n">
         <v>222642</v>
@@ -21394,7 +21394,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G725" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H725" t="n">
         <v>55765</v>
@@ -21423,7 +21423,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G726" t="n">
-        <v>0.651824057102203</v>
+        <v>0.651823997497559</v>
       </c>
       <c r="H726" t="n">
         <v>222817</v>
@@ -21452,7 +21452,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H727" t="n">
         <v>57669</v>
@@ -21481,7 +21481,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G728" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H728" t="n">
         <v>78523</v>
@@ -21539,7 +21539,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G730" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H730" t="n">
         <v>80663</v>
@@ -21568,7 +21568,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G731" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H731" t="n">
         <v>57564</v>
@@ -21655,7 +21655,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G734" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H734" t="n">
         <v>53744</v>
@@ -21684,7 +21684,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G735" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H735" t="n">
         <v>46948</v>
@@ -21713,7 +21713,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G736" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H736" t="n">
         <v>54341</v>
@@ -21742,7 +21742,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G737" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H737" t="n">
         <v>5380</v>
@@ -21858,7 +21858,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G741" t="n">
-        <v>0.632449150085449</v>
+        <v>0.632449209690094</v>
       </c>
       <c r="H741" t="n">
         <v>53897</v>
@@ -21887,7 +21887,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G742" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H742" t="n">
         <v>82682</v>
@@ -21916,7 +21916,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G743" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H743" t="n">
         <v>59135</v>
@@ -22032,7 +22032,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G747" t="n">
-        <v>0.665663182735443</v>
+        <v>0.665663123130798</v>
       </c>
       <c r="H747" t="n">
         <v>246168</v>
@@ -22177,7 +22177,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H752" t="n">
         <v>388590</v>
@@ -22351,7 +22351,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G758" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H758" t="n">
         <v>103377</v>
@@ -22380,7 +22380,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G759" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H759" t="n">
         <v>92669</v>
@@ -22409,7 +22409,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G760" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H760" t="n">
         <v>174775</v>
@@ -22438,7 +22438,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G761" t="n">
-        <v>0.651824057102203</v>
+        <v>0.651823997497559</v>
       </c>
       <c r="H761" t="n">
         <v>112676</v>
@@ -22583,7 +22583,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G766" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H766" t="n">
         <v>109701</v>
@@ -22815,7 +22815,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G774" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H774" t="n">
         <v>228965</v>
@@ -22844,7 +22844,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H775" t="n">
         <v>359900</v>
@@ -22902,7 +22902,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G777" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H777" t="n">
         <v>174998</v>
@@ -22931,7 +22931,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G778" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H778" t="n">
         <v>275985</v>
@@ -23105,7 +23105,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H784" t="n">
         <v>376786</v>
@@ -23192,7 +23192,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H787" t="n">
         <v>82370</v>
@@ -23221,7 +23221,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H788" t="n">
         <v>145075</v>
@@ -23250,7 +23250,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G789" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H789" t="n">
         <v>229318</v>
@@ -23308,7 +23308,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G791" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H791" t="n">
         <v>146801</v>
@@ -23366,7 +23366,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G793" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H793" t="n">
         <v>261442</v>
@@ -23569,7 +23569,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G800" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H800" t="n">
         <v>325657</v>
@@ -23598,7 +23598,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H801" t="n">
         <v>319507</v>
@@ -23627,7 +23627,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G802" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H802" t="n">
         <v>520584</v>
@@ -23714,7 +23714,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G805" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H805" t="n">
         <v>435328</v>
@@ -23743,7 +23743,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G806" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H806" t="n">
         <v>320023</v>
@@ -23772,7 +23772,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H807" t="n">
         <v>392161</v>
@@ -23801,7 +23801,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G808" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H808" t="n">
         <v>226093</v>
@@ -23859,7 +23859,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G810" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H810" t="n">
         <v>525234</v>
@@ -24004,7 +24004,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G815" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H815" t="n">
         <v>305887</v>
@@ -24236,7 +24236,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G823" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H823" t="n">
         <v>104698</v>
@@ -24294,7 +24294,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G825" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H825" t="n">
         <v>85392</v>
@@ -24352,7 +24352,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G827" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H827" t="n">
         <v>136318</v>
@@ -24439,7 +24439,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G830" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H830" t="n">
         <v>511380</v>
@@ -24468,7 +24468,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G831" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H831" t="n">
         <v>403805</v>
@@ -24526,7 +24526,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G833" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H833" t="n">
         <v>500408</v>
@@ -25077,7 +25077,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G852" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H852" t="n">
         <v>244060</v>
@@ -25193,7 +25193,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G856" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H856" t="n">
         <v>90403</v>
@@ -25338,7 +25338,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H861" t="n">
         <v>216088</v>
@@ -25396,7 +25396,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G863" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H863" t="n">
         <v>99861</v>
@@ -25512,7 +25512,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G867" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H867" t="n">
         <v>13841</v>
@@ -25541,7 +25541,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G868" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H868" t="n">
         <v>40045</v>
@@ -25831,7 +25831,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G878" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H878" t="n">
         <v>305495</v>
@@ -25860,7 +25860,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G879" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H879" t="n">
         <v>134656</v>
@@ -25889,7 +25889,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H880" t="n">
         <v>295035</v>
@@ -25947,7 +25947,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H882" t="n">
         <v>185348</v>
@@ -25976,7 +25976,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G883" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H883" t="n">
         <v>68756</v>
@@ -26034,7 +26034,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H885" t="n">
         <v>493105</v>
@@ -26063,7 +26063,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G886" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H886" t="n">
         <v>216811</v>
@@ -26092,7 +26092,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H887" t="n">
         <v>390492</v>
@@ -26150,7 +26150,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G889" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H889" t="n">
         <v>132291</v>
@@ -26179,7 +26179,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G890" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H890" t="n">
         <v>159006</v>
@@ -26208,7 +26208,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H891" t="n">
         <v>238771</v>
@@ -26266,7 +26266,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G893" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H893" t="n">
         <v>212453</v>
@@ -26353,7 +26353,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H896" t="n">
         <v>73030</v>
@@ -26440,7 +26440,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G899" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H899" t="n">
         <v>32697</v>
@@ -26585,7 +26585,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H904" t="n">
         <v>176654</v>
@@ -26614,7 +26614,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H905" t="n">
         <v>43325</v>
@@ -26643,7 +26643,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H906" t="n">
         <v>107319</v>
@@ -26672,7 +26672,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H907" t="n">
         <v>347972</v>
@@ -26701,7 +26701,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H908" t="n">
         <v>40674</v>
@@ -26846,7 +26846,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H913" t="n">
         <v>97295</v>
@@ -26991,7 +26991,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H918" t="n">
         <v>246514</v>
@@ -27194,7 +27194,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G925" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H925" t="n">
         <v>69631</v>
@@ -27252,7 +27252,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G927" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H927" t="n">
         <v>1097</v>
@@ -27281,7 +27281,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G928" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H928" t="n">
         <v>16208</v>
@@ -27368,7 +27368,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G931" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H931" t="n">
         <v>42869</v>
@@ -27426,7 +27426,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G933" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H933" t="n">
         <v>15766</v>
@@ -27455,7 +27455,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H934" t="n">
         <v>81656</v>
@@ -27542,7 +27542,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G937" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H937" t="n">
         <v>21775</v>
@@ -27687,7 +27687,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G942" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H942" t="n">
         <v>68857</v>
@@ -28267,7 +28267,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G962" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H962" t="n">
         <v>218220</v>
@@ -28615,7 +28615,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H974" t="n">
         <v>619655</v>
@@ -28731,7 +28731,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H978" t="n">
         <v>51501</v>
@@ -28789,7 +28789,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G980" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H980" t="n">
         <v>78455</v>
@@ -28818,7 +28818,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H981" t="n">
         <v>64980</v>
@@ -28847,7 +28847,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H982" t="n">
         <v>61200</v>
@@ -28963,7 +28963,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G986" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H986" t="n">
         <v>66452</v>
@@ -28992,7 +28992,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G987" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H987" t="n">
         <v>95757</v>
@@ -29108,7 +29108,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G991" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H991" t="n">
         <v>7575</v>
@@ -29137,7 +29137,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G992" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H992" t="n">
         <v>96747</v>
@@ -29195,7 +29195,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H994" t="n">
         <v>78705</v>
@@ -29224,7 +29224,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H995" t="n">
         <v>105388</v>
@@ -29282,7 +29282,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H997" t="n">
         <v>110766</v>
@@ -29340,7 +29340,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H999" t="n">
         <v>89509</v>
@@ -29369,7 +29369,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1000" t="n">
         <v>154172</v>
@@ -29398,7 +29398,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1001" t="n">
         <v>37170</v>
@@ -29427,7 +29427,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1002" t="n">
         <v>79129</v>
@@ -29456,7 +29456,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1003" t="n">
         <v>235612</v>
@@ -29485,7 +29485,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1004" t="n">
         <v>192053</v>
@@ -29514,7 +29514,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1005" t="n">
         <v>342278</v>
@@ -29543,7 +29543,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1006" t="n">
         <v>322567</v>
@@ -29572,7 +29572,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1007" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H1007" t="n">
         <v>265431</v>
@@ -29601,7 +29601,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H1008" t="n">
         <v>278865</v>
@@ -29630,7 +29630,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1009" t="n">
         <v>174124</v>
@@ -29659,7 +29659,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1010" t="n">
         <v>113260</v>
@@ -29688,7 +29688,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1011" t="n">
         <v>387485</v>
@@ -29717,7 +29717,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1012" t="n">
         <v>249244</v>
@@ -29949,7 +29949,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1020" t="n">
         <v>109677</v>
@@ -30094,7 +30094,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1025" t="n">
         <v>210045</v>
@@ -30123,7 +30123,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1026" t="n">
         <v>199506</v>
@@ -30529,7 +30529,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H1040" t="n">
         <v>92707</v>
@@ -30558,7 +30558,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H1041" t="n">
         <v>92366</v>
@@ -30616,7 +30616,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1043" t="n">
         <v>142728</v>
@@ -30703,7 +30703,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1046" t="n">
         <v>76577</v>
@@ -30732,7 +30732,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1047" t="n">
         <v>688629</v>
@@ -30848,7 +30848,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1051" t="n">
         <v>273699</v>
@@ -30906,7 +30906,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1053" t="n">
         <v>823602</v>
@@ -30935,7 +30935,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1054" t="n">
         <v>899148</v>
@@ -31051,7 +31051,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H1058" t="n">
         <v>731628</v>
@@ -31080,7 +31080,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1059" t="n">
         <v>163770</v>
@@ -31109,7 +31109,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H1060" t="n">
         <v>145317</v>
@@ -31138,7 +31138,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H1061" t="n">
         <v>186832</v>
@@ -31167,7 +31167,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H1062" t="n">
         <v>233993</v>
@@ -31283,7 +31283,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.575708627700806</v>
+        <v>0.57570868730545</v>
       </c>
       <c r="H1066" t="n">
         <v>506587</v>
@@ -31370,7 +31370,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1069" t="n">
         <v>131300</v>
@@ -31457,7 +31457,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.624145746231079</v>
+        <v>0.624145686626434</v>
       </c>
       <c r="H1072" t="n">
         <v>187024</v>
@@ -31573,7 +31573,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1076" t="n">
         <v>34801</v>
@@ -31747,7 +31747,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1082" t="n">
         <v>86399</v>
@@ -31805,7 +31805,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1084" t="n">
         <v>166709</v>
@@ -31892,7 +31892,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1087" t="n">
         <v>113437</v>
@@ -32095,7 +32095,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1094" t="n">
         <v>39008</v>
@@ -32153,7 +32153,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1096" t="n">
         <v>78354</v>
@@ -32182,7 +32182,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1097" t="n">
         <v>284734</v>
@@ -32211,7 +32211,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.615842282772064</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1098" t="n">
         <v>28827</v>
@@ -32298,7 +32298,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.615842282772064</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1101" t="n">
         <v>10506</v>
@@ -32327,7 +32327,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1102" t="n">
         <v>14360</v>
@@ -32356,7 +32356,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.59508353471756</v>
+        <v>0.595083475112915</v>
       </c>
       <c r="H1103" t="n">
         <v>27031</v>
@@ -32443,7 +32443,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.615842282772064</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1106" t="n">
         <v>72994</v>
@@ -32559,7 +32559,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1110" t="n">
         <v>74390</v>
@@ -32704,7 +32704,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.58401221036911</v>
+        <v>0.584012150764465</v>
       </c>
       <c r="H1115" t="n">
         <v>77035</v>
@@ -32849,7 +32849,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.60200309753418</v>
+        <v>0.602003037929535</v>
       </c>
       <c r="H1120" t="n">
         <v>76838</v>
@@ -32878,7 +32878,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.60200309753418</v>
+        <v>0.602003037929535</v>
       </c>
       <c r="H1121" t="n">
         <v>115137</v>
@@ -32994,7 +32994,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.613074362277985</v>
+        <v>0.613074421882629</v>
       </c>
       <c r="H1125" t="n">
         <v>101717</v>
@@ -33226,7 +33226,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.624145746231079</v>
+        <v>0.624145686626434</v>
       </c>
       <c r="H1133" t="n">
         <v>45723</v>
@@ -33371,7 +33371,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1138" t="n">
         <v>103661</v>
@@ -33429,7 +33429,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.632449150085449</v>
+        <v>0.632449209690094</v>
       </c>
       <c r="H1140" t="n">
         <v>18998</v>
@@ -33487,7 +33487,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1142" t="n">
         <v>15327</v>
@@ -33516,7 +33516,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1143" t="n">
         <v>47967</v>
@@ -33748,7 +33748,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.651824057102203</v>
+        <v>0.651823997497559</v>
       </c>
       <c r="H1151" t="n">
         <v>98360</v>
@@ -34009,7 +34009,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H1160" t="n">
         <v>70501</v>
@@ -34154,7 +34154,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1165" t="n">
         <v>71238</v>
@@ -34241,7 +34241,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H1168" t="n">
         <v>94123</v>
@@ -34270,7 +34270,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1169" t="n">
         <v>11833</v>
@@ -34444,7 +34444,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H1175" t="n">
         <v>285</v>
@@ -34560,7 +34560,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H1179" t="n">
         <v>8541</v>
@@ -34618,7 +34618,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H1181" t="n">
         <v>3104</v>
@@ -34647,7 +34647,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1182" t="n">
         <v>33962</v>
@@ -34676,7 +34676,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1183" t="n">
         <v>35800</v>
@@ -34792,7 +34792,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1187" t="n">
         <v>19694</v>
@@ -34821,7 +34821,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1188" t="n">
         <v>5415</v>
@@ -34850,7 +34850,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1189" t="n">
         <v>120000</v>
@@ -34879,7 +34879,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1190" t="n">
         <v>19673</v>
@@ -34937,7 +34937,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1192" t="n">
         <v>71254</v>
@@ -35053,7 +35053,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1196" t="n">
         <v>159851</v>
@@ -35082,7 +35082,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.632449150085449</v>
+        <v>0.632449209690094</v>
       </c>
       <c r="H1197" t="n">
         <v>28066</v>
@@ -35169,7 +35169,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1200" t="n">
         <v>72568</v>
@@ -35198,7 +35198,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1201" t="n">
         <v>31035</v>
@@ -35227,7 +35227,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.632449150085449</v>
+        <v>0.632449209690094</v>
       </c>
       <c r="H1202" t="n">
         <v>48788</v>
@@ -35285,7 +35285,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1204" t="n">
         <v>113573</v>
@@ -35372,7 +35372,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.632449150085449</v>
+        <v>0.632449209690094</v>
       </c>
       <c r="H1207" t="n">
         <v>150568</v>
@@ -35459,7 +35459,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440096855164</v>
       </c>
       <c r="H1210" t="n">
         <v>19679</v>
@@ -35488,7 +35488,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H1211" t="n">
         <v>14578</v>
@@ -35575,7 +35575,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1214" t="n">
         <v>32776</v>
@@ -35633,7 +35633,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1216" t="n">
         <v>19052</v>
@@ -35662,7 +35662,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1217" t="n">
         <v>115503</v>
@@ -35691,7 +35691,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1218" t="n">
         <v>160496</v>
@@ -35807,7 +35807,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1222" t="n">
         <v>66195</v>
@@ -35836,7 +35836,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1223" t="n">
         <v>102090</v>
@@ -35865,7 +35865,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.624145746231079</v>
+        <v>0.624145686626434</v>
       </c>
       <c r="H1224" t="n">
         <v>18930</v>
@@ -35923,7 +35923,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1226" t="n">
         <v>40301</v>
@@ -36068,7 +36068,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1231" t="n">
         <v>14537</v>
@@ -36126,7 +36126,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1233" t="n">
         <v>55266</v>
@@ -36155,7 +36155,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.632449150085449</v>
+        <v>0.632449209690094</v>
       </c>
       <c r="H1234" t="n">
         <v>23394</v>
@@ -36213,7 +36213,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H1236" t="n">
         <v>88958</v>
@@ -36271,7 +36271,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.632449150085449</v>
+        <v>0.632449209690094</v>
       </c>
       <c r="H1238" t="n">
         <v>50909</v>
@@ -36300,7 +36300,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.636600971221924</v>
+        <v>0.636601030826569</v>
       </c>
       <c r="H1239" t="n">
         <v>43202</v>
@@ -36445,7 +36445,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653208017349243</v>
       </c>
       <c r="H1244" t="n">
         <v>67964</v>
@@ -36532,7 +36532,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H1247" t="n">
         <v>67536</v>
@@ -36561,7 +36561,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H1248" t="n">
         <v>207160</v>
@@ -36677,7 +36677,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H1252" t="n">
         <v>75238</v>
@@ -36735,7 +36735,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H1254" t="n">
         <v>248043</v>
@@ -36880,7 +36880,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H1259" t="n">
         <v>104468</v>
@@ -37286,7 +37286,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.716175973415375</v>
+        <v>0.71617603302002</v>
       </c>
       <c r="H1273" t="n">
         <v>175476</v>
@@ -37344,7 +37344,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H1275" t="n">
         <v>158669</v>
@@ -37373,7 +37373,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1276" t="n">
         <v>52660</v>
@@ -37402,7 +37402,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H1277" t="n">
         <v>73745</v>
@@ -37431,7 +37431,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H1278" t="n">
         <v>61686</v>
@@ -37489,7 +37489,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.736934840679169</v>
+        <v>0.736934900283813</v>
       </c>
       <c r="H1280" t="n">
         <v>62148</v>
@@ -37605,7 +37605,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.736934840679169</v>
+        <v>0.736934900283813</v>
       </c>
       <c r="H1284" t="n">
         <v>76794</v>
@@ -37663,7 +37663,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635844230652</v>
       </c>
       <c r="H1286" t="n">
         <v>131829</v>
@@ -37692,7 +37692,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1287" t="n">
         <v>170197</v>
@@ -37721,7 +37721,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1288" t="n">
         <v>84581</v>
@@ -37750,7 +37750,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1289" t="n">
         <v>98666</v>
@@ -37779,7 +37779,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H1290" t="n">
         <v>34774</v>
@@ -37808,7 +37808,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.726555407047272</v>
+        <v>0.726555466651917</v>
       </c>
       <c r="H1291" t="n">
         <v>45413</v>
@@ -37982,7 +37982,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.747314274311066</v>
+        <v>0.747314155101776</v>
       </c>
       <c r="H1297" t="n">
         <v>123714</v>
@@ -38098,7 +38098,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1301" t="n">
         <v>103262</v>
@@ -38127,7 +38127,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1302" t="n">
         <v>109329</v>
@@ -38156,7 +38156,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1303" t="n">
         <v>65645</v>
@@ -38272,7 +38272,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.764613151550293</v>
+        <v>0.764613091945648</v>
       </c>
       <c r="H1307" t="n">
         <v>170070</v>
@@ -38330,7 +38330,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1309" t="n">
         <v>105632</v>
@@ -38359,7 +38359,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.747314274311066</v>
+        <v>0.747314155101776</v>
       </c>
       <c r="H1310" t="n">
         <v>131076</v>
@@ -38417,7 +38417,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1312" t="n">
         <v>86822</v>
@@ -38446,7 +38446,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.764613151550293</v>
+        <v>0.764613091945648</v>
       </c>
       <c r="H1313" t="n">
         <v>260385</v>
@@ -38475,7 +38475,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1314" t="n">
         <v>60881</v>
@@ -38504,7 +38504,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.747314274311066</v>
+        <v>0.747314155101776</v>
       </c>
       <c r="H1315" t="n">
         <v>51899</v>
@@ -38562,7 +38562,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1317" t="n">
         <v>128521</v>
@@ -38591,7 +38591,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1318" t="n">
         <v>48205</v>
@@ -38620,7 +38620,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1319" t="n">
         <v>83726</v>
@@ -38823,7 +38823,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.747314274311066</v>
+        <v>0.747314155101776</v>
       </c>
       <c r="H1326" t="n">
         <v>102293</v>
@@ -39113,7 +39113,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1336" t="n">
         <v>533202</v>
@@ -39142,7 +39142,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1337" t="n">
         <v>116215</v>
@@ -39171,7 +39171,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693469524384</v>
       </c>
       <c r="H1338" t="n">
         <v>187114</v>
@@ -39200,7 +39200,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.764613151550293</v>
+        <v>0.764613091945648</v>
       </c>
       <c r="H1339" t="n">
         <v>149115</v>
@@ -39374,7 +39374,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1345" t="n">
         <v>537402</v>
@@ -39403,7 +39403,7 @@
         <v>1.125</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.778452217578888</v>
+        <v>0.778452277183533</v>
       </c>
       <c r="H1346" t="n">
         <v>130572</v>
@@ -39490,7 +39490,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.771532714366913</v>
+        <v>0.771532654762268</v>
       </c>
       <c r="H1349" t="n">
         <v>202221</v>
@@ -39519,7 +39519,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1350" t="n">
         <v>305250</v>
@@ -39548,7 +39548,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1351" t="n">
         <v>45974</v>
@@ -39577,7 +39577,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1352" t="n">
         <v>26682</v>
@@ -39606,7 +39606,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1353" t="n">
         <v>91577</v>
@@ -39635,7 +39635,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.785371780395508</v>
+        <v>0.785371840000153</v>
       </c>
       <c r="H1354" t="n">
         <v>55193</v>
@@ -39664,7 +39664,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1355" t="n">
         <v>288218</v>
@@ -39693,7 +39693,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1356" t="n">
         <v>17024</v>
@@ -39809,7 +39809,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.806130588054657</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1360" t="n">
         <v>83021</v>
@@ -39983,7 +39983,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1366" t="n">
         <v>281388</v>
@@ -40012,7 +40012,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1367" t="n">
         <v>273985</v>
@@ -40128,7 +40128,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1371" t="n">
         <v>153196</v>
@@ -40215,7 +40215,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1374" t="n">
         <v>90444</v>
@@ -40244,7 +40244,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1375" t="n">
         <v>86876</v>
@@ -40273,7 +40273,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1376" t="n">
         <v>14034</v>
@@ -40302,7 +40302,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1377" t="n">
         <v>27809</v>
@@ -40331,7 +40331,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1378" t="n">
         <v>65291</v>
@@ -40360,7 +40360,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1379" t="n">
         <v>147569</v>
@@ -40389,7 +40389,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1380" t="n">
         <v>84546</v>
@@ -40447,7 +40447,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1382" t="n">
         <v>175384</v>
@@ -40505,7 +40505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1384" t="n">
         <v>90158</v>
@@ -40679,7 +40679,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.806130588054657</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1390" t="n">
         <v>192841</v>
@@ -40766,7 +40766,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.79575115442276</v>
+        <v>0.79575127363205</v>
       </c>
       <c r="H1393" t="n">
         <v>200154</v>
@@ -40940,7 +40940,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.806130588054657</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1399" t="n">
         <v>470494</v>
@@ -40998,7 +40998,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.806130588054657</v>
+        <v>0.806130528450012</v>
       </c>
       <c r="H1401" t="n">
         <v>120762</v>
@@ -41085,7 +41085,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1404" t="n">
         <v>451788</v>
@@ -41288,7 +41288,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1411" t="n">
         <v>52154</v>
@@ -41317,7 +41317,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1412" t="n">
         <v>218373</v>
@@ -41346,7 +41346,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1413" t="n">
         <v>583052</v>
@@ -41375,7 +41375,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1414" t="n">
         <v>94810</v>
@@ -41404,7 +41404,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1415" t="n">
         <v>926778</v>
@@ -41433,7 +41433,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1416" t="n">
         <v>335083</v>
@@ -41491,7 +41491,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1418" t="n">
         <v>281905</v>
@@ -41520,7 +41520,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1419" t="n">
         <v>190170</v>
@@ -41549,7 +41549,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1420" t="n">
         <v>114650</v>
@@ -41578,7 +41578,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1421" t="n">
         <v>66926</v>
@@ -41607,7 +41607,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1422" t="n">
         <v>148582</v>
@@ -41636,7 +41636,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1423" t="n">
         <v>274643</v>
@@ -41665,7 +41665,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1424" t="n">
         <v>138269</v>
@@ -41694,7 +41694,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1425" t="n">
         <v>60081</v>
@@ -41723,7 +41723,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1426" t="n">
         <v>92896</v>
@@ -41752,7 +41752,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1427" t="n">
         <v>69676</v>
@@ -41781,7 +41781,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1428" t="n">
         <v>27419</v>
@@ -41810,7 +41810,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1429" t="n">
         <v>16294</v>
@@ -41897,7 +41897,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1432" t="n">
         <v>116624</v>
@@ -41955,7 +41955,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1434" t="n">
         <v>58038</v>
@@ -41984,7 +41984,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1435" t="n">
         <v>70728</v>
@@ -42013,7 +42013,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1436" t="n">
         <v>122837</v>
@@ -42042,7 +42042,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1437" t="n">
         <v>181025</v>
@@ -42071,7 +42071,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1438" t="n">
         <v>31317</v>
@@ -42158,7 +42158,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429465293884</v>
       </c>
       <c r="H1441" t="n">
         <v>332446</v>
@@ -42216,7 +42216,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.847648024559021</v>
+        <v>0.847647964954376</v>
       </c>
       <c r="H1443" t="n">
         <v>259888</v>
@@ -42274,7 +42274,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.851107895374298</v>
+        <v>0.851107835769653</v>
       </c>
       <c r="H1445" t="n">
         <v>242876</v>
@@ -42303,7 +42303,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.840728461742401</v>
+        <v>0.840728521347046</v>
       </c>
       <c r="H1446" t="n">
         <v>397157</v>
@@ -42361,7 +42361,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.840728461742401</v>
+        <v>0.840728521347046</v>
       </c>
       <c r="H1448" t="n">
         <v>523781</v>
@@ -42390,7 +42390,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.840728461742401</v>
+        <v>0.840728521347046</v>
       </c>
       <c r="H1449" t="n">
         <v>417288</v>
@@ -42419,7 +42419,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.840728461742401</v>
+        <v>0.840728521347046</v>
       </c>
       <c r="H1450" t="n">
         <v>171713</v>
@@ -42448,7 +42448,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.833808958530426</v>
+        <v>0.833808898925781</v>
       </c>
       <c r="H1451" t="n">
         <v>28378</v>
@@ -42477,7 +42477,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.833808958530426</v>
+        <v>0.833808898925781</v>
       </c>
       <c r="H1452" t="n">
         <v>824448</v>
@@ -42535,7 +42535,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.833808958530426</v>
+        <v>0.833808898925781</v>
       </c>
       <c r="H1454" t="n">
         <v>320343</v>
@@ -42593,7 +42593,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.858027338981628</v>
+        <v>0.858027398586273</v>
       </c>
       <c r="H1456" t="n">
         <v>272511</v>
@@ -42622,7 +42622,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.878786087036133</v>
+        <v>0.878786146640778</v>
       </c>
       <c r="H1457" t="n">
         <v>357522</v>
@@ -42767,7 +42767,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.916843891143799</v>
+        <v>0.916843831539154</v>
       </c>
       <c r="H1462" t="n">
         <v>386374</v>
@@ -42796,7 +42796,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.906464397907257</v>
+        <v>0.906464278697968</v>
       </c>
       <c r="H1463" t="n">
         <v>657445</v>
@@ -42825,7 +42825,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.916843891143799</v>
+        <v>0.916843831539154</v>
       </c>
       <c r="H1464" t="n">
         <v>148638</v>
@@ -42854,7 +42854,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.927223265171051</v>
+        <v>0.927223145961761</v>
       </c>
       <c r="H1465" t="n">
         <v>86673</v>
@@ -42912,7 +42912,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522082805634</v>
       </c>
       <c r="H1467" t="n">
         <v>688381</v>
@@ -42941,7 +42941,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522082805634</v>
       </c>
       <c r="H1468" t="n">
         <v>303974</v>
@@ -42999,7 +42999,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522082805634</v>
       </c>
       <c r="H1470" t="n">
         <v>44738</v>
@@ -43028,7 +43028,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522082805634</v>
       </c>
       <c r="H1471" t="n">
         <v>189714</v>
@@ -43057,7 +43057,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.947981894016266</v>
+        <v>0.947981774806976</v>
       </c>
       <c r="H1472" t="n">
         <v>69196</v>
@@ -43086,7 +43086,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522082805634</v>
       </c>
       <c r="H1473" t="n">
         <v>94486</v>
@@ -43173,7 +43173,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.958361327648163</v>
+        <v>0.958361208438873</v>
       </c>
       <c r="H1476" t="n">
         <v>431293</v>
@@ -43202,7 +43202,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.947981894016266</v>
+        <v>0.947981774806976</v>
       </c>
       <c r="H1477" t="n">
         <v>106073</v>
@@ -43347,7 +43347,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.958361327648163</v>
+        <v>0.958361208438873</v>
       </c>
       <c r="H1482" t="n">
         <v>159538</v>
@@ -43376,7 +43376,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.968740522861481</v>
+        <v>0.96874064207077</v>
       </c>
       <c r="H1483" t="n">
         <v>274130</v>
@@ -43434,7 +43434,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.992959022521973</v>
+        <v>0.992959141731262</v>
       </c>
       <c r="H1485" t="n">
         <v>160211</v>
@@ -43521,7 +43521,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.992959022521973</v>
+        <v>0.992959141731262</v>
       </c>
       <c r="H1488" t="n">
         <v>196578</v>
@@ -43637,7 +43637,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.992959022521973</v>
+        <v>0.992959141731262</v>
       </c>
       <c r="H1492" t="n">
         <v>57450</v>
@@ -43666,7 +43666,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.986039400100708</v>
+        <v>0.986039519309998</v>
       </c>
       <c r="H1493" t="n">
         <v>139022</v>
@@ -43695,7 +43695,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.986039400100708</v>
+        <v>0.986039519309998</v>
       </c>
       <c r="H1494" t="n">
         <v>79009</v>
@@ -43811,7 +43811,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.934142887592316</v>
+        <v>0.934142649173737</v>
       </c>
       <c r="H1498" t="n">
         <v>381079</v>
@@ -43840,7 +43840,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.934142887592316</v>
+        <v>0.934142649173737</v>
       </c>
       <c r="H1499" t="n">
         <v>103523</v>
@@ -43898,7 +43898,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.934142887592316</v>
+        <v>0.934142649173737</v>
       </c>
       <c r="H1501" t="n">
         <v>135609</v>
@@ -43956,7 +43956,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.927223265171051</v>
+        <v>0.927223145961761</v>
       </c>
       <c r="H1503" t="n">
         <v>329891</v>
@@ -43985,7 +43985,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.934142887592316</v>
+        <v>0.934142649173737</v>
       </c>
       <c r="H1504" t="n">
         <v>203683</v>
@@ -44014,7 +44014,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522082805634</v>
       </c>
       <c r="H1505" t="n">
         <v>156551</v>
@@ -44072,7 +44072,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.968740522861481</v>
+        <v>0.96874064207077</v>
       </c>
       <c r="H1507" t="n">
         <v>253006</v>
@@ -44188,7 +44188,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.02063739299774</v>
+        <v>1.02063751220703</v>
       </c>
       <c r="H1511" t="n">
         <v>206402</v>
@@ -44275,7 +44275,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.01371777057648</v>
+        <v>1.01371788978577</v>
       </c>
       <c r="H1514" t="n">
         <v>249496</v>
@@ -44333,7 +44333,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.01371777057648</v>
+        <v>1.01371788978577</v>
       </c>
       <c r="H1516" t="n">
         <v>437735</v>
@@ -44478,7 +44478,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.01717758178711</v>
+        <v>1.0171777009964</v>
       </c>
       <c r="H1521" t="n">
         <v>273665</v>
@@ -44507,7 +44507,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.01371777057648</v>
+        <v>1.01371788978577</v>
       </c>
       <c r="H1522" t="n">
         <v>189922</v>
@@ -44536,7 +44536,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.01371777057648</v>
+        <v>1.01371788978577</v>
       </c>
       <c r="H1523" t="n">
         <v>391063</v>
@@ -44623,7 +44623,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.02409720420837</v>
+        <v>1.02409732341766</v>
       </c>
       <c r="H1526" t="n">
         <v>191478</v>
@@ -44652,7 +44652,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.06561470031738</v>
+        <v>1.06561458110809</v>
       </c>
       <c r="H1527" t="n">
         <v>782238</v>
@@ -44681,7 +44681,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.09675276279449</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1528" t="n">
         <v>621472</v>
@@ -44710,7 +44710,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.11751139163971</v>
+        <v>1.117511510849</v>
       </c>
       <c r="H1529" t="n">
         <v>421145</v>
@@ -44739,7 +44739,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.10367238521576</v>
+        <v>1.10367226600647</v>
       </c>
       <c r="H1530" t="n">
         <v>492140</v>
@@ -44797,7 +44797,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.09675276279449</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1532" t="n">
         <v>258600</v>
@@ -44942,7 +44942,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.08637344837189</v>
+        <v>1.0863733291626</v>
       </c>
       <c r="H1537" t="n">
         <v>221691</v>
@@ -45000,7 +45000,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.07599401473999</v>
+        <v>1.0759938955307</v>
       </c>
       <c r="H1539" t="n">
         <v>191861</v>
@@ -45058,7 +45058,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.07253420352936</v>
+        <v>1.07253408432007</v>
       </c>
       <c r="H1541" t="n">
         <v>86791</v>
@@ -45087,7 +45087,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.04139614105225</v>
+        <v>1.04139626026154</v>
       </c>
       <c r="H1542" t="n">
         <v>266855</v>
@@ -45116,7 +45116,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.04139614105225</v>
+        <v>1.04139626026154</v>
       </c>
       <c r="H1543" t="n">
         <v>262904</v>
@@ -45203,7 +45203,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.05523538589478</v>
+        <v>1.05523526668549</v>
       </c>
       <c r="H1546" t="n">
         <v>96630</v>
@@ -45232,7 +45232,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.07599401473999</v>
+        <v>1.0759938955307</v>
       </c>
       <c r="H1547" t="n">
         <v>82571</v>
@@ -45290,7 +45290,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.07599401473999</v>
+        <v>1.0759938955307</v>
       </c>
       <c r="H1549" t="n">
         <v>67697</v>
@@ -45348,7 +45348,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.06561470031738</v>
+        <v>1.06561458110809</v>
       </c>
       <c r="H1551" t="n">
         <v>94039</v>
@@ -45406,7 +45406,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.06561470031738</v>
+        <v>1.06561458110809</v>
       </c>
       <c r="H1553" t="n">
         <v>102708</v>
@@ -45435,7 +45435,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.08637344837189</v>
+        <v>1.0863733291626</v>
       </c>
       <c r="H1554" t="n">
         <v>303086</v>
@@ -45464,7 +45464,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.08637344837189</v>
+        <v>1.0863733291626</v>
       </c>
       <c r="H1555" t="n">
         <v>69264</v>
@@ -45580,7 +45580,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.07253420352936</v>
+        <v>1.07253408432007</v>
       </c>
       <c r="H1559" t="n">
         <v>246820</v>
@@ -45609,7 +45609,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.11751139163971</v>
+        <v>1.117511510849</v>
       </c>
       <c r="H1560" t="n">
         <v>2403157</v>
@@ -45638,7 +45638,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.15556907653809</v>
+        <v>1.15556919574738</v>
       </c>
       <c r="H1561" t="n">
         <v>1133616</v>
@@ -45696,7 +45696,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.20746600627899</v>
+        <v>1.2074658870697</v>
       </c>
       <c r="H1563" t="n">
         <v>736263</v>
@@ -45754,7 +45754,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.15556907653809</v>
+        <v>1.15556919574738</v>
       </c>
       <c r="H1565" t="n">
         <v>1454929</v>
@@ -45812,7 +45812,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1567" t="n">
         <v>415789</v>
@@ -45928,7 +45928,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.06561470031738</v>
+        <v>1.06561458110809</v>
       </c>
       <c r="H1571" t="n">
         <v>1174698</v>
@@ -45957,7 +45957,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.04139614105225</v>
+        <v>1.04139626026154</v>
       </c>
       <c r="H1572" t="n">
         <v>825976</v>
@@ -45986,7 +45986,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.07599401473999</v>
+        <v>1.0759938955307</v>
       </c>
       <c r="H1573" t="n">
         <v>637653</v>
@@ -46015,7 +46015,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.10713219642639</v>
+        <v>1.1071320772171</v>
       </c>
       <c r="H1574" t="n">
         <v>554844</v>
@@ -46044,7 +46044,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.08637344837189</v>
+        <v>1.0863733291626</v>
       </c>
       <c r="H1575" t="n">
         <v>271001</v>
@@ -46073,7 +46073,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.07253420352936</v>
+        <v>1.07253408432007</v>
       </c>
       <c r="H1576" t="n">
         <v>534202</v>
@@ -46131,7 +46131,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.09675276279449</v>
+        <v>1.09675264358521</v>
       </c>
       <c r="H1578" t="n">
         <v>231555</v>
@@ -46160,7 +46160,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.12789070606232</v>
+        <v>1.12789082527161</v>
       </c>
       <c r="H1579" t="n">
         <v>463327</v>
@@ -46189,7 +46189,7 @@
         <v>1.625</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.12443101406097</v>
+        <v>1.12443113327026</v>
       </c>
       <c r="H1580" t="n">
         <v>317784</v>
@@ -46247,7 +46247,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.16248857975006</v>
+        <v>1.16248869895935</v>
       </c>
       <c r="H1582" t="n">
         <v>806481</v>
@@ -46276,7 +46276,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.19362676143646</v>
+        <v>1.19362688064575</v>
       </c>
       <c r="H1583" t="n">
         <v>615283</v>
@@ -46305,7 +46305,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1584" t="n">
         <v>312880</v>
@@ -46334,7 +46334,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.19362676143646</v>
+        <v>1.19362688064575</v>
       </c>
       <c r="H1585" t="n">
         <v>429004</v>
@@ -46421,7 +46421,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.23168456554413</v>
+        <v>1.23168444633484</v>
       </c>
       <c r="H1588" t="n">
         <v>827658</v>
@@ -46450,7 +46450,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.26282262802124</v>
+        <v>1.26282274723053</v>
       </c>
       <c r="H1589" t="n">
         <v>1153238</v>
@@ -46479,7 +46479,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.23514425754547</v>
+        <v>1.23514413833618</v>
       </c>
       <c r="H1590" t="n">
         <v>731114</v>
@@ -46566,7 +46566,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.2386040687561</v>
+        <v>1.23860394954681</v>
       </c>
       <c r="H1593" t="n">
         <v>563589</v>
@@ -46769,7 +46769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1600" t="n">
         <v>1485021</v>
@@ -46798,7 +46798,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.19016706943512</v>
+        <v>1.19016695022583</v>
       </c>
       <c r="H1601" t="n">
         <v>890205</v>
@@ -46856,7 +46856,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1603" t="n">
         <v>2203239</v>
@@ -46943,7 +46943,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.1846410036087</v>
+        <v>1.18464112281799</v>
       </c>
       <c r="H1606" t="n">
         <v>1073830</v>
@@ -47030,7 +47030,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1609" t="n">
         <v>1151534</v>
@@ -47059,7 +47059,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1610" t="n">
         <v>1024808</v>
@@ -47088,7 +47088,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.15970134735107</v>
+        <v>1.15970122814178</v>
       </c>
       <c r="H1611" t="n">
         <v>880818</v>
@@ -47175,7 +47175,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.04747211933136</v>
+        <v>1.04747200012207</v>
       </c>
       <c r="H1614" t="n">
         <v>585100</v>
@@ -47204,7 +47204,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.997592568397522</v>
+        <v>0.997592508792877</v>
       </c>
       <c r="H1615" t="n">
         <v>788688</v>
@@ -47494,7 +47494,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1625" t="n">
-        <v>1.08072531223297</v>
+        <v>1.08072519302368</v>
       </c>
       <c r="H1625" t="n">
         <v>1282662</v>
@@ -47784,7 +47784,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.10566508769989</v>
+        <v>1.10566520690918</v>
       </c>
       <c r="H1635" t="n">
         <v>120589</v>
@@ -47900,7 +47900,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1639" t="n">
-        <v>1.08072531223297</v>
+        <v>1.08072519302368</v>
       </c>
       <c r="H1639" t="n">
         <v>342678</v>
@@ -48074,7 +48074,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.0350022315979</v>
+        <v>1.03500235080719</v>
       </c>
       <c r="H1645" t="n">
         <v>106771</v>
@@ -48161,7 +48161,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.00174915790558</v>
+        <v>1.00174927711487</v>
       </c>
       <c r="H1648" t="n">
         <v>200636</v>
@@ -48306,7 +48306,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.0350022315979</v>
+        <v>1.03500235080719</v>
       </c>
       <c r="H1653" t="n">
         <v>492971</v>
@@ -48335,7 +48335,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.0350022315979</v>
+        <v>1.03500235080719</v>
       </c>
       <c r="H1654" t="n">
         <v>68321</v>
@@ -48364,7 +48364,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.0350022315979</v>
+        <v>1.03500235080719</v>
       </c>
       <c r="H1655" t="n">
         <v>361899</v>
@@ -48393,7 +48393,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.997592568397522</v>
+        <v>0.997592508792877</v>
       </c>
       <c r="H1656" t="n">
         <v>103901</v>
@@ -48422,7 +48422,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.997592568397522</v>
+        <v>0.997592508792877</v>
       </c>
       <c r="H1657" t="n">
         <v>64763</v>
@@ -48567,7 +48567,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.997592568397522</v>
+        <v>0.997592508792877</v>
       </c>
       <c r="H1662" t="n">
         <v>220673</v>
@@ -48596,7 +48596,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.97680938243866</v>
+        <v>0.97680926322937</v>
       </c>
       <c r="H1663" t="n">
         <v>122248</v>
@@ -48625,7 +48625,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.989279329776764</v>
+        <v>0.989279210567474</v>
       </c>
       <c r="H1664" t="n">
         <v>43785</v>
@@ -48654,7 +48654,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.00174915790558</v>
+        <v>1.00174927711487</v>
       </c>
       <c r="H1665" t="n">
         <v>15682</v>
@@ -48683,7 +48683,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.04747211933136</v>
+        <v>1.04747200012207</v>
       </c>
       <c r="H1666" t="n">
         <v>210117</v>
@@ -48712,7 +48712,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.08072531223297</v>
+        <v>1.08072519302368</v>
       </c>
       <c r="H1667" t="n">
         <v>542634</v>
@@ -48741,7 +48741,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.08072531223297</v>
+        <v>1.08072519302368</v>
       </c>
       <c r="H1668" t="n">
         <v>122888</v>
@@ -48828,7 +48828,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1671" t="n">
-        <v>1.08072531223297</v>
+        <v>1.08072519302368</v>
       </c>
       <c r="H1671" t="n">
         <v>36677</v>
@@ -49147,7 +49147,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1682" t="n">
         <v>95817</v>
@@ -49205,7 +49205,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.16385793685913</v>
+        <v>1.16385805606842</v>
       </c>
       <c r="H1684" t="n">
         <v>77385</v>
@@ -49263,7 +49263,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.15970134735107</v>
+        <v>1.15970122814178</v>
       </c>
       <c r="H1686" t="n">
         <v>115592</v>
@@ -49640,7 +49640,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.04747211933136</v>
+        <v>1.04747200012207</v>
       </c>
       <c r="H1699" t="n">
         <v>98786</v>
@@ -49669,7 +49669,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.05162870883942</v>
+        <v>1.05162882804871</v>
       </c>
       <c r="H1700" t="n">
         <v>107236</v>
@@ -49785,7 +49785,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1704" t="n">
-        <v>1.08072531223297</v>
+        <v>1.08072519302368</v>
       </c>
       <c r="H1704" t="n">
         <v>36321</v>
@@ -49872,7 +49872,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.08072531223297</v>
+        <v>1.08072519302368</v>
       </c>
       <c r="H1707" t="n">
         <v>60898</v>
@@ -49901,7 +49901,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.04747211933136</v>
+        <v>1.04747200012207</v>
       </c>
       <c r="H1708" t="n">
         <v>822226</v>
@@ -50017,7 +50017,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.05162870883942</v>
+        <v>1.05162882804871</v>
       </c>
       <c r="H1712" t="n">
         <v>160506</v>
@@ -50133,7 +50133,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.05162870883942</v>
+        <v>1.05162882804871</v>
       </c>
       <c r="H1716" t="n">
         <v>45929</v>
@@ -50249,7 +50249,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1720" t="n">
-        <v>1.0350022315979</v>
+        <v>1.03500235080719</v>
       </c>
       <c r="H1720" t="n">
         <v>92429</v>
@@ -50278,7 +50278,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G1721" t="n">
-        <v>1.0350022315979</v>
+        <v>1.03500235080719</v>
       </c>
       <c r="H1721" t="n">
         <v>44408</v>
@@ -50626,7 +50626,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.08072531223297</v>
+        <v>1.08072519302368</v>
       </c>
       <c r="H1733" t="n">
         <v>35723</v>
@@ -50800,7 +50800,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.15138804912567</v>
+        <v>1.15138792991638</v>
       </c>
       <c r="H1739" t="n">
         <v>22397</v>
@@ -50829,7 +50829,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.15970134735107</v>
+        <v>1.15970122814178</v>
       </c>
       <c r="H1740" t="n">
         <v>144391</v>
@@ -50858,7 +50858,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.15554463863373</v>
+        <v>1.15554475784302</v>
       </c>
       <c r="H1741" t="n">
         <v>35424</v>
@@ -50974,7 +50974,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.15138804912567</v>
+        <v>1.15138792991638</v>
       </c>
       <c r="H1745" t="n">
         <v>102412</v>
@@ -51032,7 +51032,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.15970134735107</v>
+        <v>1.15970122814178</v>
       </c>
       <c r="H1747" t="n">
         <v>176848</v>
@@ -51090,7 +51090,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1749" t="n">
         <v>169055</v>
@@ -51322,7 +51322,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1757" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1757" t="n">
         <v>136128</v>
@@ -51351,7 +51351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1758" t="n">
         <v>82692</v>
@@ -51380,7 +51380,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.16385793685913</v>
+        <v>1.16385805606842</v>
       </c>
       <c r="H1759" t="n">
         <v>122591</v>
@@ -51409,7 +51409,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1760" t="n">
         <v>60135</v>
@@ -51467,7 +51467,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1762" t="n">
         <v>31346</v>
@@ -51496,7 +51496,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1763" t="n">
         <v>173734</v>
@@ -51525,7 +51525,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1764" t="n">
         <v>134687</v>
@@ -51554,7 +51554,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1765" t="n">
         <v>107827</v>
@@ -51583,7 +51583,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1766" t="n">
         <v>36572</v>
@@ -51612,7 +51612,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1767" t="n">
         <v>3264</v>
@@ -51641,7 +51641,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1768" t="n">
         <v>10397</v>
@@ -51728,7 +51728,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.1846410036087</v>
+        <v>1.18464112281799</v>
       </c>
       <c r="H1771" t="n">
         <v>33201</v>
@@ -51757,7 +51757,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.16385793685913</v>
+        <v>1.16385805606842</v>
       </c>
       <c r="H1772" t="n">
         <v>87953</v>
@@ -51815,7 +51815,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.15554463863373</v>
+        <v>1.15554475784302</v>
       </c>
       <c r="H1774" t="n">
         <v>91471</v>
@@ -51844,7 +51844,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.16385793685913</v>
+        <v>1.16385805606842</v>
       </c>
       <c r="H1775" t="n">
         <v>50064</v>
@@ -51873,7 +51873,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.15970134735107</v>
+        <v>1.15970122814178</v>
       </c>
       <c r="H1776" t="n">
         <v>221706</v>
@@ -52105,7 +52105,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1784" t="n">
-        <v>1.15554463863373</v>
+        <v>1.15554475784302</v>
       </c>
       <c r="H1784" t="n">
         <v>139863</v>
@@ -52134,7 +52134,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1785" t="n">
         <v>598110</v>
@@ -52163,7 +52163,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1786" t="n">
         <v>323070</v>
@@ -52337,7 +52337,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.22620749473572</v>
+        <v>1.22620761394501</v>
       </c>
       <c r="H1792" t="n">
         <v>300696</v>
@@ -52366,7 +52366,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.23452067375183</v>
+        <v>1.23452079296112</v>
       </c>
       <c r="H1793" t="n">
         <v>551408</v>
@@ -52395,7 +52395,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.23867750167847</v>
+        <v>1.23867738246918</v>
       </c>
       <c r="H1794" t="n">
         <v>153832</v>
@@ -52453,7 +52453,7 @@
         <v>1.5</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.24699068069458</v>
+        <v>1.24699079990387</v>
       </c>
       <c r="H1796" t="n">
         <v>298792</v>
@@ -52511,7 +52511,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.26361703872681</v>
+        <v>1.2636171579361</v>
       </c>
       <c r="H1798" t="n">
         <v>366320</v>
@@ -52627,7 +52627,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.31349682807922</v>
+        <v>1.31349694728851</v>
       </c>
       <c r="H1802" t="n">
         <v>618746</v>
@@ -52656,7 +52656,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.30934023857117</v>
+        <v>1.30934011936188</v>
       </c>
       <c r="H1803" t="n">
         <v>410158</v>
@@ -52685,7 +52685,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.31349682807922</v>
+        <v>1.31349694728851</v>
       </c>
       <c r="H1804" t="n">
         <v>247156</v>
@@ -52714,7 +52714,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.30934023857117</v>
+        <v>1.30934011936188</v>
       </c>
       <c r="H1805" t="n">
         <v>191857</v>
@@ -52743,7 +52743,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.30102705955505</v>
+        <v>1.30102694034576</v>
       </c>
       <c r="H1806" t="n">
         <v>313388</v>
@@ -52772,7 +52772,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.30102705955505</v>
+        <v>1.30102694034576</v>
       </c>
       <c r="H1807" t="n">
         <v>383037</v>
@@ -52801,7 +52801,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.29687023162842</v>
+        <v>1.29687035083771</v>
       </c>
       <c r="H1808" t="n">
         <v>267861</v>
@@ -52830,7 +52830,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.29687023162842</v>
+        <v>1.29687035083771</v>
       </c>
       <c r="H1809" t="n">
         <v>67247</v>
@@ -52859,7 +52859,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.30518364906311</v>
+        <v>1.3051837682724</v>
       </c>
       <c r="H1810" t="n">
         <v>175006</v>
@@ -52888,7 +52888,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1811" t="n">
-        <v>1.29687023162842</v>
+        <v>1.29687035083771</v>
       </c>
       <c r="H1811" t="n">
         <v>232923</v>
@@ -52946,7 +52946,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26361703872681</v>
+        <v>1.2636171579361</v>
       </c>
       <c r="H1813" t="n">
         <v>380172</v>
@@ -53062,7 +53062,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.23036420345306</v>
+        <v>1.23036408424377</v>
       </c>
       <c r="H1817" t="n">
         <v>431911</v>
@@ -53091,7 +53091,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1818" t="n">
-        <v>1.23452067375183</v>
+        <v>1.23452079296112</v>
       </c>
       <c r="H1818" t="n">
         <v>151967</v>
@@ -53149,7 +53149,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1820" t="n">
         <v>359212</v>
@@ -53207,7 +53207,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1822" t="n">
-        <v>1.19711112976074</v>
+        <v>1.19711101055145</v>
       </c>
       <c r="H1822" t="n">
         <v>74260</v>
@@ -53236,7 +53236,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1823" t="n">
         <v>99923</v>
@@ -53323,7 +53323,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1826" t="n">
         <v>77691</v>
@@ -53381,7 +53381,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1828" t="n">
         <v>93795</v>
@@ -53439,7 +53439,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1830" t="n">
-        <v>1.19295430183411</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1830" t="n">
         <v>127047</v>
@@ -53468,7 +53468,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.18879771232605</v>
+        <v>1.18879759311676</v>
       </c>
       <c r="H1831" t="n">
         <v>66408</v>
@@ -53526,7 +53526,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.15970134735107</v>
+        <v>1.15970122814178</v>
       </c>
       <c r="H1833" t="n">
         <v>164273</v>
@@ -53700,7 +53700,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1839" t="n">
-        <v>1.15138804912567</v>
+        <v>1.15138792991638</v>
       </c>
       <c r="H1839" t="n">
         <v>104740</v>
@@ -53758,7 +53758,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.15970134735107</v>
+        <v>1.15970122814178</v>
       </c>
       <c r="H1841" t="n">
         <v>67536</v>
@@ -53787,7 +53787,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.15970134735107</v>
+        <v>1.15970122814178</v>
       </c>
       <c r="H1842" t="n">
         <v>65862</v>
@@ -53845,7 +53845,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1844" t="n">
-        <v>1.15554463863373</v>
+        <v>1.15554475784302</v>
       </c>
       <c r="H1844" t="n">
         <v>25428</v>
@@ -53874,7 +53874,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1845" t="n">
-        <v>1.16385793685913</v>
+        <v>1.16385805606842</v>
       </c>
       <c r="H1845" t="n">
         <v>10311</v>
@@ -53903,7 +53903,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.16385793685913</v>
+        <v>1.16385805606842</v>
       </c>
       <c r="H1846" t="n">
         <v>37842</v>
@@ -53961,7 +53961,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1848" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1848" t="n">
         <v>114995</v>
@@ -54280,7 +54280,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.20043635368347</v>
+        <v>1.20043623447418</v>
       </c>
       <c r="H1859" t="n">
         <v>88637</v>
@@ -54309,7 +54309,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.18547248840332</v>
+        <v>1.18547236919403</v>
       </c>
       <c r="H1860" t="n">
         <v>107702</v>
@@ -54338,7 +54338,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1861" t="n">
         <v>91901</v>
@@ -54599,7 +54599,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1870" t="n">
         <v>105865</v>
@@ -54628,7 +54628,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.20963048934937</v>
+        <v>1.20963060855865</v>
       </c>
       <c r="H1871" t="n">
         <v>33985</v>
@@ -54715,7 +54715,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1874" t="n">
         <v>103196</v>
@@ -54831,7 +54831,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1878" t="n">
         <v>40341</v>
@@ -54860,7 +54860,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1879" t="n">
         <v>97941</v>
@@ -55005,7 +55005,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1884" t="n">
         <v>23955</v>
@@ -55034,7 +55034,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1885" t="n">
         <v>38632</v>
@@ -55092,7 +55092,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.20445382595062</v>
+        <v>1.20445394515991</v>
       </c>
       <c r="H1887" t="n">
         <v>25061</v>
@@ -55121,7 +55121,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1888" t="n">
         <v>56779</v>
@@ -55150,7 +55150,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1889" t="n">
         <v>41746</v>
@@ -55208,7 +55208,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.20963048934937</v>
+        <v>1.20963060855865</v>
       </c>
       <c r="H1891" t="n">
         <v>90261</v>
@@ -55237,7 +55237,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1892" t="n">
         <v>64215</v>
@@ -55266,7 +55266,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.20963048934937</v>
+        <v>1.20963060855865</v>
       </c>
       <c r="H1893" t="n">
         <v>10161</v>
@@ -55498,7 +55498,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1901" t="n">
         <v>56215</v>
@@ -55556,7 +55556,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.1958259344101</v>
+        <v>1.19582605361938</v>
       </c>
       <c r="H1903" t="n">
         <v>62215</v>
@@ -55585,7 +55585,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.18719804286957</v>
+        <v>1.18719816207886</v>
       </c>
       <c r="H1904" t="n">
         <v>185512</v>
@@ -55614,7 +55614,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1905" t="n">
         <v>110276</v>
@@ -55643,7 +55643,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1906" t="n">
         <v>34897</v>
@@ -55701,7 +55701,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.20445382595062</v>
+        <v>1.20445394515991</v>
       </c>
       <c r="H1908" t="n">
         <v>90651</v>
@@ -55730,7 +55730,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.20445382595062</v>
+        <v>1.20445394515991</v>
       </c>
       <c r="H1909" t="n">
         <v>70741</v>
@@ -55759,7 +55759,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.20445382595062</v>
+        <v>1.20445394515991</v>
       </c>
       <c r="H1910" t="n">
         <v>53328</v>
@@ -55788,7 +55788,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1911" t="n">
         <v>29647</v>
@@ -55817,7 +55817,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1912" t="n">
         <v>25580</v>
@@ -55933,7 +55933,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.20100259780884</v>
+        <v>1.20100271701813</v>
       </c>
       <c r="H1916" t="n">
         <v>87092</v>
@@ -55991,7 +55991,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.18719804286957</v>
+        <v>1.18719816207886</v>
       </c>
       <c r="H1918" t="n">
         <v>114549</v>
@@ -56078,7 +56078,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.22343528270721</v>
+        <v>1.22343516349792</v>
       </c>
       <c r="H1921" t="n">
         <v>41234</v>
@@ -56107,7 +56107,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1922" t="n">
         <v>132690</v>
@@ -56136,7 +56136,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1923" t="n">
         <v>103060</v>
@@ -56165,7 +56165,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1924" t="n">
         <v>138549</v>
@@ -56194,7 +56194,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1925" t="n">
         <v>339659</v>
@@ -56223,7 +56223,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1926" t="n">
         <v>98383</v>
@@ -56310,7 +56310,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.21998417377472</v>
+        <v>1.21998405456543</v>
       </c>
       <c r="H1929" t="n">
         <v>88172</v>
@@ -56368,7 +56368,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1931" t="n">
         <v>206642</v>
@@ -56397,7 +56397,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1932" t="n">
         <v>29875</v>
@@ -56426,7 +56426,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1933" t="n">
         <v>118053</v>
@@ -56513,7 +56513,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1936" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1936" t="n">
         <v>63135</v>
@@ -56542,7 +56542,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1937" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1937" t="n">
         <v>16888</v>
@@ -56571,7 +56571,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1938" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1938" t="n">
         <v>67297</v>
@@ -56658,7 +56658,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1941" t="n">
         <v>15797</v>
@@ -56687,7 +56687,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1942" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1942" t="n">
         <v>63617</v>
@@ -56745,7 +56745,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1944" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1944" t="n">
         <v>68325</v>
@@ -56774,7 +56774,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1945" t="n">
         <v>24102</v>
@@ -56803,7 +56803,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1946" t="n">
         <v>52666</v>
@@ -56832,7 +56832,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.22861206531525</v>
+        <v>1.22861194610596</v>
       </c>
       <c r="H1947" t="n">
         <v>38744</v>
@@ -56977,7 +56977,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1952" t="n">
         <v>88943</v>
@@ -57064,7 +57064,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.22343528270721</v>
+        <v>1.22343516349792</v>
       </c>
       <c r="H1955" t="n">
         <v>92814</v>
@@ -57093,7 +57093,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1956" t="n">
         <v>38147</v>
@@ -57122,7 +57122,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.22861206531525</v>
+        <v>1.22861194610596</v>
       </c>
       <c r="H1957" t="n">
         <v>88347</v>
@@ -57180,7 +57180,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1959" t="n">
-        <v>1.22861206531525</v>
+        <v>1.22861194610596</v>
       </c>
       <c r="H1959" t="n">
         <v>13136</v>
@@ -57209,7 +57209,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.2303375005722</v>
+        <v>1.23033738136292</v>
       </c>
       <c r="H1960" t="n">
         <v>56465</v>
@@ -57267,7 +57267,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1962" t="n">
         <v>177038</v>
@@ -57296,7 +57296,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1963" t="n">
         <v>309806</v>
@@ -57325,7 +57325,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.21998417377472</v>
+        <v>1.21998405456543</v>
       </c>
       <c r="H1964" t="n">
         <v>140705</v>
@@ -57354,7 +57354,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.21825838088989</v>
+        <v>1.2182582616806</v>
       </c>
       <c r="H1965" t="n">
         <v>71111</v>
@@ -57383,7 +57383,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.20963048934937</v>
+        <v>1.20963060855865</v>
       </c>
       <c r="H1966" t="n">
         <v>86051</v>
@@ -57441,7 +57441,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1968" t="n">
         <v>126228</v>
@@ -57470,7 +57470,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.19927704334259</v>
+        <v>1.19927716255188</v>
       </c>
       <c r="H1969" t="n">
         <v>302616</v>
@@ -57499,7 +57499,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1970" t="n">
         <v>164579</v>
@@ -57528,7 +57528,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1971" t="n">
         <v>84515</v>
@@ -57557,7 +57557,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1972" t="n">
         <v>129339</v>
@@ -57615,7 +57615,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1974" t="n">
-        <v>1.20963048934937</v>
+        <v>1.20963060855865</v>
       </c>
       <c r="H1974" t="n">
         <v>60478</v>
@@ -57644,7 +57644,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1975" t="n">
-        <v>1.20790493488312</v>
+        <v>1.20790505409241</v>
       </c>
       <c r="H1975" t="n">
         <v>57405</v>
@@ -57702,7 +57702,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.20963048934937</v>
+        <v>1.20963060855865</v>
       </c>
       <c r="H1977" t="n">
         <v>118187</v>
@@ -57760,7 +57760,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1979" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1979" t="n">
         <v>37329</v>
@@ -57818,7 +57818,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.23723995685577</v>
+        <v>1.23723983764648</v>
       </c>
       <c r="H1981" t="n">
         <v>146312</v>
@@ -57876,7 +57876,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.22861206531525</v>
+        <v>1.22861194610596</v>
       </c>
       <c r="H1983" t="n">
         <v>30611</v>
@@ -57905,7 +57905,7 @@
         <v>1.42400002479553</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.22861206531525</v>
+        <v>1.22861194610596</v>
       </c>
       <c r="H1984" t="n">
         <v>41956</v>
@@ -57934,7 +57934,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.2303375005722</v>
+        <v>1.23033738136292</v>
       </c>
       <c r="H1985" t="n">
         <v>49878</v>
@@ -57992,7 +57992,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1987" t="n">
         <v>92029</v>
@@ -58079,7 +58079,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.2303375005722</v>
+        <v>1.23033738136292</v>
       </c>
       <c r="H1990" t="n">
         <v>37092</v>
@@ -58108,7 +58108,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1991" t="n">
         <v>56288</v>
@@ -58137,7 +58137,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.22516083717346</v>
+        <v>1.22516071796417</v>
       </c>
       <c r="H1992" t="n">
         <v>47041</v>
@@ -58224,7 +58224,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.26312339305878</v>
+        <v>1.26312351226807</v>
       </c>
       <c r="H1995" t="n">
         <v>105068</v>
@@ -58311,7 +58311,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.26830041408539</v>
+        <v>1.2683002948761</v>
       </c>
       <c r="H1998" t="n">
         <v>47077</v>
@@ -58340,7 +58340,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.26657462120056</v>
+        <v>1.26657474040985</v>
       </c>
       <c r="H1999" t="n">
         <v>12526</v>
@@ -58369,7 +58369,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2000" t="n">
         <v>12500</v>
@@ -58398,7 +58398,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.26830041408539</v>
+        <v>1.2683002948761</v>
       </c>
       <c r="H2001" t="n">
         <v>32016</v>
@@ -58427,7 +58427,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.26830041408539</v>
+        <v>1.2683002948761</v>
       </c>
       <c r="H2002" t="n">
         <v>18919</v>
@@ -58572,7 +58572,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.26830041408539</v>
+        <v>1.2683002948761</v>
       </c>
       <c r="H2007" t="n">
         <v>52887</v>
@@ -58630,7 +58630,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.26657462120056</v>
+        <v>1.26657474040985</v>
       </c>
       <c r="H2009" t="n">
         <v>76434</v>
@@ -58717,7 +58717,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.27347695827484</v>
+        <v>1.27347683906555</v>
       </c>
       <c r="H2012" t="n">
         <v>35532</v>
@@ -58775,7 +58775,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2014" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2014" t="n">
         <v>26778</v>
@@ -58833,7 +58833,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G2016" t="n">
-        <v>1.27347695827484</v>
+        <v>1.27347683906555</v>
       </c>
       <c r="H2016" t="n">
         <v>156335</v>
@@ -58862,7 +58862,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.27692818641663</v>
+        <v>1.27692806720734</v>
       </c>
       <c r="H2017" t="n">
         <v>56183</v>
@@ -58891,7 +58891,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.26657462120056</v>
+        <v>1.26657474040985</v>
       </c>
       <c r="H2018" t="n">
         <v>64055</v>
@@ -59007,7 +59007,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.26657462120056</v>
+        <v>1.26657474040985</v>
       </c>
       <c r="H2022" t="n">
         <v>71930</v>
@@ -59065,7 +59065,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2024" t="n">
-        <v>1.26830041408539</v>
+        <v>1.2683002948761</v>
       </c>
       <c r="H2024" t="n">
         <v>138577</v>
@@ -59094,7 +59094,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.26657462120056</v>
+        <v>1.26657474040985</v>
       </c>
       <c r="H2025" t="n">
         <v>127782</v>
@@ -59123,7 +59123,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.26657462120056</v>
+        <v>1.26657474040985</v>
       </c>
       <c r="H2026" t="n">
         <v>121060</v>
@@ -59152,7 +59152,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G2027" t="n">
-        <v>1.27347695827484</v>
+        <v>1.27347683906555</v>
       </c>
       <c r="H2027" t="n">
         <v>132183</v>
@@ -59181,7 +59181,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G2028" t="n">
-        <v>1.27347695827484</v>
+        <v>1.27347683906555</v>
       </c>
       <c r="H2028" t="n">
         <v>93053</v>
@@ -59268,7 +59268,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.28555607795715</v>
+        <v>1.28555595874786</v>
       </c>
       <c r="H2031" t="n">
         <v>433500</v>
@@ -59558,7 +59558,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2041" t="n">
         <v>101446</v>
@@ -59587,7 +59587,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G2042" t="n">
-        <v>1.32179319858551</v>
+        <v>1.32179307937622</v>
       </c>
       <c r="H2042" t="n">
         <v>153916</v>
@@ -59616,7 +59616,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2043" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2043" t="n">
         <v>149475</v>
@@ -59645,7 +59645,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G2044" t="n">
-        <v>1.32179319858551</v>
+        <v>1.32179307937622</v>
       </c>
       <c r="H2044" t="n">
         <v>134255</v>
@@ -59732,7 +59732,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2047" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2047" t="n">
         <v>107937</v>
@@ -59819,7 +59819,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2050" t="n">
         <v>205091</v>
@@ -59848,7 +59848,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G2051" t="n">
-        <v>1.32524442672729</v>
+        <v>1.32524430751801</v>
       </c>
       <c r="H2051" t="n">
         <v>51256</v>
@@ -59877,7 +59877,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.31489086151123</v>
+        <v>1.31489098072052</v>
       </c>
       <c r="H2052" t="n">
         <v>66057</v>
@@ -59964,7 +59964,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.31143963336945</v>
+        <v>1.31143975257874</v>
       </c>
       <c r="H2055" t="n">
         <v>81569</v>
@@ -59993,7 +59993,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.28210484981537</v>
+        <v>1.28210473060608</v>
       </c>
       <c r="H2056" t="n">
         <v>76265</v>
@@ -60138,7 +60138,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.28555607795715</v>
+        <v>1.28555595874786</v>
       </c>
       <c r="H2061" t="n">
         <v>64382</v>
@@ -60167,7 +60167,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G2062" t="n">
-        <v>1.27002584934235</v>
+        <v>1.27002573013306</v>
       </c>
       <c r="H2062" t="n">
         <v>87863</v>
@@ -60196,7 +60196,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G2063" t="n">
-        <v>1.27002584934235</v>
+        <v>1.27002573013306</v>
       </c>
       <c r="H2063" t="n">
         <v>52782</v>
@@ -60225,7 +60225,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.28210484981537</v>
+        <v>1.28210473060608</v>
       </c>
       <c r="H2064" t="n">
         <v>57224</v>
@@ -60254,7 +60254,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G2065" t="n">
-        <v>1.28210484981537</v>
+        <v>1.28210473060608</v>
       </c>
       <c r="H2065" t="n">
         <v>88857</v>
@@ -60312,7 +60312,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.32179319858551</v>
+        <v>1.32179307937622</v>
       </c>
       <c r="H2067" t="n">
         <v>630912</v>
@@ -60457,7 +60457,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G2072" t="n">
-        <v>1.35803031921387</v>
+        <v>1.35803043842316</v>
       </c>
       <c r="H2072" t="n">
         <v>500955</v>
@@ -60602,7 +60602,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.3856395483017</v>
+        <v>1.38563966751099</v>
       </c>
       <c r="H2077" t="n">
         <v>548812</v>
@@ -60660,7 +60660,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.4201512336731</v>
+        <v>1.42015111446381</v>
       </c>
       <c r="H2079" t="n">
         <v>317842</v>
@@ -60979,7 +60979,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G2090" t="n">
-        <v>1.3821884393692</v>
+        <v>1.38218855857849</v>
       </c>
       <c r="H2090" t="n">
         <v>128951</v>
@@ -61124,7 +61124,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G2095" t="n">
-        <v>1.36493253707886</v>
+        <v>1.36493265628815</v>
       </c>
       <c r="H2095" t="n">
         <v>223370</v>
@@ -61269,7 +61269,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2100" t="n">
-        <v>1.36752104759216</v>
+        <v>1.36752092838287</v>
       </c>
       <c r="H2100" t="n">
         <v>113147</v>
@@ -61356,7 +61356,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.35457921028137</v>
+        <v>1.35457932949066</v>
       </c>
       <c r="H2103" t="n">
         <v>319988</v>
@@ -61414,7 +61414,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2105" t="n">
-        <v>1.34595119953156</v>
+        <v>1.34595131874084</v>
       </c>
       <c r="H2105" t="n">
         <v>285168</v>
@@ -61443,7 +61443,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.35889327526093</v>
+        <v>1.35889315605164</v>
       </c>
       <c r="H2106" t="n">
         <v>121039</v>
@@ -61472,7 +61472,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G2107" t="n">
-        <v>1.35889327526093</v>
+        <v>1.35889315605164</v>
       </c>
       <c r="H2107" t="n">
         <v>115047</v>
@@ -61530,7 +61530,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2109" t="n">
-        <v>1.36752104759216</v>
+        <v>1.36752092838287</v>
       </c>
       <c r="H2109" t="n">
         <v>242970</v>
@@ -61559,7 +61559,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.3502653837204</v>
+        <v>1.35026526451111</v>
       </c>
       <c r="H2110" t="n">
         <v>376256</v>
@@ -61588,7 +61588,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.34595119953156</v>
+        <v>1.34595131874084</v>
       </c>
       <c r="H2111" t="n">
         <v>203899</v>
@@ -61675,7 +61675,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.39555430412292</v>
+        <v>1.39555442333221</v>
       </c>
       <c r="H2114" t="n">
         <v>397099</v>
@@ -61820,7 +61820,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2119" t="n">
         <v>368791</v>
@@ -61849,7 +61849,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.39555430412292</v>
+        <v>1.39555442333221</v>
       </c>
       <c r="H2120" t="n">
         <v>238639</v>
@@ -61878,7 +61878,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.40479636192322</v>
+        <v>1.40479648113251</v>
       </c>
       <c r="H2121" t="n">
         <v>324051</v>
@@ -61907,7 +61907,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.40017545223236</v>
+        <v>1.40017533302307</v>
       </c>
       <c r="H2122" t="n">
         <v>367746</v>
@@ -61936,7 +61936,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.40479636192322</v>
+        <v>1.40479648113251</v>
       </c>
       <c r="H2123" t="n">
         <v>132779</v>
@@ -61994,7 +61994,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.40479636192322</v>
+        <v>1.40479648113251</v>
       </c>
       <c r="H2125" t="n">
         <v>122267</v>
@@ -62023,7 +62023,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.40479636192322</v>
+        <v>1.40479648113251</v>
       </c>
       <c r="H2126" t="n">
         <v>111405</v>
@@ -62081,7 +62081,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.40479636192322</v>
+        <v>1.40479648113251</v>
       </c>
       <c r="H2128" t="n">
         <v>191562</v>
@@ -62110,7 +62110,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2129" t="n">
         <v>82722</v>
@@ -62139,7 +62139,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2130" t="n">
-        <v>1.40479636192322</v>
+        <v>1.40479648113251</v>
       </c>
       <c r="H2130" t="n">
         <v>148885</v>
@@ -62168,7 +62168,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2131" t="n">
         <v>321550</v>
@@ -62197,7 +62197,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2132" t="n">
         <v>90636</v>
@@ -62226,7 +62226,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2133" t="n">
-        <v>1.40479636192322</v>
+        <v>1.40479648113251</v>
       </c>
       <c r="H2133" t="n">
         <v>131351</v>
@@ -62255,7 +62255,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G2134" t="n">
-        <v>1.39555430412292</v>
+        <v>1.39555442333221</v>
       </c>
       <c r="H2134" t="n">
         <v>294293</v>
@@ -62284,7 +62284,7 @@
         <v>1.5</v>
       </c>
       <c r="G2135" t="n">
-        <v>1.38631224632263</v>
+        <v>1.38631236553192</v>
       </c>
       <c r="H2135" t="n">
         <v>110917</v>
@@ -62313,7 +62313,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.37244915962219</v>
+        <v>1.37244927883148</v>
       </c>
       <c r="H2136" t="n">
         <v>324207</v>
@@ -62342,7 +62342,7 @@
         <v>1.5</v>
       </c>
       <c r="G2137" t="n">
-        <v>1.38631224632263</v>
+        <v>1.38631236553192</v>
       </c>
       <c r="H2137" t="n">
         <v>109021</v>
@@ -62371,7 +62371,7 @@
         <v>1.5</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.38631224632263</v>
+        <v>1.38631236553192</v>
       </c>
       <c r="H2138" t="n">
         <v>102443</v>
@@ -62400,7 +62400,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G2139" t="n">
-        <v>1.39555430412292</v>
+        <v>1.39555442333221</v>
       </c>
       <c r="H2139" t="n">
         <v>128884</v>
@@ -62429,7 +62429,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.37707030773163</v>
+        <v>1.37707018852234</v>
       </c>
       <c r="H2140" t="n">
         <v>170596</v>
@@ -62458,7 +62458,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2141" t="n">
-        <v>1.37244915962219</v>
+        <v>1.37244927883148</v>
       </c>
       <c r="H2141" t="n">
         <v>97827</v>
@@ -62487,7 +62487,7 @@
         <v>1.5</v>
       </c>
       <c r="G2142" t="n">
-        <v>1.38631224632263</v>
+        <v>1.38631236553192</v>
       </c>
       <c r="H2142" t="n">
         <v>219416</v>
@@ -62661,7 +62661,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.43714380264282</v>
+        <v>1.43714368343353</v>
       </c>
       <c r="H2148" t="n">
         <v>163875</v>
@@ -62748,7 +62748,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.39555430412292</v>
+        <v>1.39555442333221</v>
       </c>
       <c r="H2151" t="n">
         <v>324620</v>
@@ -62777,7 +62777,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G2152" t="n">
-        <v>1.37244915962219</v>
+        <v>1.37244927883148</v>
       </c>
       <c r="H2152" t="n">
         <v>148702</v>
@@ -62806,7 +62806,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G2153" t="n">
-        <v>1.37707030773163</v>
+        <v>1.37707018852234</v>
       </c>
       <c r="H2153" t="n">
         <v>70173</v>
@@ -62835,7 +62835,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.40017545223236</v>
+        <v>1.40017533302307</v>
       </c>
       <c r="H2154" t="n">
         <v>41508</v>
@@ -62864,7 +62864,7 @@
         <v>1.5</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.38631224632263</v>
+        <v>1.38631236553192</v>
       </c>
       <c r="H2155" t="n">
         <v>48858</v>
@@ -62893,7 +62893,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2156" t="n">
         <v>57284</v>
@@ -62951,7 +62951,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2158" t="n">
         <v>78157</v>
@@ -62980,7 +62980,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2159" t="n">
         <v>26531</v>
@@ -63009,7 +63009,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G2160" t="n">
-        <v>1.40017545223236</v>
+        <v>1.40017533302307</v>
       </c>
       <c r="H2160" t="n">
         <v>81258</v>
@@ -63038,7 +63038,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G2161" t="n">
-        <v>1.39555430412292</v>
+        <v>1.39555442333221</v>
       </c>
       <c r="H2161" t="n">
         <v>117482</v>
@@ -63067,7 +63067,7 @@
         <v>1.5</v>
       </c>
       <c r="G2162" t="n">
-        <v>1.38631224632263</v>
+        <v>1.38631236553192</v>
       </c>
       <c r="H2162" t="n">
         <v>96945</v>
@@ -63096,7 +63096,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G2163" t="n">
-        <v>1.39555430412292</v>
+        <v>1.39555442333221</v>
       </c>
       <c r="H2163" t="n">
         <v>40613</v>
@@ -63125,7 +63125,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2164" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2164" t="n">
         <v>93748</v>
@@ -63241,7 +63241,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2168" t="n">
-        <v>1.40479636192322</v>
+        <v>1.40479648113251</v>
       </c>
       <c r="H2168" t="n">
         <v>83068</v>
@@ -63560,7 +63560,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G2179" t="n">
-        <v>1.43714380264282</v>
+        <v>1.43714368343353</v>
       </c>
       <c r="H2179" t="n">
         <v>121032</v>
@@ -63589,7 +63589,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2180" t="n">
-        <v>1.46024894714355</v>
+        <v>1.46024906635284</v>
       </c>
       <c r="H2180" t="n">
         <v>245039</v>
@@ -63676,7 +63676,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2183" t="n">
-        <v>1.45100688934326</v>
+        <v>1.45100700855255</v>
       </c>
       <c r="H2183" t="n">
         <v>357193</v>
@@ -63705,7 +63705,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2184" t="n">
-        <v>1.45100688934326</v>
+        <v>1.45100700855255</v>
       </c>
       <c r="H2184" t="n">
         <v>162703</v>
@@ -63763,7 +63763,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G2186" t="n">
-        <v>1.43714380264282</v>
+        <v>1.43714368343353</v>
       </c>
       <c r="H2186" t="n">
         <v>120197</v>
@@ -63850,7 +63850,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G2189" t="n">
-        <v>1.39555430412292</v>
+        <v>1.39555442333221</v>
       </c>
       <c r="H2189" t="n">
         <v>63040</v>
@@ -63879,7 +63879,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G2190" t="n">
-        <v>1.40941751003265</v>
+        <v>1.40941739082336</v>
       </c>
       <c r="H2190" t="n">
         <v>91347</v>
@@ -64053,7 +64053,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2196" t="n">
-        <v>1.45100688934326</v>
+        <v>1.45100700855255</v>
       </c>
       <c r="H2196" t="n">
         <v>106229</v>
@@ -64082,7 +64082,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2197" t="n">
-        <v>1.46487009525299</v>
+        <v>1.4648699760437</v>
       </c>
       <c r="H2197" t="n">
         <v>65522</v>
@@ -64111,7 +64111,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2198" t="n">
-        <v>1.44176471233368</v>
+        <v>1.44176483154297</v>
       </c>
       <c r="H2198" t="n">
         <v>93741</v>
@@ -64140,7 +64140,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2199" t="n">
-        <v>1.44176471233368</v>
+        <v>1.44176483154297</v>
       </c>
       <c r="H2199" t="n">
         <v>59324</v>
@@ -64169,7 +64169,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2200" t="n">
-        <v>1.44176471233368</v>
+        <v>1.44176483154297</v>
       </c>
       <c r="H2200" t="n">
         <v>56315</v>
@@ -64285,7 +64285,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2204" t="n">
-        <v>1.44176471233368</v>
+        <v>1.44176483154297</v>
       </c>
       <c r="H2204" t="n">
         <v>136175</v>
@@ -64314,7 +64314,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G2205" t="n">
-        <v>1.4463859796524</v>
+        <v>1.44638586044312</v>
       </c>
       <c r="H2205" t="n">
         <v>73438</v>
@@ -64343,7 +64343,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.46024894714355</v>
+        <v>1.46024906635284</v>
       </c>
       <c r="H2206" t="n">
         <v>111643</v>
@@ -64372,7 +64372,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2207" t="n">
-        <v>1.45100688934326</v>
+        <v>1.45100700855255</v>
       </c>
       <c r="H2207" t="n">
         <v>111672</v>
@@ -64401,7 +64401,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.45100688934326</v>
+        <v>1.45100700855255</v>
       </c>
       <c r="H2208" t="n">
         <v>78963</v>
@@ -64430,7 +64430,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G2209" t="n">
-        <v>1.4463859796524</v>
+        <v>1.44638586044312</v>
       </c>
       <c r="H2209" t="n">
         <v>59964</v>
@@ -64459,7 +64459,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2210" t="n">
-        <v>1.44176471233368</v>
+        <v>1.44176483154297</v>
       </c>
       <c r="H2210" t="n">
         <v>71389</v>
@@ -64488,7 +64488,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G2211" t="n">
-        <v>1.44176471233368</v>
+        <v>1.44176483154297</v>
       </c>
       <c r="H2211" t="n">
         <v>102152</v>
@@ -64517,7 +64517,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G2212" t="n">
-        <v>1.43714380264282</v>
+        <v>1.43714368343353</v>
       </c>
       <c r="H2212" t="n">
         <v>92888</v>
@@ -64604,7 +64604,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2215" t="n">
-        <v>1.45100688934326</v>
+        <v>1.45100700855255</v>
       </c>
       <c r="H2215" t="n">
         <v>179031</v>
@@ -64633,7 +64633,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G2216" t="n">
-        <v>1.45100688934326</v>
+        <v>1.45100700855255</v>
       </c>
       <c r="H2216" t="n">
         <v>120963</v>
@@ -64662,7 +64662,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G2217" t="n">
-        <v>1.4556280374527</v>
+        <v>1.45562791824341</v>
       </c>
       <c r="H2217" t="n">
         <v>88322</v>
@@ -64691,7 +64691,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2218" t="n">
-        <v>1.46024894714355</v>
+        <v>1.46024906635284</v>
       </c>
       <c r="H2218" t="n">
         <v>157697</v>
@@ -64720,7 +64720,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2219" t="n">
-        <v>1.46487009525299</v>
+        <v>1.4648699760437</v>
       </c>
       <c r="H2219" t="n">
         <v>155603</v>
@@ -64749,7 +64749,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2220" t="n">
-        <v>1.46024894714355</v>
+        <v>1.46024906635284</v>
       </c>
       <c r="H2220" t="n">
         <v>407453</v>
@@ -64778,7 +64778,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2221" t="n">
-        <v>1.46487009525299</v>
+        <v>1.4648699760437</v>
       </c>
       <c r="H2221" t="n">
         <v>86852</v>
@@ -64836,7 +64836,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2223" t="n">
-        <v>1.46487009525299</v>
+        <v>1.4648699760437</v>
       </c>
       <c r="H2223" t="n">
         <v>75213</v>
@@ -64923,7 +64923,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2226" t="n">
-        <v>1.46487009525299</v>
+        <v>1.4648699760437</v>
       </c>
       <c r="H2226" t="n">
         <v>77343</v>
@@ -64952,7 +64952,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G2227" t="n">
-        <v>1.46024894714355</v>
+        <v>1.46024906635284</v>
       </c>
       <c r="H2227" t="n">
         <v>119632</v>
@@ -64981,7 +64981,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G2228" t="n">
-        <v>1.52494359016418</v>
+        <v>1.5249434709549</v>
       </c>
       <c r="H2228" t="n">
         <v>4787926</v>
@@ -65010,7 +65010,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G2229" t="n">
-        <v>1.53418564796448</v>
+        <v>1.53418552875519</v>
       </c>
       <c r="H2229" t="n">
         <v>721347</v>
@@ -65039,7 +65039,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G2230" t="n">
-        <v>1.54342770576477</v>
+        <v>1.54342758655548</v>
       </c>
       <c r="H2230" t="n">
         <v>779406</v>
@@ -65213,7 +65213,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G2236" t="n">
-        <v>1.61274337768555</v>
+        <v>1.61274325847626</v>
       </c>
       <c r="H2236" t="n">
         <v>92522</v>
@@ -65242,7 +65242,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G2237" t="n">
-        <v>1.60812222957611</v>
+        <v>1.6081223487854</v>
       </c>
       <c r="H2237" t="n">
         <v>102512</v>
@@ -65271,7 +65271,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G2238" t="n">
-        <v>1.61274337768555</v>
+        <v>1.61274325847626</v>
       </c>
       <c r="H2238" t="n">
         <v>166490</v>
@@ -65300,7 +65300,7 @@
         <v>1.75</v>
       </c>
       <c r="G2239" t="n">
-        <v>1.6173642873764</v>
+        <v>1.61736440658569</v>
       </c>
       <c r="H2239" t="n">
         <v>104288</v>
@@ -65387,7 +65387,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2242" t="n">
-        <v>1.70054316520691</v>
+        <v>1.70054304599762</v>
       </c>
       <c r="H2242" t="n">
         <v>603922</v>
@@ -65416,7 +65416,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2243" t="n">
-        <v>1.69592201709747</v>
+        <v>1.69592213630676</v>
       </c>
       <c r="H2243" t="n">
         <v>379182</v>
@@ -65445,7 +65445,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2244" t="n">
-        <v>1.69592201709747</v>
+        <v>1.69592213630676</v>
       </c>
       <c r="H2244" t="n">
         <v>188952</v>
@@ -65619,7 +65619,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2250" t="n">
-        <v>1.67281675338745</v>
+        <v>1.67281687259674</v>
       </c>
       <c r="H2250" t="n">
         <v>219876</v>
@@ -65735,7 +65735,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2254" t="n">
-        <v>1.66357469558716</v>
+        <v>1.66357481479645</v>
       </c>
       <c r="H2254" t="n">
         <v>124054</v>
@@ -65938,7 +65938,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2261" t="n">
-        <v>1.68667995929718</v>
+        <v>1.68668007850647</v>
       </c>
       <c r="H2261" t="n">
         <v>90169</v>
@@ -65967,7 +65967,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2262" t="n">
-        <v>1.68667995929718</v>
+        <v>1.68668007850647</v>
       </c>
       <c r="H2262" t="n">
         <v>102157</v>
@@ -66025,7 +66025,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2264" t="n">
-        <v>1.68667995929718</v>
+        <v>1.68668007850647</v>
       </c>
       <c r="H2264" t="n">
         <v>71848</v>
@@ -66141,7 +66141,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2268" t="n">
-        <v>1.66357469558716</v>
+        <v>1.66357481479645</v>
       </c>
       <c r="H2268" t="n">
         <v>124864</v>
@@ -66286,7 +66286,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2273" t="n">
-        <v>1.69592201709747</v>
+        <v>1.69592213630676</v>
       </c>
       <c r="H2273" t="n">
         <v>931466</v>
@@ -66373,7 +66373,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2276" t="n">
-        <v>1.67281675338745</v>
+        <v>1.67281687259674</v>
       </c>
       <c r="H2276" t="n">
         <v>144056</v>
@@ -66402,7 +66402,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2277" t="n">
-        <v>1.67281675338745</v>
+        <v>1.67281687259674</v>
       </c>
       <c r="H2277" t="n">
         <v>99049</v>
@@ -66576,7 +66576,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2283" t="n">
-        <v>1.70054316520691</v>
+        <v>1.70054304599762</v>
       </c>
       <c r="H2283" t="n">
         <v>257007</v>
@@ -66663,7 +66663,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2286" t="n">
-        <v>1.7097852230072</v>
+        <v>1.70978510379791</v>
       </c>
       <c r="H2286" t="n">
         <v>649110</v>
@@ -66721,7 +66721,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2288" t="n">
-        <v>1.69592201709747</v>
+        <v>1.69592213630676</v>
       </c>
       <c r="H2288" t="n">
         <v>66885</v>
@@ -66895,7 +66895,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2294" t="n">
-        <v>1.82531130313873</v>
+        <v>1.82531118392944</v>
       </c>
       <c r="H2294" t="n">
         <v>149984</v>
@@ -67069,7 +67069,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2300" t="n">
-        <v>1.82993221282959</v>
+        <v>1.82993233203888</v>
       </c>
       <c r="H2300" t="n">
         <v>83155</v>
@@ -67591,7 +67591,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2318" t="n">
-        <v>1.82993221282959</v>
+        <v>1.82993233203888</v>
       </c>
       <c r="H2318" t="n">
         <v>194498</v>
@@ -67620,7 +67620,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2319" t="n">
-        <v>1.82531130313873</v>
+        <v>1.82531118392944</v>
       </c>
       <c r="H2319" t="n">
         <v>365841</v>
@@ -67649,7 +67649,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G2320" t="n">
-        <v>1.82531130313873</v>
+        <v>1.82531118392944</v>
       </c>
       <c r="H2320" t="n">
         <v>106909</v>
@@ -67707,7 +67707,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2322" t="n">
-        <v>1.88538467884064</v>
+        <v>1.88538479804993</v>
       </c>
       <c r="H2322" t="n">
         <v>279894</v>
@@ -67765,7 +67765,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2324" t="n">
-        <v>1.91311097145081</v>
+        <v>1.91311085224152</v>
       </c>
       <c r="H2324" t="n">
         <v>178277</v>
@@ -67794,7 +67794,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2325" t="n">
-        <v>1.74675357341766</v>
+        <v>1.74675345420837</v>
       </c>
       <c r="H2325" t="n">
         <v>2382794</v>
@@ -67852,7 +67852,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2327" t="n">
-        <v>1.67281675338745</v>
+        <v>1.67281687259674</v>
       </c>
       <c r="H2327" t="n">
         <v>231577</v>
@@ -67910,7 +67910,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2329" t="n">
-        <v>1.68667995929718</v>
+        <v>1.68668007850647</v>
       </c>
       <c r="H2329" t="n">
         <v>79579</v>
@@ -67997,7 +67997,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2332" t="n">
-        <v>1.7097852230072</v>
+        <v>1.70978510379791</v>
       </c>
       <c r="H2332" t="n">
         <v>215149</v>
@@ -68026,7 +68026,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2333" t="n">
-        <v>1.68667995929718</v>
+        <v>1.68668007850647</v>
       </c>
       <c r="H2333" t="n">
         <v>252800</v>
@@ -68316,7 +68316,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G2343" t="n">
-        <v>1.75137448310852</v>
+        <v>1.75137460231781</v>
       </c>
       <c r="H2343" t="n">
         <v>145275</v>
@@ -68345,7 +68345,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.74675357341766</v>
+        <v>1.74675345420837</v>
       </c>
       <c r="H2344" t="n">
         <v>67544</v>
@@ -68403,7 +68403,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G2346" t="n">
-        <v>1.74675357341766</v>
+        <v>1.74675345420837</v>
       </c>
       <c r="H2346" t="n">
         <v>101837</v>
@@ -68490,7 +68490,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2349" t="n">
-        <v>1.73751151561737</v>
+        <v>1.73751139640808</v>
       </c>
       <c r="H2349" t="n">
         <v>260954</v>
@@ -68635,7 +68635,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.68667995929718</v>
+        <v>1.68668007850647</v>
       </c>
       <c r="H2354" t="n">
         <v>179211</v>
@@ -68664,7 +68664,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.69592201709747</v>
+        <v>1.69592213630676</v>
       </c>
       <c r="H2355" t="n">
         <v>313846</v>
@@ -68751,7 +68751,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2358" t="n">
-        <v>1.67281675338745</v>
+        <v>1.67281687259674</v>
       </c>
       <c r="H2358" t="n">
         <v>234666</v>
@@ -68809,7 +68809,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G2360" t="n">
-        <v>1.66911995410919</v>
+        <v>1.66912007331848</v>
       </c>
       <c r="H2360" t="n">
         <v>110296</v>
@@ -68896,7 +68896,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2363" t="n">
-        <v>1.70054316520691</v>
+        <v>1.70054304599762</v>
       </c>
       <c r="H2363" t="n">
         <v>111812</v>
@@ -68954,7 +68954,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2365" t="n">
-        <v>1.7097852230072</v>
+        <v>1.70978510379791</v>
       </c>
       <c r="H2365" t="n">
         <v>75046</v>
@@ -68983,7 +68983,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G2366" t="n">
-        <v>1.69499790668488</v>
+        <v>1.69499778747559</v>
       </c>
       <c r="H2366" t="n">
         <v>97690</v>
@@ -69012,7 +69012,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G2367" t="n">
-        <v>1.69499790668488</v>
+        <v>1.69499778747559</v>
       </c>
       <c r="H2367" t="n">
         <v>163947</v>
@@ -69041,7 +69041,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.7097852230072</v>
+        <v>1.70978510379791</v>
       </c>
       <c r="H2368" t="n">
         <v>171038</v>
@@ -69070,7 +69070,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G2369" t="n">
-        <v>1.7430567741394</v>
+        <v>1.74305665493011</v>
       </c>
       <c r="H2369" t="n">
         <v>507265</v>
@@ -80067,6 +80067,35 @@
         <v>5636</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>1.86600005626678</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>1.83399999141693</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>14183</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.485062181949615</v>
+        <v>0.48506224155426</v>
       </c>
       <c r="H2" t="n">
         <v>191859</v>
@@ -456,7 +456,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.488176077604294</v>
+        <v>0.488176047801971</v>
       </c>
       <c r="H3" t="n">
         <v>84538</v>
@@ -485,7 +485,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.481602370738983</v>
+        <v>0.481602430343628</v>
       </c>
       <c r="H4" t="n">
         <v>28934</v>
@@ -601,7 +601,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.479872614145279</v>
+        <v>0.479872584342957</v>
       </c>
       <c r="H8" t="n">
         <v>46220</v>
@@ -630,7 +630,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>0.48367840051651</v>
+        <v>0.483678340911865</v>
       </c>
       <c r="H9" t="n">
         <v>53793</v>
@@ -659,7 +659,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G10" t="n">
-        <v>0.475374817848206</v>
+        <v>0.475374847650528</v>
       </c>
       <c r="H10" t="n">
         <v>133195</v>
@@ -717,7 +717,7 @@
         <v>0.667500019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>0.461881667375565</v>
+        <v>0.461881697177887</v>
       </c>
       <c r="H12" t="n">
         <v>473449</v>
@@ -746,7 +746,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G13" t="n">
-        <v>0.466379404067993</v>
+        <v>0.466379433870316</v>
       </c>
       <c r="H13" t="n">
         <v>70046</v>
@@ -775,7 +775,7 @@
         <v>0.647499978542328</v>
       </c>
       <c r="G14" t="n">
-        <v>0.44804248213768</v>
+        <v>0.448042511940002</v>
       </c>
       <c r="H14" t="n">
         <v>185010</v>
@@ -804,7 +804,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G15" t="n">
-        <v>0.460151791572571</v>
+        <v>0.460151821374893</v>
       </c>
       <c r="H15" t="n">
         <v>66901</v>
@@ -862,7 +862,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G17" t="n">
-        <v>0.467071384191513</v>
+        <v>0.467071443796158</v>
       </c>
       <c r="H17" t="n">
         <v>129282</v>
@@ -891,7 +891,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G18" t="n">
-        <v>0.477450728416443</v>
+        <v>0.477450758218765</v>
       </c>
       <c r="H18" t="n">
         <v>119370</v>
@@ -920,7 +920,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G19" t="n">
-        <v>0.48091048002243</v>
+        <v>0.480910569429398</v>
       </c>
       <c r="H19" t="n">
         <v>50528</v>
@@ -978,7 +978,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G21" t="n">
-        <v>0.476066797971725</v>
+        <v>0.476066827774048</v>
       </c>
       <c r="H21" t="n">
         <v>53225</v>
@@ -1007,7 +1007,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G22" t="n">
-        <v>0.471915006637573</v>
+        <v>0.471915066242218</v>
       </c>
       <c r="H22" t="n">
         <v>58624</v>
@@ -1036,7 +1036,7 @@
         <v>0.66049998998642</v>
       </c>
       <c r="G23" t="n">
-        <v>0.45703798532486</v>
+        <v>0.457037955522537</v>
       </c>
       <c r="H23" t="n">
         <v>70489</v>
@@ -1094,7 +1094,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G25" t="n">
-        <v>0.455308049917221</v>
+        <v>0.455308079719543</v>
       </c>
       <c r="H25" t="n">
         <v>168696</v>
@@ -1123,7 +1123,7 @@
         <v>0.658999979496002</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456000000238419</v>
+        <v>0.456000030040741</v>
       </c>
       <c r="H26" t="n">
         <v>91179</v>
@@ -1152,7 +1152,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G27" t="n">
-        <v>0.445620596408844</v>
+        <v>0.445620685815811</v>
       </c>
       <c r="H27" t="n">
         <v>128286</v>
@@ -1181,7 +1181,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G28" t="n">
-        <v>0.422786086797714</v>
+        <v>0.422786056995392</v>
       </c>
       <c r="H28" t="n">
         <v>174406</v>
@@ -1210,7 +1210,7 @@
         <v>0.619499981403351</v>
       </c>
       <c r="G29" t="n">
-        <v>0.428667664527893</v>
+        <v>0.428667694330215</v>
       </c>
       <c r="H29" t="n">
         <v>258654</v>
@@ -1239,7 +1239,7 @@
         <v>0.614499986171722</v>
       </c>
       <c r="G30" t="n">
-        <v>0.425207912921906</v>
+        <v>0.425207942724228</v>
       </c>
       <c r="H30" t="n">
         <v>100995</v>
@@ -1268,7 +1268,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>0.425553888082504</v>
+        <v>0.425553947687149</v>
       </c>
       <c r="H31" t="n">
         <v>128707</v>
@@ -1297,7 +1297,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G32" t="n">
-        <v>0.438009172677994</v>
+        <v>0.438009142875671</v>
       </c>
       <c r="H32" t="n">
         <v>72389</v>
@@ -1326,7 +1326,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G33" t="n">
-        <v>0.433165431022644</v>
+        <v>0.433165460824966</v>
       </c>
       <c r="H33" t="n">
         <v>214463</v>
@@ -1355,7 +1355,7 @@
         <v>0.627499997615814</v>
       </c>
       <c r="G34" t="n">
-        <v>0.434203386306763</v>
+        <v>0.43420335650444</v>
       </c>
       <c r="H34" t="n">
         <v>449393</v>
@@ -1384,7 +1384,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G35" t="n">
-        <v>0.435933291912079</v>
+        <v>0.435933232307434</v>
       </c>
       <c r="H35" t="n">
         <v>126886</v>
@@ -1413,7 +1413,7 @@
         <v>0.625</v>
       </c>
       <c r="G36" t="n">
-        <v>0.432473510503769</v>
+        <v>0.432473450899124</v>
       </c>
       <c r="H36" t="n">
         <v>45866</v>
@@ -1442,7 +1442,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G37" t="n">
-        <v>0.437317222356796</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H37" t="n">
         <v>59186</v>
@@ -1471,7 +1471,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.435933291912079</v>
+        <v>0.435933232307434</v>
       </c>
       <c r="H38" t="n">
         <v>128161</v>
@@ -1500,7 +1500,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>0.429013699293137</v>
+        <v>0.429013669490814</v>
       </c>
       <c r="H39" t="n">
         <v>68431</v>
@@ -1529,7 +1529,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G40" t="n">
-        <v>0.433857440948486</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H40" t="n">
         <v>83632</v>
@@ -1558,7 +1558,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G41" t="n">
-        <v>0.432127445936203</v>
+        <v>0.432127505540848</v>
       </c>
       <c r="H41" t="n">
         <v>54191</v>
@@ -1587,7 +1587,7 @@
         <v>0.623499989509583</v>
       </c>
       <c r="G42" t="n">
-        <v>0.43143555521965</v>
+        <v>0.431435525417328</v>
       </c>
       <c r="H42" t="n">
         <v>172912</v>
@@ -1616,7 +1616,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G43" t="n">
-        <v>0.431089580059052</v>
+        <v>0.431089550256729</v>
       </c>
       <c r="H43" t="n">
         <v>51995</v>
@@ -1645,7 +1645,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G44" t="n">
-        <v>0.445620596408844</v>
+        <v>0.445620685815811</v>
       </c>
       <c r="H44" t="n">
         <v>148615</v>
@@ -1703,7 +1703,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>0.438701063394547</v>
+        <v>0.438701093196869</v>
       </c>
       <c r="H46" t="n">
         <v>177704</v>
@@ -1732,7 +1732,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G47" t="n">
-        <v>0.431089580059052</v>
+        <v>0.431089550256729</v>
       </c>
       <c r="H47" t="n">
         <v>26658</v>
@@ -1761,7 +1761,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G48" t="n">
-        <v>0.431089580059052</v>
+        <v>0.431089550256729</v>
       </c>
       <c r="H48" t="n">
         <v>122811</v>
@@ -1790,7 +1790,7 @@
         <v>0.621500015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>0.430051684379578</v>
+        <v>0.43005159497261</v>
       </c>
       <c r="H49" t="n">
         <v>65600</v>
@@ -1819,7 +1819,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G50" t="n">
-        <v>0.433857440948486</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H50" t="n">
         <v>138176</v>
@@ -1848,7 +1848,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>0.441468924283981</v>
+        <v>0.441468954086304</v>
       </c>
       <c r="H51" t="n">
         <v>265251</v>
@@ -1877,7 +1877,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G52" t="n">
-        <v>0.438701063394547</v>
+        <v>0.438701093196869</v>
       </c>
       <c r="H52" t="n">
         <v>99992</v>
@@ -1906,7 +1906,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G53" t="n">
-        <v>0.439739048480988</v>
+        <v>0.439739018678665</v>
       </c>
       <c r="H53" t="n">
         <v>22435</v>
@@ -1964,7 +1964,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G55" t="n">
-        <v>0.437317222356796</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H55" t="n">
         <v>76343</v>
@@ -1993,7 +1993,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>0.439393103122711</v>
+        <v>0.439393043518066</v>
       </c>
       <c r="H56" t="n">
         <v>61433</v>
@@ -2051,7 +2051,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G58" t="n">
-        <v>0.433511435985565</v>
+        <v>0.433511406183243</v>
       </c>
       <c r="H58" t="n">
         <v>68965</v>
@@ -2080,7 +2080,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G59" t="n">
-        <v>0.439739048480988</v>
+        <v>0.439739018678665</v>
       </c>
       <c r="H59" t="n">
         <v>123639</v>
@@ -2109,7 +2109,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G60" t="n">
-        <v>0.439739048480988</v>
+        <v>0.439739018678665</v>
       </c>
       <c r="H60" t="n">
         <v>91266</v>
@@ -2167,7 +2167,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.435933291912079</v>
+        <v>0.435933232307434</v>
       </c>
       <c r="H62" t="n">
         <v>79829</v>
@@ -2254,7 +2254,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G65" t="n">
-        <v>0.431781500577927</v>
+        <v>0.431781530380249</v>
       </c>
       <c r="H65" t="n">
         <v>57188</v>
@@ -2283,7 +2283,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G66" t="n">
-        <v>0.432127445936203</v>
+        <v>0.432127505540848</v>
       </c>
       <c r="H66" t="n">
         <v>90493</v>
@@ -2312,7 +2312,7 @@
         <v>0.617500007152557</v>
       </c>
       <c r="G67" t="n">
-        <v>0.427283763885498</v>
+        <v>0.42728379368782</v>
       </c>
       <c r="H67" t="n">
         <v>56153</v>
@@ -2341,7 +2341,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G68" t="n">
-        <v>0.422786086797714</v>
+        <v>0.422786056995392</v>
       </c>
       <c r="H68" t="n">
         <v>79242</v>
@@ -2370,7 +2370,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>0.429013699293137</v>
+        <v>0.429013669490814</v>
       </c>
       <c r="H69" t="n">
         <v>66538</v>
@@ -2399,7 +2399,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>0.425553888082504</v>
+        <v>0.425553947687149</v>
       </c>
       <c r="H70" t="n">
         <v>76151</v>
@@ -2428,7 +2428,7 @@
         <v>0.615499973297119</v>
       </c>
       <c r="G71" t="n">
-        <v>0.425899893045425</v>
+        <v>0.425899833440781</v>
       </c>
       <c r="H71" t="n">
         <v>41570</v>
@@ -2457,7 +2457,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G72" t="n">
-        <v>0.433857440948486</v>
+        <v>0.433857381343842</v>
       </c>
       <c r="H72" t="n">
         <v>69507</v>
@@ -2486,7 +2486,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G73" t="n">
-        <v>0.430397629737854</v>
+        <v>0.430397570133209</v>
       </c>
       <c r="H73" t="n">
         <v>77451</v>
@@ -2544,7 +2544,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>0.435933291912079</v>
+        <v>0.435933232307434</v>
       </c>
       <c r="H75" t="n">
         <v>67899</v>
@@ -2573,7 +2573,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G76" t="n">
-        <v>0.456691980361938</v>
+        <v>0.456692039966583</v>
       </c>
       <c r="H76" t="n">
         <v>204695</v>
@@ -2660,7 +2660,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G79" t="n">
-        <v>0.482294470071793</v>
+        <v>0.482294410467148</v>
       </c>
       <c r="H79" t="n">
         <v>117083</v>
@@ -2689,7 +2689,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G80" t="n">
-        <v>0.479872614145279</v>
+        <v>0.479872584342957</v>
       </c>
       <c r="H80" t="n">
         <v>22198</v>
@@ -2718,7 +2718,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>0.48367840051651</v>
+        <v>0.483678340911865</v>
       </c>
       <c r="H81" t="n">
         <v>129245</v>
@@ -2747,7 +2747,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>0.479180604219437</v>
+        <v>0.479180663824081</v>
       </c>
       <c r="H82" t="n">
         <v>29041</v>
@@ -2776,7 +2776,7 @@
         <v>0.683499991893768</v>
       </c>
       <c r="G83" t="n">
-        <v>0.472952991724014</v>
+        <v>0.472952961921692</v>
       </c>
       <c r="H83" t="n">
         <v>57129</v>
@@ -2805,7 +2805,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G84" t="n">
-        <v>0.463611602783203</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H84" t="n">
         <v>97915</v>
@@ -2863,7 +2863,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G86" t="n">
-        <v>0.446312636137009</v>
+        <v>0.446312576532364</v>
       </c>
       <c r="H86" t="n">
         <v>147100</v>
@@ -2892,7 +2892,7 @@
         <v>0.648500025272369</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4487344622612</v>
+        <v>0.448734521865845</v>
       </c>
       <c r="H87" t="n">
         <v>20302</v>
@@ -2950,7 +2950,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G89" t="n">
-        <v>0.445620596408844</v>
+        <v>0.445620685815811</v>
       </c>
       <c r="H89" t="n">
         <v>81033</v>
@@ -2979,7 +2979,7 @@
         <v>0.637000024318695</v>
       </c>
       <c r="G90" t="n">
-        <v>0.440776973962784</v>
+        <v>0.440777003765106</v>
       </c>
       <c r="H90" t="n">
         <v>76399</v>
@@ -3008,7 +3008,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G91" t="n">
-        <v>0.438701063394547</v>
+        <v>0.438701093196869</v>
       </c>
       <c r="H91" t="n">
         <v>29862</v>
@@ -3037,7 +3037,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>0.435933291912079</v>
+        <v>0.435933232307434</v>
       </c>
       <c r="H92" t="n">
         <v>127499</v>
@@ -3066,7 +3066,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G93" t="n">
-        <v>0.442852884531021</v>
+        <v>0.442852795124054</v>
       </c>
       <c r="H93" t="n">
         <v>137577</v>
@@ -3124,7 +3124,7 @@
         <v>0.656499981880188</v>
       </c>
       <c r="G95" t="n">
-        <v>0.454270124435425</v>
+        <v>0.454270154237747</v>
       </c>
       <c r="H95" t="n">
         <v>28570</v>
@@ -3153,7 +3153,7 @@
         <v>0.647499978542328</v>
       </c>
       <c r="G96" t="n">
-        <v>0.44804248213768</v>
+        <v>0.448042511940002</v>
       </c>
       <c r="H96" t="n">
         <v>27367</v>
@@ -3182,7 +3182,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G97" t="n">
-        <v>0.442852884531021</v>
+        <v>0.442852795124054</v>
       </c>
       <c r="H97" t="n">
         <v>41726</v>
@@ -3211,7 +3211,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G98" t="n">
-        <v>0.442852884531021</v>
+        <v>0.442852795124054</v>
       </c>
       <c r="H98" t="n">
         <v>43674</v>
@@ -3240,7 +3240,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>0.439393103122711</v>
+        <v>0.439393043518066</v>
       </c>
       <c r="H99" t="n">
         <v>79566</v>
@@ -3501,7 +3501,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G108" t="n">
-        <v>0.479180604219437</v>
+        <v>0.479180663824081</v>
       </c>
       <c r="H108" t="n">
         <v>5363</v>
@@ -3588,7 +3588,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G111" t="n">
-        <v>0.477450728416443</v>
+        <v>0.477450758218765</v>
       </c>
       <c r="H111" t="n">
         <v>81596</v>
@@ -3617,7 +3617,7 @@
         <v>0.67849999666214</v>
       </c>
       <c r="G112" t="n">
-        <v>0.469493210315704</v>
+        <v>0.46949315071106</v>
       </c>
       <c r="H112" t="n">
         <v>80180</v>
@@ -3733,7 +3733,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G116" t="n">
-        <v>0.442852884531021</v>
+        <v>0.442852795124054</v>
       </c>
       <c r="H116" t="n">
         <v>203916</v>
@@ -3762,7 +3762,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G117" t="n">
-        <v>0.449080467224121</v>
+        <v>0.449080497026443</v>
       </c>
       <c r="H117" t="n">
         <v>50524</v>
@@ -3791,7 +3791,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G118" t="n">
-        <v>0.437317222356796</v>
+        <v>0.437317162752151</v>
       </c>
       <c r="H118" t="n">
         <v>37197</v>
@@ -3820,7 +3820,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G119" t="n">
-        <v>0.447004646062851</v>
+        <v>0.447004586458206</v>
       </c>
       <c r="H119" t="n">
         <v>21491</v>
@@ -3849,7 +3849,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G120" t="n">
-        <v>0.442852884531021</v>
+        <v>0.442852795124054</v>
       </c>
       <c r="H120" t="n">
         <v>89237</v>
@@ -3907,7 +3907,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G122" t="n">
-        <v>0.445966690778732</v>
+        <v>0.44596666097641</v>
       </c>
       <c r="H122" t="n">
         <v>33393</v>
@@ -3936,7 +3936,7 @@
         <v>0.653500020503998</v>
       </c>
       <c r="G123" t="n">
-        <v>0.45219424366951</v>
+        <v>0.452194303274155</v>
       </c>
       <c r="H123" t="n">
         <v>111165</v>
@@ -3994,7 +3994,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G125" t="n">
-        <v>0.419326305389404</v>
+        <v>0.41932624578476</v>
       </c>
       <c r="H125" t="n">
         <v>164285</v>
@@ -4023,7 +4023,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G126" t="n">
-        <v>0.436625242233276</v>
+        <v>0.436625212430954</v>
       </c>
       <c r="H126" t="n">
         <v>99483</v>
@@ -4052,7 +4052,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G127" t="n">
-        <v>0.442852884531021</v>
+        <v>0.442852795124054</v>
       </c>
       <c r="H127" t="n">
         <v>82500</v>
@@ -4081,7 +4081,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>0.441468924283981</v>
+        <v>0.441468954086304</v>
       </c>
       <c r="H128" t="n">
         <v>49996</v>
@@ -4139,7 +4139,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>0.455308049917221</v>
+        <v>0.455308079719543</v>
       </c>
       <c r="H130" t="n">
         <v>41364</v>
@@ -4197,7 +4197,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G132" t="n">
-        <v>0.438701063394547</v>
+        <v>0.438701093196869</v>
       </c>
       <c r="H132" t="n">
         <v>188187</v>
@@ -4226,7 +4226,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G133" t="n">
-        <v>0.442852884531021</v>
+        <v>0.442852795124054</v>
       </c>
       <c r="H133" t="n">
         <v>152250</v>
@@ -4255,7 +4255,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G134" t="n">
-        <v>0.449772447347641</v>
+        <v>0.449772387742996</v>
       </c>
       <c r="H134" t="n">
         <v>24993</v>
@@ -4400,7 +4400,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>0.476758748292923</v>
+        <v>0.476758778095245</v>
       </c>
       <c r="H139" t="n">
         <v>24754</v>
@@ -4516,7 +4516,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>0.476758748292923</v>
+        <v>0.476758778095245</v>
       </c>
       <c r="H143" t="n">
         <v>31703</v>
@@ -4545,7 +4545,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G144" t="n">
-        <v>0.463611602783203</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H144" t="n">
         <v>51317</v>
@@ -4574,7 +4574,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G145" t="n">
-        <v>0.467071384191513</v>
+        <v>0.467071443796158</v>
       </c>
       <c r="H145" t="n">
         <v>48503</v>
@@ -4632,7 +4632,7 @@
         <v>0.67849999666214</v>
       </c>
       <c r="G147" t="n">
-        <v>0.469493210315704</v>
+        <v>0.46949315071106</v>
       </c>
       <c r="H147" t="n">
         <v>51357</v>
@@ -4661,7 +4661,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.477450728416443</v>
+        <v>0.477450758218765</v>
       </c>
       <c r="H148" t="n">
         <v>324437</v>
@@ -4719,7 +4719,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G150" t="n">
-        <v>0.466033458709717</v>
+        <v>0.466033428907394</v>
       </c>
       <c r="H150" t="n">
         <v>34614</v>
@@ -4748,7 +4748,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G151" t="n">
-        <v>0.461535662412643</v>
+        <v>0.461535722017288</v>
       </c>
       <c r="H151" t="n">
         <v>33263</v>
@@ -4777,7 +4777,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G152" t="n">
-        <v>0.456691980361938</v>
+        <v>0.456692039966583</v>
       </c>
       <c r="H152" t="n">
         <v>55357</v>
@@ -4806,7 +4806,7 @@
         <v>0.656499981880188</v>
       </c>
       <c r="G153" t="n">
-        <v>0.454270124435425</v>
+        <v>0.454270154237747</v>
       </c>
       <c r="H153" t="n">
         <v>42442</v>
@@ -4835,7 +4835,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G154" t="n">
-        <v>0.461535662412643</v>
+        <v>0.461535722017288</v>
       </c>
       <c r="H154" t="n">
         <v>28966</v>
@@ -4893,7 +4893,7 @@
         <v>0.664499998092651</v>
       </c>
       <c r="G156" t="n">
-        <v>0.459805846214294</v>
+        <v>0.459805816411972</v>
       </c>
       <c r="H156" t="n">
         <v>20377</v>
@@ -4922,7 +4922,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G157" t="n">
-        <v>0.461535662412643</v>
+        <v>0.461535722017288</v>
       </c>
       <c r="H157" t="n">
         <v>185257</v>
@@ -4951,7 +4951,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>0.466033458709717</v>
+        <v>0.466033428907394</v>
       </c>
       <c r="H158" t="n">
         <v>5763</v>
@@ -4980,7 +4980,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G159" t="n">
-        <v>0.460497796535492</v>
+        <v>0.460497736930847</v>
       </c>
       <c r="H159" t="n">
         <v>12129</v>
@@ -5009,7 +5009,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G160" t="n">
-        <v>0.456691980361938</v>
+        <v>0.456692039966583</v>
       </c>
       <c r="H160" t="n">
         <v>36233</v>
@@ -5038,7 +5038,7 @@
         <v>0.662999987602234</v>
       </c>
       <c r="G161" t="n">
-        <v>0.458767861127853</v>
+        <v>0.458767801523209</v>
       </c>
       <c r="H161" t="n">
         <v>38164</v>
@@ -5125,7 +5125,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G164" t="n">
-        <v>0.460151791572571</v>
+        <v>0.460151821374893</v>
       </c>
       <c r="H164" t="n">
         <v>39400</v>
@@ -5154,7 +5154,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G165" t="n">
-        <v>0.469839185476303</v>
+        <v>0.469839215278625</v>
       </c>
       <c r="H165" t="n">
         <v>29550</v>
@@ -5183,7 +5183,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G166" t="n">
-        <v>0.469147205352783</v>
+        <v>0.46914729475975</v>
       </c>
       <c r="H166" t="n">
         <v>9905</v>
@@ -5241,7 +5241,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>0.473298996686935</v>
+        <v>0.473299026489258</v>
       </c>
       <c r="H168" t="n">
         <v>14300</v>
@@ -5270,7 +5270,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G169" t="n">
-        <v>0.473298996686935</v>
+        <v>0.473299026489258</v>
       </c>
       <c r="H169" t="n">
         <v>1644</v>
@@ -5299,7 +5299,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G170" t="n">
-        <v>0.463611602783203</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H170" t="n">
         <v>58222</v>
@@ -5328,7 +5328,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G171" t="n">
-        <v>0.469147205352783</v>
+        <v>0.46914729475975</v>
       </c>
       <c r="H171" t="n">
         <v>30801</v>
@@ -5386,7 +5386,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G173" t="n">
-        <v>0.463611602783203</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H173" t="n">
         <v>25441</v>
@@ -5415,7 +5415,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G174" t="n">
-        <v>0.460497796535492</v>
+        <v>0.460497736930847</v>
       </c>
       <c r="H174" t="n">
         <v>28021</v>
@@ -5444,7 +5444,7 @@
         <v>0.67849999666214</v>
       </c>
       <c r="G175" t="n">
-        <v>0.469493210315704</v>
+        <v>0.46949315071106</v>
       </c>
       <c r="H175" t="n">
         <v>16908</v>
@@ -5473,7 +5473,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G176" t="n">
-        <v>0.460497796535492</v>
+        <v>0.460497736930847</v>
       </c>
       <c r="H176" t="n">
         <v>54782</v>
@@ -5502,7 +5502,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G177" t="n">
-        <v>0.461535662412643</v>
+        <v>0.461535722017288</v>
       </c>
       <c r="H177" t="n">
         <v>71591</v>
@@ -5531,7 +5531,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G178" t="n">
-        <v>0.456691980361938</v>
+        <v>0.456692039966583</v>
       </c>
       <c r="H178" t="n">
         <v>143013</v>
@@ -5589,7 +5589,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G180" t="n">
-        <v>0.449772447347641</v>
+        <v>0.449772387742996</v>
       </c>
       <c r="H180" t="n">
         <v>88496</v>
@@ -5647,7 +5647,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G182" t="n">
-        <v>0.456691980361938</v>
+        <v>0.456692039966583</v>
       </c>
       <c r="H182" t="n">
         <v>58262</v>
@@ -5705,7 +5705,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G184" t="n">
-        <v>0.447004646062851</v>
+        <v>0.447004586458206</v>
       </c>
       <c r="H184" t="n">
         <v>66988</v>
@@ -5734,7 +5734,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>0.446312636137009</v>
+        <v>0.446312576532364</v>
       </c>
       <c r="H185" t="n">
         <v>52383</v>
@@ -5763,7 +5763,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>0.446312636137009</v>
+        <v>0.446312576532364</v>
       </c>
       <c r="H186" t="n">
         <v>75110</v>
@@ -5792,7 +5792,7 @@
         <v>0.655499994754791</v>
       </c>
       <c r="G187" t="n">
-        <v>0.453578174114227</v>
+        <v>0.453578144311905</v>
       </c>
       <c r="H187" t="n">
         <v>59490</v>
@@ -5850,7 +5850,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G189" t="n">
-        <v>0.461535662412643</v>
+        <v>0.461535722017288</v>
       </c>
       <c r="H189" t="n">
         <v>176240</v>
@@ -5879,7 +5879,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G190" t="n">
-        <v>0.464995473623276</v>
+        <v>0.464995533227921</v>
       </c>
       <c r="H190" t="n">
         <v>160048</v>
@@ -5966,7 +5966,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G193" t="n">
-        <v>0.471223086118698</v>
+        <v>0.471223115921021</v>
       </c>
       <c r="H193" t="n">
         <v>122424</v>
@@ -6024,7 +6024,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G195" t="n">
-        <v>0.467763334512711</v>
+        <v>0.467763304710388</v>
       </c>
       <c r="H195" t="n">
         <v>18570</v>
@@ -6082,7 +6082,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G197" t="n">
-        <v>0.463611602783203</v>
+        <v>0.463611632585526</v>
       </c>
       <c r="H197" t="n">
         <v>99568</v>
@@ -6140,7 +6140,7 @@
         <v>0.67849999666214</v>
       </c>
       <c r="G199" t="n">
-        <v>0.469493210315704</v>
+        <v>0.46949315071106</v>
       </c>
       <c r="H199" t="n">
         <v>30898</v>
@@ -6198,7 +6198,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G201" t="n">
-        <v>0.482294470071793</v>
+        <v>0.482294410467148</v>
       </c>
       <c r="H201" t="n">
         <v>209149</v>
@@ -6285,7 +6285,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>0.489214062690735</v>
+        <v>0.489213973283768</v>
       </c>
       <c r="H204" t="n">
         <v>146400</v>
@@ -6343,7 +6343,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>0.503053188323975</v>
+        <v>0.50305312871933</v>
       </c>
       <c r="H206" t="n">
         <v>66811</v>
@@ -6372,7 +6372,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G207" t="n">
-        <v>0.508588850498199</v>
+        <v>0.508588790893555</v>
       </c>
       <c r="H207" t="n">
         <v>181176</v>
@@ -6401,7 +6401,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G208" t="n">
-        <v>0.522427916526794</v>
+        <v>0.522427976131439</v>
       </c>
       <c r="H208" t="n">
         <v>776683</v>
@@ -6430,7 +6430,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H209" t="n">
         <v>531491</v>
@@ -6488,7 +6488,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G211" t="n">
-        <v>0.51689225435257</v>
+        <v>0.516892313957214</v>
       </c>
       <c r="H211" t="n">
         <v>202768</v>
@@ -6517,7 +6517,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G212" t="n">
-        <v>0.517584323883057</v>
+        <v>0.517584264278412</v>
       </c>
       <c r="H212" t="n">
         <v>70577</v>
@@ -6546,7 +6546,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>0.522427916526794</v>
+        <v>0.522427976131439</v>
       </c>
       <c r="H213" t="n">
         <v>130992</v>
@@ -6575,7 +6575,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G214" t="n">
-        <v>0.511702597141266</v>
+        <v>0.511702656745911</v>
       </c>
       <c r="H214" t="n">
         <v>26428</v>
@@ -6662,7 +6662,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>0.497863441705704</v>
+        <v>0.497863501310349</v>
       </c>
       <c r="H217" t="n">
         <v>168732</v>
@@ -6691,7 +6691,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G218" t="n">
-        <v>0.49128982424736</v>
+        <v>0.491289854049683</v>
       </c>
       <c r="H218" t="n">
         <v>56648</v>
@@ -6720,7 +6720,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G219" t="n">
-        <v>0.497863441705704</v>
+        <v>0.497863501310349</v>
       </c>
       <c r="H219" t="n">
         <v>110019</v>
@@ -6749,7 +6749,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G220" t="n">
-        <v>0.499247372150421</v>
+        <v>0.499247342348099</v>
       </c>
       <c r="H220" t="n">
         <v>33506</v>
@@ -6778,7 +6778,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G221" t="n">
-        <v>0.49544158577919</v>
+        <v>0.495441645383835</v>
       </c>
       <c r="H221" t="n">
         <v>150686</v>
@@ -6807,7 +6807,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G222" t="n">
-        <v>0.49128982424736</v>
+        <v>0.491289854049683</v>
       </c>
       <c r="H222" t="n">
         <v>140896</v>
@@ -6836,7 +6836,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G223" t="n">
-        <v>0.49128982424736</v>
+        <v>0.491289854049683</v>
       </c>
       <c r="H223" t="n">
         <v>73200</v>
@@ -6865,7 +6865,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G224" t="n">
-        <v>0.498209476470947</v>
+        <v>0.498209416866302</v>
       </c>
       <c r="H224" t="n">
         <v>27258</v>
@@ -6894,7 +6894,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.49128982424736</v>
+        <v>0.491289854049683</v>
       </c>
       <c r="H225" t="n">
         <v>52932</v>
@@ -6923,7 +6923,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G226" t="n">
-        <v>0.49544158577919</v>
+        <v>0.495441645383835</v>
       </c>
       <c r="H226" t="n">
         <v>79074</v>
@@ -6952,7 +6952,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G227" t="n">
-        <v>0.494057685136795</v>
+        <v>0.49405762553215</v>
       </c>
       <c r="H227" t="n">
         <v>51852</v>
@@ -6981,7 +6981,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G228" t="n">
-        <v>0.491981774568558</v>
+        <v>0.491981863975525</v>
       </c>
       <c r="H228" t="n">
         <v>257048</v>
@@ -7010,7 +7010,7 @@
         <v>0.704500019550323</v>
       </c>
       <c r="G229" t="n">
-        <v>0.487484097480774</v>
+        <v>0.487484067678452</v>
       </c>
       <c r="H229" t="n">
         <v>103047</v>
@@ -7039,7 +7039,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G230" t="n">
-        <v>0.485754251480103</v>
+        <v>0.48575422167778</v>
       </c>
       <c r="H230" t="n">
         <v>149866</v>
@@ -7097,7 +7097,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G232" t="n">
-        <v>0.497863441705704</v>
+        <v>0.497863501310349</v>
       </c>
       <c r="H232" t="n">
         <v>218985</v>
@@ -7126,7 +7126,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G233" t="n">
-        <v>0.498209476470947</v>
+        <v>0.498209416866302</v>
       </c>
       <c r="H233" t="n">
         <v>26904</v>
@@ -7155,7 +7155,7 @@
         <v>0.706499993801117</v>
       </c>
       <c r="G234" t="n">
-        <v>0.488868027925491</v>
+        <v>0.488867968320847</v>
       </c>
       <c r="H234" t="n">
         <v>54717</v>
@@ -7213,7 +7213,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G236" t="n">
-        <v>0.492673873901367</v>
+        <v>0.492673724889755</v>
       </c>
       <c r="H236" t="n">
         <v>271535</v>
@@ -7242,7 +7242,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G237" t="n">
-        <v>0.492673873901367</v>
+        <v>0.492673724889755</v>
       </c>
       <c r="H237" t="n">
         <v>16612</v>
@@ -7271,7 +7271,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G238" t="n">
-        <v>0.49128982424736</v>
+        <v>0.491289854049683</v>
       </c>
       <c r="H238" t="n">
         <v>43905</v>
@@ -7300,7 +7300,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G239" t="n">
-        <v>0.491981774568558</v>
+        <v>0.491981863975525</v>
       </c>
       <c r="H239" t="n">
         <v>23384</v>
@@ -7532,7 +7532,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G247" t="n">
-        <v>0.51689225435257</v>
+        <v>0.516892313957214</v>
       </c>
       <c r="H247" t="n">
         <v>57020</v>
@@ -7590,7 +7590,7 @@
         <v>0.770500004291534</v>
       </c>
       <c r="G249" t="n">
-        <v>0.533153295516968</v>
+        <v>0.533153235912323</v>
       </c>
       <c r="H249" t="n">
         <v>288004</v>
@@ -7619,7 +7619,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G250" t="n">
-        <v>0.521735966205597</v>
+        <v>0.521736025810242</v>
       </c>
       <c r="H250" t="n">
         <v>387529</v>
@@ -7706,7 +7706,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G253" t="n">
-        <v>0.517584323883057</v>
+        <v>0.517584264278412</v>
       </c>
       <c r="H253" t="n">
         <v>73514</v>
@@ -7735,7 +7735,7 @@
         <v>0.752499997615814</v>
       </c>
       <c r="G254" t="n">
-        <v>0.520698130130768</v>
+        <v>0.520698070526123</v>
       </c>
       <c r="H254" t="n">
         <v>83322</v>
@@ -7822,7 +7822,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G257" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352125167847</v>
       </c>
       <c r="H257" t="n">
         <v>97060</v>
@@ -7851,7 +7851,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G258" t="n">
-        <v>0.530039489269257</v>
+        <v>0.530039429664612</v>
       </c>
       <c r="H258" t="n">
         <v>222408</v>
@@ -7880,7 +7880,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>0.539380848407745</v>
+        <v>0.539380967617035</v>
       </c>
       <c r="H259" t="n">
         <v>357651</v>
@@ -7909,7 +7909,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G260" t="n">
-        <v>0.534883141517639</v>
+        <v>0.534883201122284</v>
       </c>
       <c r="H260" t="n">
         <v>183482</v>
@@ -7938,7 +7938,7 @@
         <v>0.786499977111816</v>
       </c>
       <c r="G261" t="n">
-        <v>0.544224560260773</v>
+        <v>0.544224619865417</v>
       </c>
       <c r="H261" t="n">
         <v>626780</v>
@@ -8083,7 +8083,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G266" t="n">
-        <v>0.535575211048126</v>
+        <v>0.535575151443481</v>
       </c>
       <c r="H266" t="n">
         <v>145736</v>
@@ -8112,7 +8112,7 @@
         <v>0.77649998664856</v>
       </c>
       <c r="G267" t="n">
-        <v>0.537304997444153</v>
+        <v>0.537305116653442</v>
       </c>
       <c r="H267" t="n">
         <v>188591</v>
@@ -8141,7 +8141,7 @@
         <v>0.780499994754791</v>
       </c>
       <c r="G268" t="n">
-        <v>0.540072858333588</v>
+        <v>0.540072917938232</v>
       </c>
       <c r="H268" t="n">
         <v>230939</v>
@@ -8257,7 +8257,7 @@
         <v>0.768499970436096</v>
       </c>
       <c r="G272" t="n">
-        <v>0.531769335269928</v>
+        <v>0.531769394874573</v>
       </c>
       <c r="H272" t="n">
         <v>168992</v>
@@ -8315,7 +8315,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G274" t="n">
-        <v>0.542494714260101</v>
+        <v>0.542494773864746</v>
       </c>
       <c r="H274" t="n">
         <v>94788</v>
@@ -8344,7 +8344,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>0.539380848407745</v>
+        <v>0.539380967617035</v>
       </c>
       <c r="H275" t="n">
         <v>94758</v>
@@ -8431,7 +8431,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H278" t="n">
         <v>193866</v>
@@ -8460,7 +8460,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G279" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352125167847</v>
       </c>
       <c r="H279" t="n">
         <v>87634</v>
@@ -8547,7 +8547,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G282" t="n">
-        <v>0.532115399837494</v>
+        <v>0.532115340232849</v>
       </c>
       <c r="H282" t="n">
         <v>42049</v>
@@ -8576,7 +8576,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G283" t="n">
-        <v>0.527271628379822</v>
+        <v>0.527271747589111</v>
       </c>
       <c r="H283" t="n">
         <v>131626</v>
@@ -8634,7 +8634,7 @@
         <v>0.752499997615814</v>
       </c>
       <c r="G285" t="n">
-        <v>0.520698130130768</v>
+        <v>0.520698070526123</v>
       </c>
       <c r="H285" t="n">
         <v>82797</v>
@@ -8692,7 +8692,7 @@
         <v>0.768499970436096</v>
       </c>
       <c r="G287" t="n">
-        <v>0.531769335269928</v>
+        <v>0.531769394874573</v>
       </c>
       <c r="H287" t="n">
         <v>41327</v>
@@ -8721,7 +8721,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G288" t="n">
-        <v>0.535575211048126</v>
+        <v>0.535575151443481</v>
       </c>
       <c r="H288" t="n">
         <v>191680</v>
@@ -9011,7 +9011,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G298" t="n">
-        <v>0.515508413314819</v>
+        <v>0.515508353710175</v>
       </c>
       <c r="H298" t="n">
         <v>476154</v>
@@ -9040,7 +9040,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G299" t="n">
-        <v>0.524503827095032</v>
+        <v>0.524503767490387</v>
       </c>
       <c r="H299" t="n">
         <v>291053</v>
@@ -9069,7 +9069,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H300" t="n">
         <v>148794</v>
@@ -9098,7 +9098,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>0.522427916526794</v>
+        <v>0.522427976131439</v>
       </c>
       <c r="H301" t="n">
         <v>200433</v>
@@ -9127,7 +9127,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>0.515508413314819</v>
+        <v>0.515508353710175</v>
       </c>
       <c r="H302" t="n">
         <v>169321</v>
@@ -9185,7 +9185,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G304" t="n">
-        <v>0.511702597141266</v>
+        <v>0.511702656745911</v>
       </c>
       <c r="H304" t="n">
         <v>67866</v>
@@ -9243,7 +9243,7 @@
         <v>0.738499999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>0.511010706424713</v>
+        <v>0.511010646820068</v>
       </c>
       <c r="H306" t="n">
         <v>46683</v>
@@ -9301,7 +9301,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>0.503053188323975</v>
+        <v>0.50305312871933</v>
       </c>
       <c r="H308" t="n">
         <v>393889</v>
@@ -9330,7 +9330,7 @@
         <v>0.732500016689301</v>
       </c>
       <c r="G309" t="n">
-        <v>0.506858944892883</v>
+        <v>0.506858885288239</v>
       </c>
       <c r="H309" t="n">
         <v>354387</v>
@@ -9359,7 +9359,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G310" t="n">
-        <v>0.510664641857147</v>
+        <v>0.510664701461792</v>
       </c>
       <c r="H310" t="n">
         <v>313882</v>
@@ -9417,7 +9417,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G312" t="n">
-        <v>0.505475044250488</v>
+        <v>0.505474984645844</v>
       </c>
       <c r="H312" t="n">
         <v>231484</v>
@@ -9475,7 +9475,7 @@
         <v>0.737500011920929</v>
       </c>
       <c r="G314" t="n">
-        <v>0.510318756103516</v>
+        <v>0.510318696498871</v>
       </c>
       <c r="H314" t="n">
         <v>65146</v>
@@ -9504,7 +9504,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>0.506512939929962</v>
+        <v>0.506512880325317</v>
       </c>
       <c r="H315" t="n">
         <v>166630</v>
@@ -9591,7 +9591,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G318" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896840572357</v>
       </c>
       <c r="H318" t="n">
         <v>156057</v>
@@ -9765,7 +9765,7 @@
         <v>0.737500011920929</v>
       </c>
       <c r="G324" t="n">
-        <v>0.510318756103516</v>
+        <v>0.510318696498871</v>
       </c>
       <c r="H324" t="n">
         <v>37689</v>
@@ -9823,7 +9823,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G326" t="n">
-        <v>0.508588850498199</v>
+        <v>0.508588790893555</v>
       </c>
       <c r="H326" t="n">
         <v>145557</v>
@@ -9852,7 +9852,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G327" t="n">
-        <v>0.508588850498199</v>
+        <v>0.508588790893555</v>
       </c>
       <c r="H327" t="n">
         <v>117509</v>
@@ -9910,7 +9910,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G329" t="n">
-        <v>0.505475044250488</v>
+        <v>0.505474984645844</v>
       </c>
       <c r="H329" t="n">
         <v>80896</v>
@@ -9968,7 +9968,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G331" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896840572357</v>
       </c>
       <c r="H331" t="n">
         <v>177163</v>
@@ -9997,7 +9997,7 @@
         <v>0.728500008583069</v>
       </c>
       <c r="G332" t="n">
-        <v>0.504091084003448</v>
+        <v>0.504091143608093</v>
       </c>
       <c r="H332" t="n">
         <v>61694</v>
@@ -10055,7 +10055,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G334" t="n">
-        <v>0.499247372150421</v>
+        <v>0.499247342348099</v>
       </c>
       <c r="H334" t="n">
         <v>67876</v>
@@ -10113,7 +10113,7 @@
         <v>0.726499974727631</v>
       </c>
       <c r="G336" t="n">
-        <v>0.502707183361053</v>
+        <v>0.502707123756409</v>
       </c>
       <c r="H336" t="n">
         <v>229492</v>
@@ -10258,7 +10258,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G341" t="n">
-        <v>0.511702597141266</v>
+        <v>0.511702656745911</v>
       </c>
       <c r="H341" t="n">
         <v>282369</v>
@@ -10345,7 +10345,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G344" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896840572357</v>
       </c>
       <c r="H344" t="n">
         <v>119791</v>
@@ -10374,7 +10374,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G345" t="n">
-        <v>0.507896900177002</v>
+        <v>0.507896840572357</v>
       </c>
       <c r="H345" t="n">
         <v>167117</v>
@@ -10432,7 +10432,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G347" t="n">
-        <v>0.508588850498199</v>
+        <v>0.508588790893555</v>
       </c>
       <c r="H347" t="n">
         <v>152359</v>
@@ -10461,7 +10461,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G348" t="n">
-        <v>0.523119926452637</v>
+        <v>0.523119866847992</v>
       </c>
       <c r="H348" t="n">
         <v>810246</v>
@@ -10490,7 +10490,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H349" t="n">
         <v>179526</v>
@@ -10519,7 +10519,7 @@
         <v>0.762499988079071</v>
       </c>
       <c r="G350" t="n">
-        <v>0.527617633342743</v>
+        <v>0.527617692947388</v>
       </c>
       <c r="H350" t="n">
         <v>372168</v>
@@ -10548,7 +10548,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>0.522427916526794</v>
+        <v>0.522427976131439</v>
       </c>
       <c r="H351" t="n">
         <v>151622</v>
@@ -10635,7 +10635,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G354" t="n">
-        <v>0.516546368598938</v>
+        <v>0.516546308994293</v>
       </c>
       <c r="H354" t="n">
         <v>168237</v>
@@ -10809,7 +10809,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G360" t="n">
-        <v>0.520352065563202</v>
+        <v>0.520352125167847</v>
       </c>
       <c r="H360" t="n">
         <v>471079</v>
@@ -10838,7 +10838,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>0.525887727737427</v>
+        <v>0.525887787342072</v>
       </c>
       <c r="H361" t="n">
         <v>250363</v>
@@ -10867,7 +10867,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G362" t="n">
-        <v>0.526579737663269</v>
+        <v>0.526579678058624</v>
       </c>
       <c r="H362" t="n">
         <v>397546</v>
@@ -10925,7 +10925,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G364" t="n">
-        <v>0.530039489269257</v>
+        <v>0.530039429664612</v>
       </c>
       <c r="H364" t="n">
         <v>126381</v>
@@ -11041,7 +11041,7 @@
         <v>0.798500001430511</v>
       </c>
       <c r="G368" t="n">
-        <v>0.552528142929077</v>
+        <v>0.552528202533722</v>
       </c>
       <c r="H368" t="n">
         <v>1262207</v>
@@ -11099,7 +11099,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G370" t="n">
-        <v>0.568097174167633</v>
+        <v>0.568097114562988</v>
       </c>
       <c r="H370" t="n">
         <v>385663</v>
@@ -11128,7 +11128,7 @@
         <v>0.82150000333786</v>
       </c>
       <c r="G371" t="n">
-        <v>0.568443179130554</v>
+        <v>0.568443119525909</v>
       </c>
       <c r="H371" t="n">
         <v>388142</v>
@@ -11157,7 +11157,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G372" t="n">
-        <v>0.571556925773621</v>
+        <v>0.571556866168976</v>
       </c>
       <c r="H372" t="n">
         <v>236280</v>
@@ -11273,7 +11273,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G376" t="n">
-        <v>0.572940826416016</v>
+        <v>0.57294088602066</v>
       </c>
       <c r="H376" t="n">
         <v>368824</v>
@@ -11302,7 +11302,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G377" t="n">
-        <v>0.590239822864532</v>
+        <v>0.590239763259888</v>
       </c>
       <c r="H377" t="n">
         <v>1194426</v>
@@ -11418,7 +11418,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G381" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H381" t="n">
         <v>815667</v>
@@ -11505,7 +11505,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G384" t="n">
-        <v>0.646980345249176</v>
+        <v>0.646980285644531</v>
       </c>
       <c r="H384" t="n">
         <v>344710</v>
@@ -11592,7 +11592,7 @@
         <v>0.915499985218048</v>
       </c>
       <c r="G387" t="n">
-        <v>0.633487164974213</v>
+        <v>0.633487105369568</v>
       </c>
       <c r="H387" t="n">
         <v>347087</v>
@@ -11679,7 +11679,7 @@
         <v>0.936500012874603</v>
       </c>
       <c r="G390" t="n">
-        <v>0.648018300533295</v>
+        <v>0.64801824092865</v>
       </c>
       <c r="H390" t="n">
         <v>352242</v>
@@ -11708,7 +11708,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G391" t="n">
-        <v>0.646980345249176</v>
+        <v>0.646980285644531</v>
       </c>
       <c r="H391" t="n">
         <v>101808</v>
@@ -11737,7 +11737,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G392" t="n">
-        <v>0.638676822185516</v>
+        <v>0.638676762580872</v>
       </c>
       <c r="H392" t="n">
         <v>245408</v>
@@ -11766,7 +11766,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H393" t="n">
         <v>203449</v>
@@ -11824,7 +11824,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G395" t="n">
-        <v>0.638676822185516</v>
+        <v>0.638676762580872</v>
       </c>
       <c r="H395" t="n">
         <v>155679</v>
@@ -11853,7 +11853,7 @@
         <v>0.915499985218048</v>
       </c>
       <c r="G396" t="n">
-        <v>0.633487164974213</v>
+        <v>0.633487105369568</v>
       </c>
       <c r="H396" t="n">
         <v>82781</v>
@@ -11940,7 +11940,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G399" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H399" t="n">
         <v>161711</v>
@@ -12056,7 +12056,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G403" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H403" t="n">
         <v>1563687</v>
@@ -12085,7 +12085,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G404" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H404" t="n">
         <v>400954</v>
@@ -12172,7 +12172,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G407" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H407" t="n">
         <v>133207</v>
@@ -12230,7 +12230,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G409" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H409" t="n">
         <v>132125</v>
@@ -12259,7 +12259,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G410" t="n">
-        <v>0.615150332450867</v>
+        <v>0.615150213241577</v>
       </c>
       <c r="H410" t="n">
         <v>168974</v>
@@ -12346,7 +12346,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G413" t="n">
-        <v>0.617918074131012</v>
+        <v>0.617918193340302</v>
       </c>
       <c r="H413" t="n">
         <v>39750</v>
@@ -12375,7 +12375,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G414" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H414" t="n">
         <v>199929</v>
@@ -12404,7 +12404,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G415" t="n">
-        <v>0.617226123809814</v>
+        <v>0.617226183414459</v>
       </c>
       <c r="H415" t="n">
         <v>41393</v>
@@ -12636,7 +12636,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G423" t="n">
-        <v>0.615150332450867</v>
+        <v>0.615150213241577</v>
       </c>
       <c r="H423" t="n">
         <v>102772</v>
@@ -12694,7 +12694,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H425" t="n">
         <v>113618</v>
@@ -12723,7 +12723,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H426" t="n">
         <v>30382</v>
@@ -12868,7 +12868,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G431" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H431" t="n">
         <v>101366</v>
@@ -12926,7 +12926,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G433" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H433" t="n">
         <v>94241</v>
@@ -12955,7 +12955,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>0.612382411956787</v>
+        <v>0.612382471561432</v>
       </c>
       <c r="H434" t="n">
         <v>63978</v>
@@ -12984,7 +12984,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G435" t="n">
-        <v>0.612036526203156</v>
+        <v>0.612036466598511</v>
       </c>
       <c r="H435" t="n">
         <v>112829</v>
@@ -13013,7 +13013,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H436" t="n">
         <v>192904</v>
@@ -13042,7 +13042,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H437" t="n">
         <v>185924</v>
@@ -13100,7 +13100,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G439" t="n">
-        <v>0.615150332450867</v>
+        <v>0.615150213241577</v>
       </c>
       <c r="H439" t="n">
         <v>140694</v>
@@ -13158,7 +13158,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>0.621377885341644</v>
+        <v>0.621377944946289</v>
       </c>
       <c r="H441" t="n">
         <v>218077</v>
@@ -13216,7 +13216,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G443" t="n">
-        <v>0.636255025863647</v>
+        <v>0.636254906654358</v>
       </c>
       <c r="H443" t="n">
         <v>655108</v>
@@ -13245,7 +13245,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G444" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H444" t="n">
         <v>416249</v>
@@ -13361,7 +13361,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>0.636255025863647</v>
+        <v>0.636254906654358</v>
       </c>
       <c r="H448" t="n">
         <v>240947</v>
@@ -13680,7 +13680,7 @@
         <v>1.00300002098083</v>
       </c>
       <c r="G459" t="n">
-        <v>0.69403338432312</v>
+        <v>0.694033443927765</v>
       </c>
       <c r="H459" t="n">
         <v>324236</v>
@@ -13709,7 +13709,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G460" t="n">
-        <v>0.708564519882202</v>
+        <v>0.708564579486847</v>
       </c>
       <c r="H460" t="n">
         <v>939858</v>
@@ -13738,7 +13738,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G461" t="n">
-        <v>0.715484142303467</v>
+        <v>0.715484201908112</v>
       </c>
       <c r="H461" t="n">
         <v>727657</v>
@@ -13796,7 +13796,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G463" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H463" t="n">
         <v>373948</v>
@@ -13912,7 +13912,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G467" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H467" t="n">
         <v>470474</v>
@@ -14028,7 +14028,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>0.696109354496002</v>
+        <v>0.696109414100647</v>
       </c>
       <c r="H471" t="n">
         <v>102166</v>
@@ -14057,7 +14057,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G472" t="n">
-        <v>0.696109354496002</v>
+        <v>0.696109414100647</v>
       </c>
       <c r="H472" t="n">
         <v>233549</v>
@@ -14173,7 +14173,7 @@
         <v>0.970499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>0.671544849872589</v>
+        <v>0.671544790267944</v>
       </c>
       <c r="H476" t="n">
         <v>1137121</v>
@@ -14202,7 +14202,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G477" t="n">
-        <v>0.676734447479248</v>
+        <v>0.676734507083893</v>
       </c>
       <c r="H477" t="n">
         <v>169267</v>
@@ -14260,7 +14260,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G479" t="n">
-        <v>0.671198904514313</v>
+        <v>0.671198844909668</v>
       </c>
       <c r="H479" t="n">
         <v>244081</v>
@@ -14289,7 +14289,7 @@
         <v>0.972500026226044</v>
       </c>
       <c r="G480" t="n">
-        <v>0.672928750514984</v>
+        <v>0.672928810119629</v>
       </c>
       <c r="H480" t="n">
         <v>75909</v>
@@ -14318,7 +14318,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G481" t="n">
-        <v>0.65217000246048</v>
+        <v>0.652169942855835</v>
       </c>
       <c r="H481" t="n">
         <v>621225</v>
@@ -14492,7 +14492,7 @@
         <v>0.958999991416931</v>
       </c>
       <c r="G487" t="n">
-        <v>0.663587272167206</v>
+        <v>0.663587331771851</v>
       </c>
       <c r="H487" t="n">
         <v>121134</v>
@@ -14608,7 +14608,7 @@
         <v>0.961000025272369</v>
       </c>
       <c r="G491" t="n">
-        <v>0.66497129201889</v>
+        <v>0.664971232414246</v>
       </c>
       <c r="H491" t="n">
         <v>248336</v>
@@ -14637,7 +14637,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>0.669122993946075</v>
+        <v>0.669122934341431</v>
       </c>
       <c r="H492" t="n">
         <v>72723</v>
@@ -14695,7 +14695,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G494" t="n">
-        <v>0.677426397800446</v>
+        <v>0.67742645740509</v>
       </c>
       <c r="H494" t="n">
         <v>166163</v>
@@ -14753,7 +14753,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>0.676042497158051</v>
+        <v>0.676042556762695</v>
       </c>
       <c r="H496" t="n">
         <v>299253</v>
@@ -14811,7 +14811,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G498" t="n">
-        <v>0.684000074863434</v>
+        <v>0.684000015258789</v>
       </c>
       <c r="H498" t="n">
         <v>105579</v>
@@ -14840,7 +14840,7 @@
         <v>0.990499973297119</v>
       </c>
       <c r="G499" t="n">
-        <v>0.685383915901184</v>
+        <v>0.685383975505829</v>
       </c>
       <c r="H499" t="n">
         <v>219371</v>
@@ -14869,7 +14869,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G500" t="n">
-        <v>0.696109354496002</v>
+        <v>0.696109414100647</v>
       </c>
       <c r="H500" t="n">
         <v>290076</v>
@@ -15101,7 +15101,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G508" t="n">
-        <v>0.674658715724945</v>
+        <v>0.6746586561203</v>
       </c>
       <c r="H508" t="n">
         <v>240363</v>
@@ -15130,7 +15130,7 @@
         <v>0.940500020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>0.65078604221344</v>
+        <v>0.650786101818085</v>
       </c>
       <c r="H509" t="n">
         <v>972119</v>
@@ -15188,7 +15188,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G511" t="n">
-        <v>0.656667709350586</v>
+        <v>0.656667768955231</v>
       </c>
       <c r="H511" t="n">
         <v>126002</v>
@@ -15652,7 +15652,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G527" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H527" t="n">
         <v>364335</v>
@@ -15681,7 +15681,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G528" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H528" t="n">
         <v>178501</v>
@@ -15826,7 +15826,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G533" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H533" t="n">
         <v>70016</v>
@@ -15884,7 +15884,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G535" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H535" t="n">
         <v>255484</v>
@@ -15913,7 +15913,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G536" t="n">
-        <v>0.680886268615723</v>
+        <v>0.680886209011078</v>
       </c>
       <c r="H536" t="n">
         <v>552515</v>
@@ -15971,7 +15971,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G538" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H538" t="n">
         <v>233300</v>
@@ -16000,7 +16000,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G539" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H539" t="n">
         <v>285889</v>
@@ -16116,7 +16116,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G543" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H543" t="n">
         <v>181643</v>
@@ -16232,7 +16232,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G547" t="n">
-        <v>0.676734447479248</v>
+        <v>0.676734507083893</v>
       </c>
       <c r="H547" t="n">
         <v>77188</v>
@@ -16290,7 +16290,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G549" t="n">
-        <v>0.676734447479248</v>
+        <v>0.676734507083893</v>
       </c>
       <c r="H549" t="n">
         <v>63936</v>
@@ -16435,7 +16435,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G554" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H554" t="n">
         <v>444239</v>
@@ -16493,7 +16493,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G556" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H556" t="n">
         <v>696201</v>
@@ -16522,7 +16522,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G557" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H557" t="n">
         <v>107928</v>
@@ -16609,7 +16609,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G560" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H560" t="n">
         <v>573364</v>
@@ -16667,7 +16667,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G562" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H562" t="n">
         <v>244050</v>
@@ -16725,7 +16725,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G564" t="n">
-        <v>0.658743560314178</v>
+        <v>0.658743619918823</v>
       </c>
       <c r="H564" t="n">
         <v>15093</v>
@@ -16754,7 +16754,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G565" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H565" t="n">
         <v>121716</v>
@@ -16841,7 +16841,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G568" t="n">
-        <v>0.658743560314178</v>
+        <v>0.658743619918823</v>
       </c>
       <c r="H568" t="n">
         <v>117894</v>
@@ -16899,7 +16899,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H570" t="n">
         <v>38212</v>
@@ -16928,7 +16928,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G571" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H571" t="n">
         <v>36832</v>
@@ -16986,7 +16986,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H573" t="n">
         <v>153618</v>
@@ -17044,7 +17044,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G575" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H575" t="n">
         <v>149054</v>
@@ -17073,7 +17073,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G576" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H576" t="n">
         <v>91964</v>
@@ -17160,7 +17160,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G579" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H579" t="n">
         <v>33938</v>
@@ -17218,7 +17218,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G581" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H581" t="n">
         <v>64795</v>
@@ -17247,7 +17247,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G582" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H582" t="n">
         <v>167021</v>
@@ -17305,7 +17305,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G584" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H584" t="n">
         <v>69874</v>
@@ -17334,7 +17334,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G585" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H585" t="n">
         <v>65412</v>
@@ -17421,7 +17421,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G588" t="n">
-        <v>0.658743560314178</v>
+        <v>0.658743619918823</v>
       </c>
       <c r="H588" t="n">
         <v>203718</v>
@@ -17450,7 +17450,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G589" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H589" t="n">
         <v>181469</v>
@@ -17479,7 +17479,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G590" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H590" t="n">
         <v>35062</v>
@@ -17508,7 +17508,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G591" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H591" t="n">
         <v>138385</v>
@@ -17537,7 +17537,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G592" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H592" t="n">
         <v>29068</v>
@@ -17566,7 +17566,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G593" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H593" t="n">
         <v>6330</v>
@@ -17595,7 +17595,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G594" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H594" t="n">
         <v>13853</v>
@@ -17653,7 +17653,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G596" t="n">
-        <v>0.671198904514313</v>
+        <v>0.671198844909668</v>
       </c>
       <c r="H596" t="n">
         <v>216563</v>
@@ -17682,7 +17682,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G597" t="n">
-        <v>0.680886268615723</v>
+        <v>0.680886209011078</v>
       </c>
       <c r="H597" t="n">
         <v>354963</v>
@@ -17711,7 +17711,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G598" t="n">
-        <v>0.682270169258118</v>
+        <v>0.682270109653473</v>
       </c>
       <c r="H598" t="n">
         <v>505186</v>
@@ -17740,7 +17740,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G599" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H599" t="n">
         <v>257276</v>
@@ -17798,7 +17798,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G601" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H601" t="n">
         <v>173212</v>
@@ -17972,7 +17972,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G607" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H607" t="n">
         <v>265903</v>
@@ -18001,7 +18001,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G608" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H608" t="n">
         <v>267381</v>
@@ -18059,7 +18059,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G610" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H610" t="n">
         <v>63700</v>
@@ -18117,7 +18117,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H612" t="n">
         <v>182363</v>
@@ -18146,7 +18146,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G613" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H613" t="n">
         <v>294664</v>
@@ -18204,7 +18204,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G615" t="n">
-        <v>0.644904434680939</v>
+        <v>0.644904375076294</v>
       </c>
       <c r="H615" t="n">
         <v>85130</v>
@@ -18233,7 +18233,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G616" t="n">
-        <v>0.637984812259674</v>
+        <v>0.637984871864319</v>
       </c>
       <c r="H616" t="n">
         <v>171272</v>
@@ -18262,7 +18262,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G617" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H617" t="n">
         <v>118710</v>
@@ -18291,7 +18291,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H618" t="n">
         <v>504140</v>
@@ -18320,7 +18320,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H619" t="n">
         <v>135616</v>
@@ -18407,7 +18407,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G622" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H622" t="n">
         <v>52692</v>
@@ -18465,7 +18465,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G624" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H624" t="n">
         <v>32330</v>
@@ -18494,7 +18494,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G625" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H625" t="n">
         <v>12284</v>
@@ -18552,7 +18552,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G627" t="n">
-        <v>0.637984812259674</v>
+        <v>0.637984871864319</v>
       </c>
       <c r="H627" t="n">
         <v>47560</v>
@@ -18581,7 +18581,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G628" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H628" t="n">
         <v>115538</v>
@@ -18639,7 +18639,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G630" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H630" t="n">
         <v>140311</v>
@@ -18726,7 +18726,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G633" t="n">
-        <v>0.644904434680939</v>
+        <v>0.644904375076294</v>
       </c>
       <c r="H633" t="n">
         <v>189736</v>
@@ -18784,7 +18784,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G635" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H635" t="n">
         <v>55341</v>
@@ -18813,7 +18813,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G636" t="n">
-        <v>0.644904434680939</v>
+        <v>0.644904375076294</v>
       </c>
       <c r="H636" t="n">
         <v>391421</v>
@@ -18842,7 +18842,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H637" t="n">
         <v>158068</v>
@@ -18871,7 +18871,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G638" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H638" t="n">
         <v>64520</v>
@@ -18900,7 +18900,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G639" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H639" t="n">
         <v>154143</v>
@@ -18929,7 +18929,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G640" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H640" t="n">
         <v>131453</v>
@@ -18958,7 +18958,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G641" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H641" t="n">
         <v>101434</v>
@@ -18987,7 +18987,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G642" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H642" t="n">
         <v>45923</v>
@@ -19016,7 +19016,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G643" t="n">
-        <v>0.676734447479248</v>
+        <v>0.676734507083893</v>
       </c>
       <c r="H643" t="n">
         <v>503725</v>
@@ -19248,7 +19248,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G651" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H651" t="n">
         <v>142778</v>
@@ -19335,7 +19335,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G654" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H654" t="n">
         <v>52109</v>
@@ -19422,7 +19422,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G657" t="n">
-        <v>0.671198904514313</v>
+        <v>0.671198844909668</v>
       </c>
       <c r="H657" t="n">
         <v>125616</v>
@@ -19480,7 +19480,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G659" t="n">
-        <v>0.671198904514313</v>
+        <v>0.671198844909668</v>
       </c>
       <c r="H659" t="n">
         <v>72388</v>
@@ -19509,7 +19509,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G660" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H660" t="n">
         <v>301287</v>
@@ -19567,7 +19567,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G662" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H662" t="n">
         <v>138753</v>
@@ -19596,7 +19596,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G663" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H663" t="n">
         <v>140254</v>
@@ -19683,7 +19683,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G666" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H666" t="n">
         <v>93861</v>
@@ -19712,7 +19712,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H667" t="n">
         <v>167650</v>
@@ -19741,7 +19741,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H668" t="n">
         <v>20241</v>
@@ -19770,7 +19770,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G669" t="n">
-        <v>0.658743560314178</v>
+        <v>0.658743619918823</v>
       </c>
       <c r="H669" t="n">
         <v>108004</v>
@@ -19799,7 +19799,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G670" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H670" t="n">
         <v>163980</v>
@@ -19828,7 +19828,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G671" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H671" t="n">
         <v>427711</v>
@@ -19857,7 +19857,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G672" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H672" t="n">
         <v>96842</v>
@@ -19944,7 +19944,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G675" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H675" t="n">
         <v>52830</v>
@@ -20031,7 +20031,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G678" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H678" t="n">
         <v>99343</v>
@@ -20060,7 +20060,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G679" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H679" t="n">
         <v>99007</v>
@@ -20089,7 +20089,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H680" t="n">
         <v>116691</v>
@@ -20118,7 +20118,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G681" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H681" t="n">
         <v>57141</v>
@@ -20147,7 +20147,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G682" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H682" t="n">
         <v>73730</v>
@@ -20176,7 +20176,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G683" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H683" t="n">
         <v>74130</v>
@@ -20205,7 +20205,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H684" t="n">
         <v>67179</v>
@@ -20234,7 +20234,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G685" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H685" t="n">
         <v>172394</v>
@@ -20263,7 +20263,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G686" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H686" t="n">
         <v>11821</v>
@@ -20321,7 +20321,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H688" t="n">
         <v>196163</v>
@@ -20379,7 +20379,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H690" t="n">
         <v>47347</v>
@@ -20408,7 +20408,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G691" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H691" t="n">
         <v>54618</v>
@@ -20437,7 +20437,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G692" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H692" t="n">
         <v>112543</v>
@@ -20466,7 +20466,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G693" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H693" t="n">
         <v>51317</v>
@@ -20495,7 +20495,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H694" t="n">
         <v>13680</v>
@@ -20524,7 +20524,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G695" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H695" t="n">
         <v>25114</v>
@@ -20553,7 +20553,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G696" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H696" t="n">
         <v>82434</v>
@@ -20582,7 +20582,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G697" t="n">
-        <v>0.658743560314178</v>
+        <v>0.658743619918823</v>
       </c>
       <c r="H697" t="n">
         <v>49045</v>
@@ -20611,7 +20611,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G698" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H698" t="n">
         <v>67665</v>
@@ -20640,7 +20640,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G699" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H699" t="n">
         <v>129526</v>
@@ -20669,7 +20669,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G700" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H700" t="n">
         <v>8812</v>
@@ -20727,7 +20727,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G702" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H702" t="n">
         <v>197152</v>
@@ -20756,7 +20756,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G703" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H703" t="n">
         <v>121260</v>
@@ -20785,7 +20785,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G704" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H704" t="n">
         <v>46772</v>
@@ -20814,7 +20814,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H705" t="n">
         <v>28672</v>
@@ -20843,7 +20843,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H706" t="n">
         <v>24697</v>
@@ -20901,7 +20901,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G708" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H708" t="n">
         <v>98837</v>
@@ -20959,7 +20959,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H710" t="n">
         <v>151533</v>
@@ -20988,7 +20988,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G711" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H711" t="n">
         <v>61229</v>
@@ -21017,7 +21017,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>0.628297448158264</v>
+        <v>0.628297507762909</v>
       </c>
       <c r="H712" t="n">
         <v>83637</v>
@@ -21075,7 +21075,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G714" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H714" t="n">
         <v>52549</v>
@@ -21104,7 +21104,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G715" t="n">
-        <v>0.626913547515869</v>
+        <v>0.626913607120514</v>
       </c>
       <c r="H715" t="n">
         <v>44791</v>
@@ -21191,7 +21191,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>0.621377885341644</v>
+        <v>0.621377944946289</v>
       </c>
       <c r="H718" t="n">
         <v>90743</v>
@@ -21249,7 +21249,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G720" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H720" t="n">
         <v>49505</v>
@@ -21278,7 +21278,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>0.628297448158264</v>
+        <v>0.628297507762909</v>
       </c>
       <c r="H721" t="n">
         <v>468123</v>
@@ -21336,7 +21336,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H723" t="n">
         <v>182993</v>
@@ -21365,7 +21365,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H724" t="n">
         <v>222642</v>
@@ -21394,7 +21394,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G725" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H725" t="n">
         <v>55765</v>
@@ -21423,7 +21423,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G726" t="n">
-        <v>0.651823997497559</v>
+        <v>0.651824057102203</v>
       </c>
       <c r="H726" t="n">
         <v>222817</v>
@@ -21452,7 +21452,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H727" t="n">
         <v>57669</v>
@@ -21539,7 +21539,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G730" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H730" t="n">
         <v>80663</v>
@@ -21568,7 +21568,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G731" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H731" t="n">
         <v>57564</v>
@@ -21597,7 +21597,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G732" t="n">
-        <v>0.637984812259674</v>
+        <v>0.637984871864319</v>
       </c>
       <c r="H732" t="n">
         <v>8772</v>
@@ -21655,7 +21655,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G734" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H734" t="n">
         <v>53744</v>
@@ -21684,7 +21684,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G735" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H735" t="n">
         <v>46948</v>
@@ -21713,7 +21713,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G736" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H736" t="n">
         <v>54341</v>
@@ -21742,7 +21742,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G737" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H737" t="n">
         <v>5380</v>
@@ -21800,7 +21800,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H739" t="n">
         <v>63280</v>
@@ -21887,7 +21887,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G742" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H742" t="n">
         <v>82682</v>
@@ -21916,7 +21916,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G743" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H743" t="n">
         <v>59135</v>
@@ -21974,7 +21974,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H745" t="n">
         <v>306199</v>
@@ -22003,7 +22003,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G746" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H746" t="n">
         <v>138545</v>
@@ -22061,7 +22061,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G748" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H748" t="n">
         <v>308766</v>
@@ -22119,7 +22119,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G750" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H750" t="n">
         <v>820174</v>
@@ -22148,7 +22148,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G751" t="n">
-        <v>0.658743560314178</v>
+        <v>0.658743619918823</v>
       </c>
       <c r="H751" t="n">
         <v>236602</v>
@@ -22177,7 +22177,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H752" t="n">
         <v>388590</v>
@@ -22206,7 +22206,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G753" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H753" t="n">
         <v>52006</v>
@@ -22235,7 +22235,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G754" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H754" t="n">
         <v>247058</v>
@@ -22293,7 +22293,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G756" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H756" t="n">
         <v>44184</v>
@@ -22322,7 +22322,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G757" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H757" t="n">
         <v>161007</v>
@@ -22351,7 +22351,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G758" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H758" t="n">
         <v>103377</v>
@@ -22380,7 +22380,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G759" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H759" t="n">
         <v>92669</v>
@@ -22409,7 +22409,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G760" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H760" t="n">
         <v>174775</v>
@@ -22438,7 +22438,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G761" t="n">
-        <v>0.651823997497559</v>
+        <v>0.651824057102203</v>
       </c>
       <c r="H761" t="n">
         <v>112676</v>
@@ -22496,7 +22496,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G763" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H763" t="n">
         <v>39624</v>
@@ -22525,7 +22525,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G764" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H764" t="n">
         <v>146710</v>
@@ -22583,7 +22583,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G766" t="n">
-        <v>0.662895381450653</v>
+        <v>0.662895321846008</v>
       </c>
       <c r="H766" t="n">
         <v>109701</v>
@@ -22612,7 +22612,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G767" t="n">
-        <v>0.667047023773193</v>
+        <v>0.667047083377838</v>
       </c>
       <c r="H767" t="n">
         <v>116328</v>
@@ -22699,7 +22699,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G770" t="n">
-        <v>0.671198904514313</v>
+        <v>0.671198844909668</v>
       </c>
       <c r="H770" t="n">
         <v>31046</v>
@@ -22728,7 +22728,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G771" t="n">
-        <v>0.671198904514313</v>
+        <v>0.671198844909668</v>
       </c>
       <c r="H771" t="n">
         <v>60160</v>
@@ -22757,7 +22757,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G772" t="n">
-        <v>0.671198904514313</v>
+        <v>0.671198844909668</v>
       </c>
       <c r="H772" t="n">
         <v>359409</v>
@@ -22786,7 +22786,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G773" t="n">
-        <v>0.671198904514313</v>
+        <v>0.671198844909668</v>
       </c>
       <c r="H773" t="n">
         <v>65019</v>
@@ -22815,7 +22815,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G774" t="n">
-        <v>0.676734447479248</v>
+        <v>0.676734507083893</v>
       </c>
       <c r="H774" t="n">
         <v>228965</v>
@@ -22902,7 +22902,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G777" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H777" t="n">
         <v>174998</v>
@@ -22931,7 +22931,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G778" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H778" t="n">
         <v>275985</v>
@@ -22989,7 +22989,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H780" t="n">
         <v>526304</v>
@@ -23105,7 +23105,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H784" t="n">
         <v>376786</v>
@@ -23134,7 +23134,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G785" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H785" t="n">
         <v>180557</v>
@@ -23163,7 +23163,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G786" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H786" t="n">
         <v>117707</v>
@@ -23192,7 +23192,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H787" t="n">
         <v>82370</v>
@@ -23221,7 +23221,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H788" t="n">
         <v>145075</v>
@@ -23250,7 +23250,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G789" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H789" t="n">
         <v>229318</v>
@@ -23279,7 +23279,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G790" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H790" t="n">
         <v>290276</v>
@@ -23308,7 +23308,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G791" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H791" t="n">
         <v>146801</v>
@@ -23337,7 +23337,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G792" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H792" t="n">
         <v>619773</v>
@@ -23511,7 +23511,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G798" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H798" t="n">
         <v>2153597</v>
@@ -23540,7 +23540,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G799" t="n">
-        <v>0.680886268615723</v>
+        <v>0.680886209011078</v>
       </c>
       <c r="H799" t="n">
         <v>1360063</v>
@@ -23685,7 +23685,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G804" t="n">
-        <v>0.680886268615723</v>
+        <v>0.680886209011078</v>
       </c>
       <c r="H804" t="n">
         <v>213189</v>
@@ -23743,7 +23743,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G806" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H806" t="n">
         <v>320023</v>
@@ -23801,7 +23801,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G808" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H808" t="n">
         <v>226093</v>
@@ -23830,7 +23830,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G809" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H809" t="n">
         <v>208609</v>
@@ -23888,7 +23888,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G811" t="n">
-        <v>0.680886268615723</v>
+        <v>0.680886209011078</v>
       </c>
       <c r="H811" t="n">
         <v>530661</v>
@@ -23917,7 +23917,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G812" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H812" t="n">
         <v>436802</v>
@@ -23975,7 +23975,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G814" t="n">
-        <v>0.680886268615723</v>
+        <v>0.680886209011078</v>
       </c>
       <c r="H814" t="n">
         <v>34017</v>
@@ -24004,7 +24004,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G815" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H815" t="n">
         <v>305887</v>
@@ -24062,7 +24062,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G817" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H817" t="n">
         <v>80902</v>
@@ -24091,7 +24091,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G818" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H818" t="n">
         <v>277155</v>
@@ -24236,7 +24236,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G823" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H823" t="n">
         <v>104698</v>
@@ -24294,7 +24294,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G825" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H825" t="n">
         <v>85392</v>
@@ -24323,7 +24323,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G826" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H826" t="n">
         <v>122721</v>
@@ -24352,7 +24352,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G827" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H827" t="n">
         <v>136318</v>
@@ -24555,7 +24555,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G834" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H834" t="n">
         <v>204614</v>
@@ -24787,7 +24787,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G842" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H842" t="n">
         <v>105509</v>
@@ -24845,7 +24845,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G844" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H844" t="n">
         <v>80388</v>
@@ -24903,7 +24903,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G846" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H846" t="n">
         <v>52402</v>
@@ -24932,7 +24932,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G847" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H847" t="n">
         <v>61956</v>
@@ -25077,7 +25077,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G852" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H852" t="n">
         <v>244060</v>
@@ -25106,7 +25106,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G853" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H853" t="n">
         <v>275627</v>
@@ -25135,7 +25135,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G854" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H854" t="n">
         <v>124964</v>
@@ -25193,7 +25193,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G856" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H856" t="n">
         <v>90403</v>
@@ -25338,7 +25338,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H861" t="n">
         <v>216088</v>
@@ -25396,7 +25396,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G863" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H863" t="n">
         <v>99861</v>
@@ -25512,7 +25512,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G867" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H867" t="n">
         <v>13841</v>
@@ -25541,7 +25541,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G868" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H868" t="n">
         <v>40045</v>
@@ -25773,7 +25773,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G876" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H876" t="n">
         <v>81601</v>
@@ -25802,7 +25802,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G877" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H877" t="n">
         <v>104497</v>
@@ -26034,7 +26034,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H885" t="n">
         <v>493105</v>
@@ -26063,7 +26063,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G886" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H886" t="n">
         <v>216811</v>
@@ -26092,7 +26092,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H887" t="n">
         <v>390492</v>
@@ -26121,7 +26121,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G888" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H888" t="n">
         <v>173883</v>
@@ -26150,7 +26150,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G889" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H889" t="n">
         <v>132291</v>
@@ -26179,7 +26179,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G890" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H890" t="n">
         <v>159006</v>
@@ -26208,7 +26208,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H891" t="n">
         <v>238771</v>
@@ -26353,7 +26353,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H896" t="n">
         <v>73030</v>
@@ -26440,7 +26440,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G899" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H899" t="n">
         <v>32697</v>
@@ -26585,7 +26585,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H904" t="n">
         <v>176654</v>
@@ -26614,7 +26614,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H905" t="n">
         <v>43325</v>
@@ -26643,7 +26643,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H906" t="n">
         <v>107319</v>
@@ -26672,7 +26672,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H907" t="n">
         <v>347972</v>
@@ -26701,7 +26701,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H908" t="n">
         <v>40674</v>
@@ -26730,7 +26730,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G909" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H909" t="n">
         <v>92055</v>
@@ -26846,7 +26846,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H913" t="n">
         <v>97295</v>
@@ -27223,7 +27223,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G926" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H926" t="n">
         <v>632493</v>
@@ -27803,7 +27803,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G946" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H946" t="n">
         <v>87148</v>
@@ -27861,7 +27861,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G948" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H948" t="n">
         <v>63867</v>
@@ -27890,7 +27890,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G949" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H949" t="n">
         <v>41116</v>
@@ -27977,7 +27977,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G952" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H952" t="n">
         <v>133528</v>
@@ -28006,7 +28006,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G953" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H953" t="n">
         <v>44179</v>
@@ -28064,7 +28064,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G955" t="n">
-        <v>0.682270169258118</v>
+        <v>0.682270109653473</v>
       </c>
       <c r="H955" t="n">
         <v>244843</v>
@@ -28296,7 +28296,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G963" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H963" t="n">
         <v>49902</v>
@@ -28441,7 +28441,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G968" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H968" t="n">
         <v>98290</v>
@@ -28470,7 +28470,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G969" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H969" t="n">
         <v>40709</v>
@@ -28499,7 +28499,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G970" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H970" t="n">
         <v>21334</v>
@@ -28586,7 +28586,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G973" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H973" t="n">
         <v>105764</v>
@@ -28615,7 +28615,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H974" t="n">
         <v>619655</v>
@@ -28731,7 +28731,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H978" t="n">
         <v>51501</v>
@@ -28789,7 +28789,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G980" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H980" t="n">
         <v>78455</v>
@@ -28818,7 +28818,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H981" t="n">
         <v>64980</v>
@@ -28847,7 +28847,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H982" t="n">
         <v>61200</v>
@@ -28905,7 +28905,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H984" t="n">
         <v>62066</v>
@@ -28934,7 +28934,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H985" t="n">
         <v>78120</v>
@@ -28963,7 +28963,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G986" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H986" t="n">
         <v>66452</v>
@@ -28992,7 +28992,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G987" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H987" t="n">
         <v>95757</v>
@@ -29021,7 +29021,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G988" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H988" t="n">
         <v>102998</v>
@@ -29050,7 +29050,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G989" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H989" t="n">
         <v>75430</v>
@@ -29108,7 +29108,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G991" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H991" t="n">
         <v>7575</v>
@@ -29137,7 +29137,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G992" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H992" t="n">
         <v>96747</v>
@@ -29166,7 +29166,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G993" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H993" t="n">
         <v>191111</v>
@@ -29195,7 +29195,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H994" t="n">
         <v>78705</v>
@@ -29224,7 +29224,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H995" t="n">
         <v>105388</v>
@@ -29253,7 +29253,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G996" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H996" t="n">
         <v>130509</v>
@@ -29282,7 +29282,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H997" t="n">
         <v>110766</v>
@@ -29340,7 +29340,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H999" t="n">
         <v>89509</v>
@@ -29369,7 +29369,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H1000" t="n">
         <v>154172</v>
@@ -29398,7 +29398,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H1001" t="n">
         <v>37170</v>
@@ -29427,7 +29427,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H1002" t="n">
         <v>79129</v>
@@ -29456,7 +29456,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H1003" t="n">
         <v>235612</v>
@@ -29485,7 +29485,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H1004" t="n">
         <v>192053</v>
@@ -29514,7 +29514,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1005" t="n">
         <v>342278</v>
@@ -29543,7 +29543,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.730015158653259</v>
+        <v>0.730015218257904</v>
       </c>
       <c r="H1006" t="n">
         <v>322567</v>
@@ -29601,7 +29601,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H1008" t="n">
         <v>278865</v>
@@ -29630,7 +29630,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1009" t="n">
         <v>174124</v>
@@ -29659,7 +29659,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H1010" t="n">
         <v>113260</v>
@@ -29688,7 +29688,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H1011" t="n">
         <v>387485</v>
@@ -29717,7 +29717,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H1012" t="n">
         <v>249244</v>
@@ -29746,7 +29746,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H1013" t="n">
         <v>286241</v>
@@ -29775,7 +29775,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H1014" t="n">
         <v>318580</v>
@@ -29804,7 +29804,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H1015" t="n">
         <v>60551</v>
@@ -29891,7 +29891,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H1018" t="n">
         <v>35801</v>
@@ -29949,7 +29949,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H1020" t="n">
         <v>109677</v>
@@ -29978,7 +29978,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H1021" t="n">
         <v>156016</v>
@@ -30094,7 +30094,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H1025" t="n">
         <v>210045</v>
@@ -30123,7 +30123,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H1026" t="n">
         <v>199506</v>
@@ -30616,7 +30616,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H1043" t="n">
         <v>142728</v>
@@ -30645,7 +30645,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H1044" t="n">
         <v>234674</v>
@@ -30674,7 +30674,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H1045" t="n">
         <v>171115</v>
@@ -30703,7 +30703,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H1046" t="n">
         <v>76577</v>
@@ -30732,7 +30732,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.705796718597412</v>
+        <v>0.705796658992767</v>
       </c>
       <c r="H1047" t="n">
         <v>688629</v>
@@ -30819,7 +30819,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.799211025238037</v>
+        <v>0.799210906028748</v>
       </c>
       <c r="H1050" t="n">
         <v>1197758</v>
@@ -30848,7 +30848,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1051" t="n">
         <v>273699</v>
@@ -30906,7 +30906,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.730015158653259</v>
+        <v>0.730015218257904</v>
       </c>
       <c r="H1053" t="n">
         <v>823602</v>
@@ -30935,7 +30935,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.792291462421417</v>
+        <v>0.792291402816772</v>
       </c>
       <c r="H1054" t="n">
         <v>899148</v>
@@ -31051,7 +31051,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H1058" t="n">
         <v>731628</v>
@@ -31080,7 +31080,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.730015158653259</v>
+        <v>0.730015218257904</v>
       </c>
       <c r="H1059" t="n">
         <v>163770</v>
@@ -31225,7 +31225,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1064" t="n">
         <v>311827</v>
@@ -31254,7 +31254,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H1065" t="n">
         <v>357849</v>
@@ -31283,7 +31283,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.57570868730545</v>
+        <v>0.575708627700806</v>
       </c>
       <c r="H1066" t="n">
         <v>506587</v>
@@ -31370,7 +31370,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H1069" t="n">
         <v>131300</v>
@@ -31399,7 +31399,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.59646737575531</v>
+        <v>0.596467435359955</v>
       </c>
       <c r="H1070" t="n">
         <v>189836</v>
@@ -31428,7 +31428,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.628297448158264</v>
+        <v>0.628297507762909</v>
       </c>
       <c r="H1071" t="n">
         <v>34398</v>
@@ -31486,7 +31486,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.59923529624939</v>
+        <v>0.599235236644745</v>
       </c>
       <c r="H1073" t="n">
         <v>281442</v>
@@ -31515,7 +31515,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H1074" t="n">
         <v>127271</v>
@@ -31544,7 +31544,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H1075" t="n">
         <v>210749</v>
@@ -31660,7 +31660,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1079" t="n">
         <v>28824</v>
@@ -31718,7 +31718,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H1081" t="n">
         <v>12555</v>
@@ -31747,7 +31747,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H1082" t="n">
         <v>86399</v>
@@ -31776,7 +31776,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1083" t="n">
         <v>131641</v>
@@ -31805,7 +31805,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H1084" t="n">
         <v>166709</v>
@@ -31834,7 +31834,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H1085" t="n">
         <v>23669</v>
@@ -31863,7 +31863,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H1086" t="n">
         <v>52777</v>
@@ -31892,7 +31892,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H1087" t="n">
         <v>113437</v>
@@ -31921,7 +31921,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.628297448158264</v>
+        <v>0.628297507762909</v>
       </c>
       <c r="H1088" t="n">
         <v>69667</v>
@@ -31979,7 +31979,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.637984812259674</v>
+        <v>0.637984871864319</v>
       </c>
       <c r="H1090" t="n">
         <v>82780</v>
@@ -32008,7 +32008,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.628297448158264</v>
+        <v>0.628297507762909</v>
       </c>
       <c r="H1091" t="n">
         <v>32955</v>
@@ -32037,7 +32037,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.618610084056854</v>
+        <v>0.618610024452209</v>
       </c>
       <c r="H1092" t="n">
         <v>82022</v>
@@ -32095,7 +32095,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H1094" t="n">
         <v>39008</v>
@@ -32153,7 +32153,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H1096" t="n">
         <v>78354</v>
@@ -32182,7 +32182,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H1097" t="n">
         <v>284734</v>
@@ -32211,7 +32211,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.615842223167419</v>
+        <v>0.615842282772064</v>
       </c>
       <c r="H1098" t="n">
         <v>28827</v>
@@ -32240,7 +32240,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.617226123809814</v>
+        <v>0.617226183414459</v>
       </c>
       <c r="H1099" t="n">
         <v>28036</v>
@@ -32269,7 +32269,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.617226123809814</v>
+        <v>0.617226183414459</v>
       </c>
       <c r="H1100" t="n">
         <v>37867</v>
@@ -32298,7 +32298,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.615842223167419</v>
+        <v>0.615842282772064</v>
       </c>
       <c r="H1101" t="n">
         <v>10506</v>
@@ -32327,7 +32327,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H1102" t="n">
         <v>14360</v>
@@ -32443,7 +32443,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.615842223167419</v>
+        <v>0.615842282772064</v>
       </c>
       <c r="H1106" t="n">
         <v>72994</v>
@@ -32501,7 +32501,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.59923529624939</v>
+        <v>0.599235236644745</v>
       </c>
       <c r="H1108" t="n">
         <v>32728</v>
@@ -32559,7 +32559,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.614458322525024</v>
+        <v>0.614458382129669</v>
       </c>
       <c r="H1110" t="n">
         <v>74390</v>
@@ -32646,7 +32646,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.58539617061615</v>
+        <v>0.585396111011505</v>
       </c>
       <c r="H1113" t="n">
         <v>67156</v>
@@ -32704,7 +32704,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.584012150764465</v>
+        <v>0.58401221036911</v>
       </c>
       <c r="H1115" t="n">
         <v>77035</v>
@@ -32791,7 +32791,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.59923529624939</v>
+        <v>0.599235236644745</v>
       </c>
       <c r="H1118" t="n">
         <v>96110</v>
@@ -32820,7 +32820,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.59923529624939</v>
+        <v>0.599235236644745</v>
       </c>
       <c r="H1119" t="n">
         <v>35473</v>
@@ -32849,7 +32849,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.602003037929535</v>
+        <v>0.60200309753418</v>
       </c>
       <c r="H1120" t="n">
         <v>76838</v>
@@ -32878,7 +32878,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.602003037929535</v>
+        <v>0.60200309753418</v>
       </c>
       <c r="H1121" t="n">
         <v>115137</v>
@@ -32907,7 +32907,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.57847660779953</v>
+        <v>0.578476548194885</v>
       </c>
       <c r="H1122" t="n">
         <v>200693</v>
@@ -32965,7 +32965,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.60753870010376</v>
+        <v>0.607538759708405</v>
       </c>
       <c r="H1124" t="n">
         <v>193168</v>
@@ -32994,7 +32994,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.613074421882629</v>
+        <v>0.613074362277985</v>
       </c>
       <c r="H1125" t="n">
         <v>101717</v>
@@ -33052,7 +33052,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.610306560993195</v>
+        <v>0.610306620597839</v>
       </c>
       <c r="H1127" t="n">
         <v>52656</v>
@@ -33081,7 +33081,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.610306560993195</v>
+        <v>0.610306620597839</v>
       </c>
       <c r="H1128" t="n">
         <v>167445</v>
@@ -33110,7 +33110,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.610306560993195</v>
+        <v>0.610306620597839</v>
       </c>
       <c r="H1129" t="n">
         <v>211022</v>
@@ -33197,7 +33197,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H1132" t="n">
         <v>63578</v>
@@ -33284,7 +33284,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H1135" t="n">
         <v>42077</v>
@@ -33313,7 +33313,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H1136" t="n">
         <v>53591</v>
@@ -33342,7 +33342,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.628297448158264</v>
+        <v>0.628297507762909</v>
       </c>
       <c r="H1137" t="n">
         <v>73997</v>
@@ -33371,7 +33371,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.626913547515869</v>
+        <v>0.626913607120514</v>
       </c>
       <c r="H1138" t="n">
         <v>103661</v>
@@ -33400,7 +33400,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H1139" t="n">
         <v>47711</v>
@@ -33516,7 +33516,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H1143" t="n">
         <v>47967</v>
@@ -33545,7 +33545,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1144" t="n">
         <v>134257</v>
@@ -33574,7 +33574,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H1145" t="n">
         <v>71701</v>
@@ -33603,7 +33603,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H1146" t="n">
         <v>69990</v>
@@ -33632,7 +33632,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1147" t="n">
         <v>34283</v>
@@ -33661,7 +33661,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H1148" t="n">
         <v>50733</v>
@@ -33690,7 +33690,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H1149" t="n">
         <v>29344</v>
@@ -33748,7 +33748,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.651823997497559</v>
+        <v>0.651824057102203</v>
       </c>
       <c r="H1151" t="n">
         <v>98360</v>
@@ -33777,7 +33777,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1152" t="n">
         <v>107933</v>
@@ -33806,7 +33806,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H1153" t="n">
         <v>43157</v>
@@ -33835,7 +33835,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1154" t="n">
         <v>25608</v>
@@ -33893,7 +33893,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H1156" t="n">
         <v>44684</v>
@@ -33922,7 +33922,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1157" t="n">
         <v>79152</v>
@@ -33951,7 +33951,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H1158" t="n">
         <v>35471</v>
@@ -33980,7 +33980,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.654591858386993</v>
+        <v>0.654591798782349</v>
       </c>
       <c r="H1159" t="n">
         <v>5309</v>
@@ -34009,7 +34009,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H1160" t="n">
         <v>70501</v>
@@ -34038,7 +34038,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1161" t="n">
         <v>26496</v>
@@ -34067,7 +34067,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H1162" t="n">
         <v>9641</v>
@@ -34183,7 +34183,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.637984812259674</v>
+        <v>0.637984871864319</v>
       </c>
       <c r="H1166" t="n">
         <v>345</v>
@@ -34241,7 +34241,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.644904434680939</v>
+        <v>0.644904375076294</v>
       </c>
       <c r="H1168" t="n">
         <v>94123</v>
@@ -34270,7 +34270,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H1169" t="n">
         <v>11833</v>
@@ -34357,7 +34357,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H1172" t="n">
         <v>42400</v>
@@ -34386,7 +34386,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1173" t="n">
         <v>3808</v>
@@ -34415,7 +34415,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.655975818634033</v>
+        <v>0.655975759029388</v>
       </c>
       <c r="H1174" t="n">
         <v>10005</v>
@@ -34444,7 +34444,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H1175" t="n">
         <v>285</v>
@@ -34560,7 +34560,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.644904434680939</v>
+        <v>0.644904375076294</v>
       </c>
       <c r="H1179" t="n">
         <v>8541</v>
@@ -34589,7 +34589,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H1180" t="n">
         <v>24514</v>
@@ -34618,7 +34618,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H1181" t="n">
         <v>3104</v>
@@ -34676,7 +34676,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.626913547515869</v>
+        <v>0.626913607120514</v>
       </c>
       <c r="H1183" t="n">
         <v>35800</v>
@@ -34705,7 +34705,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H1184" t="n">
         <v>17169</v>
@@ -34792,7 +34792,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H1187" t="n">
         <v>19694</v>
@@ -34821,7 +34821,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H1188" t="n">
         <v>5415</v>
@@ -34908,7 +34908,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H1191" t="n">
         <v>12133</v>
@@ -34937,7 +34937,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H1192" t="n">
         <v>71254</v>
@@ -35111,7 +35111,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.635217070579529</v>
+        <v>0.635217010974884</v>
       </c>
       <c r="H1198" t="n">
         <v>34840</v>
@@ -35198,7 +35198,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.639368832111359</v>
+        <v>0.639368772506714</v>
       </c>
       <c r="H1201" t="n">
         <v>31035</v>
@@ -35343,7 +35343,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1206" t="n">
         <v>6431</v>
@@ -35459,7 +35459,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.650440156459808</v>
+        <v>0.650440037250519</v>
       </c>
       <c r="H1210" t="n">
         <v>19679</v>
@@ -35488,7 +35488,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.646288335323334</v>
+        <v>0.646288394927979</v>
       </c>
       <c r="H1211" t="n">
         <v>14578</v>
@@ -35575,7 +35575,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H1214" t="n">
         <v>32776</v>
@@ -35807,7 +35807,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.626913547515869</v>
+        <v>0.626913607120514</v>
       </c>
       <c r="H1222" t="n">
         <v>66195</v>
@@ -35836,7 +35836,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.626913547515869</v>
+        <v>0.626913607120514</v>
       </c>
       <c r="H1223" t="n">
         <v>102090</v>
@@ -35894,7 +35894,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H1225" t="n">
         <v>43500</v>
@@ -35923,7 +35923,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.626913547515869</v>
+        <v>0.626913607120514</v>
       </c>
       <c r="H1226" t="n">
         <v>40301</v>
@@ -35952,7 +35952,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.622761726379395</v>
+        <v>0.622761845588684</v>
       </c>
       <c r="H1227" t="n">
         <v>189581</v>
@@ -36126,7 +36126,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.642136633396149</v>
+        <v>0.642136573791504</v>
       </c>
       <c r="H1233" t="n">
         <v>55266</v>
@@ -36213,7 +36213,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.644904434680939</v>
+        <v>0.644904375076294</v>
       </c>
       <c r="H1236" t="n">
         <v>88958</v>
@@ -36242,7 +36242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.637984812259674</v>
+        <v>0.637984871864319</v>
       </c>
       <c r="H1237" t="n">
         <v>55565</v>
@@ -36329,7 +36329,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1240" t="n">
         <v>40915</v>
@@ -36358,7 +36358,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.647672235965729</v>
+        <v>0.647672295570374</v>
       </c>
       <c r="H1241" t="n">
         <v>45409</v>
@@ -36387,7 +36387,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1242" t="n">
         <v>155539</v>
@@ -36445,7 +36445,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.653207898139954</v>
+        <v>0.653207957744598</v>
       </c>
       <c r="H1244" t="n">
         <v>67964</v>
@@ -36474,7 +36474,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.657359719276428</v>
+        <v>0.657359659671783</v>
       </c>
       <c r="H1245" t="n">
         <v>74860</v>
@@ -36503,7 +36503,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.664279222488403</v>
+        <v>0.664279282093048</v>
       </c>
       <c r="H1246" t="n">
         <v>149953</v>
@@ -36532,7 +36532,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.676734447479248</v>
+        <v>0.676734507083893</v>
       </c>
       <c r="H1247" t="n">
         <v>67536</v>
@@ -36648,7 +36648,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H1251" t="n">
         <v>36590</v>
@@ -36677,7 +36677,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1252" t="n">
         <v>75238</v>
@@ -36706,7 +36706,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.682270169258118</v>
+        <v>0.682270109653473</v>
       </c>
       <c r="H1253" t="n">
         <v>24503</v>
@@ -36735,7 +36735,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1254" t="n">
         <v>248043</v>
@@ -36793,7 +36793,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.690573632717133</v>
+        <v>0.690573692321777</v>
       </c>
       <c r="H1256" t="n">
         <v>27967</v>
@@ -36851,7 +36851,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.686421930789948</v>
+        <v>0.686421871185303</v>
       </c>
       <c r="H1258" t="n">
         <v>93042</v>
@@ -36880,7 +36880,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.683654010295868</v>
+        <v>0.683654129505157</v>
       </c>
       <c r="H1259" t="n">
         <v>104468</v>
@@ -37228,7 +37228,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.712716281414032</v>
+        <v>0.712716221809387</v>
       </c>
       <c r="H1271" t="n">
         <v>213141</v>
@@ -37286,7 +37286,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.716176092624664</v>
+        <v>0.716175973415375</v>
       </c>
       <c r="H1273" t="n">
         <v>175476</v>
@@ -37373,7 +37373,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1276" t="n">
         <v>52660</v>
@@ -37431,7 +37431,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H1278" t="n">
         <v>61686</v>
@@ -37663,7 +37663,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.719635903835297</v>
+        <v>0.719635784626007</v>
       </c>
       <c r="H1286" t="n">
         <v>131829</v>
@@ -37692,7 +37692,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.730015158653259</v>
+        <v>0.730015218257904</v>
       </c>
       <c r="H1287" t="n">
         <v>170197</v>
@@ -37721,7 +37721,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1288" t="n">
         <v>84581</v>
@@ -37750,7 +37750,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.723095655441284</v>
+        <v>0.723095595836639</v>
       </c>
       <c r="H1289" t="n">
         <v>98666</v>
@@ -37837,7 +37837,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.743854403495789</v>
+        <v>0.743854463100433</v>
       </c>
       <c r="H1292" t="n">
         <v>224416</v>
@@ -37866,7 +37866,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.743854403495789</v>
+        <v>0.743854463100433</v>
       </c>
       <c r="H1293" t="n">
         <v>140397</v>
@@ -37895,7 +37895,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.743854403495789</v>
+        <v>0.743854463100433</v>
       </c>
       <c r="H1294" t="n">
         <v>63340</v>
@@ -37982,7 +37982,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.747314214706421</v>
+        <v>0.747314274311066</v>
       </c>
       <c r="H1297" t="n">
         <v>123714</v>
@@ -38011,7 +38011,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.743854403495789</v>
+        <v>0.743854463100433</v>
       </c>
       <c r="H1298" t="n">
         <v>269434</v>
@@ -38098,7 +38098,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1301" t="n">
         <v>103262</v>
@@ -38127,7 +38127,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1302" t="n">
         <v>109329</v>
@@ -38156,7 +38156,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1303" t="n">
         <v>65645</v>
@@ -38243,7 +38243,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.7749924659729</v>
+        <v>0.774992525577545</v>
       </c>
       <c r="H1306" t="n">
         <v>168242</v>
@@ -38272,7 +38272,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.764613091945648</v>
+        <v>0.764613151550293</v>
       </c>
       <c r="H1307" t="n">
         <v>170070</v>
@@ -38330,7 +38330,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1309" t="n">
         <v>105632</v>
@@ -38359,7 +38359,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.747314214706421</v>
+        <v>0.747314274311066</v>
       </c>
       <c r="H1310" t="n">
         <v>131076</v>
@@ -38417,7 +38417,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1312" t="n">
         <v>86822</v>
@@ -38446,7 +38446,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.764613091945648</v>
+        <v>0.764613151550293</v>
       </c>
       <c r="H1313" t="n">
         <v>260385</v>
@@ -38475,7 +38475,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1314" t="n">
         <v>60881</v>
@@ -38504,7 +38504,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.747314214706421</v>
+        <v>0.747314274311066</v>
       </c>
       <c r="H1315" t="n">
         <v>51899</v>
@@ -38562,7 +38562,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1317" t="n">
         <v>128521</v>
@@ -38591,7 +38591,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1318" t="n">
         <v>48205</v>
@@ -38620,7 +38620,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1319" t="n">
         <v>83726</v>
@@ -38823,7 +38823,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.747314214706421</v>
+        <v>0.747314274311066</v>
       </c>
       <c r="H1326" t="n">
         <v>102293</v>
@@ -38881,7 +38881,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.743854403495789</v>
+        <v>0.743854463100433</v>
       </c>
       <c r="H1328" t="n">
         <v>51128</v>
@@ -39113,7 +39113,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1336" t="n">
         <v>533202</v>
@@ -39171,7 +39171,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.757693588733673</v>
+        <v>0.757693529129028</v>
       </c>
       <c r="H1338" t="n">
         <v>187114</v>
@@ -39200,7 +39200,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.764613091945648</v>
+        <v>0.764613151550293</v>
       </c>
       <c r="H1339" t="n">
         <v>149115</v>
@@ -39432,7 +39432,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.7749924659729</v>
+        <v>0.774992525577545</v>
       </c>
       <c r="H1347" t="n">
         <v>50868</v>
@@ -39461,7 +39461,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.7749924659729</v>
+        <v>0.774992525577545</v>
       </c>
       <c r="H1348" t="n">
         <v>140318</v>
@@ -39519,7 +39519,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1350" t="n">
         <v>305250</v>
@@ -39548,7 +39548,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1351" t="n">
         <v>45974</v>
@@ -39577,7 +39577,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.781912088394165</v>
+        <v>0.781911969184875</v>
       </c>
       <c r="H1352" t="n">
         <v>26682</v>
@@ -39606,7 +39606,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.792291462421417</v>
+        <v>0.792291402816772</v>
       </c>
       <c r="H1353" t="n">
         <v>91577</v>
@@ -39635,7 +39635,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.785371840000153</v>
+        <v>0.785371780395508</v>
       </c>
       <c r="H1354" t="n">
         <v>55193</v>
@@ -39664,7 +39664,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1355" t="n">
         <v>288218</v>
@@ -39693,7 +39693,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.792291462421417</v>
+        <v>0.792291402816772</v>
       </c>
       <c r="H1356" t="n">
         <v>17024</v>
@@ -39722,7 +39722,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.809590280056</v>
+        <v>0.809590339660645</v>
       </c>
       <c r="H1357" t="n">
         <v>110877</v>
@@ -39751,7 +39751,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1358" t="n">
         <v>83258</v>
@@ -39780,7 +39780,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.809590280056</v>
+        <v>0.809590339660645</v>
       </c>
       <c r="H1359" t="n">
         <v>170926</v>
@@ -39867,7 +39867,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1362" t="n">
         <v>313246</v>
@@ -39983,7 +39983,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1366" t="n">
         <v>281388</v>
@@ -40012,7 +40012,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.792291462421417</v>
+        <v>0.792291402816772</v>
       </c>
       <c r="H1367" t="n">
         <v>273985</v>
@@ -40041,7 +40041,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.799211025238037</v>
+        <v>0.799210906028748</v>
       </c>
       <c r="H1368" t="n">
         <v>80674</v>
@@ -40070,7 +40070,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.799211025238037</v>
+        <v>0.799210906028748</v>
       </c>
       <c r="H1369" t="n">
         <v>90790</v>
@@ -40099,7 +40099,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.799211025238037</v>
+        <v>0.799210906028748</v>
       </c>
       <c r="H1370" t="n">
         <v>56184</v>
@@ -40128,7 +40128,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.792291462421417</v>
+        <v>0.792291402816772</v>
       </c>
       <c r="H1371" t="n">
         <v>153196</v>
@@ -40215,7 +40215,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.792291462421417</v>
+        <v>0.792291402816772</v>
       </c>
       <c r="H1374" t="n">
         <v>90444</v>
@@ -40244,7 +40244,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1375" t="n">
         <v>86876</v>
@@ -40273,7 +40273,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1376" t="n">
         <v>14034</v>
@@ -40302,7 +40302,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1377" t="n">
         <v>27809</v>
@@ -40331,7 +40331,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.792291462421417</v>
+        <v>0.792291402816772</v>
       </c>
       <c r="H1378" t="n">
         <v>65291</v>
@@ -40360,7 +40360,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1379" t="n">
         <v>147569</v>
@@ -40389,7 +40389,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1380" t="n">
         <v>84546</v>
@@ -40447,7 +40447,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.792291462421417</v>
+        <v>0.792291402816772</v>
       </c>
       <c r="H1382" t="n">
         <v>175384</v>
@@ -40476,7 +40476,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.799211025238037</v>
+        <v>0.799210906028748</v>
       </c>
       <c r="H1383" t="n">
         <v>162202</v>
@@ -40505,7 +40505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1384" t="n">
         <v>90158</v>
@@ -40563,7 +40563,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.809590280056</v>
+        <v>0.809590339660645</v>
       </c>
       <c r="H1386" t="n">
         <v>468354</v>
@@ -40592,7 +40592,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1387" t="n">
         <v>156054</v>
@@ -40621,7 +40621,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1388" t="n">
         <v>49722</v>
@@ -40650,7 +40650,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813050150871277</v>
+        <v>0.813050091266632</v>
       </c>
       <c r="H1389" t="n">
         <v>189258</v>
@@ -40766,7 +40766,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.795751214027405</v>
+        <v>0.79575115442276</v>
       </c>
       <c r="H1393" t="n">
         <v>200154</v>
@@ -40882,7 +40882,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.799211025238037</v>
+        <v>0.799210906028748</v>
       </c>
       <c r="H1397" t="n">
         <v>17197</v>
@@ -40911,7 +40911,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.809590280056</v>
+        <v>0.809590339660645</v>
       </c>
       <c r="H1398" t="n">
         <v>879466</v>
@@ -40969,7 +40969,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.809590280056</v>
+        <v>0.809590339660645</v>
       </c>
       <c r="H1400" t="n">
         <v>336211</v>
@@ -41027,7 +41027,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.809590280056</v>
+        <v>0.809590339660645</v>
       </c>
       <c r="H1402" t="n">
         <v>407746</v>
@@ -41056,7 +41056,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.809590280056</v>
+        <v>0.809590339660645</v>
       </c>
       <c r="H1403" t="n">
         <v>371772</v>
@@ -41085,7 +41085,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1404" t="n">
         <v>451788</v>
@@ -41230,7 +41230,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.809590280056</v>
+        <v>0.809590339660645</v>
       </c>
       <c r="H1409" t="n">
         <v>300980</v>
@@ -41288,7 +41288,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1411" t="n">
         <v>52154</v>
@@ -41317,7 +41317,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1412" t="n">
         <v>218373</v>
@@ -41346,7 +41346,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1413" t="n">
         <v>583052</v>
@@ -41375,7 +41375,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1414" t="n">
         <v>94810</v>
@@ -41404,7 +41404,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1415" t="n">
         <v>926778</v>
@@ -41433,7 +41433,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1416" t="n">
         <v>335083</v>
@@ -41491,7 +41491,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1418" t="n">
         <v>281905</v>
@@ -41520,7 +41520,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1419" t="n">
         <v>190170</v>
@@ -41549,7 +41549,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1420" t="n">
         <v>114650</v>
@@ -41578,7 +41578,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1421" t="n">
         <v>66926</v>
@@ -41607,7 +41607,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1422" t="n">
         <v>148582</v>
@@ -41636,7 +41636,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1423" t="n">
         <v>274643</v>
@@ -41665,7 +41665,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1424" t="n">
         <v>138269</v>
@@ -41694,7 +41694,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1425" t="n">
         <v>60081</v>
@@ -41723,7 +41723,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1426" t="n">
         <v>92896</v>
@@ -41752,7 +41752,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1427" t="n">
         <v>69676</v>
@@ -41781,7 +41781,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1428" t="n">
         <v>27419</v>
@@ -41810,7 +41810,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.830349087715149</v>
+        <v>0.830349147319794</v>
       </c>
       <c r="H1429" t="n">
         <v>16294</v>
@@ -41839,7 +41839,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.826889395713806</v>
+        <v>0.826889336109161</v>
       </c>
       <c r="H1430" t="n">
         <v>34025</v>
@@ -41868,7 +41868,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.826889395713806</v>
+        <v>0.826889336109161</v>
       </c>
       <c r="H1431" t="n">
         <v>4343</v>
@@ -41897,7 +41897,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1432" t="n">
         <v>116624</v>
@@ -41955,7 +41955,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1434" t="n">
         <v>58038</v>
@@ -41984,7 +41984,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1435" t="n">
         <v>70728</v>
@@ -42013,7 +42013,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1436" t="n">
         <v>122837</v>
@@ -42042,7 +42042,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1437" t="n">
         <v>181025</v>
@@ -42071,7 +42071,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1438" t="n">
         <v>31317</v>
@@ -42158,7 +42158,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.823429584503174</v>
+        <v>0.823429524898529</v>
       </c>
       <c r="H1441" t="n">
         <v>332446</v>
@@ -42216,7 +42216,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.847647964954376</v>
+        <v>0.847648024559021</v>
       </c>
       <c r="H1443" t="n">
         <v>259888</v>
@@ -42245,7 +42245,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.854567527770996</v>
+        <v>0.854567587375641</v>
       </c>
       <c r="H1444" t="n">
         <v>272372</v>
@@ -42274,7 +42274,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.851107776165009</v>
+        <v>0.851107895374298</v>
       </c>
       <c r="H1445" t="n">
         <v>242876</v>
@@ -42448,7 +42448,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.833808839321136</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1451" t="n">
         <v>28378</v>
@@ -42477,7 +42477,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.833808839321136</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1452" t="n">
         <v>824448</v>
@@ -42535,7 +42535,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.833808839321136</v>
+        <v>0.833808958530426</v>
       </c>
       <c r="H1454" t="n">
         <v>320343</v>
@@ -42593,7 +42593,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.858027398586273</v>
+        <v>0.858027338981628</v>
       </c>
       <c r="H1456" t="n">
         <v>272511</v>
@@ -42622,7 +42622,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.878786206245422</v>
+        <v>0.878786087036133</v>
       </c>
       <c r="H1457" t="n">
         <v>357522</v>
@@ -42651,7 +42651,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.868406772613525</v>
+        <v>0.868406713008881</v>
       </c>
       <c r="H1458" t="n">
         <v>78151</v>
@@ -42680,7 +42680,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.899544894695282</v>
+        <v>0.899544775485992</v>
       </c>
       <c r="H1459" t="n">
         <v>501877</v>
@@ -42709,7 +42709,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.90300452709198</v>
+        <v>0.90300464630127</v>
       </c>
       <c r="H1460" t="n">
         <v>479584</v>
@@ -42738,7 +42738,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.920303583145142</v>
+        <v>0.920303642749786</v>
       </c>
       <c r="H1461" t="n">
         <v>436738</v>
@@ -42767,7 +42767,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.916843712329865</v>
+        <v>0.916843891143799</v>
       </c>
       <c r="H1462" t="n">
         <v>386374</v>
@@ -42825,7 +42825,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.916843712329865</v>
+        <v>0.916843891143799</v>
       </c>
       <c r="H1464" t="n">
         <v>148638</v>
@@ -42854,7 +42854,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.927223205566406</v>
+        <v>0.927223265171051</v>
       </c>
       <c r="H1465" t="n">
         <v>86673</v>
@@ -42883,7 +42883,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.923763334751129</v>
+        <v>0.923763394355774</v>
       </c>
       <c r="H1466" t="n">
         <v>287349</v>
@@ -42912,7 +42912,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522202014923</v>
       </c>
       <c r="H1467" t="n">
         <v>688381</v>
@@ -42941,7 +42941,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522202014923</v>
       </c>
       <c r="H1468" t="n">
         <v>303974</v>
@@ -42999,7 +42999,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522202014923</v>
       </c>
       <c r="H1470" t="n">
         <v>44738</v>
@@ -43028,7 +43028,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522202014923</v>
       </c>
       <c r="H1471" t="n">
         <v>189714</v>
@@ -43086,7 +43086,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522202014923</v>
       </c>
       <c r="H1473" t="n">
         <v>94486</v>
@@ -43115,7 +43115,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.937602400779724</v>
+        <v>0.937602579593658</v>
       </c>
       <c r="H1474" t="n">
         <v>142236</v>
@@ -43144,7 +43144,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.937602400779724</v>
+        <v>0.937602579593658</v>
       </c>
       <c r="H1475" t="n">
         <v>50984</v>
@@ -43173,7 +43173,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.958361208438873</v>
+        <v>0.958361327648163</v>
       </c>
       <c r="H1476" t="n">
         <v>431293</v>
@@ -43260,7 +43260,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.965280830860138</v>
+        <v>0.965280711650848</v>
       </c>
       <c r="H1479" t="n">
         <v>279723</v>
@@ -43289,7 +43289,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.965280830860138</v>
+        <v>0.965280711650848</v>
       </c>
       <c r="H1480" t="n">
         <v>122253</v>
@@ -43318,7 +43318,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.965280830860138</v>
+        <v>0.965280711650848</v>
       </c>
       <c r="H1481" t="n">
         <v>54841</v>
@@ -43347,7 +43347,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.958361208438873</v>
+        <v>0.958361327648163</v>
       </c>
       <c r="H1482" t="n">
         <v>159538</v>
@@ -43376,7 +43376,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.968740582466125</v>
+        <v>0.968740522861481</v>
       </c>
       <c r="H1483" t="n">
         <v>274130</v>
@@ -43405,7 +43405,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.996418952941895</v>
+        <v>0.996418833732605</v>
       </c>
       <c r="H1484" t="n">
         <v>249252</v>
@@ -43434,7 +43434,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.992959141731262</v>
+        <v>0.992959022521973</v>
       </c>
       <c r="H1485" t="n">
         <v>160211</v>
@@ -43463,7 +43463,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.999878704547882</v>
+        <v>0.999878764152527</v>
       </c>
       <c r="H1486" t="n">
         <v>120478</v>
@@ -43492,7 +43492,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.999878704547882</v>
+        <v>0.999878764152527</v>
       </c>
       <c r="H1487" t="n">
         <v>171820</v>
@@ -43521,7 +43521,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.992959141731262</v>
+        <v>0.992959022521973</v>
       </c>
       <c r="H1488" t="n">
         <v>196578</v>
@@ -43608,7 +43608,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.996418952941895</v>
+        <v>0.996418833732605</v>
       </c>
       <c r="H1491" t="n">
         <v>62978</v>
@@ -43637,7 +43637,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.992959141731262</v>
+        <v>0.992959022521973</v>
       </c>
       <c r="H1492" t="n">
         <v>57450</v>
@@ -43724,7 +43724,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.961820960044861</v>
+        <v>0.961821138858795</v>
       </c>
       <c r="H1495" t="n">
         <v>274571</v>
@@ -43753,7 +43753,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.961820960044861</v>
+        <v>0.961821138858795</v>
       </c>
       <c r="H1496" t="n">
         <v>319492</v>
@@ -43782,7 +43782,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.920303583145142</v>
+        <v>0.920303642749786</v>
       </c>
       <c r="H1497" t="n">
         <v>1137530</v>
@@ -43811,7 +43811,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.934142768383026</v>
+        <v>0.934142887592316</v>
       </c>
       <c r="H1498" t="n">
         <v>381079</v>
@@ -43840,7 +43840,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.934142768383026</v>
+        <v>0.934142887592316</v>
       </c>
       <c r="H1499" t="n">
         <v>103523</v>
@@ -43869,7 +43869,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.920303583145142</v>
+        <v>0.920303642749786</v>
       </c>
       <c r="H1500" t="n">
         <v>453289</v>
@@ -43898,7 +43898,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.934142768383026</v>
+        <v>0.934142887592316</v>
       </c>
       <c r="H1501" t="n">
         <v>135609</v>
@@ -43927,7 +43927,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.937602400779724</v>
+        <v>0.937602579593658</v>
       </c>
       <c r="H1502" t="n">
         <v>755734</v>
@@ -43956,7 +43956,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.927223205566406</v>
+        <v>0.927223265171051</v>
       </c>
       <c r="H1503" t="n">
         <v>329891</v>
@@ -43985,7 +43985,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.934142768383026</v>
+        <v>0.934142887592316</v>
       </c>
       <c r="H1504" t="n">
         <v>203683</v>
@@ -44014,7 +44014,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.944522023200989</v>
+        <v>0.944522202014923</v>
       </c>
       <c r="H1505" t="n">
         <v>156551</v>
@@ -44043,7 +44043,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.965280830860138</v>
+        <v>0.965280711650848</v>
       </c>
       <c r="H1506" t="n">
         <v>99940</v>
@@ -44072,7 +44072,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.968740582466125</v>
+        <v>0.968740522861481</v>
       </c>
       <c r="H1507" t="n">
         <v>253006</v>
@@ -44101,7 +44101,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.965280830860138</v>
+        <v>0.965280711650848</v>
       </c>
       <c r="H1508" t="n">
         <v>176991</v>
@@ -44130,7 +44130,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.989499270915985</v>
+        <v>0.98949921131134</v>
       </c>
       <c r="H1509" t="n">
         <v>407671</v>
@@ -44188,7 +44188,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.02063751220703</v>
+        <v>1.02063739299774</v>
       </c>
       <c r="H1511" t="n">
         <v>206402</v>
@@ -44275,7 +44275,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1514" t="n">
         <v>249496</v>
@@ -44304,7 +44304,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.989499270915985</v>
+        <v>0.98949921131134</v>
       </c>
       <c r="H1515" t="n">
         <v>224195</v>
@@ -44333,7 +44333,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1516" t="n">
         <v>437735</v>
@@ -44478,7 +44478,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.0171777009964</v>
+        <v>1.01717758178711</v>
       </c>
       <c r="H1521" t="n">
         <v>273665</v>
@@ -44507,7 +44507,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1522" t="n">
         <v>189922</v>
@@ -44536,7 +44536,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.01371788978577</v>
+        <v>1.01371777057648</v>
       </c>
       <c r="H1523" t="n">
         <v>391063</v>
@@ -44594,7 +44594,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.03101682662964</v>
+        <v>1.03101670742035</v>
       </c>
       <c r="H1525" t="n">
         <v>218492</v>
@@ -44710,7 +44710,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.117511510849</v>
+        <v>1.11751139163971</v>
       </c>
       <c r="H1529" t="n">
         <v>421145</v>
@@ -44826,7 +44826,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.08983314037323</v>
+        <v>1.08983325958252</v>
       </c>
       <c r="H1533" t="n">
         <v>163796</v>
@@ -44884,7 +44884,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.09329295158386</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1535" t="n">
         <v>168043</v>
@@ -44913,7 +44913,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.08983314037323</v>
+        <v>1.08983325958252</v>
       </c>
       <c r="H1536" t="n">
         <v>438076</v>
@@ -44971,7 +44971,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.09329295158386</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1538" t="n">
         <v>370435</v>
@@ -45029,7 +45029,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.09329295158386</v>
+        <v>1.09329307079315</v>
       </c>
       <c r="H1540" t="n">
         <v>210213</v>
@@ -45087,7 +45087,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.04139626026154</v>
+        <v>1.04139614105225</v>
       </c>
       <c r="H1542" t="n">
         <v>266855</v>
@@ -45116,7 +45116,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.04139626026154</v>
+        <v>1.04139614105225</v>
       </c>
       <c r="H1543" t="n">
         <v>262904</v>
@@ -45203,7 +45203,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.05523526668549</v>
+        <v>1.05523538589478</v>
       </c>
       <c r="H1546" t="n">
         <v>96630</v>
@@ -45609,7 +45609,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.117511510849</v>
+        <v>1.11751139163971</v>
       </c>
       <c r="H1560" t="n">
         <v>2403157</v>
@@ -45812,7 +45812,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.19708657264709</v>
+        <v>1.19708669185638</v>
       </c>
       <c r="H1567" t="n">
         <v>415789</v>
@@ -45957,7 +45957,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.04139626026154</v>
+        <v>1.04139614105225</v>
       </c>
       <c r="H1572" t="n">
         <v>825976</v>
@@ -46160,7 +46160,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.12789082527161</v>
+        <v>1.12789070606232</v>
       </c>
       <c r="H1579" t="n">
         <v>463327</v>
@@ -46189,7 +46189,7 @@
         <v>1.625</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.12443113327026</v>
+        <v>1.12443101406097</v>
       </c>
       <c r="H1580" t="n">
         <v>317784</v>
@@ -46218,7 +46218,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.18670725822449</v>
+        <v>1.1867071390152</v>
       </c>
       <c r="H1581" t="n">
         <v>780997</v>
@@ -46276,7 +46276,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.19362688064575</v>
+        <v>1.19362676143646</v>
       </c>
       <c r="H1583" t="n">
         <v>615283</v>
@@ -46305,7 +46305,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.19708657264709</v>
+        <v>1.19708669185638</v>
       </c>
       <c r="H1584" t="n">
         <v>312880</v>
@@ -46334,7 +46334,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.19362688064575</v>
+        <v>1.19362676143646</v>
       </c>
       <c r="H1585" t="n">
         <v>429004</v>
@@ -46421,7 +46421,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.23168444633484</v>
+        <v>1.23168456554413</v>
       </c>
       <c r="H1588" t="n">
         <v>827658</v>
@@ -46508,7 +46508,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.24552345275879</v>
+        <v>1.24552369117737</v>
       </c>
       <c r="H1591" t="n">
         <v>435433</v>
@@ -46566,7 +46566,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.23860394954681</v>
+        <v>1.2386040687561</v>
       </c>
       <c r="H1593" t="n">
         <v>563589</v>
@@ -46595,7 +46595,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.22130501270294</v>
+        <v>1.22130525112152</v>
       </c>
       <c r="H1594" t="n">
         <v>600957</v>
@@ -46624,7 +46624,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.24552345275879</v>
+        <v>1.24552369117737</v>
       </c>
       <c r="H1595" t="n">
         <v>378069</v>
@@ -46682,7 +46682,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.24552345275879</v>
+        <v>1.24552369117737</v>
       </c>
       <c r="H1597" t="n">
         <v>657270</v>
@@ -46740,7 +46740,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.22476482391357</v>
+        <v>1.22476494312286</v>
       </c>
       <c r="H1599" t="n">
         <v>500917</v>
@@ -46769,7 +46769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.19708657264709</v>
+        <v>1.19708669185638</v>
       </c>
       <c r="H1600" t="n">
         <v>1485021</v>
@@ -46856,7 +46856,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.19708657264709</v>
+        <v>1.19708669185638</v>
       </c>
       <c r="H1603" t="n">
         <v>2203239</v>
@@ -47059,7 +47059,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1610" t="n">
         <v>1024808</v>
@@ -47146,7 +47146,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.05994200706482</v>
+        <v>1.05994212627411</v>
       </c>
       <c r="H1613" t="n">
         <v>1513410</v>
@@ -47175,7 +47175,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.04747223854065</v>
+        <v>1.04747211933136</v>
       </c>
       <c r="H1614" t="n">
         <v>585100</v>
@@ -47349,7 +47349,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.05994200706482</v>
+        <v>1.05994212627411</v>
       </c>
       <c r="H1620" t="n">
         <v>455691</v>
@@ -47378,7 +47378,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.06825530529022</v>
+        <v>1.06825542449951</v>
       </c>
       <c r="H1621" t="n">
         <v>353335</v>
@@ -47407,7 +47407,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.06409883499146</v>
+        <v>1.06409871578217</v>
       </c>
       <c r="H1622" t="n">
         <v>276933</v>
@@ -47465,7 +47465,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.06409883499146</v>
+        <v>1.06409871578217</v>
       </c>
       <c r="H1624" t="n">
         <v>396100</v>
@@ -47523,7 +47523,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.05578553676605</v>
+        <v>1.05578541755676</v>
       </c>
       <c r="H1626" t="n">
         <v>221246</v>
@@ -47552,7 +47552,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1627" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1627" t="n">
         <v>148939</v>
@@ -47581,7 +47581,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.06825530529022</v>
+        <v>1.06825542449951</v>
       </c>
       <c r="H1628" t="n">
         <v>176002</v>
@@ -47610,7 +47610,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1629" t="n">
         <v>275252</v>
@@ -47987,7 +47987,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.06409883499146</v>
+        <v>1.06409871578217</v>
       </c>
       <c r="H1642" t="n">
         <v>586662</v>
@@ -48683,7 +48683,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.04747223854065</v>
+        <v>1.04747211933136</v>
       </c>
       <c r="H1666" t="n">
         <v>210117</v>
@@ -48915,7 +48915,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.12644815444946</v>
+        <v>1.12644827365875</v>
       </c>
       <c r="H1674" t="n">
         <v>329517</v>
@@ -49147,7 +49147,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.18048441410065</v>
+        <v>1.18048453330994</v>
       </c>
       <c r="H1682" t="n">
         <v>95817</v>
@@ -49466,7 +49466,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1693" t="n">
         <v>146529</v>
@@ -49524,7 +49524,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.06825530529022</v>
+        <v>1.06825542449951</v>
       </c>
       <c r="H1695" t="n">
         <v>118248</v>
@@ -49553,7 +49553,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.05994200706482</v>
+        <v>1.05994212627411</v>
       </c>
       <c r="H1696" t="n">
         <v>141330</v>
@@ -49611,7 +49611,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.05578553676605</v>
+        <v>1.05578541755676</v>
       </c>
       <c r="H1698" t="n">
         <v>39503</v>
@@ -49640,7 +49640,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.04747223854065</v>
+        <v>1.04747211933136</v>
       </c>
       <c r="H1699" t="n">
         <v>98786</v>
@@ -49698,7 +49698,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.06409883499146</v>
+        <v>1.06409871578217</v>
       </c>
       <c r="H1701" t="n">
         <v>68212</v>
@@ -49727,7 +49727,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.06409883499146</v>
+        <v>1.06409871578217</v>
       </c>
       <c r="H1702" t="n">
         <v>92847</v>
@@ -49756,7 +49756,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.06825530529022</v>
+        <v>1.06825542449951</v>
       </c>
       <c r="H1703" t="n">
         <v>47521</v>
@@ -49901,7 +49901,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.04747223854065</v>
+        <v>1.04747211933136</v>
       </c>
       <c r="H1708" t="n">
         <v>822226</v>
@@ -49930,7 +49930,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1709" t="n">
-        <v>1.05578553676605</v>
+        <v>1.05578541755676</v>
       </c>
       <c r="H1709" t="n">
         <v>56159</v>
@@ -49959,7 +49959,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.06825530529022</v>
+        <v>1.06825542449951</v>
       </c>
       <c r="H1710" t="n">
         <v>239412</v>
@@ -49988,7 +49988,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1711" t="n">
         <v>72822</v>
@@ -50046,7 +50046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.05578553676605</v>
+        <v>1.05578541755676</v>
       </c>
       <c r="H1713" t="n">
         <v>45805</v>
@@ -50075,7 +50075,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.06409883499146</v>
+        <v>1.06409871578217</v>
       </c>
       <c r="H1714" t="n">
         <v>129641</v>
@@ -50104,7 +50104,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.05578553676605</v>
+        <v>1.05578541755676</v>
       </c>
       <c r="H1715" t="n">
         <v>19401</v>
@@ -50336,7 +50336,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1723" t="n">
         <v>120909</v>
@@ -50365,7 +50365,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1724" t="n">
         <v>91205</v>
@@ -50394,7 +50394,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.06409883499146</v>
+        <v>1.06409871578217</v>
       </c>
       <c r="H1725" t="n">
         <v>52953</v>
@@ -50423,7 +50423,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.06825530529022</v>
+        <v>1.06825542449951</v>
       </c>
       <c r="H1726" t="n">
         <v>29407</v>
@@ -50452,7 +50452,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.05578553676605</v>
+        <v>1.05578541755676</v>
       </c>
       <c r="H1727" t="n">
         <v>130467</v>
@@ -50481,7 +50481,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1728" t="n">
         <v>25254</v>
@@ -50539,7 +50539,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1730" t="n">
         <v>54563</v>
@@ -50568,7 +50568,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.07241201400757</v>
+        <v>1.07241189479828</v>
       </c>
       <c r="H1731" t="n">
         <v>29048</v>
@@ -50771,7 +50771,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.13476145267487</v>
+        <v>1.13476157188416</v>
       </c>
       <c r="H1738" t="n">
         <v>124547</v>
@@ -50887,7 +50887,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.13476145267487</v>
+        <v>1.13476157188416</v>
       </c>
       <c r="H1742" t="n">
         <v>58803</v>
@@ -51322,7 +51322,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1757" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1757" t="n">
         <v>136128</v>
@@ -51351,7 +51351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1758" t="n">
         <v>82692</v>
@@ -51409,7 +51409,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.18048441410065</v>
+        <v>1.18048453330994</v>
       </c>
       <c r="H1760" t="n">
         <v>60135</v>
@@ -51467,7 +51467,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.18048441410065</v>
+        <v>1.18048453330994</v>
       </c>
       <c r="H1762" t="n">
         <v>31346</v>
@@ -51525,7 +51525,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1764" t="n">
         <v>134687</v>
@@ -51554,7 +51554,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.18048441410065</v>
+        <v>1.18048453330994</v>
       </c>
       <c r="H1765" t="n">
         <v>107827</v>
@@ -51583,7 +51583,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1766" t="n">
         <v>36572</v>
@@ -51960,7 +51960,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.13476145267487</v>
+        <v>1.13476157188416</v>
       </c>
       <c r="H1779" t="n">
         <v>73657</v>
@@ -52018,7 +52018,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.13476145267487</v>
+        <v>1.13476157188416</v>
       </c>
       <c r="H1781" t="n">
         <v>149637</v>
@@ -52134,7 +52134,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1785" t="n">
         <v>598110</v>
@@ -52337,7 +52337,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.22620761394501</v>
+        <v>1.22620749473572</v>
       </c>
       <c r="H1792" t="n">
         <v>300696</v>
@@ -52366,7 +52366,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.23452079296112</v>
+        <v>1.23452067375183</v>
       </c>
       <c r="H1793" t="n">
         <v>551408</v>
@@ -52511,7 +52511,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.2636171579361</v>
+        <v>1.26361703872681</v>
       </c>
       <c r="H1798" t="n">
         <v>366320</v>
@@ -52946,7 +52946,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.2636171579361</v>
+        <v>1.26361703872681</v>
       </c>
       <c r="H1813" t="n">
         <v>380172</v>
@@ -53062,7 +53062,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.23036408424377</v>
+        <v>1.23036420345306</v>
       </c>
       <c r="H1817" t="n">
         <v>431911</v>
@@ -53091,7 +53091,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1818" t="n">
-        <v>1.23452079296112</v>
+        <v>1.23452067375183</v>
       </c>
       <c r="H1818" t="n">
         <v>151967</v>
@@ -53149,7 +53149,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1820" t="n">
         <v>359212</v>
@@ -53323,7 +53323,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.18048441410065</v>
+        <v>1.18048453330994</v>
       </c>
       <c r="H1826" t="n">
         <v>77691</v>
@@ -53381,7 +53381,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1828" t="n">
         <v>93795</v>
@@ -53439,7 +53439,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1830" t="n">
-        <v>1.1929544210434</v>
+        <v>1.19295430183411</v>
       </c>
       <c r="H1830" t="n">
         <v>127047</v>
@@ -53671,7 +53671,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.13476145267487</v>
+        <v>1.13476157188416</v>
       </c>
       <c r="H1838" t="n">
         <v>172488</v>
@@ -53961,7 +53961,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1848" t="n">
-        <v>1.18048441410065</v>
+        <v>1.18048453330994</v>
       </c>
       <c r="H1848" t="n">
         <v>114995</v>
@@ -54280,7 +54280,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.20043647289276</v>
+        <v>1.20043635368347</v>
       </c>
       <c r="H1859" t="n">
         <v>88637</v>
@@ -80110,7 +80110,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="D2750" t="n">
-        <v>1.86199998855591</v>
+        <v>1.86800003051758</v>
       </c>
       <c r="E2750" t="n">
         <v>1.84200000762939</v>
@@ -80125,6 +80125,35 @@
         <v>9673</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>1.8639999628067</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>1.82200002670288</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>1.85599994659424</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>1.85599994659424</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>81969</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.48506224155426</v>
+        <v>0.485062211751938</v>
       </c>
       <c r="H2" t="n">
         <v>191859</v>
@@ -456,7 +456,7 @@
         <v>0.70550000667572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.488176047801971</v>
+        <v>0.488176077604294</v>
       </c>
       <c r="H3" t="n">
         <v>84538</v>
@@ -601,7 +601,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.479872584342957</v>
+        <v>0.479872614145279</v>
       </c>
       <c r="H8" t="n">
         <v>46220</v>
@@ -659,7 +659,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G10" t="n">
-        <v>0.475374847650528</v>
+        <v>0.47537487745285</v>
       </c>
       <c r="H10" t="n">
         <v>133195</v>
@@ -688,7 +688,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G11" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H11" t="n">
         <v>328341</v>
@@ -717,7 +717,7 @@
         <v>0.667500019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>0.461881697177887</v>
+        <v>0.461881726980209</v>
       </c>
       <c r="H12" t="n">
         <v>473449</v>
@@ -746,7 +746,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G13" t="n">
-        <v>0.466379433870316</v>
+        <v>0.466379404067993</v>
       </c>
       <c r="H13" t="n">
         <v>70046</v>
@@ -804,7 +804,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G15" t="n">
-        <v>0.460151821374893</v>
+        <v>0.460151731967926</v>
       </c>
       <c r="H15" t="n">
         <v>66901</v>
@@ -862,7 +862,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G17" t="n">
-        <v>0.467071443796158</v>
+        <v>0.467071354389191</v>
       </c>
       <c r="H17" t="n">
         <v>129282</v>
@@ -891,7 +891,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G18" t="n">
-        <v>0.477450758218765</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H18" t="n">
         <v>119370</v>
@@ -920,7 +920,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G19" t="n">
-        <v>0.480910569429398</v>
+        <v>0.48091048002243</v>
       </c>
       <c r="H19" t="n">
         <v>50528</v>
@@ -949,7 +949,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G20" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H20" t="n">
         <v>46550</v>
@@ -978,7 +978,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G21" t="n">
-        <v>0.476066827774048</v>
+        <v>0.476066797971725</v>
       </c>
       <c r="H21" t="n">
         <v>53225</v>
@@ -1036,7 +1036,7 @@
         <v>0.66049998998642</v>
       </c>
       <c r="G23" t="n">
-        <v>0.457037955522537</v>
+        <v>0.457037925720215</v>
       </c>
       <c r="H23" t="n">
         <v>70489</v>
@@ -1094,7 +1094,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G25" t="n">
-        <v>0.455308079719543</v>
+        <v>0.455308049917221</v>
       </c>
       <c r="H25" t="n">
         <v>168696</v>
@@ -1123,7 +1123,7 @@
         <v>0.658999979496002</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456000030040741</v>
+        <v>0.456000000238419</v>
       </c>
       <c r="H26" t="n">
         <v>91179</v>
@@ -1152,7 +1152,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G27" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620656013489</v>
       </c>
       <c r="H27" t="n">
         <v>128286</v>
@@ -1181,7 +1181,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G28" t="n">
-        <v>0.422786056995392</v>
+        <v>0.422786027193069</v>
       </c>
       <c r="H28" t="n">
         <v>174406</v>
@@ -1210,7 +1210,7 @@
         <v>0.619499981403351</v>
       </c>
       <c r="G29" t="n">
-        <v>0.428667694330215</v>
+        <v>0.428667664527893</v>
       </c>
       <c r="H29" t="n">
         <v>258654</v>
@@ -1268,7 +1268,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G31" t="n">
-        <v>0.425553947687149</v>
+        <v>0.425553888082504</v>
       </c>
       <c r="H31" t="n">
         <v>128707</v>
@@ -1297,7 +1297,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G32" t="n">
-        <v>0.438009142875671</v>
+        <v>0.438009113073349</v>
       </c>
       <c r="H32" t="n">
         <v>72389</v>
@@ -1326,7 +1326,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G33" t="n">
-        <v>0.433165460824966</v>
+        <v>0.433165401220322</v>
       </c>
       <c r="H33" t="n">
         <v>214463</v>
@@ -1355,7 +1355,7 @@
         <v>0.627499997615814</v>
       </c>
       <c r="G34" t="n">
-        <v>0.43420335650444</v>
+        <v>0.434203386306763</v>
       </c>
       <c r="H34" t="n">
         <v>449393</v>
@@ -1384,7 +1384,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G35" t="n">
-        <v>0.435933232307434</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H35" t="n">
         <v>126886</v>
@@ -1413,7 +1413,7 @@
         <v>0.625</v>
       </c>
       <c r="G36" t="n">
-        <v>0.432473450899124</v>
+        <v>0.432473510503769</v>
       </c>
       <c r="H36" t="n">
         <v>45866</v>
@@ -1471,7 +1471,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G38" t="n">
-        <v>0.435933232307434</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H38" t="n">
         <v>128161</v>
@@ -1500,7 +1500,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>0.429013669490814</v>
+        <v>0.429013699293137</v>
       </c>
       <c r="H39" t="n">
         <v>68431</v>
@@ -1529,7 +1529,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G40" t="n">
-        <v>0.433857381343842</v>
+        <v>0.433857440948486</v>
       </c>
       <c r="H40" t="n">
         <v>83632</v>
@@ -1558,7 +1558,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G41" t="n">
-        <v>0.432127505540848</v>
+        <v>0.432127445936203</v>
       </c>
       <c r="H41" t="n">
         <v>54191</v>
@@ -1587,7 +1587,7 @@
         <v>0.623499989509583</v>
       </c>
       <c r="G42" t="n">
-        <v>0.431435525417328</v>
+        <v>0.43143555521965</v>
       </c>
       <c r="H42" t="n">
         <v>172912</v>
@@ -1616,7 +1616,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G43" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089609861374</v>
       </c>
       <c r="H43" t="n">
         <v>51995</v>
@@ -1645,7 +1645,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G44" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620656013489</v>
       </c>
       <c r="H44" t="n">
         <v>148615</v>
@@ -1732,7 +1732,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G47" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089609861374</v>
       </c>
       <c r="H47" t="n">
         <v>26658</v>
@@ -1761,7 +1761,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G48" t="n">
-        <v>0.431089550256729</v>
+        <v>0.431089609861374</v>
       </c>
       <c r="H48" t="n">
         <v>122811</v>
@@ -1790,7 +1790,7 @@
         <v>0.621500015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>0.43005159497261</v>
+        <v>0.430051624774933</v>
       </c>
       <c r="H49" t="n">
         <v>65600</v>
@@ -1819,7 +1819,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G50" t="n">
-        <v>0.433857381343842</v>
+        <v>0.433857440948486</v>
       </c>
       <c r="H50" t="n">
         <v>138176</v>
@@ -1848,7 +1848,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>0.441468954086304</v>
+        <v>0.441468924283981</v>
       </c>
       <c r="H51" t="n">
         <v>265251</v>
@@ -1906,7 +1906,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G53" t="n">
-        <v>0.439739018678665</v>
+        <v>0.439739048480988</v>
       </c>
       <c r="H53" t="n">
         <v>22435</v>
@@ -1993,7 +1993,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G56" t="n">
-        <v>0.439393043518066</v>
+        <v>0.439393103122711</v>
       </c>
       <c r="H56" t="n">
         <v>61433</v>
@@ -2022,7 +2022,7 @@
         <v>0.631500005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>0.436971217393875</v>
+        <v>0.436971187591553</v>
       </c>
       <c r="H57" t="n">
         <v>57158</v>
@@ -2051,7 +2051,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G58" t="n">
-        <v>0.433511406183243</v>
+        <v>0.43351137638092</v>
       </c>
       <c r="H58" t="n">
         <v>68965</v>
@@ -2080,7 +2080,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G59" t="n">
-        <v>0.439739018678665</v>
+        <v>0.439739048480988</v>
       </c>
       <c r="H59" t="n">
         <v>123639</v>
@@ -2109,7 +2109,7 @@
         <v>0.635500013828278</v>
       </c>
       <c r="G60" t="n">
-        <v>0.439739018678665</v>
+        <v>0.439739048480988</v>
       </c>
       <c r="H60" t="n">
         <v>91266</v>
@@ -2138,7 +2138,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G61" t="n">
-        <v>0.434549361467361</v>
+        <v>0.434549421072006</v>
       </c>
       <c r="H61" t="n">
         <v>91042</v>
@@ -2167,7 +2167,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.435933232307434</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H62" t="n">
         <v>79829</v>
@@ -2196,7 +2196,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>0.434549361467361</v>
+        <v>0.434549421072006</v>
       </c>
       <c r="H63" t="n">
         <v>33873</v>
@@ -2254,7 +2254,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G65" t="n">
-        <v>0.431781530380249</v>
+        <v>0.431781500577927</v>
       </c>
       <c r="H65" t="n">
         <v>57188</v>
@@ -2283,7 +2283,7 @@
         <v>0.624499976634979</v>
       </c>
       <c r="G66" t="n">
-        <v>0.432127505540848</v>
+        <v>0.432127445936203</v>
       </c>
       <c r="H66" t="n">
         <v>90493</v>
@@ -2312,7 +2312,7 @@
         <v>0.617500007152557</v>
       </c>
       <c r="G67" t="n">
-        <v>0.42728379368782</v>
+        <v>0.427283763885498</v>
       </c>
       <c r="H67" t="n">
         <v>56153</v>
@@ -2341,7 +2341,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G68" t="n">
-        <v>0.422786056995392</v>
+        <v>0.422786027193069</v>
       </c>
       <c r="H68" t="n">
         <v>79242</v>
@@ -2370,7 +2370,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G69" t="n">
-        <v>0.429013669490814</v>
+        <v>0.429013699293137</v>
       </c>
       <c r="H69" t="n">
         <v>66538</v>
@@ -2399,7 +2399,7 @@
         <v>0.615000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>0.425553947687149</v>
+        <v>0.425553888082504</v>
       </c>
       <c r="H70" t="n">
         <v>76151</v>
@@ -2428,7 +2428,7 @@
         <v>0.615499973297119</v>
       </c>
       <c r="G71" t="n">
-        <v>0.425899833440781</v>
+        <v>0.425899893045425</v>
       </c>
       <c r="H71" t="n">
         <v>41570</v>
@@ -2457,7 +2457,7 @@
         <v>0.626999974250793</v>
       </c>
       <c r="G72" t="n">
-        <v>0.433857381343842</v>
+        <v>0.433857440948486</v>
       </c>
       <c r="H72" t="n">
         <v>69507</v>
@@ -2486,7 +2486,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G73" t="n">
-        <v>0.430397570133209</v>
+        <v>0.430397629737854</v>
       </c>
       <c r="H73" t="n">
         <v>77451</v>
@@ -2544,7 +2544,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>0.435933232307434</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H75" t="n">
         <v>67899</v>
@@ -2631,7 +2631,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G78" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H78" t="n">
         <v>132097</v>
@@ -2689,7 +2689,7 @@
         <v>0.693499982357025</v>
       </c>
       <c r="G80" t="n">
-        <v>0.479872584342957</v>
+        <v>0.479872614145279</v>
       </c>
       <c r="H80" t="n">
         <v>22198</v>
@@ -2805,7 +2805,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G84" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611543178558</v>
       </c>
       <c r="H84" t="n">
         <v>97915</v>
@@ -2863,7 +2863,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G86" t="n">
-        <v>0.446312576532364</v>
+        <v>0.446312606334686</v>
       </c>
       <c r="H86" t="n">
         <v>147100</v>
@@ -2950,7 +2950,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G89" t="n">
-        <v>0.445620685815811</v>
+        <v>0.445620656013489</v>
       </c>
       <c r="H89" t="n">
         <v>81033</v>
@@ -2979,7 +2979,7 @@
         <v>0.637000024318695</v>
       </c>
       <c r="G90" t="n">
-        <v>0.440777003765106</v>
+        <v>0.440776973962784</v>
       </c>
       <c r="H90" t="n">
         <v>76399</v>
@@ -3037,7 +3037,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G92" t="n">
-        <v>0.435933232307434</v>
+        <v>0.435933291912079</v>
       </c>
       <c r="H92" t="n">
         <v>127499</v>
@@ -3066,7 +3066,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G93" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H93" t="n">
         <v>137577</v>
@@ -3124,7 +3124,7 @@
         <v>0.656499981880188</v>
       </c>
       <c r="G95" t="n">
-        <v>0.454270154237747</v>
+        <v>0.454270124435425</v>
       </c>
       <c r="H95" t="n">
         <v>28570</v>
@@ -3182,7 +3182,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G97" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H97" t="n">
         <v>41726</v>
@@ -3211,7 +3211,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G98" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H98" t="n">
         <v>43674</v>
@@ -3240,7 +3240,7 @@
         <v>0.634999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>0.439393043518066</v>
+        <v>0.439393103122711</v>
       </c>
       <c r="H99" t="n">
         <v>79566</v>
@@ -3298,7 +3298,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>0.443890780210495</v>
+        <v>0.44389083981514</v>
       </c>
       <c r="H101" t="n">
         <v>21942</v>
@@ -3385,7 +3385,7 @@
         <v>0.6875</v>
       </c>
       <c r="G104" t="n">
-        <v>0.475720852613449</v>
+        <v>0.475720822811127</v>
       </c>
       <c r="H104" t="n">
         <v>124171</v>
@@ -3472,7 +3472,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G107" t="n">
-        <v>0.474682867527008</v>
+        <v>0.474682927131653</v>
       </c>
       <c r="H107" t="n">
         <v>51910</v>
@@ -3559,7 +3559,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G110" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H110" t="n">
         <v>62146</v>
@@ -3588,7 +3588,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G111" t="n">
-        <v>0.477450758218765</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H111" t="n">
         <v>81596</v>
@@ -3646,7 +3646,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G113" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H113" t="n">
         <v>77229</v>
@@ -3704,7 +3704,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>0.443890780210495</v>
+        <v>0.44389083981514</v>
       </c>
       <c r="H115" t="n">
         <v>154035</v>
@@ -3733,7 +3733,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G116" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H116" t="n">
         <v>203916</v>
@@ -3762,7 +3762,7 @@
         <v>0.648999989032745</v>
       </c>
       <c r="G117" t="n">
-        <v>0.449080497026443</v>
+        <v>0.449080467224121</v>
       </c>
       <c r="H117" t="n">
         <v>50524</v>
@@ -3849,7 +3849,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G120" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H120" t="n">
         <v>89237</v>
@@ -3936,7 +3936,7 @@
         <v>0.653500020503998</v>
       </c>
       <c r="G123" t="n">
-        <v>0.452194303274155</v>
+        <v>0.45219424366951</v>
       </c>
       <c r="H123" t="n">
         <v>111165</v>
@@ -3965,7 +3965,7 @@
         <v>0.604499995708466</v>
       </c>
       <c r="G124" t="n">
-        <v>0.418288320302963</v>
+        <v>0.418288350105286</v>
       </c>
       <c r="H124" t="n">
         <v>486768</v>
@@ -4023,7 +4023,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G126" t="n">
-        <v>0.436625212430954</v>
+        <v>0.436625182628632</v>
       </c>
       <c r="H126" t="n">
         <v>99483</v>
@@ -4052,7 +4052,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G127" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H127" t="n">
         <v>82500</v>
@@ -4081,7 +4081,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G128" t="n">
-        <v>0.441468954086304</v>
+        <v>0.441468924283981</v>
       </c>
       <c r="H128" t="n">
         <v>49996</v>
@@ -4110,7 +4110,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G129" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H129" t="n">
         <v>182844</v>
@@ -4139,7 +4139,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G130" t="n">
-        <v>0.455308079719543</v>
+        <v>0.455308049917221</v>
       </c>
       <c r="H130" t="n">
         <v>41364</v>
@@ -4226,7 +4226,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G133" t="n">
-        <v>0.442852795124054</v>
+        <v>0.442852854728699</v>
       </c>
       <c r="H133" t="n">
         <v>152250</v>
@@ -4255,7 +4255,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G134" t="n">
-        <v>0.449772387742996</v>
+        <v>0.449772447347641</v>
       </c>
       <c r="H134" t="n">
         <v>24993</v>
@@ -4342,7 +4342,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G137" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H137" t="n">
         <v>44437</v>
@@ -4400,7 +4400,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>0.476758778095245</v>
+        <v>0.476758807897568</v>
       </c>
       <c r="H139" t="n">
         <v>24754</v>
@@ -4429,7 +4429,7 @@
         <v>0.690500020980835</v>
       </c>
       <c r="G140" t="n">
-        <v>0.477796733379364</v>
+        <v>0.477796673774719</v>
       </c>
       <c r="H140" t="n">
         <v>71001</v>
@@ -4458,7 +4458,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G141" t="n">
-        <v>0.474682867527008</v>
+        <v>0.474682927131653</v>
       </c>
       <c r="H141" t="n">
         <v>80976</v>
@@ -4516,7 +4516,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>0.476758778095245</v>
+        <v>0.476758807897568</v>
       </c>
       <c r="H143" t="n">
         <v>31703</v>
@@ -4545,7 +4545,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G144" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611543178558</v>
       </c>
       <c r="H144" t="n">
         <v>51317</v>
@@ -4574,7 +4574,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G145" t="n">
-        <v>0.467071443796158</v>
+        <v>0.467071354389191</v>
       </c>
       <c r="H145" t="n">
         <v>48503</v>
@@ -4661,7 +4661,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.477450758218765</v>
+        <v>0.47745069861412</v>
       </c>
       <c r="H148" t="n">
         <v>324437</v>
@@ -4690,7 +4690,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G149" t="n">
-        <v>0.474682867527008</v>
+        <v>0.474682927131653</v>
       </c>
       <c r="H149" t="n">
         <v>70330</v>
@@ -4719,7 +4719,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G150" t="n">
-        <v>0.466033428907394</v>
+        <v>0.466033458709717</v>
       </c>
       <c r="H150" t="n">
         <v>34614</v>
@@ -4806,7 +4806,7 @@
         <v>0.656499981880188</v>
       </c>
       <c r="G153" t="n">
-        <v>0.454270154237747</v>
+        <v>0.454270124435425</v>
       </c>
       <c r="H153" t="n">
         <v>42442</v>
@@ -4893,7 +4893,7 @@
         <v>0.664499998092651</v>
       </c>
       <c r="G156" t="n">
-        <v>0.459805816411972</v>
+        <v>0.459805846214294</v>
       </c>
       <c r="H156" t="n">
         <v>20377</v>
@@ -4951,7 +4951,7 @@
         <v>0.673500001430511</v>
       </c>
       <c r="G158" t="n">
-        <v>0.466033428907394</v>
+        <v>0.466033458709717</v>
       </c>
       <c r="H158" t="n">
         <v>5763</v>
@@ -5038,7 +5038,7 @@
         <v>0.662999987602234</v>
       </c>
       <c r="G161" t="n">
-        <v>0.458767801523209</v>
+        <v>0.458767861127853</v>
       </c>
       <c r="H161" t="n">
         <v>38164</v>
@@ -5125,7 +5125,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G164" t="n">
-        <v>0.460151821374893</v>
+        <v>0.460151731967926</v>
       </c>
       <c r="H164" t="n">
         <v>39400</v>
@@ -5154,7 +5154,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G165" t="n">
-        <v>0.469839215278625</v>
+        <v>0.469839185476303</v>
       </c>
       <c r="H165" t="n">
         <v>29550</v>
@@ -5183,7 +5183,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G166" t="n">
-        <v>0.46914729475975</v>
+        <v>0.469147205352783</v>
       </c>
       <c r="H166" t="n">
         <v>9905</v>
@@ -5212,7 +5212,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G167" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H167" t="n">
         <v>30130</v>
@@ -5241,7 +5241,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G168" t="n">
-        <v>0.473299026489258</v>
+        <v>0.473298996686935</v>
       </c>
       <c r="H168" t="n">
         <v>14300</v>
@@ -5270,7 +5270,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G169" t="n">
-        <v>0.473299026489258</v>
+        <v>0.473298996686935</v>
       </c>
       <c r="H169" t="n">
         <v>1644</v>
@@ -5299,7 +5299,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G170" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611543178558</v>
       </c>
       <c r="H170" t="n">
         <v>58222</v>
@@ -5328,7 +5328,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G171" t="n">
-        <v>0.46914729475975</v>
+        <v>0.469147205352783</v>
       </c>
       <c r="H171" t="n">
         <v>30801</v>
@@ -5386,7 +5386,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G173" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611543178558</v>
       </c>
       <c r="H173" t="n">
         <v>25441</v>
@@ -5560,7 +5560,7 @@
         <v>0.658500015735626</v>
       </c>
       <c r="G179" t="n">
-        <v>0.455654054880142</v>
+        <v>0.455653995275497</v>
       </c>
       <c r="H179" t="n">
         <v>20378</v>
@@ -5589,7 +5589,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G180" t="n">
-        <v>0.449772387742996</v>
+        <v>0.449772447347641</v>
       </c>
       <c r="H180" t="n">
         <v>88496</v>
@@ -5734,7 +5734,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>0.446312576532364</v>
+        <v>0.446312606334686</v>
       </c>
       <c r="H185" t="n">
         <v>52383</v>
@@ -5763,7 +5763,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>0.446312576532364</v>
+        <v>0.446312606334686</v>
       </c>
       <c r="H186" t="n">
         <v>75110</v>
@@ -5792,7 +5792,7 @@
         <v>0.655499994754791</v>
       </c>
       <c r="G187" t="n">
-        <v>0.453578144311905</v>
+        <v>0.453578174114227</v>
       </c>
       <c r="H187" t="n">
         <v>59490</v>
@@ -5879,7 +5879,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G190" t="n">
-        <v>0.464995533227921</v>
+        <v>0.464995414018631</v>
       </c>
       <c r="H190" t="n">
         <v>160048</v>
@@ -6024,7 +6024,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G195" t="n">
-        <v>0.467763304710388</v>
+        <v>0.467763334512711</v>
       </c>
       <c r="H195" t="n">
         <v>18570</v>
@@ -6053,7 +6053,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G196" t="n">
-        <v>0.470531135797501</v>
+        <v>0.470531195402145</v>
       </c>
       <c r="H196" t="n">
         <v>98271</v>
@@ -6082,7 +6082,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G197" t="n">
-        <v>0.463611632585526</v>
+        <v>0.463611543178558</v>
       </c>
       <c r="H197" t="n">
         <v>99568</v>
@@ -6169,7 +6169,7 @@
         <v>0.6875</v>
       </c>
       <c r="G200" t="n">
-        <v>0.475720852613449</v>
+        <v>0.475720822811127</v>
       </c>
       <c r="H200" t="n">
         <v>120951</v>
@@ -6227,7 +6227,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G202" t="n">
-        <v>0.487830072641373</v>
+        <v>0.48783004283905</v>
       </c>
       <c r="H202" t="n">
         <v>469900</v>
@@ -6256,7 +6256,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G203" t="n">
-        <v>0.498555421829224</v>
+        <v>0.498555481433868</v>
       </c>
       <c r="H203" t="n">
         <v>121289</v>
@@ -6285,7 +6285,7 @@
         <v>0.707000017166138</v>
       </c>
       <c r="G204" t="n">
-        <v>0.489213973283768</v>
+        <v>0.489214062690735</v>
       </c>
       <c r="H204" t="n">
         <v>146400</v>
@@ -6314,7 +6314,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G205" t="n">
-        <v>0.493019700050354</v>
+        <v>0.493019759654999</v>
       </c>
       <c r="H205" t="n">
         <v>36091</v>
@@ -6343,7 +6343,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>0.50305312871933</v>
+        <v>0.503053188323975</v>
       </c>
       <c r="H206" t="n">
         <v>66811</v>
@@ -6372,7 +6372,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G207" t="n">
-        <v>0.508588790893555</v>
+        <v>0.508588850498199</v>
       </c>
       <c r="H207" t="n">
         <v>181176</v>
@@ -6401,7 +6401,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G208" t="n">
-        <v>0.522427976131439</v>
+        <v>0.522427916526794</v>
       </c>
       <c r="H208" t="n">
         <v>776683</v>
@@ -6430,7 +6430,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>0.525887787342072</v>
+        <v>0.525887727737427</v>
       </c>
       <c r="H209" t="n">
         <v>531491</v>
@@ -6488,7 +6488,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G211" t="n">
-        <v>0.516892313957214</v>
+        <v>0.51689225435257</v>
       </c>
       <c r="H211" t="n">
         <v>202768</v>
@@ -6517,7 +6517,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G212" t="n">
-        <v>0.517584264278412</v>
+        <v>0.517584323883057</v>
       </c>
       <c r="H212" t="n">
         <v>70577</v>
@@ -6546,7 +6546,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G213" t="n">
-        <v>0.522427976131439</v>
+        <v>0.522427916526794</v>
       </c>
       <c r="H213" t="n">
         <v>130992</v>
@@ -6662,7 +6662,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>0.497863501310349</v>
+        <v>0.497863441705704</v>
       </c>
       <c r="H217" t="n">
         <v>168732</v>
@@ -6691,7 +6691,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G218" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H218" t="n">
         <v>56648</v>
@@ -6720,7 +6720,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G219" t="n">
-        <v>0.497863501310349</v>
+        <v>0.497863441705704</v>
       </c>
       <c r="H219" t="n">
         <v>110019</v>
@@ -6749,7 +6749,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G220" t="n">
-        <v>0.499247342348099</v>
+        <v>0.499247401952744</v>
       </c>
       <c r="H220" t="n">
         <v>33506</v>
@@ -6778,7 +6778,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G221" t="n">
-        <v>0.495441645383835</v>
+        <v>0.495441615581512</v>
       </c>
       <c r="H221" t="n">
         <v>150686</v>
@@ -6807,7 +6807,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G222" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H222" t="n">
         <v>140896</v>
@@ -6836,7 +6836,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G223" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H223" t="n">
         <v>73200</v>
@@ -6865,7 +6865,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G224" t="n">
-        <v>0.498209416866302</v>
+        <v>0.498209476470947</v>
       </c>
       <c r="H224" t="n">
         <v>27258</v>
@@ -6894,7 +6894,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H225" t="n">
         <v>52932</v>
@@ -6923,7 +6923,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G226" t="n">
-        <v>0.495441645383835</v>
+        <v>0.495441615581512</v>
       </c>
       <c r="H226" t="n">
         <v>79074</v>
@@ -6952,7 +6952,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G227" t="n">
-        <v>0.49405762553215</v>
+        <v>0.494057685136795</v>
       </c>
       <c r="H227" t="n">
         <v>51852</v>
@@ -6981,7 +6981,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G228" t="n">
-        <v>0.491981863975525</v>
+        <v>0.491981834173203</v>
       </c>
       <c r="H228" t="n">
         <v>257048</v>
@@ -7010,7 +7010,7 @@
         <v>0.704500019550323</v>
       </c>
       <c r="G229" t="n">
-        <v>0.487484067678452</v>
+        <v>0.487484097480774</v>
       </c>
       <c r="H229" t="n">
         <v>103047</v>
@@ -7068,7 +7068,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G231" t="n">
-        <v>0.493019700050354</v>
+        <v>0.493019759654999</v>
       </c>
       <c r="H231" t="n">
         <v>140299</v>
@@ -7097,7 +7097,7 @@
         <v>0.719500005245209</v>
       </c>
       <c r="G232" t="n">
-        <v>0.497863501310349</v>
+        <v>0.497863441705704</v>
       </c>
       <c r="H232" t="n">
         <v>218985</v>
@@ -7126,7 +7126,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G233" t="n">
-        <v>0.498209416866302</v>
+        <v>0.498209476470947</v>
       </c>
       <c r="H233" t="n">
         <v>26904</v>
@@ -7155,7 +7155,7 @@
         <v>0.706499993801117</v>
       </c>
       <c r="G234" t="n">
-        <v>0.488867968320847</v>
+        <v>0.488868027925491</v>
       </c>
       <c r="H234" t="n">
         <v>54717</v>
@@ -7213,7 +7213,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G236" t="n">
-        <v>0.492673724889755</v>
+        <v>0.492673814296722</v>
       </c>
       <c r="H236" t="n">
         <v>271535</v>
@@ -7242,7 +7242,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G237" t="n">
-        <v>0.492673724889755</v>
+        <v>0.492673814296722</v>
       </c>
       <c r="H237" t="n">
         <v>16612</v>
@@ -7271,7 +7271,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G238" t="n">
-        <v>0.491289854049683</v>
+        <v>0.491289883852005</v>
       </c>
       <c r="H238" t="n">
         <v>43905</v>
@@ -7300,7 +7300,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G239" t="n">
-        <v>0.491981863975525</v>
+        <v>0.491981834173203</v>
       </c>
       <c r="H239" t="n">
         <v>23384</v>
@@ -7532,7 +7532,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G247" t="n">
-        <v>0.516892313957214</v>
+        <v>0.51689225435257</v>
       </c>
       <c r="H247" t="n">
         <v>57020</v>
@@ -7561,7 +7561,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G248" t="n">
-        <v>0.529347538948059</v>
+        <v>0.529347598552704</v>
       </c>
       <c r="H248" t="n">
         <v>1097273</v>
@@ -7590,7 +7590,7 @@
         <v>0.770500004291534</v>
       </c>
       <c r="G249" t="n">
-        <v>0.533153235912323</v>
+        <v>0.533153295516968</v>
       </c>
       <c r="H249" t="n">
         <v>288004</v>
@@ -7619,7 +7619,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G250" t="n">
-        <v>0.521736025810242</v>
+        <v>0.521735966205597</v>
       </c>
       <c r="H250" t="n">
         <v>387529</v>
@@ -7648,7 +7648,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G251" t="n">
-        <v>0.51135665178299</v>
+        <v>0.511356711387634</v>
       </c>
       <c r="H251" t="n">
         <v>428592</v>
@@ -7677,7 +7677,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G252" t="n">
-        <v>0.51135665178299</v>
+        <v>0.511356711387634</v>
       </c>
       <c r="H252" t="n">
         <v>277440</v>
@@ -7706,7 +7706,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G253" t="n">
-        <v>0.517584264278412</v>
+        <v>0.517584323883057</v>
       </c>
       <c r="H253" t="n">
         <v>73514</v>
@@ -7735,7 +7735,7 @@
         <v>0.752499997615814</v>
       </c>
       <c r="G254" t="n">
-        <v>0.520698070526123</v>
+        <v>0.520698130130768</v>
       </c>
       <c r="H254" t="n">
         <v>83322</v>
@@ -7764,7 +7764,7 @@
         <v>0.75</v>
       </c>
       <c r="G255" t="n">
-        <v>0.518968164920807</v>
+        <v>0.518968105316162</v>
       </c>
       <c r="H255" t="n">
         <v>190032</v>
@@ -7822,7 +7822,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G257" t="n">
-        <v>0.520352125167847</v>
+        <v>0.520352065563202</v>
       </c>
       <c r="H257" t="n">
         <v>97060</v>
@@ -7851,7 +7851,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G258" t="n">
-        <v>0.530039429664612</v>
+        <v>0.530039489269257</v>
       </c>
       <c r="H258" t="n">
         <v>222408</v>
@@ -7880,7 +7880,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>0.539380967617035</v>
+        <v>0.53938090801239</v>
       </c>
       <c r="H259" t="n">
         <v>357651</v>
@@ -7996,7 +7996,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G263" t="n">
-        <v>0.531423389911652</v>
+        <v>0.531423449516296</v>
       </c>
       <c r="H263" t="n">
         <v>280499</v>
@@ -8083,7 +8083,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G266" t="n">
-        <v>0.535575151443481</v>
+        <v>0.535575211048126</v>
       </c>
       <c r="H266" t="n">
         <v>145736</v>
@@ -8112,7 +8112,7 @@
         <v>0.77649998664856</v>
       </c>
       <c r="G267" t="n">
-        <v>0.537305116653442</v>
+        <v>0.537304997444153</v>
       </c>
       <c r="H267" t="n">
         <v>188591</v>
@@ -8199,7 +8199,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G270" t="n">
-        <v>0.540418922901154</v>
+        <v>0.540418863296509</v>
       </c>
       <c r="H270" t="n">
         <v>35906</v>
@@ -8257,7 +8257,7 @@
         <v>0.768499970436096</v>
       </c>
       <c r="G272" t="n">
-        <v>0.531769394874573</v>
+        <v>0.531769335269928</v>
       </c>
       <c r="H272" t="n">
         <v>168992</v>
@@ -8286,7 +8286,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G273" t="n">
-        <v>0.540418922901154</v>
+        <v>0.540418863296509</v>
       </c>
       <c r="H273" t="n">
         <v>139226</v>
@@ -8315,7 +8315,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G274" t="n">
-        <v>0.542494773864746</v>
+        <v>0.542494714260101</v>
       </c>
       <c r="H274" t="n">
         <v>94788</v>
@@ -8344,7 +8344,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>0.539380967617035</v>
+        <v>0.53938090801239</v>
       </c>
       <c r="H275" t="n">
         <v>94758</v>
@@ -8373,7 +8373,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G276" t="n">
-        <v>0.540418922901154</v>
+        <v>0.540418863296509</v>
       </c>
       <c r="H276" t="n">
         <v>80710</v>
@@ -8402,7 +8402,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G277" t="n">
-        <v>0.538688957691193</v>
+        <v>0.538689017295837</v>
       </c>
       <c r="H277" t="n">
         <v>76279</v>
@@ -8431,7 +8431,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>0.525887787342072</v>
+        <v>0.525887727737427</v>
       </c>
       <c r="H278" t="n">
         <v>193866</v>
@@ -8460,7 +8460,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G279" t="n">
-        <v>0.520352125167847</v>
+        <v>0.520352065563202</v>
       </c>
       <c r="H279" t="n">
         <v>87634</v>
@@ -8547,7 +8547,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G282" t="n">
-        <v>0.532115340232849</v>
+        <v>0.532115399837494</v>
       </c>
       <c r="H282" t="n">
         <v>42049</v>
@@ -8576,7 +8576,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G283" t="n">
-        <v>0.527271747589111</v>
+        <v>0.527271628379822</v>
       </c>
       <c r="H283" t="n">
         <v>131626</v>
@@ -8634,7 +8634,7 @@
         <v>0.752499997615814</v>
       </c>
       <c r="G285" t="n">
-        <v>0.520698070526123</v>
+        <v>0.520698130130768</v>
       </c>
       <c r="H285" t="n">
         <v>82797</v>
@@ -8692,7 +8692,7 @@
         <v>0.768499970436096</v>
       </c>
       <c r="G287" t="n">
-        <v>0.531769394874573</v>
+        <v>0.531769335269928</v>
       </c>
       <c r="H287" t="n">
         <v>41327</v>
@@ -8721,7 +8721,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G288" t="n">
-        <v>0.535575151443481</v>
+        <v>0.535575211048126</v>
       </c>
       <c r="H288" t="n">
         <v>191680</v>
@@ -8982,7 +8982,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G297" t="n">
-        <v>0.51135665178299</v>
+        <v>0.511356711387634</v>
       </c>
       <c r="H297" t="n">
         <v>189797</v>
@@ -9011,7 +9011,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G298" t="n">
-        <v>0.515508353710175</v>
+        <v>0.515508413314819</v>
       </c>
       <c r="H298" t="n">
         <v>476154</v>
@@ -9040,7 +9040,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G299" t="n">
-        <v>0.524503767490387</v>
+        <v>0.524503886699677</v>
       </c>
       <c r="H299" t="n">
         <v>291053</v>
@@ -9069,7 +9069,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>0.525887787342072</v>
+        <v>0.525887727737427</v>
       </c>
       <c r="H300" t="n">
         <v>148794</v>
@@ -9098,7 +9098,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>0.522427976131439</v>
+        <v>0.522427916526794</v>
       </c>
       <c r="H301" t="n">
         <v>200433</v>
@@ -9127,7 +9127,7 @@
         <v>0.745000004768372</v>
       </c>
       <c r="G302" t="n">
-        <v>0.515508353710175</v>
+        <v>0.515508413314819</v>
       </c>
       <c r="H302" t="n">
         <v>169321</v>
@@ -9243,7 +9243,7 @@
         <v>0.738499999046326</v>
       </c>
       <c r="G306" t="n">
-        <v>0.511010646820068</v>
+        <v>0.511010706424713</v>
       </c>
       <c r="H306" t="n">
         <v>46683</v>
@@ -9301,7 +9301,7 @@
         <v>0.726999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>0.50305312871933</v>
+        <v>0.503053188323975</v>
       </c>
       <c r="H308" t="n">
         <v>393889</v>
@@ -9330,7 +9330,7 @@
         <v>0.732500016689301</v>
       </c>
       <c r="G309" t="n">
-        <v>0.506858885288239</v>
+        <v>0.506858944892883</v>
       </c>
       <c r="H309" t="n">
         <v>354387</v>
@@ -9359,7 +9359,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G310" t="n">
-        <v>0.510664701461792</v>
+        <v>0.510664641857147</v>
       </c>
       <c r="H310" t="n">
         <v>313882</v>
@@ -9504,7 +9504,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>0.506512880325317</v>
+        <v>0.506512939929962</v>
       </c>
       <c r="H315" t="n">
         <v>166630</v>
@@ -9533,7 +9533,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G316" t="n">
-        <v>0.505820989608765</v>
+        <v>0.50582093000412</v>
       </c>
       <c r="H316" t="n">
         <v>38462</v>
@@ -9823,7 +9823,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G326" t="n">
-        <v>0.508588790893555</v>
+        <v>0.508588850498199</v>
       </c>
       <c r="H326" t="n">
         <v>145557</v>
@@ -9852,7 +9852,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G327" t="n">
-        <v>0.508588790893555</v>
+        <v>0.508588850498199</v>
       </c>
       <c r="H327" t="n">
         <v>117509</v>
@@ -9881,7 +9881,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G328" t="n">
-        <v>0.505820989608765</v>
+        <v>0.50582093000412</v>
       </c>
       <c r="H328" t="n">
         <v>104030</v>
@@ -9997,7 +9997,7 @@
         <v>0.728500008583069</v>
       </c>
       <c r="G332" t="n">
-        <v>0.504091143608093</v>
+        <v>0.504091084003448</v>
       </c>
       <c r="H332" t="n">
         <v>61694</v>
@@ -10026,7 +10026,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G333" t="n">
-        <v>0.498555421829224</v>
+        <v>0.498555481433868</v>
       </c>
       <c r="H333" t="n">
         <v>457777</v>
@@ -10055,7 +10055,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G334" t="n">
-        <v>0.499247342348099</v>
+        <v>0.499247401952744</v>
       </c>
       <c r="H334" t="n">
         <v>67876</v>
@@ -10113,7 +10113,7 @@
         <v>0.726499974727631</v>
       </c>
       <c r="G336" t="n">
-        <v>0.502707123756409</v>
+        <v>0.502707183361053</v>
       </c>
       <c r="H336" t="n">
         <v>229492</v>
@@ -10142,7 +10142,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G337" t="n">
-        <v>0.505820989608765</v>
+        <v>0.50582093000412</v>
       </c>
       <c r="H337" t="n">
         <v>99133</v>
@@ -10432,7 +10432,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G347" t="n">
-        <v>0.508588790893555</v>
+        <v>0.508588850498199</v>
       </c>
       <c r="H347" t="n">
         <v>152359</v>
@@ -10490,7 +10490,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>0.525887787342072</v>
+        <v>0.525887727737427</v>
       </c>
       <c r="H349" t="n">
         <v>179526</v>
@@ -10519,7 +10519,7 @@
         <v>0.762499988079071</v>
       </c>
       <c r="G350" t="n">
-        <v>0.527617692947388</v>
+        <v>0.527617633342743</v>
       </c>
       <c r="H350" t="n">
         <v>372168</v>
@@ -10548,7 +10548,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G351" t="n">
-        <v>0.522427976131439</v>
+        <v>0.522427916526794</v>
       </c>
       <c r="H351" t="n">
         <v>151622</v>
@@ -10635,7 +10635,7 @@
         <v>0.746500015258789</v>
       </c>
       <c r="G354" t="n">
-        <v>0.516546308994293</v>
+        <v>0.516546368598938</v>
       </c>
       <c r="H354" t="n">
         <v>168237</v>
@@ -10751,7 +10751,7 @@
         <v>0.742500007152557</v>
       </c>
       <c r="G358" t="n">
-        <v>0.513778507709503</v>
+        <v>0.513778448104858</v>
       </c>
       <c r="H358" t="n">
         <v>125302</v>
@@ -10780,7 +10780,7 @@
         <v>0.75</v>
       </c>
       <c r="G359" t="n">
-        <v>0.518968164920807</v>
+        <v>0.518968105316162</v>
       </c>
       <c r="H359" t="n">
         <v>262928</v>
@@ -10809,7 +10809,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G360" t="n">
-        <v>0.520352125167847</v>
+        <v>0.520352065563202</v>
       </c>
       <c r="H360" t="n">
         <v>471079</v>
@@ -10838,7 +10838,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>0.525887787342072</v>
+        <v>0.525887727737427</v>
       </c>
       <c r="H361" t="n">
         <v>250363</v>
@@ -10925,7 +10925,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G364" t="n">
-        <v>0.530039429664612</v>
+        <v>0.530039489269257</v>
       </c>
       <c r="H364" t="n">
         <v>126381</v>
@@ -10954,7 +10954,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>0.532807350158691</v>
+        <v>0.532807290554047</v>
       </c>
       <c r="H365" t="n">
         <v>384026</v>
@@ -11041,7 +11041,7 @@
         <v>0.798500001430511</v>
       </c>
       <c r="G368" t="n">
-        <v>0.552528202533722</v>
+        <v>0.552528142929077</v>
       </c>
       <c r="H368" t="n">
         <v>1262207</v>
@@ -11099,7 +11099,7 @@
         <v>0.820999979972839</v>
       </c>
       <c r="G370" t="n">
-        <v>0.568097114562988</v>
+        <v>0.568097174167633</v>
       </c>
       <c r="H370" t="n">
         <v>385663</v>
@@ -11128,7 +11128,7 @@
         <v>0.82150000333786</v>
       </c>
       <c r="G371" t="n">
-        <v>0.568443119525909</v>
+        <v>0.568443179130554</v>
       </c>
       <c r="H371" t="n">
         <v>388142</v>
@@ -11157,7 +11157,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G372" t="n">
-        <v>0.571556866168976</v>
+        <v>0.571556925773621</v>
       </c>
       <c r="H372" t="n">
         <v>236280</v>
@@ -11302,7 +11302,7 @@
         <v>0.852999985218048</v>
       </c>
       <c r="G377" t="n">
-        <v>0.590239763259888</v>
+        <v>0.590239822864532</v>
       </c>
       <c r="H377" t="n">
         <v>1194426</v>
@@ -11447,7 +11447,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G382" t="n">
-        <v>0.640060782432556</v>
+        <v>0.640060722827911</v>
       </c>
       <c r="H382" t="n">
         <v>611757</v>
@@ -11505,7 +11505,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G384" t="n">
-        <v>0.646980285644531</v>
+        <v>0.646980345249176</v>
       </c>
       <c r="H384" t="n">
         <v>344710</v>
@@ -11592,7 +11592,7 @@
         <v>0.915499985218048</v>
       </c>
       <c r="G387" t="n">
-        <v>0.633487105369568</v>
+        <v>0.633487224578857</v>
       </c>
       <c r="H387" t="n">
         <v>347087</v>
@@ -11621,7 +11621,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G388" t="n">
-        <v>0.634525060653687</v>
+        <v>0.634525120258331</v>
       </c>
       <c r="H388" t="n">
         <v>135604</v>
@@ -11679,7 +11679,7 @@
         <v>0.936500012874603</v>
       </c>
       <c r="G390" t="n">
-        <v>0.64801824092865</v>
+        <v>0.648018300533295</v>
       </c>
       <c r="H390" t="n">
         <v>352242</v>
@@ -11708,7 +11708,7 @@
         <v>0.935000002384186</v>
       </c>
       <c r="G391" t="n">
-        <v>0.646980285644531</v>
+        <v>0.646980345249176</v>
       </c>
       <c r="H391" t="n">
         <v>101808</v>
@@ -11737,7 +11737,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G392" t="n">
-        <v>0.638676762580872</v>
+        <v>0.638676822185516</v>
       </c>
       <c r="H392" t="n">
         <v>245408</v>
@@ -11824,7 +11824,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G395" t="n">
-        <v>0.638676762580872</v>
+        <v>0.638676822185516</v>
       </c>
       <c r="H395" t="n">
         <v>155679</v>
@@ -11853,7 +11853,7 @@
         <v>0.915499985218048</v>
       </c>
       <c r="G396" t="n">
-        <v>0.633487105369568</v>
+        <v>0.633487224578857</v>
       </c>
       <c r="H396" t="n">
         <v>82781</v>
@@ -11911,7 +11911,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G398" t="n">
-        <v>0.640060782432556</v>
+        <v>0.640060722827911</v>
       </c>
       <c r="H398" t="n">
         <v>127454</v>
@@ -11940,7 +11940,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G399" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H399" t="n">
         <v>161711</v>
@@ -12056,7 +12056,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G403" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H403" t="n">
         <v>1563687</v>
@@ -12085,7 +12085,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G404" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H404" t="n">
         <v>400954</v>
@@ -12172,7 +12172,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G407" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H407" t="n">
         <v>133207</v>
@@ -12230,7 +12230,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G409" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H409" t="n">
         <v>132125</v>
@@ -12259,7 +12259,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G410" t="n">
-        <v>0.615150213241577</v>
+        <v>0.615150272846222</v>
       </c>
       <c r="H410" t="n">
         <v>168974</v>
@@ -12346,7 +12346,7 @@
         <v>0.89300000667572</v>
       </c>
       <c r="G413" t="n">
-        <v>0.617918193340302</v>
+        <v>0.617918074131012</v>
       </c>
       <c r="H413" t="n">
         <v>39750</v>
@@ -12636,7 +12636,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G423" t="n">
-        <v>0.615150213241577</v>
+        <v>0.615150272846222</v>
       </c>
       <c r="H423" t="n">
         <v>102772</v>
@@ -12723,7 +12723,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G426" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H426" t="n">
         <v>30382</v>
@@ -12781,7 +12781,7 @@
         <v>0.891499996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>0.616880178451538</v>
+        <v>0.616880118846893</v>
       </c>
       <c r="H428" t="n">
         <v>79302</v>
@@ -13013,7 +13013,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G436" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H436" t="n">
         <v>192904</v>
@@ -13042,7 +13042,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G437" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H437" t="n">
         <v>185924</v>
@@ -13100,7 +13100,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G439" t="n">
-        <v>0.615150213241577</v>
+        <v>0.615150272846222</v>
       </c>
       <c r="H439" t="n">
         <v>140694</v>
@@ -13158,7 +13158,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>0.621377944946289</v>
+        <v>0.621377885341644</v>
       </c>
       <c r="H441" t="n">
         <v>218077</v>
@@ -13216,7 +13216,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G443" t="n">
-        <v>0.636254906654358</v>
+        <v>0.636254966259003</v>
       </c>
       <c r="H443" t="n">
         <v>655108</v>
@@ -13245,7 +13245,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G444" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H444" t="n">
         <v>416249</v>
@@ -13303,7 +13303,7 @@
         <v>0.921500027179718</v>
       </c>
       <c r="G446" t="n">
-        <v>0.637638926506042</v>
+        <v>0.637638866901398</v>
       </c>
       <c r="H446" t="n">
         <v>142109</v>
@@ -13361,7 +13361,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>0.636254906654358</v>
+        <v>0.636254966259003</v>
       </c>
       <c r="H448" t="n">
         <v>240947</v>
@@ -13506,7 +13506,7 @@
         <v>0.934499979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>0.646634340286255</v>
+        <v>0.64663428068161</v>
       </c>
       <c r="H453" t="n">
         <v>146365</v>
@@ -13622,7 +13622,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H457" t="n">
         <v>684112</v>
@@ -13651,7 +13651,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G458" t="n">
-        <v>0.700261056423187</v>
+        <v>0.700260996818542</v>
       </c>
       <c r="H458" t="n">
         <v>762804</v>
@@ -13767,7 +13767,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G462" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H462" t="n">
         <v>739518</v>
@@ -13912,7 +13912,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G467" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H467" t="n">
         <v>470474</v>
@@ -13941,7 +13941,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G468" t="n">
-        <v>0.68849778175354</v>
+        <v>0.688497841358185</v>
       </c>
       <c r="H468" t="n">
         <v>633728</v>
@@ -14028,7 +14028,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>0.696109414100647</v>
+        <v>0.696109354496002</v>
       </c>
       <c r="H471" t="n">
         <v>102166</v>
@@ -14057,7 +14057,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G472" t="n">
-        <v>0.696109414100647</v>
+        <v>0.696109354496002</v>
       </c>
       <c r="H472" t="n">
         <v>233549</v>
@@ -14086,7 +14086,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G473" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H473" t="n">
         <v>79950</v>
@@ -14144,7 +14144,7 @@
         <v>1.00899994373322</v>
       </c>
       <c r="G475" t="n">
-        <v>0.69818514585495</v>
+        <v>0.698185205459595</v>
       </c>
       <c r="H475" t="n">
         <v>330294</v>
@@ -14202,7 +14202,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G477" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H477" t="n">
         <v>169267</v>
@@ -14231,7 +14231,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H478" t="n">
         <v>300513</v>
@@ -14260,7 +14260,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G479" t="n">
-        <v>0.671198844909668</v>
+        <v>0.671198904514313</v>
       </c>
       <c r="H479" t="n">
         <v>244081</v>
@@ -14289,7 +14289,7 @@
         <v>0.972500026226044</v>
       </c>
       <c r="G480" t="n">
-        <v>0.672928810119629</v>
+        <v>0.672928690910339</v>
       </c>
       <c r="H480" t="n">
         <v>75909</v>
@@ -14318,7 +14318,7 @@
         <v>0.942499995231628</v>
       </c>
       <c r="G481" t="n">
-        <v>0.652169942855835</v>
+        <v>0.65217000246048</v>
       </c>
       <c r="H481" t="n">
         <v>621225</v>
@@ -14347,7 +14347,7 @@
         <v>0.935500025749207</v>
       </c>
       <c r="G482" t="n">
-        <v>0.647326290607452</v>
+        <v>0.647326350212097</v>
       </c>
       <c r="H482" t="n">
         <v>210242</v>
@@ -14492,7 +14492,7 @@
         <v>0.958999991416931</v>
       </c>
       <c r="G487" t="n">
-        <v>0.663587331771851</v>
+        <v>0.663587272167206</v>
       </c>
       <c r="H487" t="n">
         <v>121134</v>
@@ -14521,7 +14521,7 @@
         <v>0.966499984264374</v>
       </c>
       <c r="G488" t="n">
-        <v>0.668776988983154</v>
+        <v>0.66877692937851</v>
       </c>
       <c r="H488" t="n">
         <v>98374</v>
@@ -14550,7 +14550,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G489" t="n">
-        <v>0.670506834983826</v>
+        <v>0.67050689458847</v>
       </c>
       <c r="H489" t="n">
         <v>212997</v>
@@ -14637,7 +14637,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>0.669122934341431</v>
+        <v>0.669122993946075</v>
       </c>
       <c r="H492" t="n">
         <v>72723</v>
@@ -14782,7 +14782,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G497" t="n">
-        <v>0.679156363010406</v>
+        <v>0.679156422615051</v>
       </c>
       <c r="H497" t="n">
         <v>117054</v>
@@ -14811,7 +14811,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G498" t="n">
-        <v>0.684000015258789</v>
+        <v>0.684000074863434</v>
       </c>
       <c r="H498" t="n">
         <v>105579</v>
@@ -14869,7 +14869,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G500" t="n">
-        <v>0.696109414100647</v>
+        <v>0.696109354496002</v>
       </c>
       <c r="H500" t="n">
         <v>290076</v>
@@ -14898,7 +14898,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>0.68849778175354</v>
+        <v>0.688497841358185</v>
       </c>
       <c r="H501" t="n">
         <v>294181</v>
@@ -15014,7 +15014,7 @@
         <v>0.999499976634979</v>
       </c>
       <c r="G505" t="n">
-        <v>0.691611588001251</v>
+        <v>0.691611528396606</v>
       </c>
       <c r="H505" t="n">
         <v>151127</v>
@@ -15043,7 +15043,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H506" t="n">
         <v>140023</v>
@@ -15072,7 +15072,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G507" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H507" t="n">
         <v>93279</v>
@@ -15246,7 +15246,7 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H513" t="n">
         <v>250337</v>
@@ -15304,7 +15304,7 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H515" t="n">
         <v>228631</v>
@@ -15333,7 +15333,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G516" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H516" t="n">
         <v>241960</v>
@@ -15449,7 +15449,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G520" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H520" t="n">
         <v>103679</v>
@@ -15594,7 +15594,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H525" t="n">
         <v>271747</v>
@@ -15623,7 +15623,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G526" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H526" t="n">
         <v>487693</v>
@@ -15652,7 +15652,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G527" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H527" t="n">
         <v>364335</v>
@@ -15681,7 +15681,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G528" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H528" t="n">
         <v>178501</v>
@@ -15710,7 +15710,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H529" t="n">
         <v>250609</v>
@@ -15739,7 +15739,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G530" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H530" t="n">
         <v>250612</v>
@@ -15768,7 +15768,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H531" t="n">
         <v>82371</v>
@@ -15797,7 +15797,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G532" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H532" t="n">
         <v>107041</v>
@@ -15826,7 +15826,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G533" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H533" t="n">
         <v>70016</v>
@@ -15884,7 +15884,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G535" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H535" t="n">
         <v>255484</v>
@@ -15913,7 +15913,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G536" t="n">
-        <v>0.680886209011078</v>
+        <v>0.680886268615723</v>
       </c>
       <c r="H536" t="n">
         <v>552515</v>
@@ -16000,7 +16000,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G539" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H539" t="n">
         <v>285889</v>
@@ -16029,7 +16029,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H540" t="n">
         <v>141144</v>
@@ -16058,7 +16058,7 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H541" t="n">
         <v>391068</v>
@@ -16087,7 +16087,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G542" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H542" t="n">
         <v>191039</v>
@@ -16116,7 +16116,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G543" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H543" t="n">
         <v>181643</v>
@@ -16145,7 +16145,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H544" t="n">
         <v>451706</v>
@@ -16174,7 +16174,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G545" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H545" t="n">
         <v>390066</v>
@@ -16232,7 +16232,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G547" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H547" t="n">
         <v>77188</v>
@@ -16261,7 +16261,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H548" t="n">
         <v>167644</v>
@@ -16290,7 +16290,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G549" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H549" t="n">
         <v>63936</v>
@@ -16319,7 +16319,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G550" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H550" t="n">
         <v>91476</v>
@@ -16435,7 +16435,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G554" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H554" t="n">
         <v>444239</v>
@@ -16493,7 +16493,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G556" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H556" t="n">
         <v>696201</v>
@@ -16522,7 +16522,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G557" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H557" t="n">
         <v>107928</v>
@@ -16667,7 +16667,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G562" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H562" t="n">
         <v>244050</v>
@@ -16754,7 +16754,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G565" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H565" t="n">
         <v>121716</v>
@@ -16899,7 +16899,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H570" t="n">
         <v>38212</v>
@@ -16928,7 +16928,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G571" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H571" t="n">
         <v>36832</v>
@@ -16986,7 +16986,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G573" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H573" t="n">
         <v>153618</v>
@@ -17044,7 +17044,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G575" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H575" t="n">
         <v>149054</v>
@@ -17073,7 +17073,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G576" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H576" t="n">
         <v>91964</v>
@@ -17160,7 +17160,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G579" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H579" t="n">
         <v>33938</v>
@@ -17218,7 +17218,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G581" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H581" t="n">
         <v>64795</v>
@@ -17247,7 +17247,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G582" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H582" t="n">
         <v>167021</v>
@@ -17305,7 +17305,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G584" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H584" t="n">
         <v>69874</v>
@@ -17334,7 +17334,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G585" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H585" t="n">
         <v>65412</v>
@@ -17450,7 +17450,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G589" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H589" t="n">
         <v>181469</v>
@@ -17479,7 +17479,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G590" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H590" t="n">
         <v>35062</v>
@@ -17508,7 +17508,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G591" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H591" t="n">
         <v>138385</v>
@@ -17537,7 +17537,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G592" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H592" t="n">
         <v>29068</v>
@@ -17566,7 +17566,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G593" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H593" t="n">
         <v>6330</v>
@@ -17595,7 +17595,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G594" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H594" t="n">
         <v>13853</v>
@@ -17653,7 +17653,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G596" t="n">
-        <v>0.671198844909668</v>
+        <v>0.671198904514313</v>
       </c>
       <c r="H596" t="n">
         <v>216563</v>
@@ -17682,7 +17682,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G597" t="n">
-        <v>0.680886209011078</v>
+        <v>0.680886268615723</v>
       </c>
       <c r="H597" t="n">
         <v>354963</v>
@@ -17711,7 +17711,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G598" t="n">
-        <v>0.682270109653473</v>
+        <v>0.682270169258118</v>
       </c>
       <c r="H598" t="n">
         <v>505186</v>
@@ -17740,7 +17740,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G599" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H599" t="n">
         <v>257276</v>
@@ -17798,7 +17798,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G601" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H601" t="n">
         <v>173212</v>
@@ -17972,7 +17972,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G607" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H607" t="n">
         <v>265903</v>
@@ -18001,7 +18001,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G608" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H608" t="n">
         <v>267381</v>
@@ -18059,7 +18059,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G610" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H610" t="n">
         <v>63700</v>
@@ -18117,7 +18117,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G612" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H612" t="n">
         <v>182363</v>
@@ -18146,7 +18146,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G613" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H613" t="n">
         <v>294664</v>
@@ -18233,7 +18233,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G616" t="n">
-        <v>0.637984871864319</v>
+        <v>0.637984931468964</v>
       </c>
       <c r="H616" t="n">
         <v>171272</v>
@@ -18262,7 +18262,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G617" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H617" t="n">
         <v>118710</v>
@@ -18291,7 +18291,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H618" t="n">
         <v>504140</v>
@@ -18320,7 +18320,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H619" t="n">
         <v>135616</v>
@@ -18378,7 +18378,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G621" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H621" t="n">
         <v>60308</v>
@@ -18465,7 +18465,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G624" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H624" t="n">
         <v>32330</v>
@@ -18494,7 +18494,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G625" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H625" t="n">
         <v>12284</v>
@@ -18552,7 +18552,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G627" t="n">
-        <v>0.637984871864319</v>
+        <v>0.637984931468964</v>
       </c>
       <c r="H627" t="n">
         <v>47560</v>
@@ -18639,7 +18639,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G630" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H630" t="n">
         <v>140311</v>
@@ -18755,7 +18755,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G634" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H634" t="n">
         <v>108287</v>
@@ -18784,7 +18784,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G635" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H635" t="n">
         <v>55341</v>
@@ -18871,7 +18871,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G638" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H638" t="n">
         <v>64520</v>
@@ -18958,7 +18958,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G641" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H641" t="n">
         <v>101434</v>
@@ -19016,7 +19016,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G643" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H643" t="n">
         <v>503725</v>
@@ -19248,7 +19248,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G651" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H651" t="n">
         <v>142778</v>
@@ -19335,7 +19335,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G654" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H654" t="n">
         <v>52109</v>
@@ -19422,7 +19422,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G657" t="n">
-        <v>0.671198844909668</v>
+        <v>0.671198904514313</v>
       </c>
       <c r="H657" t="n">
         <v>125616</v>
@@ -19480,7 +19480,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G659" t="n">
-        <v>0.671198844909668</v>
+        <v>0.671198904514313</v>
       </c>
       <c r="H659" t="n">
         <v>72388</v>
@@ -19509,7 +19509,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G660" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H660" t="n">
         <v>301287</v>
@@ -19567,7 +19567,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G662" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H662" t="n">
         <v>138753</v>
@@ -19596,7 +19596,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G663" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H663" t="n">
         <v>140254</v>
@@ -19683,7 +19683,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G666" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H666" t="n">
         <v>93861</v>
@@ -19712,7 +19712,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H667" t="n">
         <v>167650</v>
@@ -19799,7 +19799,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G670" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H670" t="n">
         <v>163980</v>
@@ -19857,7 +19857,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G672" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H672" t="n">
         <v>96842</v>
@@ -19944,7 +19944,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G675" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H675" t="n">
         <v>52830</v>
@@ -20031,7 +20031,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G678" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H678" t="n">
         <v>99343</v>
@@ -20060,7 +20060,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G679" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H679" t="n">
         <v>99007</v>
@@ -20118,7 +20118,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G681" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H681" t="n">
         <v>57141</v>
@@ -20205,7 +20205,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H684" t="n">
         <v>67179</v>
@@ -20234,7 +20234,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G685" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H685" t="n">
         <v>172394</v>
@@ -20292,7 +20292,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G687" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H687" t="n">
         <v>31036</v>
@@ -20321,7 +20321,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H688" t="n">
         <v>196163</v>
@@ -20379,7 +20379,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H690" t="n">
         <v>47347</v>
@@ -20408,7 +20408,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G691" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H691" t="n">
         <v>54618</v>
@@ -20437,7 +20437,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G692" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H692" t="n">
         <v>112543</v>
@@ -20466,7 +20466,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G693" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H693" t="n">
         <v>51317</v>
@@ -20495,7 +20495,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G694" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H694" t="n">
         <v>13680</v>
@@ -20524,7 +20524,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G695" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H695" t="n">
         <v>25114</v>
@@ -20553,7 +20553,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G696" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H696" t="n">
         <v>82434</v>
@@ -20611,7 +20611,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G698" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H698" t="n">
         <v>67665</v>
@@ -20640,7 +20640,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G699" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H699" t="n">
         <v>129526</v>
@@ -20669,7 +20669,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G700" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H700" t="n">
         <v>8812</v>
@@ -20756,7 +20756,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G703" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H703" t="n">
         <v>121260</v>
@@ -20814,7 +20814,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H705" t="n">
         <v>28672</v>
@@ -20843,7 +20843,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G706" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H706" t="n">
         <v>24697</v>
@@ -21017,7 +21017,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H712" t="n">
         <v>83637</v>
@@ -21104,7 +21104,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G715" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H715" t="n">
         <v>44791</v>
@@ -21162,7 +21162,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G717" t="n">
-        <v>0.629681408405304</v>
+        <v>0.629681468009949</v>
       </c>
       <c r="H717" t="n">
         <v>89967</v>
@@ -21191,7 +21191,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G718" t="n">
-        <v>0.621377944946289</v>
+        <v>0.621377885341644</v>
       </c>
       <c r="H718" t="n">
         <v>90743</v>
@@ -21249,7 +21249,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G720" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H720" t="n">
         <v>49505</v>
@@ -21278,7 +21278,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H721" t="n">
         <v>468123</v>
@@ -21336,7 +21336,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G723" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H723" t="n">
         <v>182993</v>
@@ -21365,7 +21365,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G724" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H724" t="n">
         <v>222642</v>
@@ -21394,7 +21394,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G725" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H725" t="n">
         <v>55765</v>
@@ -21423,7 +21423,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G726" t="n">
-        <v>0.651824057102203</v>
+        <v>0.651823997497559</v>
       </c>
       <c r="H726" t="n">
         <v>222817</v>
@@ -21452,7 +21452,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G727" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H727" t="n">
         <v>57669</v>
@@ -21568,7 +21568,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G731" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H731" t="n">
         <v>57564</v>
@@ -21597,7 +21597,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G732" t="n">
-        <v>0.637984871864319</v>
+        <v>0.637984931468964</v>
       </c>
       <c r="H732" t="n">
         <v>8772</v>
@@ -21742,7 +21742,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G737" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H737" t="n">
         <v>5380</v>
@@ -21829,7 +21829,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G740" t="n">
-        <v>0.629681408405304</v>
+        <v>0.629681468009949</v>
       </c>
       <c r="H740" t="n">
         <v>48907</v>
@@ -21887,7 +21887,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G742" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H742" t="n">
         <v>82682</v>
@@ -21974,7 +21974,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H745" t="n">
         <v>306199</v>
@@ -22061,7 +22061,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G748" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H748" t="n">
         <v>308766</v>
@@ -22119,7 +22119,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G750" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H750" t="n">
         <v>820174</v>
@@ -22177,7 +22177,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G752" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H752" t="n">
         <v>388590</v>
@@ -22235,7 +22235,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G754" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H754" t="n">
         <v>247058</v>
@@ -22293,7 +22293,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G756" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H756" t="n">
         <v>44184</v>
@@ -22322,7 +22322,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G757" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H757" t="n">
         <v>161007</v>
@@ -22351,7 +22351,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G758" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H758" t="n">
         <v>103377</v>
@@ -22380,7 +22380,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G759" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H759" t="n">
         <v>92669</v>
@@ -22409,7 +22409,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G760" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H760" t="n">
         <v>174775</v>
@@ -22438,7 +22438,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G761" t="n">
-        <v>0.651824057102203</v>
+        <v>0.651823997497559</v>
       </c>
       <c r="H761" t="n">
         <v>112676</v>
@@ -22496,7 +22496,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G763" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H763" t="n">
         <v>39624</v>
@@ -22525,7 +22525,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G764" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H764" t="n">
         <v>146710</v>
@@ -22583,7 +22583,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G766" t="n">
-        <v>0.662895321846008</v>
+        <v>0.662895381450653</v>
       </c>
       <c r="H766" t="n">
         <v>109701</v>
@@ -22612,7 +22612,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G767" t="n">
-        <v>0.667047083377838</v>
+        <v>0.667047023773193</v>
       </c>
       <c r="H767" t="n">
         <v>116328</v>
@@ -22699,7 +22699,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G770" t="n">
-        <v>0.671198844909668</v>
+        <v>0.671198904514313</v>
       </c>
       <c r="H770" t="n">
         <v>31046</v>
@@ -22728,7 +22728,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G771" t="n">
-        <v>0.671198844909668</v>
+        <v>0.671198904514313</v>
       </c>
       <c r="H771" t="n">
         <v>60160</v>
@@ -22757,7 +22757,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G772" t="n">
-        <v>0.671198844909668</v>
+        <v>0.671198904514313</v>
       </c>
       <c r="H772" t="n">
         <v>359409</v>
@@ -22786,7 +22786,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G773" t="n">
-        <v>0.671198844909668</v>
+        <v>0.671198904514313</v>
       </c>
       <c r="H773" t="n">
         <v>65019</v>
@@ -22815,7 +22815,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G774" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H774" t="n">
         <v>228965</v>
@@ -22844,7 +22844,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H775" t="n">
         <v>359900</v>
@@ -22873,7 +22873,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H776" t="n">
         <v>210137</v>
@@ -22902,7 +22902,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G777" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H777" t="n">
         <v>174998</v>
@@ -22931,7 +22931,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G778" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H778" t="n">
         <v>275985</v>
@@ -22989,7 +22989,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G780" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H780" t="n">
         <v>526304</v>
@@ -23105,7 +23105,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G784" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H784" t="n">
         <v>376786</v>
@@ -23134,7 +23134,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G785" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H785" t="n">
         <v>180557</v>
@@ -23163,7 +23163,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G786" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H786" t="n">
         <v>117707</v>
@@ -23250,7 +23250,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G789" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H789" t="n">
         <v>229318</v>
@@ -23279,7 +23279,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G790" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H790" t="n">
         <v>290276</v>
@@ -23308,7 +23308,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G791" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H791" t="n">
         <v>146801</v>
@@ -23337,7 +23337,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G792" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H792" t="n">
         <v>619773</v>
@@ -23395,7 +23395,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G794" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733475029468536</v>
       </c>
       <c r="H794" t="n">
         <v>353515</v>
@@ -23424,7 +23424,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G795" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733475029468536</v>
       </c>
       <c r="H795" t="n">
         <v>349231</v>
@@ -23482,7 +23482,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H797" t="n">
         <v>3149209</v>
@@ -23511,7 +23511,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G798" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H798" t="n">
         <v>2153597</v>
@@ -23540,7 +23540,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G799" t="n">
-        <v>0.680886209011078</v>
+        <v>0.680886268615723</v>
       </c>
       <c r="H799" t="n">
         <v>1360063</v>
@@ -23569,7 +23569,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G800" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H800" t="n">
         <v>325657</v>
@@ -23598,7 +23598,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H801" t="n">
         <v>319507</v>
@@ -23627,7 +23627,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G802" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H802" t="n">
         <v>520584</v>
@@ -23656,7 +23656,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G803" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H803" t="n">
         <v>211249</v>
@@ -23685,7 +23685,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G804" t="n">
-        <v>0.680886209011078</v>
+        <v>0.680886268615723</v>
       </c>
       <c r="H804" t="n">
         <v>213189</v>
@@ -23714,7 +23714,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G805" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H805" t="n">
         <v>435328</v>
@@ -23743,7 +23743,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G806" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H806" t="n">
         <v>320023</v>
@@ -23772,7 +23772,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>0.679502367973328</v>
+        <v>0.679502308368683</v>
       </c>
       <c r="H807" t="n">
         <v>392161</v>
@@ -23801,7 +23801,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G808" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H808" t="n">
         <v>226093</v>
@@ -23859,7 +23859,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G810" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H810" t="n">
         <v>525234</v>
@@ -23888,7 +23888,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G811" t="n">
-        <v>0.680886209011078</v>
+        <v>0.680886268615723</v>
       </c>
       <c r="H811" t="n">
         <v>530661</v>
@@ -23946,7 +23946,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G813" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H813" t="n">
         <v>175222</v>
@@ -23975,7 +23975,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G814" t="n">
-        <v>0.680886209011078</v>
+        <v>0.680886268615723</v>
       </c>
       <c r="H814" t="n">
         <v>34017</v>
@@ -24004,7 +24004,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G815" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H815" t="n">
         <v>305887</v>
@@ -24062,7 +24062,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G817" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H817" t="n">
         <v>80902</v>
@@ -24149,7 +24149,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H820" t="n">
         <v>65351</v>
@@ -24236,7 +24236,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G823" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H823" t="n">
         <v>104698</v>
@@ -24265,7 +24265,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H824" t="n">
         <v>77471</v>
@@ -24294,7 +24294,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G825" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H825" t="n">
         <v>85392</v>
@@ -24352,7 +24352,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G827" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H827" t="n">
         <v>136318</v>
@@ -24410,7 +24410,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G829" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H829" t="n">
         <v>193723</v>
@@ -24439,7 +24439,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G830" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H830" t="n">
         <v>511380</v>
@@ -24468,7 +24468,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G831" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H831" t="n">
         <v>403805</v>
@@ -24526,7 +24526,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G833" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H833" t="n">
         <v>500408</v>
@@ -24555,7 +24555,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G834" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H834" t="n">
         <v>204614</v>
@@ -24642,7 +24642,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G837" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H837" t="n">
         <v>311717</v>
@@ -24700,7 +24700,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G839" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H839" t="n">
         <v>261587</v>
@@ -24758,7 +24758,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G841" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H841" t="n">
         <v>153205</v>
@@ -24874,7 +24874,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G845" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H845" t="n">
         <v>128303</v>
@@ -24961,7 +24961,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H848" t="n">
         <v>73636</v>
@@ -25019,7 +25019,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G850" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H850" t="n">
         <v>114935</v>
@@ -25048,7 +25048,7 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H851" t="n">
         <v>147121</v>
@@ -25077,7 +25077,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G852" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H852" t="n">
         <v>244060</v>
@@ -25164,7 +25164,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G855" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H855" t="n">
         <v>372391</v>
@@ -25193,7 +25193,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G856" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H856" t="n">
         <v>90403</v>
@@ -25599,7 +25599,7 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H870" t="n">
         <v>187220</v>
@@ -25628,7 +25628,7 @@
         <v>1</v>
       </c>
       <c r="G871" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H871" t="n">
         <v>143153</v>
@@ -25715,7 +25715,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H874" t="n">
         <v>84308</v>
@@ -25773,7 +25773,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G876" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H876" t="n">
         <v>81601</v>
@@ -25802,7 +25802,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G877" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H877" t="n">
         <v>104497</v>
@@ -25831,7 +25831,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G878" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H878" t="n">
         <v>305495</v>
@@ -25860,7 +25860,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G879" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H879" t="n">
         <v>134656</v>
@@ -25889,7 +25889,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H880" t="n">
         <v>295035</v>
@@ -25947,7 +25947,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H882" t="n">
         <v>185348</v>
@@ -25976,7 +25976,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G883" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H883" t="n">
         <v>68756</v>
@@ -26034,7 +26034,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H885" t="n">
         <v>493105</v>
@@ -26063,7 +26063,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G886" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H886" t="n">
         <v>216811</v>
@@ -26092,7 +26092,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H887" t="n">
         <v>390492</v>
@@ -26121,7 +26121,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G888" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H888" t="n">
         <v>173883</v>
@@ -26150,7 +26150,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G889" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H889" t="n">
         <v>132291</v>
@@ -26179,7 +26179,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G890" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H890" t="n">
         <v>159006</v>
@@ -26237,7 +26237,7 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H892" t="n">
         <v>1088893</v>
@@ -26266,7 +26266,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G893" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H893" t="n">
         <v>212453</v>
@@ -26585,7 +26585,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G904" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H904" t="n">
         <v>176654</v>
@@ -26614,7 +26614,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G905" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H905" t="n">
         <v>43325</v>
@@ -26643,7 +26643,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G906" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H906" t="n">
         <v>107319</v>
@@ -26672,7 +26672,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G907" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H907" t="n">
         <v>347972</v>
@@ -26701,7 +26701,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H908" t="n">
         <v>40674</v>
@@ -26730,7 +26730,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G909" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H909" t="n">
         <v>92055</v>
@@ -26991,7 +26991,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H918" t="n">
         <v>246514</v>
@@ -27194,7 +27194,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G925" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H925" t="n">
         <v>69631</v>
@@ -27223,7 +27223,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G926" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H926" t="n">
         <v>632493</v>
@@ -27252,7 +27252,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G927" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H927" t="n">
         <v>1097</v>
@@ -27281,7 +27281,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G928" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H928" t="n">
         <v>16208</v>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G930" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H930" t="n">
         <v>145435</v>
@@ -27368,7 +27368,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G931" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H931" t="n">
         <v>42869</v>
@@ -27426,7 +27426,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G933" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H933" t="n">
         <v>15766</v>
@@ -27455,7 +27455,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H934" t="n">
         <v>81656</v>
@@ -27542,7 +27542,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G937" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H937" t="n">
         <v>21775</v>
@@ -27571,7 +27571,7 @@
         <v>1</v>
       </c>
       <c r="G938" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H938" t="n">
         <v>153375</v>
@@ -27600,7 +27600,7 @@
         <v>1</v>
       </c>
       <c r="G939" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H939" t="n">
         <v>69959</v>
@@ -27629,7 +27629,7 @@
         <v>1</v>
       </c>
       <c r="G940" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H940" t="n">
         <v>26335</v>
@@ -27658,7 +27658,7 @@
         <v>1</v>
       </c>
       <c r="G941" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H941" t="n">
         <v>78845</v>
@@ -27687,7 +27687,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G942" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H942" t="n">
         <v>68857</v>
@@ -27716,7 +27716,7 @@
         <v>1</v>
       </c>
       <c r="G943" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H943" t="n">
         <v>88334</v>
@@ -27745,7 +27745,7 @@
         <v>1</v>
       </c>
       <c r="G944" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H944" t="n">
         <v>61072</v>
@@ -27774,7 +27774,7 @@
         <v>1</v>
       </c>
       <c r="G945" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H945" t="n">
         <v>55996</v>
@@ -27803,7 +27803,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G946" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H946" t="n">
         <v>87148</v>
@@ -27832,7 +27832,7 @@
         <v>1</v>
       </c>
       <c r="G947" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H947" t="n">
         <v>78831</v>
@@ -27861,7 +27861,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G948" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H948" t="n">
         <v>63867</v>
@@ -27890,7 +27890,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G949" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H949" t="n">
         <v>41116</v>
@@ -27919,7 +27919,7 @@
         <v>1</v>
       </c>
       <c r="G950" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H950" t="n">
         <v>199826</v>
@@ -27948,7 +27948,7 @@
         <v>1</v>
       </c>
       <c r="G951" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H951" t="n">
         <v>101696</v>
@@ -27977,7 +27977,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G952" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H952" t="n">
         <v>133528</v>
@@ -28006,7 +28006,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G953" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H953" t="n">
         <v>44179</v>
@@ -28064,7 +28064,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G955" t="n">
-        <v>0.682270109653473</v>
+        <v>0.682270169258118</v>
       </c>
       <c r="H955" t="n">
         <v>244843</v>
@@ -28267,7 +28267,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G962" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H962" t="n">
         <v>218220</v>
@@ -28296,7 +28296,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G963" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H963" t="n">
         <v>49902</v>
@@ -28383,7 +28383,7 @@
         <v>1</v>
       </c>
       <c r="G966" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H966" t="n">
         <v>55243</v>
@@ -28441,7 +28441,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G968" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H968" t="n">
         <v>98290</v>
@@ -28557,7 +28557,7 @@
         <v>1</v>
       </c>
       <c r="G972" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H972" t="n">
         <v>97743</v>
@@ -28586,7 +28586,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G973" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H973" t="n">
         <v>105764</v>
@@ -28615,7 +28615,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H974" t="n">
         <v>619655</v>
@@ -28905,7 +28905,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H984" t="n">
         <v>62066</v>
@@ -28934,7 +28934,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G985" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H985" t="n">
         <v>78120</v>
@@ -28963,7 +28963,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G986" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H986" t="n">
         <v>66452</v>
@@ -28992,7 +28992,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G987" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H987" t="n">
         <v>95757</v>
@@ -29021,7 +29021,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G988" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H988" t="n">
         <v>102998</v>
@@ -29050,7 +29050,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G989" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H989" t="n">
         <v>75430</v>
@@ -29108,7 +29108,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G991" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H991" t="n">
         <v>7575</v>
@@ -29137,7 +29137,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G992" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H992" t="n">
         <v>96747</v>
@@ -29166,7 +29166,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G993" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H993" t="n">
         <v>191111</v>
@@ -29195,7 +29195,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G994" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H994" t="n">
         <v>78705</v>
@@ -29224,7 +29224,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G995" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H995" t="n">
         <v>105388</v>
@@ -29253,7 +29253,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G996" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H996" t="n">
         <v>130509</v>
@@ -29282,7 +29282,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H997" t="n">
         <v>110766</v>
@@ -29456,7 +29456,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H1003" t="n">
         <v>235612</v>
@@ -29485,7 +29485,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H1004" t="n">
         <v>192053</v>
@@ -29514,7 +29514,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1005" t="n">
         <v>342278</v>
@@ -29543,7 +29543,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1006" t="n">
         <v>322567</v>
@@ -29601,7 +29601,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H1008" t="n">
         <v>278865</v>
@@ -29630,7 +29630,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1009" t="n">
         <v>174124</v>
@@ -29659,7 +29659,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H1010" t="n">
         <v>113260</v>
@@ -29688,7 +29688,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H1011" t="n">
         <v>387485</v>
@@ -29717,7 +29717,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H1012" t="n">
         <v>249244</v>
@@ -29746,7 +29746,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1013" t="n">
         <v>286241</v>
@@ -29775,7 +29775,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1014" t="n">
         <v>318580</v>
@@ -29804,7 +29804,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1015" t="n">
         <v>60551</v>
@@ -29891,7 +29891,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1018" t="n">
         <v>35801</v>
@@ -29949,7 +29949,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H1020" t="n">
         <v>109677</v>
@@ -29978,7 +29978,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1021" t="n">
         <v>156016</v>
@@ -30529,7 +30529,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H1040" t="n">
         <v>92707</v>
@@ -30558,7 +30558,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.695417404174805</v>
+        <v>0.69541734457016</v>
       </c>
       <c r="H1041" t="n">
         <v>92366</v>
@@ -30645,7 +30645,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1044" t="n">
         <v>234674</v>
@@ -30674,7 +30674,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1045" t="n">
         <v>171115</v>
@@ -30703,7 +30703,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H1046" t="n">
         <v>76577</v>
@@ -30761,7 +30761,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733475029468536</v>
       </c>
       <c r="H1048" t="n">
         <v>1713322</v>
@@ -30819,7 +30819,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799211025238037</v>
       </c>
       <c r="H1050" t="n">
         <v>1197758</v>
@@ -30848,7 +30848,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1051" t="n">
         <v>273699</v>
@@ -30906,7 +30906,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1053" t="n">
         <v>823602</v>
@@ -30993,7 +30993,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1056" t="n">
         <v>602371</v>
@@ -31051,7 +31051,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H1058" t="n">
         <v>731628</v>
@@ -31080,7 +31080,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1059" t="n">
         <v>163770</v>
@@ -31225,7 +31225,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H1064" t="n">
         <v>311827</v>
@@ -31254,7 +31254,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H1065" t="n">
         <v>357849</v>
@@ -31283,7 +31283,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.575708627700806</v>
+        <v>0.57570868730545</v>
       </c>
       <c r="H1066" t="n">
         <v>506587</v>
@@ -31370,7 +31370,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1069" t="n">
         <v>131300</v>
@@ -31399,7 +31399,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.596467435359955</v>
+        <v>0.59646737575531</v>
       </c>
       <c r="H1070" t="n">
         <v>189836</v>
@@ -31428,7 +31428,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1071" t="n">
         <v>34398</v>
@@ -31457,7 +31457,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.624145746231079</v>
+        <v>0.624145686626434</v>
       </c>
       <c r="H1072" t="n">
         <v>187024</v>
@@ -31515,7 +31515,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H1074" t="n">
         <v>127271</v>
@@ -31660,7 +31660,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H1079" t="n">
         <v>28824</v>
@@ -31689,7 +31689,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H1080" t="n">
         <v>10767</v>
@@ -31747,7 +31747,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H1082" t="n">
         <v>86399</v>
@@ -31776,7 +31776,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1083" t="n">
         <v>131641</v>
@@ -31805,7 +31805,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H1084" t="n">
         <v>166709</v>
@@ -31834,7 +31834,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H1085" t="n">
         <v>23669</v>
@@ -31863,7 +31863,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1086" t="n">
         <v>52777</v>
@@ -31892,7 +31892,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1087" t="n">
         <v>113437</v>
@@ -31921,7 +31921,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1088" t="n">
         <v>69667</v>
@@ -31950,7 +31950,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.629681408405304</v>
+        <v>0.629681468009949</v>
       </c>
       <c r="H1089" t="n">
         <v>108498</v>
@@ -31979,7 +31979,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.637984871864319</v>
+        <v>0.637984931468964</v>
       </c>
       <c r="H1090" t="n">
         <v>82780</v>
@@ -32008,7 +32008,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1091" t="n">
         <v>32955</v>
@@ -32037,7 +32037,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.618610024452209</v>
+        <v>0.618610084056854</v>
       </c>
       <c r="H1092" t="n">
         <v>82022</v>
@@ -32095,7 +32095,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1094" t="n">
         <v>39008</v>
@@ -32124,7 +32124,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.629681408405304</v>
+        <v>0.629681468009949</v>
       </c>
       <c r="H1095" t="n">
         <v>172934</v>
@@ -32153,7 +32153,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1096" t="n">
         <v>78354</v>
@@ -32182,7 +32182,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1097" t="n">
         <v>284734</v>
@@ -32327,7 +32327,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1102" t="n">
         <v>14360</v>
@@ -32559,7 +32559,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.614458382129669</v>
+        <v>0.614458322525024</v>
       </c>
       <c r="H1110" t="n">
         <v>74390</v>
@@ -32704,7 +32704,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.58401221036911</v>
+        <v>0.584012150764465</v>
       </c>
       <c r="H1115" t="n">
         <v>77035</v>
@@ -32762,7 +32762,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.59785133600235</v>
+        <v>0.597851395606995</v>
       </c>
       <c r="H1117" t="n">
         <v>114903</v>
@@ -32849,7 +32849,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.60200309753418</v>
+        <v>0.602003037929535</v>
       </c>
       <c r="H1120" t="n">
         <v>76838</v>
@@ -32878,7 +32878,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.60200309753418</v>
+        <v>0.602003037929535</v>
       </c>
       <c r="H1121" t="n">
         <v>115137</v>
@@ -32907,7 +32907,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.578476548194885</v>
+        <v>0.57847648859024</v>
       </c>
       <c r="H1122" t="n">
         <v>200693</v>
@@ -32936,7 +32936,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.588163912296295</v>
+        <v>0.58816397190094</v>
       </c>
       <c r="H1123" t="n">
         <v>186789</v>
@@ -32965,7 +32965,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.607538759708405</v>
+        <v>0.60753870010376</v>
       </c>
       <c r="H1124" t="n">
         <v>193168</v>
@@ -32994,7 +32994,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.613074362277985</v>
+        <v>0.613074421882629</v>
       </c>
       <c r="H1125" t="n">
         <v>101717</v>
@@ -33052,7 +33052,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.610306620597839</v>
+        <v>0.610306560993195</v>
       </c>
       <c r="H1127" t="n">
         <v>52656</v>
@@ -33081,7 +33081,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.610306620597839</v>
+        <v>0.610306560993195</v>
       </c>
       <c r="H1128" t="n">
         <v>167445</v>
@@ -33110,7 +33110,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.610306620597839</v>
+        <v>0.610306560993195</v>
       </c>
       <c r="H1129" t="n">
         <v>211022</v>
@@ -33168,7 +33168,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.629681408405304</v>
+        <v>0.629681468009949</v>
       </c>
       <c r="H1131" t="n">
         <v>143550</v>
@@ -33226,7 +33226,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.624145746231079</v>
+        <v>0.624145686626434</v>
       </c>
       <c r="H1133" t="n">
         <v>45723</v>
@@ -33255,7 +33255,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.629681408405304</v>
+        <v>0.629681468009949</v>
       </c>
       <c r="H1134" t="n">
         <v>95950</v>
@@ -33284,7 +33284,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H1135" t="n">
         <v>42077</v>
@@ -33313,7 +33313,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H1136" t="n">
         <v>53591</v>
@@ -33342,7 +33342,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.628297507762909</v>
+        <v>0.628297448158264</v>
       </c>
       <c r="H1137" t="n">
         <v>73997</v>
@@ -33371,7 +33371,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1138" t="n">
         <v>103661</v>
@@ -33516,7 +33516,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1143" t="n">
         <v>47967</v>
@@ -33545,7 +33545,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H1144" t="n">
         <v>134257</v>
@@ -33574,7 +33574,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1145" t="n">
         <v>71701</v>
@@ -33632,7 +33632,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1147" t="n">
         <v>34283</v>
@@ -33748,7 +33748,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.651824057102203</v>
+        <v>0.651823997497559</v>
       </c>
       <c r="H1151" t="n">
         <v>98360</v>
@@ -33777,7 +33777,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1152" t="n">
         <v>107933</v>
@@ -33806,7 +33806,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1153" t="n">
         <v>43157</v>
@@ -33835,7 +33835,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1154" t="n">
         <v>25608</v>
@@ -33893,7 +33893,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1156" t="n">
         <v>44684</v>
@@ -33922,7 +33922,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1157" t="n">
         <v>79152</v>
@@ -33951,7 +33951,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H1158" t="n">
         <v>35471</v>
@@ -33980,7 +33980,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.654591798782349</v>
+        <v>0.654591858386993</v>
       </c>
       <c r="H1159" t="n">
         <v>5309</v>
@@ -34038,7 +34038,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1161" t="n">
         <v>26496</v>
@@ -34183,7 +34183,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.637984871864319</v>
+        <v>0.637984931468964</v>
       </c>
       <c r="H1166" t="n">
         <v>345</v>
@@ -34270,7 +34270,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H1169" t="n">
         <v>11833</v>
@@ -34386,7 +34386,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1173" t="n">
         <v>3808</v>
@@ -34502,7 +34502,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H1177" t="n">
         <v>19107</v>
@@ -34618,7 +34618,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H1181" t="n">
         <v>3104</v>
@@ -34676,7 +34676,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1183" t="n">
         <v>35800</v>
@@ -34734,7 +34734,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.629681408405304</v>
+        <v>0.629681468009949</v>
       </c>
       <c r="H1185" t="n">
         <v>47037</v>
@@ -34821,7 +34821,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1188" t="n">
         <v>5415</v>
@@ -34937,7 +34937,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1192" t="n">
         <v>71254</v>
@@ -34995,7 +34995,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H1194" t="n">
         <v>18420</v>
@@ -35024,7 +35024,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H1195" t="n">
         <v>8103</v>
@@ -35198,7 +35198,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.639368772506714</v>
+        <v>0.639368832111359</v>
       </c>
       <c r="H1201" t="n">
         <v>31035</v>
@@ -35343,7 +35343,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H1206" t="n">
         <v>6431</v>
@@ -35459,7 +35459,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.650440037250519</v>
+        <v>0.650440156459808</v>
       </c>
       <c r="H1210" t="n">
         <v>19679</v>
@@ -35488,7 +35488,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.646288394927979</v>
+        <v>0.646288335323334</v>
       </c>
       <c r="H1211" t="n">
         <v>14578</v>
@@ -35517,7 +35517,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H1212" t="n">
         <v>3435</v>
@@ -35546,7 +35546,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.649056196212769</v>
+        <v>0.649056255817413</v>
       </c>
       <c r="H1213" t="n">
         <v>41863</v>
@@ -35749,7 +35749,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.629681408405304</v>
+        <v>0.629681468009949</v>
       </c>
       <c r="H1220" t="n">
         <v>58098</v>
@@ -35807,7 +35807,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1222" t="n">
         <v>66195</v>
@@ -35836,7 +35836,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1223" t="n">
         <v>102090</v>
@@ -35865,7 +35865,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.624145746231079</v>
+        <v>0.624145686626434</v>
       </c>
       <c r="H1224" t="n">
         <v>18930</v>
@@ -35894,7 +35894,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H1225" t="n">
         <v>43500</v>
@@ -35923,7 +35923,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.626913607120514</v>
+        <v>0.626913547515869</v>
       </c>
       <c r="H1226" t="n">
         <v>40301</v>
@@ -35952,7 +35952,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.622761845588684</v>
+        <v>0.622761726379395</v>
       </c>
       <c r="H1227" t="n">
         <v>189581</v>
@@ -36242,7 +36242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.637984871864319</v>
+        <v>0.637984931468964</v>
       </c>
       <c r="H1237" t="n">
         <v>55565</v>
@@ -36329,7 +36329,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H1240" t="n">
         <v>40915</v>
@@ -36358,7 +36358,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.647672295570374</v>
+        <v>0.647672355175018</v>
       </c>
       <c r="H1241" t="n">
         <v>45409</v>
@@ -36387,7 +36387,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1242" t="n">
         <v>155539</v>
@@ -36474,7 +36474,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.657359659671783</v>
+        <v>0.657359719276428</v>
       </c>
       <c r="H1245" t="n">
         <v>74860</v>
@@ -36503,7 +36503,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.664279282093048</v>
+        <v>0.664279222488403</v>
       </c>
       <c r="H1246" t="n">
         <v>149953</v>
@@ -36532,7 +36532,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.676734507083893</v>
+        <v>0.676734447479248</v>
       </c>
       <c r="H1247" t="n">
         <v>67536</v>
@@ -36561,7 +36561,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.678118467330933</v>
+        <v>0.678118407726288</v>
       </c>
       <c r="H1248" t="n">
         <v>207160</v>
@@ -36619,7 +36619,7 @@
         <v>1</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H1250" t="n">
         <v>61786</v>
@@ -36677,7 +36677,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H1252" t="n">
         <v>75238</v>
@@ -36706,7 +36706,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.682270109653473</v>
+        <v>0.682270169258118</v>
       </c>
       <c r="H1253" t="n">
         <v>24503</v>
@@ -36735,7 +36735,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H1254" t="n">
         <v>248043</v>
@@ -36793,7 +36793,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.690573692321777</v>
+        <v>0.690573632717133</v>
       </c>
       <c r="H1256" t="n">
         <v>27967</v>
@@ -36880,7 +36880,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.683654129505157</v>
+        <v>0.683654069900513</v>
       </c>
       <c r="H1259" t="n">
         <v>104468</v>
@@ -36909,7 +36909,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1260" t="n">
         <v>95974</v>
@@ -36938,7 +36938,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1261" t="n">
         <v>40481</v>
@@ -36967,7 +36967,7 @@
         <v>1</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.691957592964172</v>
+        <v>0.691957533359528</v>
       </c>
       <c r="H1262" t="n">
         <v>31200</v>
@@ -37054,7 +37054,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.685038030147552</v>
+        <v>0.685037970542908</v>
       </c>
       <c r="H1265" t="n">
         <v>177918</v>
@@ -37228,7 +37228,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.712716221809387</v>
+        <v>0.712716281414032</v>
       </c>
       <c r="H1271" t="n">
         <v>213141</v>
@@ -37286,7 +37286,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.716175973415375</v>
+        <v>0.716176092624664</v>
       </c>
       <c r="H1273" t="n">
         <v>175476</v>
@@ -37373,7 +37373,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1276" t="n">
         <v>52660</v>
@@ -37431,7 +37431,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H1278" t="n">
         <v>61686</v>
@@ -37518,7 +37518,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733475029468536</v>
       </c>
       <c r="H1281" t="n">
         <v>28087</v>
@@ -37547,7 +37547,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733475029468536</v>
       </c>
       <c r="H1282" t="n">
         <v>43403</v>
@@ -37576,7 +37576,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733475029468536</v>
       </c>
       <c r="H1283" t="n">
         <v>36252</v>
@@ -37634,7 +37634,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733475029468536</v>
       </c>
       <c r="H1285" t="n">
         <v>129493</v>
@@ -37663,7 +37663,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.719635784626007</v>
+        <v>0.719635903835297</v>
       </c>
       <c r="H1286" t="n">
         <v>131829</v>
@@ -37692,7 +37692,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.730015218257904</v>
+        <v>0.730015158653259</v>
       </c>
       <c r="H1287" t="n">
         <v>170197</v>
@@ -37721,7 +37721,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1288" t="n">
         <v>84581</v>
@@ -37750,7 +37750,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.723095595836639</v>
+        <v>0.723095655441284</v>
       </c>
       <c r="H1289" t="n">
         <v>98666</v>
@@ -37837,7 +37837,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1292" t="n">
         <v>224416</v>
@@ -37866,7 +37866,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1293" t="n">
         <v>140397</v>
@@ -37895,7 +37895,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1294" t="n">
         <v>63340</v>
@@ -37924,7 +37924,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1295" t="n">
         <v>133140</v>
@@ -37953,7 +37953,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1296" t="n">
         <v>219334</v>
@@ -37982,7 +37982,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.747314274311066</v>
+        <v>0.747314214706421</v>
       </c>
       <c r="H1297" t="n">
         <v>123714</v>
@@ -38011,7 +38011,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1298" t="n">
         <v>269434</v>
@@ -38040,7 +38040,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1299" t="n">
         <v>347129</v>
@@ -38069,7 +38069,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773906707764</v>
       </c>
       <c r="H1300" t="n">
         <v>100350</v>
@@ -38098,7 +38098,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1301" t="n">
         <v>103262</v>
@@ -38127,7 +38127,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1302" t="n">
         <v>109329</v>
@@ -38156,7 +38156,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1303" t="n">
         <v>65645</v>
@@ -38243,7 +38243,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.774992525577545</v>
+        <v>0.774992406368256</v>
       </c>
       <c r="H1306" t="n">
         <v>168242</v>
@@ -38272,7 +38272,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.764613151550293</v>
+        <v>0.764613091945648</v>
       </c>
       <c r="H1307" t="n">
         <v>170070</v>
@@ -38330,7 +38330,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1309" t="n">
         <v>105632</v>
@@ -38359,7 +38359,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.747314274311066</v>
+        <v>0.747314214706421</v>
       </c>
       <c r="H1310" t="n">
         <v>131076</v>
@@ -38417,7 +38417,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1312" t="n">
         <v>86822</v>
@@ -38446,7 +38446,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.764613151550293</v>
+        <v>0.764613091945648</v>
       </c>
       <c r="H1313" t="n">
         <v>260385</v>
@@ -38475,7 +38475,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1314" t="n">
         <v>60881</v>
@@ -38504,7 +38504,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.747314274311066</v>
+        <v>0.747314214706421</v>
       </c>
       <c r="H1315" t="n">
         <v>51899</v>
@@ -38533,7 +38533,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773906707764</v>
       </c>
       <c r="H1316" t="n">
         <v>137499</v>
@@ -38562,7 +38562,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1317" t="n">
         <v>128521</v>
@@ -38591,7 +38591,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1318" t="n">
         <v>48205</v>
@@ -38620,7 +38620,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1319" t="n">
         <v>83726</v>
@@ -38649,7 +38649,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1320" t="n">
         <v>44291</v>
@@ -38678,7 +38678,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1321" t="n">
         <v>113521</v>
@@ -38707,7 +38707,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1322" t="n">
         <v>79157</v>
@@ -38765,7 +38765,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.733474969863892</v>
+        <v>0.733475029468536</v>
       </c>
       <c r="H1324" t="n">
         <v>88274</v>
@@ -38823,7 +38823,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.747314274311066</v>
+        <v>0.747314214706421</v>
       </c>
       <c r="H1326" t="n">
         <v>102293</v>
@@ -38881,7 +38881,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.743854463100433</v>
+        <v>0.743854403495789</v>
       </c>
       <c r="H1328" t="n">
         <v>51128</v>
@@ -38910,7 +38910,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773906707764</v>
       </c>
       <c r="H1329" t="n">
         <v>70641</v>
@@ -38968,7 +38968,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1331" t="n">
         <v>97824</v>
@@ -39026,7 +39026,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773906707764</v>
       </c>
       <c r="H1333" t="n">
         <v>66358</v>
@@ -39055,7 +39055,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.750774025917053</v>
+        <v>0.750773906707764</v>
       </c>
       <c r="H1334" t="n">
         <v>300870</v>
@@ -39084,7 +39084,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1335" t="n">
         <v>106831</v>
@@ -39113,7 +39113,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1336" t="n">
         <v>533202</v>
@@ -39171,7 +39171,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.757693529129028</v>
+        <v>0.757693648338318</v>
       </c>
       <c r="H1338" t="n">
         <v>187114</v>
@@ -39200,7 +39200,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.764613151550293</v>
+        <v>0.764613091945648</v>
       </c>
       <c r="H1339" t="n">
         <v>149115</v>
@@ -39229,7 +39229,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.768072903156281</v>
+        <v>0.768072843551636</v>
       </c>
       <c r="H1340" t="n">
         <v>97960</v>
@@ -39287,7 +39287,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.754233777523041</v>
+        <v>0.754233837127686</v>
       </c>
       <c r="H1342" t="n">
         <v>231631</v>
@@ -39403,7 +39403,7 @@
         <v>1.125</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.778452217578888</v>
+        <v>0.778452277183533</v>
       </c>
       <c r="H1346" t="n">
         <v>130572</v>
@@ -39432,7 +39432,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.774992525577545</v>
+        <v>0.774992406368256</v>
       </c>
       <c r="H1347" t="n">
         <v>50868</v>
@@ -39461,7 +39461,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.774992525577545</v>
+        <v>0.774992406368256</v>
       </c>
       <c r="H1348" t="n">
         <v>140318</v>
@@ -39519,7 +39519,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1350" t="n">
         <v>305250</v>
@@ -39548,7 +39548,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1351" t="n">
         <v>45974</v>
@@ -39577,7 +39577,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.781911969184875</v>
+        <v>0.78191202878952</v>
       </c>
       <c r="H1352" t="n">
         <v>26682</v>
@@ -39635,7 +39635,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.785371780395508</v>
+        <v>0.785371840000153</v>
       </c>
       <c r="H1354" t="n">
         <v>55193</v>
@@ -39722,7 +39722,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1357" t="n">
         <v>110877</v>
@@ -39780,7 +39780,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1359" t="n">
         <v>170926</v>
@@ -39809,7 +39809,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.806130588054657</v>
+        <v>0.806130647659302</v>
       </c>
       <c r="H1360" t="n">
         <v>83021</v>
@@ -40041,7 +40041,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799211025238037</v>
       </c>
       <c r="H1368" t="n">
         <v>80674</v>
@@ -40070,7 +40070,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799211025238037</v>
       </c>
       <c r="H1369" t="n">
         <v>90790</v>
@@ -40099,7 +40099,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799211025238037</v>
       </c>
       <c r="H1370" t="n">
         <v>56184</v>
@@ -40476,7 +40476,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799211025238037</v>
       </c>
       <c r="H1383" t="n">
         <v>162202</v>
@@ -40563,7 +40563,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1386" t="n">
         <v>468354</v>
@@ -40679,7 +40679,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.806130588054657</v>
+        <v>0.806130647659302</v>
       </c>
       <c r="H1390" t="n">
         <v>192841</v>
@@ -40882,7 +40882,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.799210906028748</v>
+        <v>0.799211025238037</v>
       </c>
       <c r="H1397" t="n">
         <v>17197</v>
@@ -40911,7 +40911,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1398" t="n">
         <v>879466</v>
@@ -40940,7 +40940,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.806130588054657</v>
+        <v>0.806130647659302</v>
       </c>
       <c r="H1399" t="n">
         <v>470494</v>
@@ -40969,7 +40969,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1400" t="n">
         <v>336211</v>
@@ -40998,7 +40998,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.806130588054657</v>
+        <v>0.806130647659302</v>
       </c>
       <c r="H1401" t="n">
         <v>120762</v>
@@ -41027,7 +41027,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1402" t="n">
         <v>407746</v>
@@ -41056,7 +41056,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1403" t="n">
         <v>371772</v>
@@ -41085,7 +41085,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1404" t="n">
         <v>451788</v>
@@ -41230,7 +41230,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.809590339660645</v>
+        <v>0.809590280056</v>
       </c>
       <c r="H1409" t="n">
         <v>300980</v>
@@ -41288,7 +41288,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1411" t="n">
         <v>52154</v>
@@ -41317,7 +41317,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1412" t="n">
         <v>218373</v>
@@ -41897,7 +41897,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1432" t="n">
         <v>116624</v>
@@ -41955,7 +41955,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1434" t="n">
         <v>58038</v>
@@ -41984,7 +41984,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1435" t="n">
         <v>70728</v>
@@ -42013,7 +42013,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1436" t="n">
         <v>122837</v>
@@ -42042,7 +42042,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1437" t="n">
         <v>181025</v>
@@ -42071,7 +42071,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1438" t="n">
         <v>31317</v>
@@ -42158,7 +42158,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.823429524898529</v>
+        <v>0.823429584503174</v>
       </c>
       <c r="H1441" t="n">
         <v>332446</v>
@@ -42216,7 +42216,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.847648024559021</v>
+        <v>0.847647964954376</v>
       </c>
       <c r="H1443" t="n">
         <v>259888</v>
@@ -42245,7 +42245,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.854567587375641</v>
+        <v>0.854567527770996</v>
       </c>
       <c r="H1444" t="n">
         <v>272372</v>
@@ -42274,7 +42274,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.851107895374298</v>
+        <v>0.851107776165009</v>
       </c>
       <c r="H1445" t="n">
         <v>242876</v>
@@ -42303,7 +42303,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.840728461742401</v>
+        <v>0.840728521347046</v>
       </c>
       <c r="H1446" t="n">
         <v>397157</v>
@@ -42332,7 +42332,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.844188272953033</v>
+        <v>0.844188213348389</v>
       </c>
       <c r="H1447" t="n">
         <v>238874</v>
@@ -42361,7 +42361,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.840728461742401</v>
+        <v>0.840728521347046</v>
       </c>
       <c r="H1448" t="n">
         <v>523781</v>
@@ -42390,7 +42390,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.840728461742401</v>
+        <v>0.840728521347046</v>
       </c>
       <c r="H1449" t="n">
         <v>417288</v>
@@ -42419,7 +42419,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.840728461742401</v>
+        <v>0.840728521347046</v>
       </c>
       <c r="H1450" t="n">
         <v>171713</v>
@@ -42448,7 +42448,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.833808958530426</v>
+        <v>0.833808839321136</v>
       </c>
       <c r="H1451" t="n">
         <v>28378</v>
@@ -42477,7 +42477,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.833808958530426</v>
+        <v>0.833808839321136</v>
       </c>
       <c r="H1452" t="n">
         <v>824448</v>
@@ -42535,7 +42535,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.833808958530426</v>
+        <v>0.833808839321136</v>
       </c>
       <c r="H1454" t="n">
         <v>320343</v>
@@ -42593,7 +42593,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.858027338981628</v>
+        <v>0.858027398586273</v>
       </c>
       <c r="H1456" t="n">
         <v>272511</v>
@@ -42622,7 +42622,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.878786087036133</v>
+        <v>0.878786206245422</v>
       </c>
       <c r="H1457" t="n">
         <v>357522</v>
@@ -42651,7 +42651,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.868406713008881</v>
+        <v>0.868406772613525</v>
       </c>
       <c r="H1458" t="n">
         <v>78151</v>
@@ -42680,7 +42680,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.899544775485992</v>
+        <v>0.899544894695282</v>
       </c>
       <c r="H1459" t="n">
         <v>501877</v>
@@ -42709,7 +42709,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.90300464630127</v>
+        <v>0.90300452709198</v>
       </c>
       <c r="H1460" t="n">
         <v>479584</v>
@@ -42738,7 +42738,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.920303642749786</v>
+        <v>0.920303463935852</v>
       </c>
       <c r="H1461" t="n">
         <v>436738</v>
@@ -42767,7 +42767,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.916843891143799</v>
+        <v>0.916843712329865</v>
       </c>
       <c r="H1462" t="n">
         <v>386374</v>
@@ -42825,7 +42825,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.916843891143799</v>
+        <v>0.916843712329865</v>
       </c>
       <c r="H1464" t="n">
         <v>148638</v>
@@ -42854,7 +42854,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.927223265171051</v>
+        <v>0.927223086357117</v>
       </c>
       <c r="H1465" t="n">
         <v>86673</v>
@@ -42883,7 +42883,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.923763394355774</v>
+        <v>0.923763453960419</v>
       </c>
       <c r="H1466" t="n">
         <v>287349</v>
@@ -42912,7 +42912,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1467" t="n">
         <v>688381</v>
@@ -42941,7 +42941,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1468" t="n">
         <v>303974</v>
@@ -42970,7 +42970,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.941062271595001</v>
+        <v>0.941062390804291</v>
       </c>
       <c r="H1469" t="n">
         <v>129426</v>
@@ -42999,7 +42999,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1470" t="n">
         <v>44738</v>
@@ -43028,7 +43028,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1471" t="n">
         <v>189714</v>
@@ -43086,7 +43086,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1473" t="n">
         <v>94486</v>
@@ -43115,7 +43115,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.937602579593658</v>
+        <v>0.937602519989014</v>
       </c>
       <c r="H1474" t="n">
         <v>142236</v>
@@ -43144,7 +43144,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.937602579593658</v>
+        <v>0.937602519989014</v>
       </c>
       <c r="H1475" t="n">
         <v>50984</v>
@@ -43260,7 +43260,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.965280711650848</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1479" t="n">
         <v>279723</v>
@@ -43289,7 +43289,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.965280711650848</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1480" t="n">
         <v>122253</v>
@@ -43318,7 +43318,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.965280711650848</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1481" t="n">
         <v>54841</v>
@@ -43376,7 +43376,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.968740522861481</v>
+        <v>0.968740582466125</v>
       </c>
       <c r="H1483" t="n">
         <v>274130</v>
@@ -43405,7 +43405,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.996418833732605</v>
+        <v>0.996418952941895</v>
       </c>
       <c r="H1484" t="n">
         <v>249252</v>
@@ -43434,7 +43434,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.992959022521973</v>
+        <v>0.992958903312683</v>
       </c>
       <c r="H1485" t="n">
         <v>160211</v>
@@ -43463,7 +43463,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.999878764152527</v>
+        <v>0.999878704547882</v>
       </c>
       <c r="H1486" t="n">
         <v>120478</v>
@@ -43492,7 +43492,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.999878764152527</v>
+        <v>0.999878704547882</v>
       </c>
       <c r="H1487" t="n">
         <v>171820</v>
@@ -43521,7 +43521,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.992959022521973</v>
+        <v>0.992958903312683</v>
       </c>
       <c r="H1488" t="n">
         <v>196578</v>
@@ -43608,7 +43608,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.996418833732605</v>
+        <v>0.996418952941895</v>
       </c>
       <c r="H1491" t="n">
         <v>62978</v>
@@ -43637,7 +43637,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.992959022521973</v>
+        <v>0.992958903312683</v>
       </c>
       <c r="H1492" t="n">
         <v>57450</v>
@@ -43666,7 +43666,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.986039400100708</v>
+        <v>0.986039519309998</v>
       </c>
       <c r="H1493" t="n">
         <v>139022</v>
@@ -43695,7 +43695,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.986039400100708</v>
+        <v>0.986039519309998</v>
       </c>
       <c r="H1494" t="n">
         <v>79009</v>
@@ -43724,7 +43724,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.961821138858795</v>
+        <v>0.961820960044861</v>
       </c>
       <c r="H1495" t="n">
         <v>274571</v>
@@ -43753,7 +43753,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.961821138858795</v>
+        <v>0.961820960044861</v>
       </c>
       <c r="H1496" t="n">
         <v>319492</v>
@@ -43782,7 +43782,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.920303642749786</v>
+        <v>0.920303463935852</v>
       </c>
       <c r="H1497" t="n">
         <v>1137530</v>
@@ -43811,7 +43811,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.934142887592316</v>
+        <v>0.934142708778381</v>
       </c>
       <c r="H1498" t="n">
         <v>381079</v>
@@ -43840,7 +43840,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.934142887592316</v>
+        <v>0.934142708778381</v>
       </c>
       <c r="H1499" t="n">
         <v>103523</v>
@@ -43869,7 +43869,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.920303642749786</v>
+        <v>0.920303463935852</v>
       </c>
       <c r="H1500" t="n">
         <v>453289</v>
@@ -43898,7 +43898,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.934142887592316</v>
+        <v>0.934142708778381</v>
       </c>
       <c r="H1501" t="n">
         <v>135609</v>
@@ -43927,7 +43927,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.937602579593658</v>
+        <v>0.937602519989014</v>
       </c>
       <c r="H1502" t="n">
         <v>755734</v>
@@ -43956,7 +43956,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.927223265171051</v>
+        <v>0.927223086357117</v>
       </c>
       <c r="H1503" t="n">
         <v>329891</v>
@@ -43985,7 +43985,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.934142887592316</v>
+        <v>0.934142708778381</v>
       </c>
       <c r="H1504" t="n">
         <v>203683</v>
@@ -44014,7 +44014,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.944522202014923</v>
+        <v>0.944522142410278</v>
       </c>
       <c r="H1505" t="n">
         <v>156551</v>
@@ -44043,7 +44043,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.965280711650848</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1506" t="n">
         <v>99940</v>
@@ -44072,7 +44072,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.968740522861481</v>
+        <v>0.968740582466125</v>
       </c>
       <c r="H1507" t="n">
         <v>253006</v>
@@ -44101,7 +44101,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.965280711650848</v>
+        <v>0.965280830860138</v>
       </c>
       <c r="H1508" t="n">
         <v>176991</v>
@@ -44130,7 +44130,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.98949921131134</v>
+        <v>0.989499270915985</v>
       </c>
       <c r="H1509" t="n">
         <v>407671</v>
@@ -44217,7 +44217,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.02755701541901</v>
+        <v>1.02755689620972</v>
       </c>
       <c r="H1512" t="n">
         <v>458228</v>
@@ -44246,7 +44246,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.02755701541901</v>
+        <v>1.02755689620972</v>
       </c>
       <c r="H1513" t="n">
         <v>220523</v>
@@ -44275,7 +44275,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.01371777057648</v>
+        <v>1.01371788978577</v>
       </c>
       <c r="H1514" t="n">
         <v>249496</v>
@@ -44304,7 +44304,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.98949921131134</v>
+        <v>0.989499270915985</v>
       </c>
       <c r="H1515" t="n">
         <v>224195</v>
@@ -44333,7 +44333,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.01371777057648</v>
+        <v>1.01371788978577</v>
       </c>
       <c r="H1516" t="n">
         <v>437735</v>
@@ -44478,7 +44478,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.01717758178711</v>
+        <v>1.0171777009964</v>
       </c>
       <c r="H1521" t="n">
         <v>273665</v>
@@ -44507,7 +44507,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.01371777057648</v>
+        <v>1.01371788978577</v>
       </c>
       <c r="H1522" t="n">
         <v>189922</v>
@@ -44536,7 +44536,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.01371777057648</v>
+        <v>1.01371788978577</v>
       </c>
       <c r="H1523" t="n">
         <v>391063</v>
@@ -44565,7 +44565,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.02755701541901</v>
+        <v>1.02755689620972</v>
       </c>
       <c r="H1524" t="n">
         <v>793175</v>
@@ -44594,7 +44594,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.03101670742035</v>
+        <v>1.03101682662964</v>
       </c>
       <c r="H1525" t="n">
         <v>218492</v>
@@ -44652,7 +44652,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.06561470031738</v>
+        <v>1.06561458110809</v>
       </c>
       <c r="H1527" t="n">
         <v>782238</v>
@@ -44710,7 +44710,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.11751139163971</v>
+        <v>1.117511510849</v>
       </c>
       <c r="H1529" t="n">
         <v>421145</v>
@@ -44884,7 +44884,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.09329307079315</v>
+        <v>1.09329295158386</v>
       </c>
       <c r="H1535" t="n">
         <v>168043</v>
@@ -44971,7 +44971,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.09329307079315</v>
+        <v>1.09329295158386</v>
       </c>
       <c r="H1538" t="n">
         <v>370435</v>
@@ -45029,7 +45029,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.09329307079315</v>
+        <v>1.09329295158386</v>
       </c>
       <c r="H1540" t="n">
         <v>210213</v>
@@ -45087,7 +45087,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.04139614105225</v>
+        <v>1.04139626026154</v>
       </c>
       <c r="H1542" t="n">
         <v>266855</v>
@@ -45116,7 +45116,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.04139614105225</v>
+        <v>1.04139626026154</v>
       </c>
       <c r="H1543" t="n">
         <v>262904</v>
@@ -45145,7 +45145,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.05869507789612</v>
+        <v>1.05869519710541</v>
       </c>
       <c r="H1544" t="n">
         <v>116868</v>
@@ -45174,7 +45174,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.06215488910675</v>
+        <v>1.06215476989746</v>
       </c>
       <c r="H1545" t="n">
         <v>133753</v>
@@ -45203,7 +45203,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.05523538589478</v>
+        <v>1.05523526668549</v>
       </c>
       <c r="H1546" t="n">
         <v>96630</v>
@@ -45319,7 +45319,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.06215488910675</v>
+        <v>1.06215476989746</v>
       </c>
       <c r="H1550" t="n">
         <v>112492</v>
@@ -45348,7 +45348,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.06561470031738</v>
+        <v>1.06561458110809</v>
       </c>
       <c r="H1551" t="n">
         <v>94039</v>
@@ -45377,7 +45377,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.05869507789612</v>
+        <v>1.05869519710541</v>
       </c>
       <c r="H1552" t="n">
         <v>115710</v>
@@ -45406,7 +45406,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.06561470031738</v>
+        <v>1.06561458110809</v>
       </c>
       <c r="H1553" t="n">
         <v>102708</v>
@@ -45522,7 +45522,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.05869507789612</v>
+        <v>1.05869519710541</v>
       </c>
       <c r="H1557" t="n">
         <v>223368</v>
@@ -45609,7 +45609,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.11751139163971</v>
+        <v>1.117511510849</v>
       </c>
       <c r="H1560" t="n">
         <v>2403157</v>
@@ -45667,7 +45667,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1562" t="n">
         <v>1416932</v>
@@ -45725,7 +45725,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1564" t="n">
         <v>988135</v>
@@ -45812,7 +45812,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1567" t="n">
         <v>415789</v>
@@ -45841,7 +45841,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.20054638385773</v>
+        <v>1.20054650306702</v>
       </c>
       <c r="H1568" t="n">
         <v>951811</v>
@@ -45870,7 +45870,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1569" t="n">
         <v>510397</v>
@@ -45928,7 +45928,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.06561470031738</v>
+        <v>1.06561458110809</v>
       </c>
       <c r="H1571" t="n">
         <v>1174698</v>
@@ -45957,7 +45957,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.04139614105225</v>
+        <v>1.04139626026154</v>
       </c>
       <c r="H1572" t="n">
         <v>825976</v>
@@ -46160,7 +46160,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.12789070606232</v>
+        <v>1.12789082527161</v>
       </c>
       <c r="H1579" t="n">
         <v>463327</v>
@@ -46189,7 +46189,7 @@
         <v>1.625</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.12443101406097</v>
+        <v>1.12443113327026</v>
       </c>
       <c r="H1580" t="n">
         <v>317784</v>
@@ -46218,7 +46218,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.1867071390152</v>
+        <v>1.18670725822449</v>
       </c>
       <c r="H1581" t="n">
         <v>780997</v>
@@ -46247,7 +46247,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.16248857975006</v>
+        <v>1.16248869895935</v>
       </c>
       <c r="H1582" t="n">
         <v>806481</v>
@@ -46305,7 +46305,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1584" t="n">
         <v>312880</v>
@@ -46363,7 +46363,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.20054638385773</v>
+        <v>1.20054650306702</v>
       </c>
       <c r="H1586" t="n">
         <v>279699</v>
@@ -46450,7 +46450,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.26282262802124</v>
+        <v>1.26282250881195</v>
       </c>
       <c r="H1589" t="n">
         <v>1153238</v>
@@ -46508,7 +46508,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.24552369117737</v>
+        <v>1.24552345275879</v>
       </c>
       <c r="H1591" t="n">
         <v>435433</v>
@@ -46537,7 +46537,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.25244319438934</v>
+        <v>1.25244307518005</v>
       </c>
       <c r="H1592" t="n">
         <v>759956</v>
@@ -46566,7 +46566,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.2386040687561</v>
+        <v>1.23860394954681</v>
       </c>
       <c r="H1593" t="n">
         <v>563589</v>
@@ -46595,7 +46595,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.22130525112152</v>
+        <v>1.22130513191223</v>
       </c>
       <c r="H1594" t="n">
         <v>600957</v>
@@ -46624,7 +46624,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.24552369117737</v>
+        <v>1.24552345275879</v>
       </c>
       <c r="H1595" t="n">
         <v>378069</v>
@@ -46682,7 +46682,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.24552369117737</v>
+        <v>1.24552345275879</v>
       </c>
       <c r="H1597" t="n">
         <v>657270</v>
@@ -46769,7 +46769,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1600" t="n">
         <v>1485021</v>
@@ -46856,7 +46856,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.19708669185638</v>
+        <v>1.19708657264709</v>
       </c>
       <c r="H1603" t="n">
         <v>2203239</v>
@@ -46885,7 +46885,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.17632782459259</v>
+        <v>1.17632794380188</v>
       </c>
       <c r="H1604" t="n">
         <v>2339616</v>
@@ -46943,7 +46943,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.1846410036087</v>
+        <v>1.18464112281799</v>
       </c>
       <c r="H1606" t="n">
         <v>1073830</v>
@@ -46972,7 +46972,7 @@
         <v>1.375</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.14307487010956</v>
+        <v>1.14307475090027</v>
       </c>
       <c r="H1607" t="n">
         <v>888663</v>
@@ -47059,7 +47059,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1610" t="n">
         <v>1024808</v>
@@ -47146,7 +47146,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.05994212627411</v>
+        <v>1.05994200706482</v>
       </c>
       <c r="H1613" t="n">
         <v>1513410</v>
@@ -47175,7 +47175,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.04747211933136</v>
+        <v>1.04747223854065</v>
       </c>
       <c r="H1614" t="n">
         <v>585100</v>
@@ -47204,7 +47204,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.997592568397522</v>
+        <v>0.997592628002167</v>
       </c>
       <c r="H1615" t="n">
         <v>788688</v>
@@ -47291,7 +47291,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.01006245613098</v>
+        <v>1.01006257534027</v>
       </c>
       <c r="H1618" t="n">
         <v>241214</v>
@@ -47349,7 +47349,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.05994212627411</v>
+        <v>1.05994200706482</v>
       </c>
       <c r="H1620" t="n">
         <v>455691</v>
@@ -47378,7 +47378,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.06825542449951</v>
+        <v>1.06825530529022</v>
       </c>
       <c r="H1621" t="n">
         <v>353335</v>
@@ -47436,7 +47436,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.07656848430634</v>
+        <v>1.07656860351562</v>
       </c>
       <c r="H1623" t="n">
         <v>897447</v>
@@ -47523,7 +47523,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.05578541755676</v>
+        <v>1.05578553676605</v>
       </c>
       <c r="H1626" t="n">
         <v>221246</v>
@@ -47581,7 +47581,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.06825542449951</v>
+        <v>1.06825530529022</v>
       </c>
       <c r="H1628" t="n">
         <v>176002</v>
@@ -47639,7 +47639,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.09735178947449</v>
+        <v>1.09735190868378</v>
       </c>
       <c r="H1630" t="n">
         <v>580808</v>
@@ -47697,7 +47697,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.09735178947449</v>
+        <v>1.09735190868378</v>
       </c>
       <c r="H1632" t="n">
         <v>174475</v>
@@ -47726,7 +47726,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.09735178947449</v>
+        <v>1.09735190868378</v>
       </c>
       <c r="H1633" t="n">
         <v>130651</v>
@@ -47784,7 +47784,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.10566508769989</v>
+        <v>1.1056649684906</v>
       </c>
       <c r="H1635" t="n">
         <v>120589</v>
@@ -48045,7 +48045,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1644" t="n">
-        <v>1.01006245613098</v>
+        <v>1.01006257534027</v>
       </c>
       <c r="H1644" t="n">
         <v>120234</v>
@@ -48190,7 +48190,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.01421916484833</v>
+        <v>1.01421904563904</v>
       </c>
       <c r="H1649" t="n">
         <v>53800</v>
@@ -48393,7 +48393,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.997592568397522</v>
+        <v>0.997592628002167</v>
       </c>
       <c r="H1656" t="n">
         <v>103901</v>
@@ -48422,7 +48422,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.997592568397522</v>
+        <v>0.997592628002167</v>
       </c>
       <c r="H1657" t="n">
         <v>64763</v>
@@ -48509,7 +48509,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.01006245613098</v>
+        <v>1.01006257534027</v>
       </c>
       <c r="H1660" t="n">
         <v>148658</v>
@@ -48538,7 +48538,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.01006245613098</v>
+        <v>1.01006257534027</v>
       </c>
       <c r="H1661" t="n">
         <v>64077</v>
@@ -48567,7 +48567,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.997592568397522</v>
+        <v>0.997592628002167</v>
       </c>
       <c r="H1662" t="n">
         <v>220673</v>
@@ -48596,7 +48596,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.97680938243866</v>
+        <v>0.976809322834015</v>
       </c>
       <c r="H1663" t="n">
         <v>122248</v>
@@ -48683,7 +48683,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.04747211933136</v>
+        <v>1.04747223854065</v>
       </c>
       <c r="H1666" t="n">
         <v>210117</v>
@@ -49002,7 +49002,7 @@
         <v>1.375</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.14307487010956</v>
+        <v>1.14307475090027</v>
       </c>
       <c r="H1677" t="n">
         <v>65289</v>
@@ -49031,7 +49031,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.14723145961761</v>
+        <v>1.14723134040833</v>
       </c>
       <c r="H1678" t="n">
         <v>68600</v>
@@ -49118,7 +49118,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1681" t="n">
         <v>61636</v>
@@ -49176,7 +49176,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1683" t="n">
         <v>109056</v>
@@ -49321,7 +49321,7 @@
         <v>1.375</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.14307487010956</v>
+        <v>1.14307475090027</v>
       </c>
       <c r="H1688" t="n">
         <v>157739</v>
@@ -49350,7 +49350,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.09735178947449</v>
+        <v>1.09735190868378</v>
       </c>
       <c r="H1689" t="n">
         <v>307777</v>
@@ -49379,7 +49379,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.09735178947449</v>
+        <v>1.09735190868378</v>
       </c>
       <c r="H1690" t="n">
         <v>115683</v>
@@ -49408,7 +49408,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.09735178947449</v>
+        <v>1.09735190868378</v>
       </c>
       <c r="H1691" t="n">
         <v>49665</v>
@@ -49524,7 +49524,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.06825542449951</v>
+        <v>1.06825530529022</v>
       </c>
       <c r="H1695" t="n">
         <v>118248</v>
@@ -49553,7 +49553,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.05994212627411</v>
+        <v>1.05994200706482</v>
       </c>
       <c r="H1696" t="n">
         <v>141330</v>
@@ -49611,7 +49611,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.05578541755676</v>
+        <v>1.05578553676605</v>
       </c>
       <c r="H1698" t="n">
         <v>39503</v>
@@ -49640,7 +49640,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.04747211933136</v>
+        <v>1.04747223854065</v>
       </c>
       <c r="H1699" t="n">
         <v>98786</v>
@@ -49756,7 +49756,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.06825542449951</v>
+        <v>1.06825530529022</v>
       </c>
       <c r="H1703" t="n">
         <v>47521</v>
@@ -49814,7 +49814,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.07656848430634</v>
+        <v>1.07656860351562</v>
       </c>
       <c r="H1705" t="n">
         <v>91839</v>
@@ -49843,7 +49843,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.07656848430634</v>
+        <v>1.07656860351562</v>
       </c>
       <c r="H1706" t="n">
         <v>137105</v>
@@ -49901,7 +49901,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.04747211933136</v>
+        <v>1.04747223854065</v>
       </c>
       <c r="H1708" t="n">
         <v>822226</v>
@@ -49930,7 +49930,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1709" t="n">
-        <v>1.05578541755676</v>
+        <v>1.05578553676605</v>
       </c>
       <c r="H1709" t="n">
         <v>56159</v>
@@ -49959,7 +49959,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.06825542449951</v>
+        <v>1.06825530529022</v>
       </c>
       <c r="H1710" t="n">
         <v>239412</v>
@@ -50046,7 +50046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.05578541755676</v>
+        <v>1.05578553676605</v>
       </c>
       <c r="H1713" t="n">
         <v>45805</v>
@@ -50104,7 +50104,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.05578541755676</v>
+        <v>1.05578553676605</v>
       </c>
       <c r="H1715" t="n">
         <v>19401</v>
@@ -50191,7 +50191,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.01421916484833</v>
+        <v>1.01421904563904</v>
       </c>
       <c r="H1718" t="n">
         <v>71085</v>
@@ -50423,7 +50423,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.06825542449951</v>
+        <v>1.06825530529022</v>
       </c>
       <c r="H1726" t="n">
         <v>29407</v>
@@ -50452,7 +50452,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.05578541755676</v>
+        <v>1.05578553676605</v>
       </c>
       <c r="H1727" t="n">
         <v>130467</v>
@@ -50510,7 +50510,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.07656848430634</v>
+        <v>1.07656860351562</v>
       </c>
       <c r="H1729" t="n">
         <v>24362</v>
@@ -50713,7 +50713,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.13060486316681</v>
+        <v>1.1306049823761</v>
       </c>
       <c r="H1736" t="n">
         <v>124290</v>
@@ -50800,7 +50800,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.15138804912567</v>
+        <v>1.15138816833496</v>
       </c>
       <c r="H1739" t="n">
         <v>22397</v>
@@ -50916,7 +50916,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1743" t="n">
-        <v>1.14723145961761</v>
+        <v>1.14723134040833</v>
       </c>
       <c r="H1743" t="n">
         <v>57529</v>
@@ -50945,7 +50945,7 @@
         <v>1.375</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.14307487010956</v>
+        <v>1.14307475090027</v>
       </c>
       <c r="H1744" t="n">
         <v>94131</v>
@@ -50974,7 +50974,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.15138804912567</v>
+        <v>1.15138816833496</v>
       </c>
       <c r="H1745" t="n">
         <v>102412</v>
@@ -51003,7 +51003,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.14723145961761</v>
+        <v>1.14723134040833</v>
       </c>
       <c r="H1746" t="n">
         <v>61890</v>
@@ -51322,7 +51322,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1757" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1757" t="n">
         <v>136128</v>
@@ -51351,7 +51351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1758" t="n">
         <v>82692</v>
@@ -51525,7 +51525,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1764" t="n">
         <v>134687</v>
@@ -51583,7 +51583,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1766" t="n">
         <v>36572</v>
@@ -51728,7 +51728,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.1846410036087</v>
+        <v>1.18464112281799</v>
       </c>
       <c r="H1771" t="n">
         <v>33201</v>
@@ -51902,7 +51902,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.14723145961761</v>
+        <v>1.14723134040833</v>
       </c>
       <c r="H1777" t="n">
         <v>80532</v>
@@ -51931,7 +51931,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.14723145961761</v>
+        <v>1.14723134040833</v>
       </c>
       <c r="H1778" t="n">
         <v>77100</v>
@@ -51989,7 +51989,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.14723145961761</v>
+        <v>1.14723134040833</v>
       </c>
       <c r="H1780" t="n">
         <v>31482</v>
@@ -52047,7 +52047,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.13060486316681</v>
+        <v>1.1306049823761</v>
       </c>
       <c r="H1782" t="n">
         <v>77581</v>
@@ -52076,7 +52076,7 @@
         <v>1.375</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.14307487010956</v>
+        <v>1.14307475090027</v>
       </c>
       <c r="H1783" t="n">
         <v>23217</v>
@@ -52134,7 +52134,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1785" t="n">
         <v>598110</v>
@@ -52192,7 +52192,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1787" t="n">
         <v>134209</v>
@@ -52453,7 +52453,7 @@
         <v>1.5</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.24699068069458</v>
+        <v>1.24699056148529</v>
       </c>
       <c r="H1796" t="n">
         <v>298792</v>
@@ -52511,7 +52511,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.26361703872681</v>
+        <v>1.2636171579361</v>
       </c>
       <c r="H1798" t="n">
         <v>366320</v>
@@ -52540,7 +52540,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.2719304561615</v>
+        <v>1.27193057537079</v>
       </c>
       <c r="H1799" t="n">
         <v>282328</v>
@@ -52569,7 +52569,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.27608716487885</v>
+        <v>1.27608704566956</v>
       </c>
       <c r="H1800" t="n">
         <v>167588</v>
@@ -52598,7 +52598,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.27608716487885</v>
+        <v>1.27608704566956</v>
       </c>
       <c r="H1801" t="n">
         <v>146522</v>
@@ -52656,7 +52656,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.30934023857117</v>
+        <v>1.30934035778046</v>
       </c>
       <c r="H1803" t="n">
         <v>410158</v>
@@ -52714,7 +52714,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.30934023857117</v>
+        <v>1.30934035778046</v>
       </c>
       <c r="H1805" t="n">
         <v>191857</v>
@@ -52917,7 +52917,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.2802437543869</v>
+        <v>1.28024363517761</v>
       </c>
       <c r="H1812" t="n">
         <v>355199</v>
@@ -52946,7 +52946,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.26361703872681</v>
+        <v>1.2636171579361</v>
       </c>
       <c r="H1813" t="n">
         <v>380172</v>
@@ -52975,7 +52975,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.2802437543869</v>
+        <v>1.28024363517761</v>
       </c>
       <c r="H1814" t="n">
         <v>224082</v>
@@ -53149,7 +53149,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1820" t="n">
         <v>359212</v>
@@ -53265,7 +53265,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1824" t="n">
         <v>159581</v>
@@ -53381,7 +53381,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1828" t="n">
         <v>93795</v>
@@ -53439,7 +53439,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1830" t="n">
-        <v>1.19295430183411</v>
+        <v>1.19295418262482</v>
       </c>
       <c r="H1830" t="n">
         <v>127047</v>
@@ -53497,7 +53497,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1832" t="n">
         <v>211202</v>
@@ -53584,7 +53584,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.13060486316681</v>
+        <v>1.1306049823761</v>
       </c>
       <c r="H1835" t="n">
         <v>193872</v>
@@ -53613,7 +53613,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.13060486316681</v>
+        <v>1.1306049823761</v>
       </c>
       <c r="H1836" t="n">
         <v>91206</v>
@@ -53642,7 +53642,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.13060486316681</v>
+        <v>1.1306049823761</v>
       </c>
       <c r="H1837" t="n">
         <v>78241</v>
@@ -53700,7 +53700,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1839" t="n">
-        <v>1.15138804912567</v>
+        <v>1.15138816833496</v>
       </c>
       <c r="H1839" t="n">
         <v>104740</v>
@@ -53729,7 +53729,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.14723145961761</v>
+        <v>1.14723134040833</v>
       </c>
       <c r="H1840" t="n">
         <v>163124</v>
@@ -53816,7 +53816,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1843" t="n">
         <v>82942</v>
@@ -53932,7 +53932,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.17217123508453</v>
+        <v>1.17217111587524</v>
       </c>
       <c r="H1847" t="n">
         <v>41416</v>
@@ -80139,7 +80139,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="D2751" t="n">
-        <v>1.8639999628067</v>
+        <v>1.86600005626678</v>
       </c>
       <c r="E2751" t="n">
         <v>1.82200002670288</v>
@@ -80154,6 +80154,35 @@
         <v>81969</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>1.87600004673004</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>1.84399998188019</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>58932</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EDNR.MI.xlsx
+++ b/data/EDNR.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.485062211751938</v>
+        <v>0.485062181949615</v>
       </c>
       <c r="H2" t="n">
         <v>191859</v>
@@ -485,7 +485,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.481602430343628</v>
+        <v>0.481602370738983</v>
       </c>
       <c r="H4" t="n">
         <v>28934</v>
@@ -630,7 +630,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G9" t="n">
-        <v>0.483678340911865</v>
+        <v>0.48367840051651</v>
       </c>
       <c r="H9" t="n">
         <v>53793</v>
@@ -659,7 +659,7 @@
         <v>0.686999976634979</v>
       </c>
       <c r="G10" t="n">
-        <v>0.47537487745285</v>
+        <v>0.475374817848206</v>
       </c>
       <c r="H10" t="n">
         <v>133195</v>
@@ -688,7 +688,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G11" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H11" t="n">
         <v>328341</v>
@@ -717,7 +717,7 @@
         <v>0.667500019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>0.461881726980209</v>
+        <v>0.461881667375565</v>
       </c>
       <c r="H12" t="n">
         <v>473449</v>
@@ -775,7 +775,7 @@
         <v>0.647499978542328</v>
       </c>
       <c r="G14" t="n">
-        <v>0.448042511940002</v>
+        <v>0.44804248213768</v>
       </c>
       <c r="H14" t="n">
         <v>185010</v>
@@ -804,7 +804,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G15" t="n">
-        <v>0.460151731967926</v>
+        <v>0.460151791572571</v>
       </c>
       <c r="H15" t="n">
         <v>66901</v>
@@ -862,7 +862,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G17" t="n">
-        <v>0.467071354389191</v>
+        <v>0.467071384191513</v>
       </c>
       <c r="H17" t="n">
         <v>129282</v>
@@ -891,7 +891,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G18" t="n">
-        <v>0.47745069861412</v>
+        <v>0.477450728416443</v>
       </c>
       <c r="H18" t="n">
         <v>119370</v>
@@ -949,7 +949,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G20" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H20" t="n">
         <v>46550</v>
@@ -1007,7 +1007,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G22" t="n">
-        <v>0.471915066242218</v>
+        <v>0.471915006637573</v>
       </c>
       <c r="H22" t="n">
         <v>58624</v>
@@ -1036,7 +1036,7 @@
         <v>0.66049998998642</v>
       </c>
       <c r="G23" t="n">
-        <v>0.457037925720215</v>
+        <v>0.45703798532486</v>
       </c>
       <c r="H23" t="n">
         <v>70489</v>
@@ -1152,7 +1152,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G27" t="n">
-        <v>0.445620656013489</v>
+        <v>0.445620596408844</v>
       </c>
       <c r="H27" t="n">
         <v>128286</v>
@@ -1181,7 +1181,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G28" t="n">
-        <v>0.422786027193069</v>
+        <v>0.422786086797714</v>
       </c>
       <c r="H28" t="n">
         <v>174406</v>
@@ -1239,7 +1239,7 @@
         <v>0.614499986171722</v>
       </c>
       <c r="G30" t="n">
-        <v>0.425207942724228</v>
+        <v>0.425207912921906</v>
       </c>
       <c r="H30" t="n">
         <v>100995</v>
@@ -1297,7 +1297,7 @@
         <v>0.633000016212463</v>
       </c>
       <c r="G32" t="n">
-        <v>0.438009113073349</v>
+        <v>0.438009172677994</v>
       </c>
       <c r="H32" t="n">
         <v>72389</v>
@@ -1326,7 +1326,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G33" t="n">
-        <v>0.433165401220322</v>
+        <v>0.433165431022644</v>
       </c>
       <c r="H33" t="n">
         <v>214463</v>
@@ -1442,7 +1442,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G37" t="n">
-        <v>0.437317162752151</v>
+        <v>0.437317222356796</v>
       </c>
       <c r="H37" t="n">
         <v>59186</v>
@@ -1616,7 +1616,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G43" t="n">
-        <v>0.431089609861374</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H43" t="n">
         <v>51995</v>
@@ -1645,7 +1645,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G44" t="n">
-        <v>0.445620656013489</v>
+        <v>0.445620596408844</v>
       </c>
       <c r="H44" t="n">
         <v>148615</v>
@@ -1703,7 +1703,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>0.438701093196869</v>
+        <v>0.438701063394547</v>
       </c>
       <c r="H46" t="n">
         <v>177704</v>
@@ -1732,7 +1732,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G47" t="n">
-        <v>0.431089609861374</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H47" t="n">
         <v>26658</v>
@@ -1761,7 +1761,7 @@
         <v>0.623000025749207</v>
       </c>
       <c r="G48" t="n">
-        <v>0.431089609861374</v>
+        <v>0.431089580059052</v>
       </c>
       <c r="H48" t="n">
         <v>122811</v>
@@ -1790,7 +1790,7 @@
         <v>0.621500015258789</v>
       </c>
       <c r="G49" t="n">
-        <v>0.430051624774933</v>
+        <v>0.430051684379578</v>
       </c>
       <c r="H49" t="n">
         <v>65600</v>
@@ -1877,7 +1877,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G52" t="n">
-        <v>0.438701093196869</v>
+        <v>0.438701063394547</v>
       </c>
       <c r="H52" t="n">
         <v>99992</v>
@@ -1964,7 +1964,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G55" t="n">
-        <v>0.437317162752151</v>
+        <v>0.437317222356796</v>
       </c>
       <c r="H55" t="n">
         <v>76343</v>
@@ -2022,7 +2022,7 @@
         <v>0.631500005722046</v>
       </c>
       <c r="G57" t="n">
-        <v>0.436971187591553</v>
+        <v>0.436971217393875</v>
       </c>
       <c r="H57" t="n">
         <v>57158</v>
@@ -2051,7 +2051,7 @@
         <v>0.626500010490417</v>
       </c>
       <c r="G58" t="n">
-        <v>0.43351137638092</v>
+        <v>0.433511435985565</v>
       </c>
       <c r="H58" t="n">
         <v>68965</v>
@@ -2138,7 +2138,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G61" t="n">
-        <v>0.434549421072006</v>
+        <v>0.434549361467361</v>
       </c>
       <c r="H61" t="n">
         <v>91042</v>
@@ -2196,7 +2196,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G63" t="n">
-        <v>0.434549421072006</v>
+        <v>0.434549361467361</v>
       </c>
       <c r="H63" t="n">
         <v>33873</v>
@@ -2341,7 +2341,7 @@
         <v>0.611000001430511</v>
       </c>
       <c r="G68" t="n">
-        <v>0.422786027193069</v>
+        <v>0.422786086797714</v>
       </c>
       <c r="H68" t="n">
         <v>79242</v>
@@ -2573,7 +2573,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G76" t="n">
-        <v>0.456692039966583</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H76" t="n">
         <v>204695</v>
@@ -2631,7 +2631,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G78" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H78" t="n">
         <v>132097</v>
@@ -2660,7 +2660,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G79" t="n">
-        <v>0.482294410467148</v>
+        <v>0.482294470071793</v>
       </c>
       <c r="H79" t="n">
         <v>117083</v>
@@ -2718,7 +2718,7 @@
         <v>0.699000000953674</v>
       </c>
       <c r="G81" t="n">
-        <v>0.483678340911865</v>
+        <v>0.48367840051651</v>
       </c>
       <c r="H81" t="n">
         <v>129245</v>
@@ -2747,7 +2747,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>0.479180663824081</v>
+        <v>0.479180604219437</v>
       </c>
       <c r="H82" t="n">
         <v>29041</v>
@@ -2776,7 +2776,7 @@
         <v>0.683499991893768</v>
       </c>
       <c r="G83" t="n">
-        <v>0.472952961921692</v>
+        <v>0.472952991724014</v>
       </c>
       <c r="H83" t="n">
         <v>57129</v>
@@ -2805,7 +2805,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G84" t="n">
-        <v>0.463611543178558</v>
+        <v>0.463611602783203</v>
       </c>
       <c r="H84" t="n">
         <v>97915</v>
@@ -2863,7 +2863,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G86" t="n">
-        <v>0.446312606334686</v>
+        <v>0.446312636137009</v>
       </c>
       <c r="H86" t="n">
         <v>147100</v>
@@ -2892,7 +2892,7 @@
         <v>0.648500025272369</v>
       </c>
       <c r="G87" t="n">
-        <v>0.448734521865845</v>
+        <v>0.4487344622612</v>
       </c>
       <c r="H87" t="n">
         <v>20302</v>
@@ -2950,7 +2950,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G89" t="n">
-        <v>0.445620656013489</v>
+        <v>0.445620596408844</v>
       </c>
       <c r="H89" t="n">
         <v>81033</v>
@@ -3008,7 +3008,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G91" t="n">
-        <v>0.438701093196869</v>
+        <v>0.438701063394547</v>
       </c>
       <c r="H91" t="n">
         <v>29862</v>
@@ -3066,7 +3066,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G93" t="n">
-        <v>0.442852854728699</v>
+        <v>0.442852884531021</v>
       </c>
       <c r="H93" t="n">
         <v>137577</v>
@@ -3153,7 +3153,7 @@
         <v>0.647499978542328</v>
       </c>
       <c r="G96" t="n">
-        <v>0.448042511940002</v>
+        <v>0.44804248213768</v>
       </c>
       <c r="H96" t="n">
         <v>27367</v>
@@ -3182,7 +3182,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G97" t="n">
-        <v>0.442852854728699</v>
+        <v>0.442852884531021</v>
       </c>
       <c r="H97" t="n">
         <v>41726</v>
@@ -3211,7 +3211,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G98" t="n">
-        <v>0.442852854728699</v>
+        <v>0.442852884531021</v>
       </c>
       <c r="H98" t="n">
         <v>43674</v>
@@ -3298,7 +3298,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>0.44389083981514</v>
+        <v>0.443890780210495</v>
       </c>
       <c r="H101" t="n">
         <v>21942</v>
@@ -3385,7 +3385,7 @@
         <v>0.6875</v>
       </c>
       <c r="G104" t="n">
-        <v>0.475720822811127</v>
+        <v>0.475720852613449</v>
       </c>
       <c r="H104" t="n">
         <v>124171</v>
@@ -3472,7 +3472,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G107" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H107" t="n">
         <v>51910</v>
@@ -3501,7 +3501,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G108" t="n">
-        <v>0.479180663824081</v>
+        <v>0.479180604219437</v>
       </c>
       <c r="H108" t="n">
         <v>5363</v>
@@ -3559,7 +3559,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G110" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H110" t="n">
         <v>62146</v>
@@ -3588,7 +3588,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G111" t="n">
-        <v>0.47745069861412</v>
+        <v>0.477450728416443</v>
       </c>
       <c r="H111" t="n">
         <v>81596</v>
@@ -3617,7 +3617,7 @@
         <v>0.67849999666214</v>
       </c>
       <c r="G112" t="n">
-        <v>0.46949315071106</v>
+        <v>0.469493210315704</v>
       </c>
       <c r="H112" t="n">
         <v>80180</v>
@@ -3646,7 +3646,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G113" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H113" t="n">
         <v>77229</v>
@@ -3704,7 +3704,7 @@
         <v>0.641499996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>0.44389083981514</v>
+        <v>0.443890780210495</v>
       </c>
       <c r="H115" t="n">
         <v>154035</v>
@@ -3733,7 +3733,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G116" t="n">
-        <v>0.442852854728699</v>
+        <v>0.442852884531021</v>
       </c>
       <c r="H116" t="n">
         <v>203916</v>
@@ -3791,7 +3791,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G118" t="n">
-        <v>0.437317162752151</v>
+        <v>0.437317222356796</v>
       </c>
       <c r="H118" t="n">
         <v>37197</v>
@@ -3820,7 +3820,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G119" t="n">
-        <v>0.447004586458206</v>
+        <v>0.447004646062851</v>
       </c>
       <c r="H119" t="n">
         <v>21491</v>
@@ -3849,7 +3849,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G120" t="n">
-        <v>0.442852854728699</v>
+        <v>0.442852884531021</v>
       </c>
       <c r="H120" t="n">
         <v>89237</v>
@@ -3907,7 +3907,7 @@
         <v>0.644500017166138</v>
       </c>
       <c r="G122" t="n">
-        <v>0.44596666097641</v>
+        <v>0.445966690778732</v>
       </c>
       <c r="H122" t="n">
         <v>33393</v>
@@ -3965,7 +3965,7 @@
         <v>0.604499995708466</v>
       </c>
       <c r="G124" t="n">
-        <v>0.418288350105286</v>
+        <v>0.418288320302963</v>
       </c>
       <c r="H124" t="n">
         <v>486768</v>
@@ -3994,7 +3994,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G125" t="n">
-        <v>0.41932624578476</v>
+        <v>0.419326305389404</v>
       </c>
       <c r="H125" t="n">
         <v>164285</v>
@@ -4023,7 +4023,7 @@
         <v>0.630999982357025</v>
       </c>
       <c r="G126" t="n">
-        <v>0.436625182628632</v>
+        <v>0.436625242233276</v>
       </c>
       <c r="H126" t="n">
         <v>99483</v>
@@ -4052,7 +4052,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G127" t="n">
-        <v>0.442852854728699</v>
+        <v>0.442852884531021</v>
       </c>
       <c r="H127" t="n">
         <v>82500</v>
@@ -4110,7 +4110,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G129" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H129" t="n">
         <v>182844</v>
@@ -4197,7 +4197,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G132" t="n">
-        <v>0.438701093196869</v>
+        <v>0.438701063394547</v>
       </c>
       <c r="H132" t="n">
         <v>188187</v>
@@ -4226,7 +4226,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G133" t="n">
-        <v>0.442852854728699</v>
+        <v>0.442852884531021</v>
       </c>
       <c r="H133" t="n">
         <v>152250</v>
@@ -4342,7 +4342,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G137" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H137" t="n">
         <v>44437</v>
@@ -4400,7 +4400,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G139" t="n">
-        <v>0.476758807897568</v>
+        <v>0.476758748292923</v>
       </c>
       <c r="H139" t="n">
         <v>24754</v>
@@ -4429,7 +4429,7 @@
         <v>0.690500020980835</v>
       </c>
       <c r="G140" t="n">
-        <v>0.477796673774719</v>
+        <v>0.477796733379364</v>
       </c>
       <c r="H140" t="n">
         <v>71001</v>
@@ -4458,7 +4458,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G141" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H141" t="n">
         <v>80976</v>
@@ -4516,7 +4516,7 @@
         <v>0.689000010490417</v>
       </c>
       <c r="G143" t="n">
-        <v>0.476758807897568</v>
+        <v>0.476758748292923</v>
       </c>
       <c r="H143" t="n">
         <v>31703</v>
@@ -4545,7 +4545,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G144" t="n">
-        <v>0.463611543178558</v>
+        <v>0.463611602783203</v>
       </c>
       <c r="H144" t="n">
         <v>51317</v>
@@ -4574,7 +4574,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G145" t="n">
-        <v>0.467071354389191</v>
+        <v>0.467071384191513</v>
       </c>
       <c r="H145" t="n">
         <v>48503</v>
@@ -4632,7 +4632,7 @@
         <v>0.67849999666214</v>
       </c>
       <c r="G147" t="n">
-        <v>0.46949315071106</v>
+        <v>0.469493210315704</v>
       </c>
       <c r="H147" t="n">
         <v>51357</v>
@@ -4661,7 +4661,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G148" t="n">
-        <v>0.47745069861412</v>
+        <v>0.477450728416443</v>
       </c>
       <c r="H148" t="n">
         <v>324437</v>
@@ -4690,7 +4690,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G149" t="n">
-        <v>0.474682927131653</v>
+        <v>0.474682867527008</v>
       </c>
       <c r="H149" t="n">
         <v>70330</v>
@@ -4748,7 +4748,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G151" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H151" t="n">
         <v>33263</v>
@@ -4777,7 +4777,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G152" t="n">
-        <v>0.456692039966583</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H152" t="n">
         <v>55357</v>
@@ -4835,7 +4835,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G154" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H154" t="n">
         <v>28966</v>
@@ -4922,7 +4922,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G157" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H157" t="n">
         <v>185257</v>
@@ -4980,7 +4980,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G159" t="n">
-        <v>0.460497736930847</v>
+        <v>0.460497796535492</v>
       </c>
       <c r="H159" t="n">
         <v>12129</v>
@@ -5009,7 +5009,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G160" t="n">
-        <v>0.456692039966583</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H160" t="n">
         <v>36233</v>
@@ -5125,7 +5125,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G164" t="n">
-        <v>0.460151731967926</v>
+        <v>0.460151791572571</v>
       </c>
       <c r="H164" t="n">
         <v>39400</v>
@@ -5212,7 +5212,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G167" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H167" t="n">
         <v>30130</v>
@@ -5299,7 +5299,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G170" t="n">
-        <v>0.463611543178558</v>
+        <v>0.463611602783203</v>
       </c>
       <c r="H170" t="n">
         <v>58222</v>
@@ -5386,7 +5386,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G173" t="n">
-        <v>0.463611543178558</v>
+        <v>0.463611602783203</v>
       </c>
       <c r="H173" t="n">
         <v>25441</v>
@@ -5415,7 +5415,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G174" t="n">
-        <v>0.460497736930847</v>
+        <v>0.460497796535492</v>
       </c>
       <c r="H174" t="n">
         <v>28021</v>
@@ -5444,7 +5444,7 @@
         <v>0.67849999666214</v>
       </c>
       <c r="G175" t="n">
-        <v>0.46949315071106</v>
+        <v>0.469493210315704</v>
       </c>
       <c r="H175" t="n">
         <v>16908</v>
@@ -5473,7 +5473,7 @@
         <v>0.665499985218048</v>
       </c>
       <c r="G176" t="n">
-        <v>0.460497736930847</v>
+        <v>0.460497796535492</v>
       </c>
       <c r="H176" t="n">
         <v>54782</v>
@@ -5502,7 +5502,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G177" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H177" t="n">
         <v>71591</v>
@@ -5531,7 +5531,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G178" t="n">
-        <v>0.456692039966583</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H178" t="n">
         <v>143013</v>
@@ -5560,7 +5560,7 @@
         <v>0.658500015735626</v>
       </c>
       <c r="G179" t="n">
-        <v>0.455653995275497</v>
+        <v>0.455654054880142</v>
       </c>
       <c r="H179" t="n">
         <v>20378</v>
@@ -5647,7 +5647,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G182" t="n">
-        <v>0.456692039966583</v>
+        <v>0.456691980361938</v>
       </c>
       <c r="H182" t="n">
         <v>58262</v>
@@ -5705,7 +5705,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G184" t="n">
-        <v>0.447004586458206</v>
+        <v>0.447004646062851</v>
       </c>
       <c r="H184" t="n">
         <v>66988</v>
@@ -5734,7 +5734,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>0.446312606334686</v>
+        <v>0.446312636137009</v>
       </c>
       <c r="H185" t="n">
         <v>52383</v>
@@ -5763,7 +5763,7 @@
         <v>0.644999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>0.446312606334686</v>
+        <v>0.446312636137009</v>
       </c>
       <c r="H186" t="n">
         <v>75110</v>
@@ -5850,7 +5850,7 @@
         <v>0.666999995708466</v>
       </c>
       <c r="G189" t="n">
-        <v>0.461535722017288</v>
+        <v>0.461535662412643</v>
       </c>
       <c r="H189" t="n">
         <v>176240</v>
@@ -5879,7 +5879,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G190" t="n">
-        <v>0.464995414018631</v>
+        <v>0.464995473623276</v>
       </c>
       <c r="H190" t="n">
         <v>160048</v>
@@ -5966,7 +5966,7 @@
         <v>0.680999994277954</v>
       </c>
       <c r="G193" t="n">
-        <v>0.471223115921021</v>
+        <v>0.471223086118698</v>
       </c>
       <c r="H193" t="n">
         <v>122424</v>
@@ -6053,7 +6053,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G196" t="n">
-        <v>0.470531195402145</v>
+        <v>0.470531135797501</v>
       </c>
       <c r="H196" t="n">
         <v>98271</v>
@@ -6082,7 +6082,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G197" t="n">
-        <v>0.463611543178558</v>
+        <v>0.463611602783203</v>
       </c>
       <c r="H197" t="n">
         <v>99568</v>
@@ -6140,7 +6140,7 @@
         <v>0.67849999666214</v>
       </c>
       <c r="G199" t="n">
-        <v>0.46949315071106</v>
+        <v>0.469493210315704</v>
       </c>
       <c r="H199" t="n">
         <v>30898</v>
@@ -6169,7 +6169,7 @@
         <v>0.6875</v>
       </c>
       <c r="G200" t="n">
-        <v>0.475720822811127</v>
+        <v>0.475720852613449</v>
       </c>
       <c r="H200" t="n">
         <v>120951</v>
@@ -6198,7 +6198,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G201" t="n">
-        <v>0.482294410467148</v>
+        <v>0.482294470071793</v>
       </c>
       <c r="H201" t="n">
         <v>209149</v>
@@ -6227,7 +6227,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G202" t="n">
-        <v>0.48783004283905</v>
+        <v>0.487830072641373</v>
       </c>
       <c r="H202" t="n">
         <v>469900</v>
@@ -6256,7 +6256,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G203" t="n">
-        <v>0.498555481433868</v>
+        <v>0.498555421829224</v>
       </c>
       <c r="H203" t="n">
         <v>121289</v>
@@ -6314,7 +6314,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G205" t="n">
-        <v>0.493019759654999</v>
+        <v>0.493019700050354</v>
       </c>
       <c r="H205" t="n">
         <v>36091</v>
@@ -6575,7 +6575,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G214" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H214" t="n">
         <v>26428</v>
@@ -6691,7 +6691,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G218" t="n">
-        <v>0.491289883852005</v>
+        <v>0.49128982424736</v>
       </c>
       <c r="H218" t="n">
         <v>56648</v>
@@ -6749,7 +6749,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G220" t="n">
-        <v>0.499247401952744</v>
+        <v>0.499247372150421</v>
       </c>
       <c r="H220" t="n">
         <v>33506</v>
@@ -6778,7 +6778,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G221" t="n">
-        <v>0.495441615581512</v>
+        <v>0.49544158577919</v>
       </c>
       <c r="H221" t="n">
         <v>150686</v>
@@ -6807,7 +6807,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G222" t="n">
-        <v>0.491289883852005</v>
+        <v>0.49128982424736</v>
       </c>
       <c r="H222" t="n">
         <v>140896</v>
@@ -6836,7 +6836,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G223" t="n">
-        <v>0.491289883852005</v>
+        <v>0.49128982424736</v>
       </c>
       <c r="H223" t="n">
         <v>73200</v>
@@ -6894,7 +6894,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G225" t="n">
-        <v>0.491289883852005</v>
+        <v>0.49128982424736</v>
       </c>
       <c r="H225" t="n">
         <v>52932</v>
@@ -6923,7 +6923,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G226" t="n">
-        <v>0.495441615581512</v>
+        <v>0.49544158577919</v>
       </c>
       <c r="H226" t="n">
         <v>79074</v>
@@ -6981,7 +6981,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G228" t="n">
-        <v>0.491981834173203</v>
+        <v>0.491981774568558</v>
       </c>
       <c r="H228" t="n">
         <v>257048</v>
@@ -7039,7 +7039,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G230" t="n">
-        <v>0.48575422167778</v>
+        <v>0.485754251480103</v>
       </c>
       <c r="H230" t="n">
         <v>149866</v>
@@ -7068,7 +7068,7 @@
         <v>0.712499976158142</v>
       </c>
       <c r="G231" t="n">
-        <v>0.493019759654999</v>
+        <v>0.493019700050354</v>
       </c>
       <c r="H231" t="n">
         <v>140299</v>
@@ -7213,7 +7213,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G236" t="n">
-        <v>0.492673814296722</v>
+        <v>0.492673873901367</v>
       </c>
       <c r="H236" t="n">
         <v>271535</v>
@@ -7242,7 +7242,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G237" t="n">
-        <v>0.492673814296722</v>
+        <v>0.492673873901367</v>
       </c>
       <c r="H237" t="n">
         <v>16612</v>
@@ -7271,7 +7271,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G238" t="n">
-        <v>0.491289883852005</v>
+        <v>0.49128982424736</v>
       </c>
       <c r="H238" t="n">
         <v>43905</v>
@@ -7300,7 +7300,7 @@
         <v>0.711000025272369</v>
       </c>
       <c r="G239" t="n">
-        <v>0.491981834173203</v>
+        <v>0.491981774568558</v>
       </c>
       <c r="H239" t="n">
         <v>23384</v>
@@ -7561,7 +7561,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G248" t="n">
-        <v>0.529347598552704</v>
+        <v>0.529347538948059</v>
       </c>
       <c r="H248" t="n">
         <v>1097273</v>
@@ -7648,7 +7648,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G251" t="n">
-        <v>0.511356711387634</v>
+        <v>0.51135665178299</v>
       </c>
       <c r="H251" t="n">
         <v>428592</v>
@@ -7677,7 +7677,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G252" t="n">
-        <v>0.511356711387634</v>
+        <v>0.51135665178299</v>
       </c>
       <c r="H252" t="n">
         <v>277440</v>
@@ -7764,7 +7764,7 @@
         <v>0.75</v>
       </c>
       <c r="G255" t="n">
-        <v>0.518968105316162</v>
+        <v>0.518968164920807</v>
       </c>
       <c r="H255" t="n">
         <v>190032</v>
@@ -7880,7 +7880,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>0.53938090801239</v>
+        <v>0.539380848407745</v>
       </c>
       <c r="H259" t="n">
         <v>357651</v>
@@ -7909,7 +7909,7 @@
         <v>0.773000001907349</v>
       </c>
       <c r="G260" t="n">
-        <v>0.534883201122284</v>
+        <v>0.534883141517639</v>
       </c>
       <c r="H260" t="n">
         <v>183482</v>
@@ -7938,7 +7938,7 @@
         <v>0.786499977111816</v>
       </c>
       <c r="G261" t="n">
-        <v>0.544224619865417</v>
+        <v>0.544224560260773</v>
       </c>
       <c r="H261" t="n">
         <v>626780</v>
@@ -7996,7 +7996,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G263" t="n">
-        <v>0.531423449516296</v>
+        <v>0.531423389911652</v>
       </c>
       <c r="H263" t="n">
         <v>280499</v>
@@ -8141,7 +8141,7 @@
         <v>0.780499994754791</v>
       </c>
       <c r="G268" t="n">
-        <v>0.540072917938232</v>
+        <v>0.540072858333588</v>
       </c>
       <c r="H268" t="n">
         <v>230939</v>
@@ -8199,7 +8199,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G270" t="n">
-        <v>0.540418863296509</v>
+        <v>0.540418922901154</v>
       </c>
       <c r="H270" t="n">
         <v>35906</v>
@@ -8286,7 +8286,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G273" t="n">
-        <v>0.540418863296509</v>
+        <v>0.540418922901154</v>
       </c>
       <c r="H273" t="n">
         <v>139226</v>
@@ -8344,7 +8344,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>0.53938090801239</v>
+        <v>0.539380848407745</v>
       </c>
       <c r="H275" t="n">
         <v>94758</v>
@@ -8373,7 +8373,7 @@
         <v>0.781000018119812</v>
       </c>
       <c r="G276" t="n">
-        <v>0.540418863296509</v>
+        <v>0.540418922901154</v>
       </c>
       <c r="H276" t="n">
         <v>80710</v>
@@ -8402,7 +8402,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G277" t="n">
-        <v>0.538689017295837</v>
+        <v>0.538688957691193</v>
       </c>
       <c r="H277" t="n">
         <v>76279</v>
@@ -8982,7 +8982,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G297" t="n">
-        <v>0.511356711387634</v>
+        <v>0.51135665178299</v>
       </c>
       <c r="H297" t="n">
         <v>189797</v>
@@ -9040,7 +9040,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G299" t="n">
-        <v>0.524503886699677</v>
+        <v>0.524503827095032</v>
       </c>
       <c r="H299" t="n">
         <v>291053</v>
@@ -9185,7 +9185,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G304" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H304" t="n">
         <v>67866</v>
@@ -9417,7 +9417,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G312" t="n">
-        <v>0.505474984645844</v>
+        <v>0.505475044250488</v>
       </c>
       <c r="H312" t="n">
         <v>231484</v>
@@ -9475,7 +9475,7 @@
         <v>0.737500011920929</v>
       </c>
       <c r="G314" t="n">
-        <v>0.510318696498871</v>
+        <v>0.510318756103516</v>
       </c>
       <c r="H314" t="n">
         <v>65146</v>
@@ -9533,7 +9533,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G316" t="n">
-        <v>0.50582093000412</v>
+        <v>0.505820989608765</v>
       </c>
       <c r="H316" t="n">
         <v>38462</v>
@@ -9591,7 +9591,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G318" t="n">
-        <v>0.507896840572357</v>
+        <v>0.507896900177002</v>
       </c>
       <c r="H318" t="n">
         <v>156057</v>
@@ -9765,7 +9765,7 @@
         <v>0.737500011920929</v>
       </c>
       <c r="G324" t="n">
-        <v>0.510318696498871</v>
+        <v>0.510318756103516</v>
       </c>
       <c r="H324" t="n">
         <v>37689</v>
@@ -9881,7 +9881,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G328" t="n">
-        <v>0.50582093000412</v>
+        <v>0.505820989608765</v>
       </c>
       <c r="H328" t="n">
         <v>104030</v>
@@ -9910,7 +9910,7 @@
         <v>0.730499982833862</v>
       </c>
       <c r="G329" t="n">
-        <v>0.505474984645844</v>
+        <v>0.505475044250488</v>
       </c>
       <c r="H329" t="n">
         <v>80896</v>
@@ -9968,7 +9968,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G331" t="n">
-        <v>0.507896840572357</v>
+        <v>0.507896900177002</v>
       </c>
       <c r="H331" t="n">
         <v>177163</v>
@@ -10026,7 +10026,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G333" t="n">
-        <v>0.498555481433868</v>
+        <v>0.498555421829224</v>
       </c>
       <c r="H333" t="n">
         <v>457777</v>
@@ -10055,7 +10055,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G334" t="n">
-        <v>0.499247401952744</v>
+        <v>0.499247372150421</v>
       </c>
       <c r="H334" t="n">
         <v>67876</v>
@@ -10142,7 +10142,7 @@
         <v>0.731000006198883</v>
       </c>
       <c r="G337" t="n">
-        <v>0.50582093000412</v>
+        <v>0.505820989608765</v>
       </c>
       <c r="H337" t="n">
         <v>99133</v>
@@ -10258,7 +10258,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G341" t="n">
-        <v>0.511702656745911</v>
+        <v>0.511702597141266</v>
       </c>
       <c r="H341" t="n">
         <v>282369</v>
@@ -10345,7 +10345,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G344" t="n">
-        <v>0.507896840572357</v>
+        <v>0.507896900177002</v>
       </c>
       <c r="H344" t="n">
         <v>119791</v>
@@ -10374,7 +10374,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G345" t="n">
-        <v>0.507896840572357</v>
+        <v>0.507896900177002</v>
       </c>
       <c r="H345" t="n">
         <v>167117</v>
@@ -10461,7 +10461,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G348" t="n">
-        <v>0.523119866847992</v>
+        <v>0.523119926452637</v>
       </c>
       <c r="H348" t="n">
         <v>810246</v>
@@ -10751,7 +10751,7 @@
         <v>0.742500007152557</v>
       </c>
       <c r="G358" t="n">
-        <v>0.513778448104858</v>
+        <v>0.513778507709503</v>
       </c>
       <c r="H358" t="n">
         <v>125302</v>
@@ -10780,7 +10780,7 @@
         <v>0.75</v>
       </c>
       <c r="G359" t="n">
-        <v>0.518968105316162</v>
+        <v>0.518968164920807</v>
       </c>
       <c r="H359" t="n">
         <v>262928</v>
@@ -10867,7 +10867,7 @@
         <v>0.760999977588654</v>
       </c>
       <c r="G362" t="n">
-        <v>0.526579678058624</v>
+        <v>0.526579737663269</v>
       </c>
       <c r="H362" t="n">
         <v>397546</v>
@@ -10954,7 +10954,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G365" t="n">
-        <v>0.532807290554047</v>
+        <v>0.532807350158691</v>
       </c>
       <c r="H365" t="n">
         <v>384026</v>
@@ -11273,7 +11273,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G376" t="n">
-        <v>0.57294088602066</v>
+        <v>0.572940826416016</v>
       </c>
       <c r="H376" t="n">
         <v>368824</v>
@@ -11418,7 +11418,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G381" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H381" t="n">
         <v>815667</v>
@@ -11447,7 +11447,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G382" t="n">
-        <v>0.640060722827911</v>
+        <v>0.640060782432556</v>
       </c>
       <c r="H382" t="n">
         <v>611757</v>
@@ -11592,7 +11592,7 @@
         <v>0.915499985218048</v>
       </c>
       <c r="G387" t="n">
-        <v>0.633487224578857</v>
+        <v>0.633487164974213</v>
       </c>
       <c r="H387" t="n">
         <v>347087</v>
@@ -11621,7 +11621,7 @@
         <v>0.916999995708466</v>
       </c>
       <c r="G388" t="n">
-        <v>0.634525120258331</v>
+        <v>0.634525060653687</v>
       </c>
       <c r="H388" t="n">
         <v>135604</v>
@@ -11766,7 +11766,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G393" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H393" t="n">
         <v>203449</v>
@@ -11853,7 +11853,7 @@
         <v>0.915499985218048</v>
       </c>
       <c r="G396" t="n">
-        <v>0.633487224578857</v>
+        <v>0.633487164974213</v>
       </c>
       <c r="H396" t="n">
         <v>82781</v>
@@ -11911,7 +11911,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G398" t="n">
-        <v>0.640060722827911</v>
+        <v>0.640060782432556</v>
       </c>
       <c r="H398" t="n">
         <v>127454</v>
@@ -12259,7 +12259,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G410" t="n">
-        <v>0.615150272846222</v>
+        <v>0.615150332450867</v>
       </c>
       <c r="H410" t="n">
         <v>168974</v>
@@ -12375,7 +12375,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G414" t="n">
-        <v>0.612036466598511</v>
+        <v>0.612036526203156</v>
       </c>
       <c r="H414" t="n">
         <v>199929</v>
@@ -12404,7 +12404,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G415" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H415" t="n">
         <v>41393</v>
@@ -12636,7 +12636,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G423" t="n">
-        <v>0.615150272846222</v>
+        <v>0.615150332450867</v>
       </c>
       <c r="H423" t="n">
         <v>102772</v>
@@ -12694,7 +12694,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>0.612382471561432</v>
+        <v>0.612382411956787</v>
       </c>
       <c r="H425" t="n">
         <v>113618</v>
@@ -12781,7 +12781,7 @@
         <v>0.891499996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>0.616880118846893</v>
+        <v>0.616880178451538</v>
       </c>
       <c r="H428" t="n">
         <v>79302</v>
@@ -12868,7 +12868,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G431" t="n">
-        <v>0.612036466598511</v>
+        <v>0.612036526203156</v>
       </c>
       <c r="H431" t="n">
         <v>101366</v>
@@ -12926,7 +12926,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G433" t="n">
-        <v>0.612382471561432</v>
+        <v>0.612382411956787</v>
       </c>
       <c r="H433" t="n">
         <v>94241</v>
@@ -12955,7 +12955,7 @@
         <v>0.884999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>0.612382471561432</v>
+        <v>0.612382411956787</v>
       </c>
       <c r="H434" t="n">
         <v>63978</v>
@@ -12984,7 +12984,7 @@
         <v>0.884500026702881</v>
       </c>
       <c r="G435" t="n">
-        <v>0.612036466598511</v>
+        <v>0.612036526203156</v>
       </c>
       <c r="H435" t="n">
         <v>112829</v>
@@ -13100,7 +13100,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G439" t="n">
-        <v>0.615150272846222</v>
+        <v>0.615150332450867</v>
       </c>
       <c r="H439" t="n">
         <v>140694</v>
@@ -13216,7 +13216,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G443" t="n">
-        <v>0.636254966259003</v>
+        <v>0.636255025863647</v>
       </c>
       <c r="H443" t="n">
         <v>655108</v>
@@ -13303,7 +13303,7 @@
         <v>0.921500027179718</v>
       </c>
       <c r="G446" t="n">
-        <v>0.637638866901398</v>
+        <v>0.637638926506042</v>
       </c>
       <c r="H446" t="n">
         <v>142109</v>
@@ -13361,7 +13361,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G448" t="n">
-        <v>0.636254966259003</v>
+        <v>0.636255025863647</v>
       </c>
       <c r="H448" t="n">
         <v>240947</v>
@@ -13506,7 +13506,7 @@
         <v>0.934499979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>0.64663428068161</v>
+        <v>0.646634340286255</v>
       </c>
       <c r="H453" t="n">
         <v>146365</v>
@@ -13622,7 +13622,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G457" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H457" t="n">
         <v>684112</v>
@@ -13651,7 +13651,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G458" t="n">
-        <v>0.700260996818542</v>
+        <v>0.700261056423187</v>
       </c>
       <c r="H458" t="n">
         <v>762804</v>
@@ -13680,7 +13680,7 @@
         <v>1.00300002098083</v>
       </c>
       <c r="G459" t="n">
-        <v>0.694033443927765</v>
+        <v>0.69403338432312</v>
       </c>
       <c r="H459" t="n">
         <v>324236</v>
@@ -13709,7 +13709,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G460" t="n">
-        <v>0.708564579486847</v>
+        <v>0.708564519882202</v>
       </c>
       <c r="H460" t="n">
         <v>939858</v>
@@ -13738,7 +13738,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G461" t="n">
-        <v>0.715484201908112</v>
+        <v>0.715484142303467</v>
       </c>
       <c r="H461" t="n">
         <v>727657</v>
@@ -13767,7 +13767,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G462" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H462" t="n">
         <v>739518</v>
@@ -13796,7 +13796,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G463" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H463" t="n">
         <v>373948</v>
@@ -13941,7 +13941,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G468" t="n">
-        <v>0.688497841358185</v>
+        <v>0.68849778175354</v>
       </c>
       <c r="H468" t="n">
         <v>633728</v>
@@ -14086,7 +14086,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G473" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H473" t="n">
         <v>79950</v>
@@ -14144,7 +14144,7 @@
         <v>1.00899994373322</v>
       </c>
       <c r="G475" t="n">
-        <v>0.698185205459595</v>
+        <v>0.69818514585495</v>
       </c>
       <c r="H475" t="n">
         <v>330294</v>
@@ -14173,7 +14173,7 @@
         <v>0.970499992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>0.671544790267944</v>
+        <v>0.671544849872589</v>
       </c>
       <c r="H476" t="n">
         <v>1137121</v>
@@ -14231,7 +14231,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>0.678118407726288</v>
+        <v>0.678118467330933</v>
       </c>
       <c r="H478" t="n">
         <v>300513</v>
@@ -14289,7 +14289,7 @@
         <v>0.972500026226044</v>
       </c>
       <c r="G480" t="n">
-        <v>0.672928690910339</v>
+        <v>0.672928750514984</v>
       </c>
       <c r="H480" t="n">
         <v>75909</v>
@@ -14347,7 +14347,7 @@
         <v>0.935500025749207</v>
       </c>
       <c r="G482" t="n">
-        <v>0.647326350212097</v>
+        <v>0.647326290607452</v>
       </c>
       <c r="H482" t="n">
         <v>210242</v>
@@ -14521,7 +14521,7 @@
         <v>0.966499984264374</v>
       </c>
       <c r="G488" t="n">
-        <v>0.66877692937851</v>
+        <v>0.668776988983154</v>
       </c>
       <c r="H488" t="n">
         <v>98374</v>
@@ -14550,7 +14550,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G489" t="n">
-        <v>0.67050689458847</v>
+        <v>0.670506834983826</v>
       </c>
       <c r="H489" t="n">
         <v>212997</v>
@@ -14608,7 +14608,7 @@
         <v>0.961000025272369</v>
       </c>
       <c r="G491" t="n">
-        <v>0.664971232414246</v>
+        <v>0.66497129201889</v>
       </c>
       <c r="H491" t="n">
         <v>248336</v>
@@ -14695,7 +14695,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G494" t="n">
-        <v>0.67742645740509</v>
+        <v>0.677426397800446</v>
       </c>
       <c r="H494" t="n">
         <v>166163</v>
@@ -14753,7 +14753,7 @@
         <v>0.976999998092651</v>
       </c>
       <c r="G496" t="n">
-        <v>0.676042556762695</v>
+        <v>0.676042497158051</v>
       </c>
       <c r="H496" t="n">
         <v>299253</v>
@@ -14782,7 +14782,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G497" t="n">
-        <v>0.679156422615051</v>
+        <v>0.679156363010406</v>
       </c>
       <c r="H497" t="n">
         <v>117054</v>
@@ -14840,7 +14840,7 @@
         <v>0.990499973297119</v>
       </c>
       <c r="G499" t="n">
-        <v>0.685383975505829</v>
+        <v>0.685383915901184</v>
       </c>
       <c r="H499" t="n">
         <v>219371</v>
@@ -14898,7 +14898,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G501" t="n">
-        <v>0.688497841358185</v>
+        <v>0.68849778175354</v>
       </c>
       <c r="H501" t="n">
         <v>294181</v>
@@ -15014,7 +15014,7 @@
         <v>0.999499976634979</v>
       </c>
       <c r="G505" t="n">
-        <v>0.691611528396606</v>
+        <v>0.691611588001251</v>
       </c>
       <c r="H505" t="n">
         <v>151127</v>
@@ -15043,7 +15043,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G506" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H506" t="n">
         <v>140023</v>
@@ -15072,7 +15072,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G507" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H507" t="n">
         <v>93279</v>
@@ -15101,7 +15101,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G508" t="n">
-        <v>0.6746586561203</v>
+        <v>0.674658715724945</v>
       </c>
       <c r="H508" t="n">
         <v>240363</v>
@@ -15130,7 +15130,7 @@
         <v>0.940500020980835</v>
       </c>
       <c r="G509" t="n">
-        <v>0.650786101818085</v>
+        <v>0.65078604221344</v>
       </c>
       <c r="H509" t="n">
         <v>972119</v>
@@ -15188,7 +15188,7 @@
         <v>0.949000000953674</v>
       </c>
       <c r="G511" t="n">
-        <v>0.656667768955231</v>
+        <v>0.656667709350586</v>
       </c>
       <c r="H511" t="n">
         <v>126002</v>
@@ -15246,7 +15246,7 @@
         <v>1</v>
       </c>
       <c r="G513" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H513" t="n">
         <v>250337</v>
@@ -15304,7 +15304,7 @@
         <v>1</v>
       </c>
       <c r="G515" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H515" t="n">
         <v>228631</v>
@@ -15333,7 +15333,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G516" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H516" t="n">
         <v>241960</v>
@@ -15449,7 +15449,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G520" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H520" t="n">
         <v>103679</v>
@@ -15594,7 +15594,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H525" t="n">
         <v>271747</v>
@@ -15623,7 +15623,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G526" t="n">
-        <v>0.679502308368683</v>
+        <v>0.679502367973328</v>
       </c>
       <c r="H526" t="n">
         <v>487693</v>
@@ -15652,7 +15652,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G527" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H527" t="n">
         <v>364335</v>
@@ -15710,7 +15710,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H529" t="n">
         <v>250609</v>
@@ -15739,7 +15739,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G530" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H530" t="n">
         <v>250612</v>
@@ -15768,7 +15768,7 @@
         <v>1</v>
       </c>
       <c r="G531" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H531" t="n">
         <v>82371</v>
@@ -15797,7 +15797,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G532" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H532" t="n">
         <v>107041</v>
@@ -15884,7 +15884,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G535" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H535" t="n">
         <v>255484</v>
@@ -15971,7 +15971,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G538" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H538" t="n">
         <v>233300</v>
@@ -16029,7 +16029,7 @@
         <v>1</v>
       </c>
       <c r="G540" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H540" t="n">
         <v>141144</v>
@@ -16058,7 +16058,7 @@
         <v>1</v>
       </c>
       <c r="G541" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H541" t="n">
         <v>391068</v>
@@ -16087,7 +16087,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G542" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H542" t="n">
         <v>191039</v>
@@ -16145,7 +16145,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G544" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H544" t="n">
         <v>451706</v>
@@ -16174,7 +16174,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G545" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H545" t="n">
         <v>390066</v>
@@ -16261,7 +16261,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>0.678118407726288</v>
+        <v>0.678118467330933</v>
       </c>
       <c r="H548" t="n">
         <v>167644</v>
@@ -16319,7 +16319,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G550" t="n">
-        <v>0.679502308368683</v>
+        <v>0.679502367973328</v>
       </c>
       <c r="H550" t="n">
         <v>91476</v>
@@ -16609,7 +16609,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G560" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H560" t="n">
         <v>573364</v>
@@ -16725,7 +16725,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G564" t="n">
-        <v>0.658743619918823</v>
+        <v>0.658743560314178</v>
       </c>
       <c r="H564" t="n">
         <v>15093</v>
@@ -16841,7 +16841,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G568" t="n">
-        <v>0.658743619918823</v>
+        <v>0.658743560314178</v>
       </c>
       <c r="H568" t="n">
         <v>117894</v>
@@ -17421,7 +17421,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G588" t="n">
-        <v>0.658743619918823</v>
+        <v>0.658743560314178</v>
       </c>
       <c r="H588" t="n">
         <v>203718</v>
@@ -18204,7 +18204,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G615" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H615" t="n">
         <v>85130</v>
@@ -18233,7 +18233,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G616" t="n">
-        <v>0.637984931468964</v>
+        <v>0.637984812259674</v>
       </c>
       <c r="H616" t="n">
         <v>171272</v>
@@ -18378,7 +18378,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G621" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H621" t="n">
         <v>60308</v>
@@ -18407,7 +18407,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G622" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H622" t="n">
         <v>52692</v>
@@ -18465,7 +18465,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G624" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H624" t="n">
         <v>32330</v>
@@ -18494,7 +18494,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G625" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H625" t="n">
         <v>12284</v>
@@ -18552,7 +18552,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G627" t="n">
-        <v>0.637984931468964</v>
+        <v>0.637984812259674</v>
       </c>
       <c r="H627" t="n">
         <v>47560</v>
@@ -18581,7 +18581,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G628" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H628" t="n">
         <v>115538</v>
@@ -18726,7 +18726,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G633" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H633" t="n">
         <v>189736</v>
@@ -18755,7 +18755,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G634" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H634" t="n">
         <v>108287</v>
@@ -18813,7 +18813,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G636" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H636" t="n">
         <v>391421</v>
@@ -18842,7 +18842,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G637" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H637" t="n">
         <v>158068</v>
@@ -18900,7 +18900,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G639" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H639" t="n">
         <v>154143</v>
@@ -18929,7 +18929,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G640" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H640" t="n">
         <v>131453</v>
@@ -18987,7 +18987,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G642" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H642" t="n">
         <v>45923</v>
@@ -19741,7 +19741,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H668" t="n">
         <v>20241</v>
@@ -19770,7 +19770,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G669" t="n">
-        <v>0.658743619918823</v>
+        <v>0.658743560314178</v>
       </c>
       <c r="H669" t="n">
         <v>108004</v>
@@ -19828,7 +19828,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G671" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H671" t="n">
         <v>427711</v>
@@ -20089,7 +20089,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H680" t="n">
         <v>116691</v>
@@ -20147,7 +20147,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G682" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H682" t="n">
         <v>73730</v>
@@ -20176,7 +20176,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G683" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H683" t="n">
         <v>74130</v>
@@ -20263,7 +20263,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G686" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H686" t="n">
         <v>11821</v>
@@ -20292,7 +20292,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G687" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H687" t="n">
         <v>31036</v>
@@ -20321,7 +20321,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H688" t="n">
         <v>196163</v>
@@ -20379,7 +20379,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H690" t="n">
         <v>47347</v>
@@ -20408,7 +20408,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G691" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H691" t="n">
         <v>54618</v>
@@ -20582,7 +20582,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G697" t="n">
-        <v>0.658743619918823</v>
+        <v>0.658743560314178</v>
       </c>
       <c r="H697" t="n">
         <v>49045</v>
@@ -20727,7 +20727,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G702" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H702" t="n">
         <v>197152</v>
@@ -20785,7 +20785,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G704" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H704" t="n">
         <v>46772</v>
@@ -20814,7 +20814,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H705" t="n">
         <v>28672</v>
@@ -20901,7 +20901,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G708" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H708" t="n">
         <v>98837</v>
@@ -20959,7 +20959,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H710" t="n">
         <v>151533</v>
@@ -20988,7 +20988,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G711" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H711" t="n">
         <v>61229</v>
@@ -21075,7 +21075,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G714" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H714" t="n">
         <v>52549</v>
@@ -21162,7 +21162,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G717" t="n">
-        <v>0.629681468009949</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H717" t="n">
         <v>89967</v>
@@ -21539,7 +21539,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G730" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H730" t="n">
         <v>80663</v>
@@ -21597,7 +21597,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G732" t="n">
-        <v>0.637984931468964</v>
+        <v>0.637984812259674</v>
       </c>
       <c r="H732" t="n">
         <v>8772</v>
@@ -21655,7 +21655,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G734" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H734" t="n">
         <v>53744</v>
@@ -21684,7 +21684,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G735" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H735" t="n">
         <v>46948</v>
@@ -21713,7 +21713,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G736" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H736" t="n">
         <v>54341</v>
@@ -21800,7 +21800,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H739" t="n">
         <v>63280</v>
@@ -21829,7 +21829,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G740" t="n">
-        <v>0.629681468009949</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H740" t="n">
         <v>48907</v>
@@ -21916,7 +21916,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G743" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H743" t="n">
         <v>59135</v>
@@ -21974,7 +21974,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G745" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H745" t="n">
         <v>306199</v>
@@ -22003,7 +22003,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G746" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H746" t="n">
         <v>138545</v>
@@ -22148,7 +22148,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G751" t="n">
-        <v>0.658743619918823</v>
+        <v>0.658743560314178</v>
       </c>
       <c r="H751" t="n">
         <v>236602</v>
@@ -22206,7 +22206,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G753" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H753" t="n">
         <v>52006</v>
@@ -22844,7 +22844,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>0.678118407726288</v>
+        <v>0.678118467330933</v>
       </c>
       <c r="H775" t="n">
         <v>359900</v>
@@ -22873,7 +22873,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H776" t="n">
         <v>210137</v>
@@ -22902,7 +22902,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G777" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H777" t="n">
         <v>174998</v>
@@ -22931,7 +22931,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G778" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H778" t="n">
         <v>275985</v>
@@ -23192,7 +23192,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H787" t="n">
         <v>82370</v>
@@ -23221,7 +23221,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G788" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H788" t="n">
         <v>145075</v>
@@ -23395,7 +23395,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G794" t="n">
-        <v>0.733475029468536</v>
+        <v>0.733474969863892</v>
       </c>
       <c r="H794" t="n">
         <v>353515</v>
@@ -23424,7 +23424,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G795" t="n">
-        <v>0.733475029468536</v>
+        <v>0.733474969863892</v>
       </c>
       <c r="H795" t="n">
         <v>349231</v>
@@ -23482,7 +23482,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H797" t="n">
         <v>3149209</v>
@@ -23569,7 +23569,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G800" t="n">
-        <v>0.678118407726288</v>
+        <v>0.678118467330933</v>
       </c>
       <c r="H800" t="n">
         <v>325657</v>
@@ -23598,7 +23598,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>0.679502308368683</v>
+        <v>0.679502367973328</v>
       </c>
       <c r="H801" t="n">
         <v>319507</v>
@@ -23627,7 +23627,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G802" t="n">
-        <v>0.679502308368683</v>
+        <v>0.679502367973328</v>
       </c>
       <c r="H802" t="n">
         <v>520584</v>
@@ -23656,7 +23656,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G803" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H803" t="n">
         <v>211249</v>
@@ -23714,7 +23714,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G805" t="n">
-        <v>0.679502308368683</v>
+        <v>0.679502367973328</v>
       </c>
       <c r="H805" t="n">
         <v>435328</v>
@@ -23743,7 +23743,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G806" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H806" t="n">
         <v>320023</v>
@@ -23772,7 +23772,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>0.679502308368683</v>
+        <v>0.679502367973328</v>
       </c>
       <c r="H807" t="n">
         <v>392161</v>
@@ -23801,7 +23801,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G808" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H808" t="n">
         <v>226093</v>
@@ -23830,7 +23830,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G809" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H809" t="n">
         <v>208609</v>
@@ -23859,7 +23859,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G810" t="n">
-        <v>0.678118407726288</v>
+        <v>0.678118467330933</v>
       </c>
       <c r="H810" t="n">
         <v>525234</v>
@@ -23917,7 +23917,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G812" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H812" t="n">
         <v>436802</v>
@@ -23946,7 +23946,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G813" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H813" t="n">
         <v>175222</v>
@@ -24004,7 +24004,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G815" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H815" t="n">
         <v>305887</v>
@@ -24091,7 +24091,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G818" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H818" t="n">
         <v>277155</v>
@@ -24149,7 +24149,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G820" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H820" t="n">
         <v>65351</v>
@@ -24236,7 +24236,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G823" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H823" t="n">
         <v>104698</v>
@@ -24265,7 +24265,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G824" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H824" t="n">
         <v>77471</v>
@@ -24294,7 +24294,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G825" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H825" t="n">
         <v>85392</v>
@@ -24323,7 +24323,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G826" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H826" t="n">
         <v>122721</v>
@@ -24352,7 +24352,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G827" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H827" t="n">
         <v>136318</v>
@@ -24410,7 +24410,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G829" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H829" t="n">
         <v>193723</v>
@@ -24439,7 +24439,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G830" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H830" t="n">
         <v>511380</v>
@@ -24468,7 +24468,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G831" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H831" t="n">
         <v>403805</v>
@@ -24526,7 +24526,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G833" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H833" t="n">
         <v>500408</v>
@@ -24642,7 +24642,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G837" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H837" t="n">
         <v>311717</v>
@@ -24700,7 +24700,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G839" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H839" t="n">
         <v>261587</v>
@@ -24758,7 +24758,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G841" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H841" t="n">
         <v>153205</v>
@@ -24787,7 +24787,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G842" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H842" t="n">
         <v>105509</v>
@@ -24845,7 +24845,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G844" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H844" t="n">
         <v>80388</v>
@@ -24874,7 +24874,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G845" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H845" t="n">
         <v>128303</v>
@@ -24903,7 +24903,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G846" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H846" t="n">
         <v>52402</v>
@@ -24932,7 +24932,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G847" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H847" t="n">
         <v>61956</v>
@@ -24961,7 +24961,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G848" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H848" t="n">
         <v>73636</v>
@@ -25019,7 +25019,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G850" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H850" t="n">
         <v>114935</v>
@@ -25048,7 +25048,7 @@
         <v>1</v>
       </c>
       <c r="G851" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H851" t="n">
         <v>147121</v>
@@ -25077,7 +25077,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G852" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H852" t="n">
         <v>244060</v>
@@ -25106,7 +25106,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G853" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H853" t="n">
         <v>275627</v>
@@ -25135,7 +25135,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G854" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H854" t="n">
         <v>124964</v>
@@ -25164,7 +25164,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G855" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H855" t="n">
         <v>372391</v>
@@ -25193,7 +25193,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G856" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H856" t="n">
         <v>90403</v>
@@ -25338,7 +25338,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H861" t="n">
         <v>216088</v>
@@ -25396,7 +25396,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G863" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H863" t="n">
         <v>99861</v>
@@ -25512,7 +25512,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G867" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H867" t="n">
         <v>13841</v>
@@ -25541,7 +25541,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G868" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H868" t="n">
         <v>40045</v>
@@ -25599,7 +25599,7 @@
         <v>1</v>
       </c>
       <c r="G870" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H870" t="n">
         <v>187220</v>
@@ -25628,7 +25628,7 @@
         <v>1</v>
       </c>
       <c r="G871" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H871" t="n">
         <v>143153</v>
@@ -25715,7 +25715,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H874" t="n">
         <v>84308</v>
@@ -25831,7 +25831,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G878" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H878" t="n">
         <v>305495</v>
@@ -25860,7 +25860,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G879" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H879" t="n">
         <v>134656</v>
@@ -25889,7 +25889,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G880" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H880" t="n">
         <v>295035</v>
@@ -25947,7 +25947,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G882" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H882" t="n">
         <v>185348</v>
@@ -25976,7 +25976,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G883" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H883" t="n">
         <v>68756</v>
@@ -26208,7 +26208,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H891" t="n">
         <v>238771</v>
@@ -26237,7 +26237,7 @@
         <v>1</v>
       </c>
       <c r="G892" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H892" t="n">
         <v>1088893</v>
@@ -26266,7 +26266,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G893" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H893" t="n">
         <v>212453</v>
@@ -26353,7 +26353,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H896" t="n">
         <v>73030</v>
@@ -26440,7 +26440,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G899" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H899" t="n">
         <v>32697</v>
@@ -26846,7 +26846,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G913" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H913" t="n">
         <v>97295</v>
@@ -26991,7 +26991,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G918" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H918" t="n">
         <v>246514</v>
@@ -27194,7 +27194,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G925" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H925" t="n">
         <v>69631</v>
@@ -27252,7 +27252,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G927" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H927" t="n">
         <v>1097</v>
@@ -27281,7 +27281,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G928" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H928" t="n">
         <v>16208</v>
@@ -27339,7 +27339,7 @@
         <v>1</v>
       </c>
       <c r="G930" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H930" t="n">
         <v>145435</v>
@@ -27368,7 +27368,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G931" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H931" t="n">
         <v>42869</v>
@@ -27426,7 +27426,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G933" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H933" t="n">
         <v>15766</v>
@@ -27455,7 +27455,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H934" t="n">
         <v>81656</v>
@@ -27542,7 +27542,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G937" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H937" t="n">
         <v>21775</v>
@@ -27571,7 +27571,7 @@
         <v>1</v>
       </c>
       <c r="G938" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H938" t="n">
         <v>153375</v>
@@ -27600,7 +27600,7 @@
         <v>1</v>
       </c>
       <c r="G939" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H939" t="n">
         <v>69959</v>
@@ -27629,7 +27629,7 @@
         <v>1</v>
       </c>
       <c r="G940" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H940" t="n">
         <v>26335</v>
@@ -27658,7 +27658,7 @@
         <v>1</v>
       </c>
       <c r="G941" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H941" t="n">
         <v>78845</v>
@@ -27687,7 +27687,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G942" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H942" t="n">
         <v>68857</v>
@@ -27716,7 +27716,7 @@
         <v>1</v>
       </c>
       <c r="G943" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H943" t="n">
         <v>88334</v>
@@ -27745,7 +27745,7 @@
         <v>1</v>
       </c>
       <c r="G944" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H944" t="n">
         <v>61072</v>
@@ -27774,7 +27774,7 @@
         <v>1</v>
       </c>
       <c r="G945" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H945" t="n">
         <v>55996</v>
@@ -27832,7 +27832,7 @@
         <v>1</v>
       </c>
       <c r="G947" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H947" t="n">
         <v>78831</v>
@@ -27919,7 +27919,7 @@
         <v>1</v>
       </c>
       <c r="G950" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H950" t="n">
         <v>199826</v>
@@ -27948,7 +27948,7 @@
         <v>1</v>
       </c>
       <c r="G951" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H951" t="n">
         <v>101696</v>
@@ -28267,7 +28267,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G962" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H962" t="n">
         <v>218220</v>
@@ -28383,7 +28383,7 @@
         <v>1</v>
       </c>
       <c r="G966" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H966" t="n">
         <v>55243</v>
@@ -28470,7 +28470,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G969" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H969" t="n">
         <v>40709</v>
@@ -28499,7 +28499,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G970" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H970" t="n">
         <v>21334</v>
@@ -28557,7 +28557,7 @@
         <v>1</v>
       </c>
       <c r="G972" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H972" t="n">
         <v>97743</v>
@@ -28731,7 +28731,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G978" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H978" t="n">
         <v>51501</v>
@@ -28789,7 +28789,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G980" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H980" t="n">
         <v>78455</v>
@@ -28818,7 +28818,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G981" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H981" t="n">
         <v>64980</v>
@@ -28847,7 +28847,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H982" t="n">
         <v>61200</v>
@@ -29340,7 +29340,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H999" t="n">
         <v>89509</v>
@@ -29369,7 +29369,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1000" t="n">
         <v>154172</v>
@@ -29398,7 +29398,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1001" t="n">
         <v>37170</v>
@@ -29427,7 +29427,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1002" t="n">
         <v>79129</v>
@@ -30094,7 +30094,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1025" t="n">
         <v>210045</v>
@@ -30123,7 +30123,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1026" t="n">
         <v>199506</v>
@@ -30529,7 +30529,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H1040" t="n">
         <v>92707</v>
@@ -30558,7 +30558,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.69541734457016</v>
+        <v>0.695417404174805</v>
       </c>
       <c r="H1041" t="n">
         <v>92366</v>
@@ -30616,7 +30616,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1043" t="n">
         <v>142728</v>
@@ -30732,7 +30732,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.705796658992767</v>
+        <v>0.705796718597412</v>
       </c>
       <c r="H1047" t="n">
         <v>688629</v>
@@ -30761,7 +30761,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.733475029468536</v>
+        <v>0.733474969863892</v>
       </c>
       <c r="H1048" t="n">
         <v>1713322</v>
@@ -30848,7 +30848,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.78191202878952</v>
+        <v>0.781912088394165</v>
       </c>
       <c r="H1051" t="n">
         <v>273699</v>
@@ -30935,7 +30935,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1054" t="n">
         <v>899148</v>
@@ -30993,7 +30993,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1056" t="n">
         <v>602371</v>
@@ -31225,7 +31225,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H1064" t="n">
         <v>311827</v>
@@ -31457,7 +31457,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.624145686626434</v>
+        <v>0.624145746231079</v>
       </c>
       <c r="H1072" t="n">
         <v>187024</v>
@@ -31486,7 +31486,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.599235236644745</v>
+        <v>0.59923529624939</v>
       </c>
       <c r="H1073" t="n">
         <v>281442</v>
@@ -31544,7 +31544,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H1075" t="n">
         <v>210749</v>
@@ -31660,7 +31660,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H1079" t="n">
         <v>28824</v>
@@ -31689,7 +31689,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1080" t="n">
         <v>10767</v>
@@ -31718,7 +31718,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H1081" t="n">
         <v>12555</v>
@@ -31950,7 +31950,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.629681468009949</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1089" t="n">
         <v>108498</v>
@@ -31979,7 +31979,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.637984931468964</v>
+        <v>0.637984812259674</v>
       </c>
       <c r="H1090" t="n">
         <v>82780</v>
@@ -32124,7 +32124,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.629681468009949</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1095" t="n">
         <v>172934</v>
@@ -32211,7 +32211,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.615842282772064</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1098" t="n">
         <v>28827</v>
@@ -32240,7 +32240,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H1099" t="n">
         <v>28036</v>
@@ -32269,7 +32269,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.617226183414459</v>
+        <v>0.617226123809814</v>
       </c>
       <c r="H1100" t="n">
         <v>37867</v>
@@ -32298,7 +32298,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.615842282772064</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1101" t="n">
         <v>10506</v>
@@ -32443,7 +32443,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.615842282772064</v>
+        <v>0.615842223167419</v>
       </c>
       <c r="H1106" t="n">
         <v>72994</v>
@@ -32501,7 +32501,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.599235236644745</v>
+        <v>0.59923529624939</v>
       </c>
       <c r="H1108" t="n">
         <v>32728</v>
@@ -32646,7 +32646,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.585396111011505</v>
+        <v>0.58539617061615</v>
       </c>
       <c r="H1113" t="n">
         <v>67156</v>
@@ -32762,7 +32762,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.597851395606995</v>
+        <v>0.59785133600235</v>
       </c>
       <c r="H1117" t="n">
         <v>114903</v>
@@ -32791,7 +32791,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.599235236644745</v>
+        <v>0.59923529624939</v>
       </c>
       <c r="H1118" t="n">
         <v>96110</v>
@@ -32820,7 +32820,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.599235236644745</v>
+        <v>0.59923529624939</v>
       </c>
       <c r="H1119" t="n">
         <v>35473</v>
@@ -32907,7 +32907,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.57847648859024</v>
+        <v>0.57847660779953</v>
       </c>
       <c r="H1122" t="n">
         <v>200693</v>
@@ -32936,7 +32936,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.58816397190094</v>
+        <v>0.588163912296295</v>
       </c>
       <c r="H1123" t="n">
         <v>186789</v>
@@ -33168,7 +33168,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.629681468009949</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1131" t="n">
         <v>143550</v>
@@ -33197,7 +33197,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H1132" t="n">
         <v>63578</v>
@@ -33226,7 +33226,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.624145686626434</v>
+        <v>0.624145746231079</v>
       </c>
       <c r="H1133" t="n">
         <v>45723</v>
@@ -33255,7 +33255,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.629681468009949</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1134" t="n">
         <v>95950</v>
@@ -33400,7 +33400,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H1139" t="n">
         <v>47711</v>
@@ -33545,7 +33545,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H1144" t="n">
         <v>134257</v>
@@ -33603,7 +33603,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H1146" t="n">
         <v>69990</v>
@@ -33661,7 +33661,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H1148" t="n">
         <v>50733</v>
@@ -33690,7 +33690,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H1149" t="n">
         <v>29344</v>
@@ -34009,7 +34009,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H1160" t="n">
         <v>70501</v>
@@ -34067,7 +34067,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H1162" t="n">
         <v>9641</v>
@@ -34183,7 +34183,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.637984931468964</v>
+        <v>0.637984812259674</v>
       </c>
       <c r="H1166" t="n">
         <v>345</v>
@@ -34241,7 +34241,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H1168" t="n">
         <v>94123</v>
@@ -34357,7 +34357,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H1172" t="n">
         <v>42400</v>
@@ -34415,7 +34415,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.655975759029388</v>
+        <v>0.655975818634033</v>
       </c>
       <c r="H1174" t="n">
         <v>10005</v>
@@ -34444,7 +34444,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H1175" t="n">
         <v>285</v>
@@ -34502,7 +34502,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1177" t="n">
         <v>19107</v>
@@ -34560,7 +34560,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H1179" t="n">
         <v>8541</v>
@@ -34589,7 +34589,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H1180" t="n">
         <v>24514</v>
@@ -34705,7 +34705,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H1184" t="n">
         <v>17169</v>
@@ -34734,7 +34734,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.629681468009949</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1185" t="n">
         <v>47037</v>
@@ -34792,7 +34792,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1187" t="n">
         <v>19694</v>
@@ -34908,7 +34908,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H1191" t="n">
         <v>12133</v>
@@ -34995,7 +34995,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1194" t="n">
         <v>18420</v>
@@ -35024,7 +35024,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1195" t="n">
         <v>8103</v>
@@ -35111,7 +35111,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.635217010974884</v>
+        <v>0.635217070579529</v>
       </c>
       <c r="H1198" t="n">
         <v>34840</v>
@@ -35343,7 +35343,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H1206" t="n">
         <v>6431</v>
@@ -35517,7 +35517,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1212" t="n">
         <v>3435</v>
@@ -35546,7 +35546,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.649056255817413</v>
+        <v>0.649056196212769</v>
       </c>
       <c r="H1213" t="n">
         <v>41863</v>
@@ -35575,7 +35575,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1214" t="n">
         <v>32776</v>
@@ -35749,7 +35749,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.629681468009949</v>
+        <v>0.629681408405304</v>
       </c>
       <c r="H1220" t="n">
         <v>58098</v>
@@ -35865,7 +35865,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.624145686626434</v>
+        <v>0.624145746231079</v>
       </c>
       <c r="H1224" t="n">
         <v>18930</v>
@@ -36126,7 +36126,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.642136573791504</v>
+        <v>0.642136633396149</v>
       </c>
       <c r="H1233" t="n">
         <v>55266</v>
@@ -36213,7 +36213,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.644904375076294</v>
+        <v>0.644904434680939</v>
       </c>
       <c r="H1236" t="n">
         <v>88958</v>
@@ -36242,7 +36242,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.637984931468964</v>
+        <v>0.637984812259674</v>
       </c>
       <c r="H1237" t="n">
         <v>55565</v>
@@ -36329,7 +36329,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H1240" t="n">
         <v>40915</v>
@@ -36358,7 +36358,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.647672355175018</v>
+        <v>0.647672235965729</v>
       </c>
       <c r="H1241" t="n">
         <v>45409</v>
@@ -36445,7 +36445,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.653207957744598</v>
+        <v>0.653207898139954</v>
       </c>
       <c r="H1244" t="n">
         <v>67964</v>
@@ -36561,7 +36561,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.678118407726288</v>
+        <v>0.678118467330933</v>
       </c>
       <c r="H1248" t="n">
         <v>207160</v>
@@ -36619,7 +36619,7 @@
         <v>1</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H1250" t="n">
         <v>61786</v>
@@ -36648,7 +36648,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H1251" t="n">
         <v>36590</v>
@@ -36677,7 +36677,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H1252" t="n">
         <v>75238</v>
@@ -36735,7 +36735,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H1254" t="n">
         <v>248043</v>
@@ -36851,7 +36851,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.686421871185303</v>
+        <v>0.686421930789948</v>
       </c>
       <c r="H1258" t="n">
         <v>93042</v>
@@ -36880,7 +36880,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.683654069900513</v>
+        <v>0.683654010295868</v>
       </c>
       <c r="H1259" t="n">
         <v>104468</v>
@@ -36909,7 +36909,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H1260" t="n">
         <v>95974</v>
@@ -36938,7 +36938,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H1261" t="n">
         <v>40481</v>
@@ -36967,7 +36967,7 @@
         <v>1</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.691957533359528</v>
+        <v>0.691957592964172</v>
       </c>
       <c r="H1262" t="n">
         <v>31200</v>
@@ -37054,7 +37054,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.685037970542908</v>
+        <v>0.685038030147552</v>
       </c>
       <c r="H1265" t="n">
         <v>177918</v>
@@ -37518,7 +37518,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.733475029468536</v>
+        <v>0.733474969863892</v>
       </c>
       <c r="H1281" t="n">
         <v>28087</v>
@@ -37547,7 +37547,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.733475029468536</v>
+        <v>0.733474969863892</v>
       </c>
       <c r="H1282" t="n">
         <v>43403</v>
@@ -37576,7 +37576,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.733475029468536</v>
+        <v>0.733474969863892</v>
       </c>
       <c r="H1283" t="n">
         <v>36252</v>
@@ -37634,7 +37634,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.733475029468536</v>
+        <v>0.733474969863892</v>
       </c>
       <c r="H1285" t="n">
         <v>129493</v>
@@ -37924,7 +37924,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1295" t="n">
         <v>133140</v>
@@ -37953,7 +37953,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1296" t="n">
         <v>219334</v>
@@ -38040,7 +38040,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1299" t="n">
         <v>347129</v>
@@ -38069,7 +38069,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.750773906707764</v>
+        <v>0.750774025917053</v>
       </c>
       <c r="H1300" t="n">
         <v>100350</v>
@@ -38098,7 +38098,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1301" t="n">
         <v>103262</v>
@@ -38127,7 +38127,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1302" t="n">
         <v>109329</v>
@@ -38156,7 +38156,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1303" t="n">
         <v>65645</v>
@@ -38243,7 +38243,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.774992406368256</v>
+        <v>0.7749924659729</v>
       </c>
       <c r="H1306" t="n">
         <v>168242</v>
@@ -38330,7 +38330,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1309" t="n">
         <v>105632</v>
@@ -38417,7 +38417,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1312" t="n">
         <v>86822</v>
@@ -38475,7 +38475,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1314" t="n">
         <v>60881</v>
@@ -38533,7 +38533,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.750773906707764</v>
+        <v>0.750774025917053</v>
       </c>
       <c r="H1316" t="n">
         <v>137499</v>
@@ -38562,7 +38562,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1317" t="n">
         <v>128521</v>
@@ -38591,7 +38591,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1318" t="n">
         <v>48205</v>
@@ -38620,7 +38620,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1319" t="n">
         <v>83726</v>
@@ -38649,7 +38649,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1320" t="n">
         <v>44291</v>
@@ -38678,7 +38678,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1321" t="n">
         <v>113521</v>
@@ -38707,7 +38707,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1322" t="n">
         <v>79157</v>
@@ -38765,7 +38765,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.733475029468536</v>
+        <v>0.733474969863892</v>
       </c>
       <c r="H1324" t="n">
         <v>88274</v>
@@ -38910,7 +38910,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.750773906707764</v>
+        <v>0.750774025917053</v>
       </c>
       <c r="H1329" t="n">
         <v>70641</v>
@@ -38968,7 +38968,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1331" t="n">
         <v>97824</v>
@@ -39026,7 +39026,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.750773906707764</v>
+        <v>0.750774025917053</v>
       </c>
       <c r="H1333" t="n">
         <v>66358</v>
@@ -39055,7 +39055,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.750773906707764</v>
+        <v>0.750774025917053</v>
       </c>
       <c r="H1334" t="n">
         <v>300870</v>
@@ -39084,7 +39084,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1335" t="n">
         <v>106831</v>
@@ -39113,7 +39113,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.78191202878952</v>
+        <v>0.781912088394165</v>
       </c>
       <c r="H1336" t="n">
         <v>533202</v>
@@ -39171,7 +39171,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.757693648338318</v>
+        <v>0.757693588733673</v>
       </c>
       <c r="H1338" t="n">
         <v>187114</v>
@@ -39229,7 +39229,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.768072843551636</v>
+        <v>0.768072903156281</v>
       </c>
       <c r="H1340" t="n">
         <v>97960</v>
@@ -39287,7 +39287,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.754233837127686</v>
+        <v>0.754233777523041</v>
       </c>
       <c r="H1342" t="n">
         <v>231631</v>
@@ -39403,7 +39403,7 @@
         <v>1.125</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.778452277183533</v>
+        <v>0.778452217578888</v>
       </c>
       <c r="H1346" t="n">
         <v>130572</v>
@@ -39432,7 +39432,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.774992406368256</v>
+        <v>0.7749924659729</v>
       </c>
       <c r="H1347" t="n">
         <v>50868</v>
@@ -39461,7 +39461,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.774992406368256</v>
+        <v>0.7749924659729</v>
       </c>
       <c r="H1348" t="n">
         <v>140318</v>
@@ -39519,7 +39519,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.78191202878952</v>
+        <v>0.781912088394165</v>
       </c>
       <c r="H1350" t="n">
         <v>305250</v>
@@ -39548,7 +39548,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.78191202878952</v>
+        <v>0.781912088394165</v>
       </c>
       <c r="H1351" t="n">
         <v>45974</v>
@@ -39577,7 +39577,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.78191202878952</v>
+        <v>0.781912088394165</v>
       </c>
       <c r="H1352" t="n">
         <v>26682</v>
@@ -39606,7 +39606,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1353" t="n">
         <v>91577</v>
@@ -39664,7 +39664,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1355" t="n">
         <v>288218</v>
@@ -39693,7 +39693,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1356" t="n">
         <v>17024</v>
@@ -39751,7 +39751,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.813050091266632</v>
+        <v>0.813050150871277</v>
       </c>
       <c r="H1358" t="n">
         <v>83258</v>
@@ -39809,7 +39809,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.806130647659302</v>
+        <v>0.806130588054657</v>
       </c>
       <c r="H1360" t="n">
         <v>83021</v>
@@ -39867,7 +39867,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.813050091266632</v>
+        <v>0.813050150871277</v>
       </c>
       <c r="H1362" t="n">
         <v>313246</v>
@@ -39983,7 +39983,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1366" t="n">
         <v>281388</v>
@@ -40012,7 +40012,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1367" t="n">
         <v>273985</v>
@@ -40128,7 +40128,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1371" t="n">
         <v>153196</v>
@@ -40215,7 +40215,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1374" t="n">
         <v>90444</v>
@@ -40244,7 +40244,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1375" t="n">
         <v>86876</v>
@@ -40273,7 +40273,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1376" t="n">
         <v>14034</v>
@@ -40302,7 +40302,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1377" t="n">
         <v>27809</v>
@@ -40331,7 +40331,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1378" t="n">
         <v>65291</v>
@@ -40360,7 +40360,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1379" t="n">
         <v>147569</v>
@@ -40389,7 +40389,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1380" t="n">
         <v>84546</v>
@@ -40447,7 +40447,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.792291402816772</v>
+        <v>0.792291462421417</v>
       </c>
       <c r="H1382" t="n">
         <v>175384</v>
@@ -40505,7 +40505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1384" t="n">
         <v>90158</v>
@@ -40592,7 +40592,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.813050091266632</v>
+        <v>0.813050150871277</v>
       </c>
       <c r="H1387" t="n">
         <v>156054</v>
@@ -40621,7 +40621,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.813050091266632</v>
+        <v>0.813050150871277</v>
       </c>
       <c r="H1388" t="n">
         <v>49722</v>
@@ -40650,7 +40650,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813050091266632</v>
+        <v>0.813050150871277</v>
       </c>
       <c r="H1389" t="n">
         <v>189258</v>
@@ -40679,7 +40679,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.806130647659302</v>
+        <v>0.806130588054657</v>
       </c>
       <c r="H1390" t="n">
         <v>192841</v>
@@ -40766,7 +40766,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.79575115442276</v>
+        <v>0.795751214027405</v>
       </c>
       <c r="H1393" t="n">
         <v>200154</v>
@@ -40940,7 +40940,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.806130647659302</v>
+        <v>0.806130588054657</v>
       </c>
       <c r="H1399" t="n">
         <v>470494</v>
@@ -40998,7 +40998,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.806130647659302</v>
+        <v>0.806130588054657</v>
       </c>
       <c r="H1401" t="n">
         <v>120762</v>
@@ -41346,7 +41346,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1413" t="n">
         <v>583052</v>
@@ -41375,7 +41375,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1414" t="n">
         <v>94810</v>
@@ -41404,7 +41404,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1415" t="n">
         <v>926778</v>
@@ -41433,7 +41433,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1416" t="n">
         <v>335083</v>
@@ -41491,7 +41491,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1418" t="n">
         <v>281905</v>
@@ -41520,7 +41520,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1419" t="n">
         <v>190170</v>
@@ -41549,7 +41549,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1420" t="n">
         <v>114650</v>
@@ -41578,7 +41578,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1421" t="n">
         <v>66926</v>
@@ -41607,7 +41607,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1422" t="n">
         <v>148582</v>
@@ -41636,7 +41636,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1423" t="n">
         <v>274643</v>
@@ -41665,7 +41665,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1424" t="n">
         <v>138269</v>
@@ -41694,7 +41694,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1425" t="n">
         <v>60081</v>
@@ -41723,7 +41723,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1426" t="n">
         <v>92896</v>
@@ -41752,7 +41752,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1427" t="n">
         <v>69676</v>
@@ -41781,7 +41781,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1428" t="n">
         <v>27419</v>
@@ -41810,7 +41810,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.830349147319794</v>
+        <v>0.830349087715149</v>
       </c>
       <c r="H1429" t="n">
         <v>16294</v>
@@ -41839,7 +41839,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.826889336109161</v>
+        <v>0.826889395713806</v>
       </c>
       <c r="H1430" t="n">
         <v>34025</v>
@@ -41868,7 +41868,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.826889336109161</v>
+        <v>0.826889395713806</v>
       </c>
       <c r="H1431" t="n">
         <v>4343</v>
@@ -42303,7 +42303,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.840728521347046</v>
+        <v>0.840728461742401</v>
       </c>
       <c r="H1446" t="n">
         <v>397157</v>
@@ -42332,7 +42332,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.844188213348389</v>
+        <v>0.844188272953033</v>
       </c>
       <c r="H1447" t="n">
         <v>238874</v>
@@ -42361,7 +42361,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.840728521347046</v>
+        <v>0.840728461742401</v>
       </c>
       <c r="H1448" t="n">
         <v>523781</v>
@@ -42390,7 +42390,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.840728521347046</v>
+        <v>0.840728461742401</v>
       </c>
       <c r="H1449" t="n">
         <v>417288</v>
@@ -42419,7 +42419,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.840728521347046</v>
+        <v>0.840728461742401</v>
       </c>
       <c r="H1450" t="n">
         <v>171713</v>
@@ -42738,7 +42738,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.920303463935852</v>
+        <v>0.920303583145142</v>
       </c>
       <c r="H1461" t="n">
         <v>436738</v>
@@ -42854,7 +42854,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.927223086357117</v>
+        <v>0.927223205566406</v>
       </c>
       <c r="H1465" t="n">
         <v>86673</v>
@@ -42883,7 +42883,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.923763453960419</v>
+        <v>0.923763334751129</v>
       </c>
       <c r="H1466" t="n">
         <v>287349</v>
@@ -42912,7 +42912,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.944522142410278</v>
+        <v>0.944522023200989</v>
       </c>
       <c r="H1467" t="n">
         <v>688381</v>
@@ -42941,7 +42941,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.944522142410278</v>
+        <v>0.944522023200989</v>
       </c>
       <c r="H1468" t="n">
         <v>303974</v>
@@ -42970,7 +42970,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.941062390804291</v>
+        <v>0.941062271595001</v>
       </c>
       <c r="H1469" t="n">
         <v>129426</v>
@@ -42999,7 +42999,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.944522142410278</v>
+        <v>0.944522023200989</v>
       </c>
       <c r="H1470" t="n">
         <v>44738</v>
@@ -43028,7 +43028,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.944522142410278</v>
+        <v>0.944522023200989</v>
       </c>
       <c r="H1471" t="n">
         <v>189714</v>
@@ -43086,7 +43086,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.944522142410278</v>
+        <v>0.944522023200989</v>
       </c>
       <c r="H1473" t="n">
         <v>94486</v>
@@ -43115,7 +43115,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602400779724</v>
       </c>
       <c r="H1474" t="n">
         <v>142236</v>
@@ -43144,7 +43144,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602400779724</v>
       </c>
       <c r="H1475" t="n">
         <v>50984</v>
@@ -43173,7 +43173,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.958361327648163</v>
+        <v>0.958361208438873</v>
       </c>
       <c r="H1476" t="n">
         <v>431293</v>
@@ -43347,7 +43347,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.958361327648163</v>
+        <v>0.958361208438873</v>
       </c>
       <c r="H1482" t="n">
         <v>159538</v>
@@ -43434,7 +43434,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.992958903312683</v>
+        <v>0.992959141731262</v>
       </c>
       <c r="H1485" t="n">
         <v>160211</v>
@@ -43521,7 +43521,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.992958903312683</v>
+        <v>0.992959141731262</v>
       </c>
       <c r="H1488" t="n">
         <v>196578</v>
@@ -43637,7 +43637,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.992958903312683</v>
+        <v>0.992959141731262</v>
       </c>
       <c r="H1492" t="n">
         <v>57450</v>
@@ -43666,7 +43666,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.986039519309998</v>
+        <v>0.986039400100708</v>
       </c>
       <c r="H1493" t="n">
         <v>139022</v>
@@ -43695,7 +43695,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.986039519309998</v>
+        <v>0.986039400100708</v>
       </c>
       <c r="H1494" t="n">
         <v>79009</v>
@@ -43782,7 +43782,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.920303463935852</v>
+        <v>0.920303583145142</v>
       </c>
       <c r="H1497" t="n">
         <v>1137530</v>
@@ -43811,7 +43811,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.934142708778381</v>
+        <v>0.934142768383026</v>
       </c>
       <c r="H1498" t="n">
         <v>381079</v>
@@ -43840,7 +43840,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.934142708778381</v>
+        <v>0.934142768383026</v>
       </c>
       <c r="H1499" t="n">
         <v>103523</v>
@@ -43869,7 +43869,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.920303463935852</v>
+        <v>0.920303583145142</v>
       </c>
       <c r="H1500" t="n">
         <v>453289</v>
@@ -43898,7 +43898,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.934142708778381</v>
+        <v>0.934142768383026</v>
       </c>
       <c r="H1501" t="n">
         <v>135609</v>
@@ -43927,7 +43927,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.937602519989014</v>
+        <v>0.937602400779724</v>
       </c>
       <c r="H1502" t="n">
         <v>755734</v>
@@ -43956,7 +43956,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.927223086357117</v>
+        <v>0.927223205566406</v>
       </c>
       <c r="H1503" t="n">
         <v>329891</v>
@@ -43985,7 +43985,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.934142708778381</v>
+        <v>0.934142768383026</v>
       </c>
       <c r="H1504" t="n">
         <v>203683</v>
@@ -44014,7 +44014,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.944522142410278</v>
+        <v>0.944522023200989</v>
       </c>
       <c r="H1505" t="n">
         <v>156551</v>
@@ -44188,7 +44188,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.02063739299774</v>
+        <v>1.02063751220703</v>
       </c>
       <c r="H1511" t="n">
         <v>206402</v>
@@ -44217,7 +44217,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1512" t="n">
         <v>458228</v>
@@ -44246,7 +44246,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1513" t="n">
         <v>220523</v>
@@ -44565,7 +44565,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.02755689620972</v>
+        <v>1.02755701541901</v>
       </c>
       <c r="H1524" t="n">
         <v>793175</v>
@@ -44652,7 +44652,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1527" t="n">
         <v>782238</v>
@@ -44826,7 +44826,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.08983325958252</v>
+        <v>1.08983314037323</v>
       </c>
       <c r="H1533" t="n">
         <v>163796</v>
@@ -44913,7 +44913,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.08983325958252</v>
+        <v>1.08983314037323</v>
       </c>
       <c r="H1536" t="n">
         <v>438076</v>
@@ -45145,7 +45145,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.05869519710541</v>
+        <v>1.05869507789612</v>
       </c>
       <c r="H1544" t="n">
         <v>116868</v>
@@ -45174,7 +45174,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.06215476989746</v>
+        <v>1.06215488910675</v>
       </c>
       <c r="H1545" t="n">
         <v>133753</v>
@@ -45319,7 +45319,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.06215476989746</v>
+        <v>1.06215488910675</v>
       </c>
       <c r="H1550" t="n">
         <v>112492</v>
@@ -45348,7 +45348,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1551" t="n">
         <v>94039</v>
@@ -45377,7 +45377,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.05869519710541</v>
+        <v>1.05869507789612</v>
       </c>
       <c r="H1552" t="n">
         <v>115710</v>
@@ -45406,7 +45406,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1553" t="n">
         <v>102708</v>
@@ -45522,7 +45522,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.05869519710541</v>
+        <v>1.05869507789612</v>
       </c>
       <c r="H1557" t="n">
         <v>223368</v>
@@ -45667,7 +45667,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.17632794380188</v>
+        <v>1.17632782459259</v>
       </c>
       <c r="H1562" t="n">
         <v>1416932</v>
@@ -45725,7 +45725,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.17632794380188</v>
+        <v>1.17632782459259</v>
       </c>
       <c r="H1564" t="n">
         <v>988135</v>
@@ -45841,7 +45841,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.20054650306702</v>
+        <v>1.20054638385773</v>
       </c>
       <c r="H1568" t="n">
         <v>951811</v>
@@ -45870,7 +45870,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.17632794380188</v>
+        <v>1.17632782459259</v>
       </c>
       <c r="H1569" t="n">
         <v>510397</v>
@@ -45928,7 +45928,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.06561458110809</v>
+        <v>1.06561470031738</v>
       </c>
       <c r="H1571" t="n">
         <v>1174698</v>
@@ -46247,7 +46247,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.16248869895935</v>
+        <v>1.16248857975006</v>
       </c>
       <c r="H1582" t="n">
         <v>806481</v>
@@ -46276,7 +46276,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.19362676143646</v>
+        <v>1.19362688064575</v>
       </c>
       <c r="H1583" t="n">
         <v>615283</v>
@@ -46334,7 +46334,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.19362676143646</v>
+        <v>1.19362688064575</v>
       </c>
       <c r="H1585" t="n">
         <v>429004</v>
@@ -46363,7 +46363,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.20054650306702</v>
+        <v>1.20054638385773</v>
       </c>
       <c r="H1586" t="n">
         <v>279699</v>
@@ -46421,7 +46421,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.23168456554413</v>
+        <v>1.23168444633484</v>
       </c>
       <c r="H1588" t="n">
         <v>827658</v>
@@ -46450,7 +46450,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.26282250881195</v>
+        <v>1.26282262802124</v>
       </c>
       <c r="H1589" t="n">
         <v>1153238</v>
@@ -46537,7 +46537,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.25244307518005</v>
+        <v>1.25244319438934</v>
       </c>
       <c r="H1592" t="n">
         <v>759956</v>
@@ -46595,7 +46595,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.22130513191223</v>
+        <v>1.22130501270294</v>
       </c>
       <c r="H1594" t="n">
         <v>600957</v>
@@ -46740,7 +46740,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.22476494312286</v>
+        <v>1.22476482391357</v>
       </c>
       <c r="H1599" t="n">
         <v>500917</v>
@@ -46885,7 +46885,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.17632794380188</v>
+        <v>1.17632782459259</v>
       </c>
       <c r="H1604" t="n">
         <v>2339616</v>
@@ -46943,7 +46943,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.18464112281799</v>
+        <v>1.1846410036087</v>
       </c>
       <c r="H1606" t="n">
         <v>1073830</v>
@@ -46972,7 +46972,7 @@
         <v>1.375</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.14307475090027</v>
+        <v>1.14307487010956</v>
       </c>
       <c r="H1607" t="n">
         <v>888663</v>
@@ -47059,7 +47059,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1610" t="n">
         <v>1024808</v>
@@ -47204,7 +47204,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.997592628002167</v>
+        <v>0.997592568397522</v>
       </c>
       <c r="H1615" t="n">
         <v>788688</v>
@@ -47291,7 +47291,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.01006257534027</v>
+        <v>1.01006245613098</v>
       </c>
       <c r="H1618" t="n">
         <v>241214</v>
@@ -47407,7 +47407,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.06409871578217</v>
+        <v>1.06409883499146</v>
       </c>
       <c r="H1622" t="n">
         <v>276933</v>
@@ -47436,7 +47436,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.07656860351562</v>
+        <v>1.07656848430634</v>
       </c>
       <c r="H1623" t="n">
         <v>897447</v>
@@ -47465,7 +47465,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.06409871578217</v>
+        <v>1.06409883499146</v>
       </c>
       <c r="H1624" t="n">
         <v>396100</v>
@@ -47552,7 +47552,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1627" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1627" t="n">
         <v>148939</v>
@@ -47610,7 +47610,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1629" t="n">
         <v>275252</v>
@@ -47639,7 +47639,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.09735190868378</v>
+        <v>1.09735178947449</v>
       </c>
       <c r="H1630" t="n">
         <v>580808</v>
@@ -47697,7 +47697,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.09735190868378</v>
+        <v>1.09735178947449</v>
       </c>
       <c r="H1632" t="n">
         <v>174475</v>
@@ -47726,7 +47726,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.09735190868378</v>
+        <v>1.09735178947449</v>
       </c>
       <c r="H1633" t="n">
         <v>130651</v>
@@ -47784,7 +47784,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.1056649684906</v>
+        <v>1.10566508769989</v>
       </c>
       <c r="H1635" t="n">
         <v>120589</v>
@@ -47987,7 +47987,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.06409871578217</v>
+        <v>1.06409883499146</v>
       </c>
       <c r="H1642" t="n">
         <v>586662</v>
@@ -48045,7 +48045,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1644" t="n">
-        <v>1.01006257534027</v>
+        <v>1.01006245613098</v>
       </c>
       <c r="H1644" t="n">
         <v>120234</v>
@@ -48190,7 +48190,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.01421904563904</v>
+        <v>1.01421916484833</v>
       </c>
       <c r="H1649" t="n">
         <v>53800</v>
@@ -48393,7 +48393,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.997592628002167</v>
+        <v>0.997592568397522</v>
       </c>
       <c r="H1656" t="n">
         <v>103901</v>
@@ -48422,7 +48422,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.997592628002167</v>
+        <v>0.997592568397522</v>
       </c>
       <c r="H1657" t="n">
         <v>64763</v>
@@ -48509,7 +48509,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.01006257534027</v>
+        <v>1.01006245613098</v>
       </c>
       <c r="H1660" t="n">
         <v>148658</v>
@@ -48538,7 +48538,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.01006257534027</v>
+        <v>1.01006245613098</v>
       </c>
       <c r="H1661" t="n">
         <v>64077</v>
@@ -48567,7 +48567,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.997592628002167</v>
+        <v>0.997592568397522</v>
       </c>
       <c r="H1662" t="n">
         <v>220673</v>
@@ -48596,7 +48596,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.976809322834015</v>
+        <v>0.97680938243866</v>
       </c>
       <c r="H1663" t="n">
         <v>122248</v>
@@ -48915,7 +48915,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.12644827365875</v>
+        <v>1.12644815444946</v>
       </c>
       <c r="H1674" t="n">
         <v>329517</v>
@@ -49002,7 +49002,7 @@
         <v>1.375</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.14307475090027</v>
+        <v>1.14307487010956</v>
       </c>
       <c r="H1677" t="n">
         <v>65289</v>
@@ -49031,7 +49031,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.14723134040833</v>
+        <v>1.14723145961761</v>
       </c>
       <c r="H1678" t="n">
         <v>68600</v>
@@ -49118,7 +49118,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.17217111587524</v>
+        <v>1.17217123508453</v>
       </c>
       <c r="H1681" t="n">
         <v>61636</v>
@@ -49147,7 +49147,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1682" t="n">
         <v>95817</v>
@@ -49176,7 +49176,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.17217111587524</v>
+        <v>1.17217123508453</v>
       </c>
       <c r="H1683" t="n">
         <v>109056</v>
@@ -49321,7 +49321,7 @@
         <v>1.375</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.14307475090027</v>
+        <v>1.14307487010956</v>
       </c>
       <c r="H1688" t="n">
         <v>157739</v>
@@ -49350,7 +49350,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.09735190868378</v>
+        <v>1.09735178947449</v>
       </c>
       <c r="H1689" t="n">
         <v>307777</v>
@@ -49379,7 +49379,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.09735190868378</v>
+        <v>1.09735178947449</v>
       </c>
       <c r="H1690" t="n">
         <v>115683</v>
@@ -49408,7 +49408,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.09735190868378</v>
+        <v>1.09735178947449</v>
       </c>
       <c r="H1691" t="n">
         <v>49665</v>
@@ -49466,7 +49466,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1693" t="n">
         <v>146529</v>
@@ -49698,7 +49698,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.06409871578217</v>
+        <v>1.06409883499146</v>
       </c>
       <c r="H1701" t="n">
         <v>68212</v>
@@ -49727,7 +49727,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.06409871578217</v>
+        <v>1.06409883499146</v>
       </c>
       <c r="H1702" t="n">
         <v>92847</v>
@@ -49814,7 +49814,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.07656860351562</v>
+        <v>1.07656848430634</v>
       </c>
       <c r="H1705" t="n">
         <v>91839</v>
@@ -49843,7 +49843,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.07656860351562</v>
+        <v>1.07656848430634</v>
       </c>
       <c r="H1706" t="n">
         <v>137105</v>
@@ -49988,7 +49988,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1711" t="n">
         <v>72822</v>
@@ -50075,7 +50075,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.06409871578217</v>
+        <v>1.06409883499146</v>
       </c>
       <c r="H1714" t="n">
         <v>129641</v>
@@ -50191,7 +50191,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.01421904563904</v>
+        <v>1.01421916484833</v>
       </c>
       <c r="H1718" t="n">
         <v>71085</v>
@@ -50336,7 +50336,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1723" t="n">
         <v>120909</v>
@@ -50365,7 +50365,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1724" t="n">
         <v>91205</v>
@@ -50394,7 +50394,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.06409871578217</v>
+        <v>1.06409883499146</v>
       </c>
       <c r="H1725" t="n">
         <v>52953</v>
@@ -50481,7 +50481,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1728" t="n">
         <v>25254</v>
@@ -50510,7 +50510,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.07656860351562</v>
+        <v>1.07656848430634</v>
       </c>
       <c r="H1729" t="n">
         <v>24362</v>
@@ -50539,7 +50539,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1730" t="n">
         <v>54563</v>
@@ -50568,7 +50568,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.07241189479828</v>
+        <v>1.07241201400757</v>
       </c>
       <c r="H1731" t="n">
         <v>29048</v>
@@ -50713,7 +50713,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.1306049823761</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1736" t="n">
         <v>124290</v>
@@ -50771,7 +50771,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.13476157188416</v>
+        <v>1.13476145267487</v>
       </c>
       <c r="H1738" t="n">
         <v>124547</v>
@@ -50800,7 +50800,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.15138816833496</v>
+        <v>1.15138804912567</v>
       </c>
       <c r="H1739" t="n">
         <v>22397</v>
@@ -50887,7 +50887,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.13476157188416</v>
+        <v>1.13476145267487</v>
       </c>
       <c r="H1742" t="n">
         <v>58803</v>
@@ -50916,7 +50916,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1743" t="n">
-        <v>1.14723134040833</v>
+        <v>1.14723145961761</v>
       </c>
       <c r="H1743" t="n">
         <v>57529</v>
@@ -50945,7 +50945,7 @@
         <v>1.375</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.14307475090027</v>
+        <v>1.14307487010956</v>
       </c>
       <c r="H1744" t="n">
         <v>94131</v>
@@ -50974,7 +50974,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.15138816833496</v>
+        <v>1.15138804912567</v>
       </c>
       <c r="H1745" t="n">
         <v>102412</v>
@@ -51003,7 +51003,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.14723134040833</v>
+        <v>1.14723145961761</v>
       </c>
       <c r="H1746" t="n">
         <v>61890</v>
@@ -51322,7 +51322,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1757" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1757" t="n">
         <v>136128</v>
@@ -51351,7 +51351,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1758" t="n">
         <v>82692</v>
@@ -51409,7 +51409,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1760" t="n">
         <v>60135</v>
@@ -51467,7 +51467,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1762" t="n">
         <v>31346</v>
@@ -51525,7 +51525,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1764" t="n">
         <v>134687</v>
@@ -51554,7 +51554,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1765" t="n">
         <v>107827</v>
@@ -51583,7 +51583,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1766" t="n">
         <v>36572</v>
@@ -51728,7 +51728,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.18464112281799</v>
+        <v>1.1846410036087</v>
       </c>
       <c r="H1771" t="n">
         <v>33201</v>
@@ -51902,7 +51902,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.14723134040833</v>
+        <v>1.14723145961761</v>
       </c>
       <c r="H1777" t="n">
         <v>80532</v>
@@ -51931,7 +51931,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.14723134040833</v>
+        <v>1.14723145961761</v>
       </c>
       <c r="H1778" t="n">
         <v>77100</v>
@@ -51960,7 +51960,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.13476157188416</v>
+        <v>1.13476145267487</v>
       </c>
       <c r="H1779" t="n">
         <v>73657</v>
@@ -51989,7 +51989,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.14723134040833</v>
+        <v>1.14723145961761</v>
       </c>
       <c r="H1780" t="n">
         <v>31482</v>
@@ -52018,7 +52018,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.13476157188416</v>
+        <v>1.13476145267487</v>
       </c>
       <c r="H1781" t="n">
         <v>149637</v>
@@ -52047,7 +52047,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.1306049823761</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1782" t="n">
         <v>77581</v>
@@ -52076,7 +52076,7 @@
         <v>1.375</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.14307475090027</v>
+        <v>1.14307487010956</v>
       </c>
       <c r="H1783" t="n">
         <v>23217</v>
@@ -52134,7 +52134,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1785" t="n">
         <v>598110</v>
@@ -52192,7 +52192,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.17217111587524</v>
+        <v>1.17217123508453</v>
       </c>
       <c r="H1787" t="n">
         <v>134209</v>
@@ -52337,7 +52337,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.22620749473572</v>
+        <v>1.22620761394501</v>
       </c>
       <c r="H1792" t="n">
         <v>300696</v>
@@ -52366,7 +52366,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.23452067375183</v>
+        <v>1.23452079296112</v>
       </c>
       <c r="H1793" t="n">
         <v>551408</v>
@@ -52453,7 +52453,7 @@
         <v>1.5</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.24699056148529</v>
+        <v>1.24699068069458</v>
       </c>
       <c r="H1796" t="n">
         <v>298792</v>
@@ -52540,7 +52540,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.27193057537079</v>
+        <v>1.2719304561615</v>
       </c>
       <c r="H1799" t="n">
         <v>282328</v>
@@ -52569,7 +52569,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.27608704566956</v>
+        <v>1.27608716487885</v>
       </c>
       <c r="H1800" t="n">
         <v>167588</v>
@@ -52598,7 +52598,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.27608704566956</v>
+        <v>1.27608716487885</v>
       </c>
       <c r="H1801" t="n">
         <v>146522</v>
@@ -52656,7 +52656,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.30934035778046</v>
+        <v>1.30934023857117</v>
       </c>
       <c r="H1803" t="n">
         <v>410158</v>
@@ -52714,7 +52714,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.30934035778046</v>
+        <v>1.30934023857117</v>
       </c>
       <c r="H1805" t="n">
         <v>191857</v>
@@ -52917,7 +52917,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.28024363517761</v>
+        <v>1.2802437543869</v>
       </c>
       <c r="H1812" t="n">
         <v>355199</v>
@@ -52975,7 +52975,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.28024363517761</v>
+        <v>1.2802437543869</v>
       </c>
       <c r="H1814" t="n">
         <v>224082</v>
@@ -53062,7 +53062,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.23036420345306</v>
+        <v>1.23036408424377</v>
       </c>
       <c r="H1817" t="n">
         <v>431911</v>
@@ -53091,7 +53091,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1818" t="n">
-        <v>1.23452067375183</v>
+        <v>1.23452079296112</v>
       </c>
       <c r="H1818" t="n">
         <v>151967</v>
@@ -53149,7 +53149,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1820" t="n">
         <v>359212</v>
@@ -53265,7 +53265,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.17217111587524</v>
+        <v>1.17217123508453</v>
       </c>
       <c r="H1824" t="n">
         <v>159581</v>
@@ -53323,7 +53323,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1826" t="n">
         <v>77691</v>
@@ -53381,7 +53381,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1828" t="n">
         <v>93795</v>
@@ -53439,7 +53439,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1830" t="n">
-        <v>1.19295418262482</v>
+        <v>1.1929544210434</v>
       </c>
       <c r="H1830" t="n">
         <v>127047</v>
@@ -53497,7 +53497,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.17217111587524</v>
+        <v>1.17217123508453</v>
       </c>
       <c r="H1832" t="n">
         <v>211202</v>
@@ -53584,7 +53584,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.1306049823761</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1835" t="n">
         <v>193872</v>
@@ -53613,7 +53613,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.1306049823761</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1836" t="n">
         <v>91206</v>
@@ -53642,7 +53642,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.1306049823761</v>
+        <v>1.13060486316681</v>
       </c>
       <c r="H1837" t="n">
         <v>78241</v>
@@ -53671,7 +53671,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.13476157188416</v>
+        <v>1.13476145267487</v>
       </c>
       <c r="H1838" t="n">
         <v>172488</v>
@@ -53700,7 +53700,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1839" t="n">
-        <v>1.15138816833496</v>
+        <v>1.15138804912567</v>
       </c>
       <c r="H1839" t="n">
         <v>104740</v>
@@ -53729,7 +53729,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.14723134040833</v>
+        <v>1.14723145961761</v>
       </c>
       <c r="H1840" t="n">
         <v>163124</v>
@@ -53816,7 +53816,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1843" t="n">
-        <v>1.17217111587524</v>
+        <v>1.17217123508453</v>
       </c>
       <c r="H1843" t="n">
         <v>82942</v>
@@ -53932,7 +53932,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.17217111587524</v>
+        <v>1.17217123508453</v>
       </c>
       <c r="H1847" t="n">
         <v>41416</v>
@@ -53961,7 +53961,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1848" t="n">
-        <v>1.18048453330994</v>
+        <v>1.18048441410065</v>
       </c>
       <c r="H1848" t="n">
         <v>114995</v>
@@ -54280,7 +54280,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.20043635368347</v>
+        <v>1.20043647289276</v>
       </c>
       <c r="H1859" t="n">
         <v>88637</v>
@@ -80180,9 +80180,38 @@
         <v>1.87000000476837</v>
       </c>
       <c r="H2752" t="n">
-        <v>58932</v>
+        <v>62009</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>1.86800003051758</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>1.87199997901917</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>1.85599994659424</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>8878</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>
